--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>792542</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>44.8400001525879</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>44.1100006103516</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>44.6500015258789</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>44.3400001525879</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>1087428</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>44.439998626709</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>43.3899993896484</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>44.439998626709</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>43.4599990844727</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>1177904</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>43.9099998474121</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>42.939998626709</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>43.4599990844727</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>2189308</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>45.6500015258789</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>43.3499984741211</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>44.2599983215332</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>43.9900016784668</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>848748</v>
+        <v>773968</v>
       </c>
       <c r="C2715" t="n">
-        <v>46.6300010681152</v>
+        <v>46.7099990844727</v>
       </c>
       <c r="D2715" t="n">
-        <v>45.5999984741211</v>
+        <v>45.7299995422363</v>
       </c>
       <c r="E2715" t="n">
-        <v>45.9000015258789</v>
+        <v>46.3199996948242</v>
       </c>
       <c r="F2715" t="n">
-        <v>45.9599990844727</v>
+        <v>46.1800003051758</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>1169354</v>
+        <v>848748</v>
       </c>
       <c r="C2716" t="n">
         <v>46.6300010681152</v>
       </c>
       <c r="D2716" t="n">
-        <v>44.9900016784668</v>
+        <v>45.5999984741211</v>
       </c>
       <c r="E2716" t="n">
-        <v>45.5</v>
+        <v>45.9000015258789</v>
       </c>
       <c r="F2716" t="n">
-        <v>45.1599998474121</v>
+        <v>45.9599990844727</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>1744528</v>
+        <v>1169354</v>
       </c>
       <c r="C2717" t="n">
-        <v>45</v>
+        <v>46.6300010681152</v>
       </c>
       <c r="D2717" t="n">
-        <v>43.5699996948242</v>
+        <v>44.9900016784668</v>
       </c>
       <c r="E2717" t="n">
-        <v>44.939998626709</v>
+        <v>45.5</v>
       </c>
       <c r="F2717" t="n">
-        <v>43.5999984741211</v>
+        <v>45.1599998474121</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>1429119</v>
+        <v>1744528</v>
       </c>
       <c r="C2718" t="n">
-        <v>45.3300018310547</v>
+        <v>45</v>
       </c>
       <c r="D2718" t="n">
-        <v>43.7900009155273</v>
+        <v>43.5699996948242</v>
       </c>
       <c r="E2718" t="n">
-        <v>43.8899993896484</v>
+        <v>44.939998626709</v>
       </c>
       <c r="F2718" t="n">
-        <v>44.689998626709</v>
+        <v>43.5999984741211</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>792542</v>
+        <v>1429119</v>
       </c>
       <c r="C2719" t="n">
-        <v>44.8400001525879</v>
+        <v>45.3300018310547</v>
       </c>
       <c r="D2719" t="n">
-        <v>44.1100006103516</v>
+        <v>43.7900009155273</v>
       </c>
       <c r="E2719" t="n">
-        <v>44.6500015258789</v>
+        <v>43.8899993896484</v>
       </c>
       <c r="F2719" t="n">
-        <v>44.3400001525879</v>
+        <v>44.689998626709</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>1087428</v>
+        <v>792542</v>
       </c>
       <c r="C2720" t="n">
-        <v>44.439998626709</v>
+        <v>44.8400001525879</v>
       </c>
       <c r="D2720" t="n">
-        <v>43.3899993896484</v>
+        <v>44.1100006103516</v>
       </c>
       <c r="E2720" t="n">
-        <v>44.439998626709</v>
+        <v>44.6500015258789</v>
       </c>
       <c r="F2720" t="n">
-        <v>43.4599990844727</v>
+        <v>44.3400001525879</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>1177904</v>
+        <v>1087428</v>
       </c>
       <c r="C2721" t="n">
-        <v>43.9099998474121</v>
+        <v>44.439998626709</v>
       </c>
       <c r="D2721" t="n">
-        <v>42.939998626709</v>
+        <v>43.3899993896484</v>
       </c>
       <c r="E2721" t="n">
+        <v>44.439998626709</v>
+      </c>
+      <c r="F2721" t="n">
         <v>43.4599990844727</v>
-      </c>
-      <c r="F2721" t="n">
-        <v>43.75</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>2189308</v>
+        <v>1177904</v>
       </c>
       <c r="C2722" t="n">
-        <v>45.6500015258789</v>
+        <v>43.9099998474121</v>
       </c>
       <c r="D2722" t="n">
-        <v>43.3499984741211</v>
+        <v>42.939998626709</v>
       </c>
       <c r="E2722" t="n">
-        <v>44.2599983215332</v>
+        <v>43.4599990844727</v>
       </c>
       <c r="F2722" t="n">
-        <v>43.9900016784668</v>
+        <v>43.75</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>2785383</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>44.5200004577637</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>42.9099998474121</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>44.1599998474121</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>10.7646207809448</v>
+        <v>10.7646198272705</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G4" t="n">
-        <v>10.5398149490356</v>
+        <v>10.53981590271</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G7" t="n">
-        <v>10.8597278594971</v>
+        <v>10.8597288131714</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G9" t="n">
-        <v>11.300687789917</v>
+        <v>11.3006887435913</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G13" t="n">
-        <v>11.4044427871704</v>
+        <v>11.404444694519</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G14" t="n">
-        <v>11.0845308303833</v>
+        <v>11.084529876709</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G16" t="n">
-        <v>11.77623462677</v>
+        <v>11.7762336730957</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G17" t="n">
-        <v>11.6638317108154</v>
+        <v>11.6638307571411</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G18" t="n">
-        <v>11.7848815917969</v>
+        <v>11.7848806381226</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G24" t="n">
-        <v>11.430383682251</v>
+        <v>11.430380821228</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G25" t="n">
-        <v>11.5773696899414</v>
+        <v>11.5773687362671</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G26" t="n">
-        <v>11.0931797027588</v>
+        <v>11.0931787490845</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G28" t="n">
-        <v>10.7300338745117</v>
+        <v>10.730034828186</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>10.9375448226929</v>
+        <v>10.9375429153442</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>10.6349229812622</v>
+        <v>10.6349258422852</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>10.9807748794556</v>
+        <v>10.9807758331299</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G32" t="n">
-        <v>11.3439197540283</v>
+        <v>11.3439207077026</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>11.5427846908569</v>
+        <v>11.5427856445312</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G34" t="n">
-        <v>12.0615587234497</v>
+        <v>12.0615606307983</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G36" t="n">
-        <v>11.9232206344604</v>
+        <v>11.9232215881348</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>12.0529146194458</v>
+        <v>12.0529155731201</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G38" t="n">
-        <v>11.77623462677</v>
+        <v>11.7762336730957</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G39" t="n">
-        <v>11.4649686813354</v>
+        <v>11.4649677276611</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G41" t="n">
-        <v>12.0615587234497</v>
+        <v>12.0615606307983</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G45" t="n">
-        <v>12.4074115753174</v>
+        <v>12.407413482666</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G46" t="n">
-        <v>12.8397254943848</v>
+        <v>12.8397264480591</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G48" t="n">
-        <v>13.0991134643555</v>
+        <v>13.0991153717041</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G49" t="n">
-        <v>13.5746603012085</v>
+        <v>13.5746583938599</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G50" t="n">
-        <v>13.0731744766235</v>
+        <v>13.0731773376465</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>13.3239183425903</v>
+        <v>13.323917388916</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G53" t="n">
-        <v>13.0731744766235</v>
+        <v>13.0731773376465</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G55" t="n">
-        <v>12.6754465103149</v>
+        <v>12.6754474639893</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G56" t="n">
-        <v>12.69273853302</v>
+        <v>12.6927394866943</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G57" t="n">
-        <v>12.6235685348511</v>
+        <v>12.6235694885254</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>14.5</v>
       </c>
       <c r="G58" t="n">
-        <v>12.5371074676514</v>
+        <v>12.5371055603027</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G59" t="n">
-        <v>12.649507522583</v>
+        <v>12.6495084762573</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G61" t="n">
-        <v>12.7273244857788</v>
+        <v>12.7273235321045</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G62" t="n">
-        <v>13.1336984634399</v>
+        <v>13.1336994171143</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>12.8397254943848</v>
+        <v>12.8397264480591</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G66" t="n">
-        <v>12.563045501709</v>
+        <v>12.5630464553833</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>14.5</v>
       </c>
       <c r="G67" t="n">
-        <v>12.5371074676514</v>
+        <v>12.5371055603027</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G69" t="n">
-        <v>12.4333505630493</v>
+        <v>12.4333515167236</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G70" t="n">
-        <v>12.4679346084595</v>
+        <v>12.4679374694824</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G71" t="n">
-        <v>12.4679346084595</v>
+        <v>12.4679374694824</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>12.6667985916138</v>
+        <v>12.6667995452881</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>12.6235685348511</v>
+        <v>12.6235694885254</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G74" t="n">
-        <v>12.5111684799194</v>
+        <v>12.5111675262451</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G75" t="n">
-        <v>12.7792024612427</v>
+        <v>12.7792015075684</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G76" t="n">
-        <v>13.0731744766235</v>
+        <v>13.0731773376465</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G77" t="n">
-        <v>12.8310813903809</v>
+        <v>12.8310804367065</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>12.7964954376221</v>
+        <v>12.7964944839478</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G80" t="n">
-        <v>12.4333505630493</v>
+        <v>12.4333515167236</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>12.4074115753174</v>
+        <v>12.407413482666</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G83" t="n">
-        <v>12.1566715240479</v>
+        <v>12.1566696166992</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G84" t="n">
-        <v>12.2431335449219</v>
+        <v>12.2431316375732</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G85" t="n">
-        <v>12.6062755584717</v>
+        <v>12.606276512146</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G86" t="n">
-        <v>12.7273244857788</v>
+        <v>12.7273235321045</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>12.8397254943848</v>
+        <v>12.8397264480591</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>12.6667985916138</v>
+        <v>12.6667995452881</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>14.5</v>
       </c>
       <c r="G89" t="n">
-        <v>12.5371074676514</v>
+        <v>12.5371055603027</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G90" t="n">
-        <v>12.6322154998779</v>
+        <v>12.6322145462036</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G91" t="n">
-        <v>12.9434804916382</v>
+        <v>12.9434814453125</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G92" t="n">
-        <v>13.5400743484497</v>
+        <v>13.5400733947754</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>13.6611232757568</v>
+        <v>13.6611223220825</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G94" t="n">
-        <v>13.6005992889404</v>
+        <v>13.6005983352661</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G95" t="n">
-        <v>13.5573692321777</v>
+        <v>13.5573682785034</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G96" t="n">
-        <v>13.2547473907471</v>
+        <v>13.2547464370728</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>15.25</v>
       </c>
       <c r="G97" t="n">
-        <v>13.1855773925781</v>
+        <v>13.1855783462524</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G98" t="n">
-        <v>12.9867124557495</v>
+        <v>12.9867134094238</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="n">
-        <v>12.9694213867188</v>
+        <v>12.9694204330444</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G100" t="n">
-        <v>12.8559589385986</v>
+        <v>12.8559608459473</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G103" t="n">
-        <v>12.8995981216431</v>
+        <v>12.8995971679688</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>15</v>
       </c>
       <c r="G104" t="n">
-        <v>13.0916090011597</v>
+        <v>13.0916080474854</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G105" t="n">
-        <v>13.2137966156006</v>
+        <v>13.2137975692749</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>15</v>
       </c>
       <c r="G107" t="n">
-        <v>13.0916090011597</v>
+        <v>13.0916080474854</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G109" t="n">
-        <v>12.9868764877319</v>
+        <v>12.9868745803833</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G110" t="n">
-        <v>12.9432373046875</v>
+        <v>12.9432363510132</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G111" t="n">
-        <v>13.283618927002</v>
+        <v>13.2836198806763</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G112" t="n">
-        <v>13.3447122573853</v>
+        <v>13.3447132110596</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G113" t="n">
-        <v>13.3534412384033</v>
+        <v>13.353440284729</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>12.7861356735229</v>
+        <v>12.7861366271973</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>15</v>
       </c>
       <c r="G119" t="n">
-        <v>13.0916090011597</v>
+        <v>13.0916080474854</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G121" t="n">
-        <v>13.2923460006714</v>
+        <v>13.2923450469971</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G123" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G125" t="n">
-        <v>11.9570026397705</v>
+        <v>11.9570007324219</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G126" t="n">
-        <v>12.3410234451294</v>
+        <v>12.3410224914551</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G128" t="n">
-        <v>12.3410234451294</v>
+        <v>12.3410224914551</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G130" t="n">
-        <v>12.62903881073</v>
+        <v>12.6290378570557</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G131" t="n">
-        <v>12.3410234451294</v>
+        <v>12.3410224914551</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G133" t="n">
-        <v>12.4893941879272</v>
+        <v>12.4893960952759</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G134" t="n">
-        <v>12.5155782699585</v>
+        <v>12.5155773162842</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G135" t="n">
-        <v>12.6028547286987</v>
+        <v>12.6028537750244</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G136" t="n">
-        <v>12.5592164993286</v>
+        <v>12.5592155456543</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G137" t="n">
-        <v>12.62903881073</v>
+        <v>12.6290378570557</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G138" t="n">
-        <v>12.8035926818848</v>
+        <v>12.8035936355591</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G139" t="n">
-        <v>12.5941286087036</v>
+        <v>12.594126701355</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G140" t="n">
-        <v>12.5853986740112</v>
+        <v>12.5854005813599</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G141" t="n">
-        <v>12.4108448028564</v>
+        <v>12.4108457565308</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>15</v>
       </c>
       <c r="G143" t="n">
-        <v>13.0916090011597</v>
+        <v>13.0916080474854</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G144" t="n">
-        <v>13.4407167434692</v>
+        <v>13.4407176971436</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>16</v>
       </c>
       <c r="G147" t="n">
-        <v>13.9643812179565</v>
+        <v>13.9643831253052</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G149" t="n">
-        <v>13.6850967407227</v>
+        <v>13.6850957870483</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G151" t="n">
-        <v>13.1265201568604</v>
+        <v>13.126519203186</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>13.22252368927</v>
+        <v>13.2225255966187</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>13.3534412384033</v>
+        <v>13.353440284729</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G156" t="n">
-        <v>13.6240005493164</v>
+        <v>13.6239995956421</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G158" t="n">
-        <v>13.6501846313477</v>
+        <v>13.6501836776733</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G159" t="n">
-        <v>13.6240005493164</v>
+        <v>13.6239995956421</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G160" t="n">
-        <v>13.5978164672852</v>
+        <v>13.5978183746338</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>15.5</v>
       </c>
       <c r="G162" t="n">
-        <v>13.5279960632324</v>
+        <v>13.5279941558838</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G163" t="n">
-        <v>13.3796234130859</v>
+        <v>13.3796224594116</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G164" t="n">
-        <v>13.4407167434692</v>
+        <v>13.4407176971436</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G165" t="n">
-        <v>13.5978164672852</v>
+        <v>13.5978183746338</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>15.25</v>
       </c>
       <c r="G168" t="n">
-        <v>13.3098020553589</v>
+        <v>13.3098030090332</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G170" t="n">
-        <v>13.1439752578735</v>
+        <v>13.1439762115479</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G172" t="n">
-        <v>13.0392427444458</v>
+        <v>13.0392398834229</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G176" t="n">
-        <v>13.3185291290283</v>
+        <v>13.3185300827026</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G177" t="n">
-        <v>13.283618927002</v>
+        <v>13.2836198806763</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G178" t="n">
-        <v>13.2137966156006</v>
+        <v>13.2137975692749</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>13.3534412384033</v>
+        <v>13.353440284729</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>15.25</v>
       </c>
       <c r="G181" t="n">
-        <v>13.3098020553589</v>
+        <v>13.3098030090332</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G182" t="n">
-        <v>13.8247385025024</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G183" t="n">
-        <v>13.2312507629395</v>
+        <v>13.2312526702881</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>13.6152725219727</v>
+        <v>13.615273475647</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>13.6152725219727</v>
+        <v>13.615273475647</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G190" t="n">
-        <v>13.0741529464722</v>
+        <v>13.0741519927979</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G192" t="n">
-        <v>13.1265201568604</v>
+        <v>13.126519203186</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G193" t="n">
-        <v>13.2574338912964</v>
+        <v>13.2574348449707</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G195" t="n">
-        <v>13.3185291290283</v>
+        <v>13.3185300827026</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G197" t="n">
-        <v>13.3970804214478</v>
+        <v>13.3970794677734</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G198" t="n">
-        <v>13.1003370285034</v>
+        <v>13.1003360748291</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>15.25</v>
       </c>
       <c r="G199" t="n">
-        <v>13.3098020553589</v>
+        <v>13.3098030090332</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G200" t="n">
-        <v>13.4494466781616</v>
+        <v>13.4494457244873</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G201" t="n">
-        <v>13.3970804214478</v>
+        <v>13.3970794677734</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G203" t="n">
-        <v>13.3534412384033</v>
+        <v>13.353440284729</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>13.7025508880615</v>
+        <v>13.7025489807129</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G206" t="n">
-        <v>13.5978164672852</v>
+        <v>13.5978183746338</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G207" t="n">
-        <v>13.4407167434692</v>
+        <v>13.4407176971436</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G208" t="n">
-        <v>13.6240005493164</v>
+        <v>13.6239995956421</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>15.5</v>
       </c>
       <c r="G209" t="n">
-        <v>13.5279960632324</v>
+        <v>13.5279941558838</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G213" t="n">
-        <v>13.4058055877686</v>
+        <v>13.4058074951172</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G217" t="n">
-        <v>13.0217876434326</v>
+        <v>13.021785736084</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>15</v>
       </c>
       <c r="G222" t="n">
-        <v>13.0916090011597</v>
+        <v>13.0916080474854</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G224" t="n">
-        <v>13.1265201568604</v>
+        <v>13.126519203186</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G225" t="n">
-        <v>13.0217876434326</v>
+        <v>13.021785736084</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G226" t="n">
-        <v>12.9868764877319</v>
+        <v>12.9868745803833</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G227" t="n">
-        <v>13.1439752578735</v>
+        <v>13.1439762115479</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G228" t="n">
-        <v>12.9606914520264</v>
+        <v>12.9606924057007</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G229" t="n">
-        <v>13.1265201568604</v>
+        <v>13.126519203186</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>15.25</v>
       </c>
       <c r="G230" t="n">
-        <v>13.3098020553589</v>
+        <v>13.3098030090332</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G232" t="n">
-        <v>13.1003370285034</v>
+        <v>13.1003360748291</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G234" t="n">
-        <v>12.9519662857056</v>
+        <v>12.9519653320312</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G235" t="n">
-        <v>13.2923460006714</v>
+        <v>13.2923450469971</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G239" t="n">
-        <v>13.6589107513428</v>
+        <v>13.6589117050171</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G240" t="n">
-        <v>14.2349424362183</v>
+        <v>14.2349414825439</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>14.2262144088745</v>
+        <v>14.2262134552002</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>16.8099994659424</v>
       </c>
       <c r="G243" t="n">
-        <v>14.671329498291</v>
+        <v>14.6713266372681</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G245" t="n">
-        <v>14.4793176651001</v>
+        <v>14.4793195724487</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G247" t="n">
-        <v>14.3222208023071</v>
+        <v>14.3222188949585</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G248" t="n">
-        <v>14.3571329116821</v>
+        <v>14.3571319580078</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G249" t="n">
-        <v>14.4531345367432</v>
+        <v>14.4531354904175</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G250" t="n">
-        <v>14.4793176651001</v>
+        <v>14.4793195724487</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G251" t="n">
-        <v>14.3745861053467</v>
+        <v>14.374587059021</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G252" t="n">
-        <v>14.243670463562</v>
+        <v>14.2436695098877</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G256" t="n">
-        <v>14.4531345367432</v>
+        <v>14.4531354904175</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>14.6626005172729</v>
+        <v>14.6626024246216</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G259" t="n">
-        <v>14.5491428375244</v>
+        <v>14.5491399765015</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G261" t="n">
-        <v>14.2611265182495</v>
+        <v>14.2611255645752</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G262" t="n">
-        <v>14.4793176651001</v>
+        <v>14.4793195724487</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G263" t="n">
-        <v>14.243670463562</v>
+        <v>14.2436695098877</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G265" t="n">
-        <v>15.0029830932617</v>
+        <v>15.0029821395874</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G266" t="n">
-        <v>15.0378932952881</v>
+        <v>15.0378942489624</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G267" t="n">
-        <v>15.2473592758179</v>
+        <v>15.2473602294922</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G268" t="n">
-        <v>15.2822723388672</v>
+        <v>15.2822713851929</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G269" t="n">
-        <v>15.0466222763062</v>
+        <v>15.0466194152832</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G270" t="n">
-        <v>15.3346357345581</v>
+        <v>15.3346366882324</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G271" t="n">
-        <v>15.6401081085205</v>
+        <v>15.6401071548462</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>18</v>
       </c>
       <c r="G272" t="n">
-        <v>15.7099304199219</v>
+        <v>15.7099294662476</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G273" t="n">
-        <v>15.7448406219482</v>
+        <v>15.7448415756226</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G274" t="n">
-        <v>15.7361154556274</v>
+        <v>15.7361173629761</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G275" t="n">
-        <v>15.7884788513184</v>
+        <v>15.788480758667</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G276" t="n">
-        <v>15.6575651168823</v>
+        <v>15.657567024231</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G277" t="n">
-        <v>15.7361154556274</v>
+        <v>15.7361173629761</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>15.5790128707886</v>
+        <v>15.5790147781372</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>15.5353736877441</v>
+        <v>15.5353755950928</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>18</v>
       </c>
       <c r="G280" t="n">
-        <v>15.7099304199219</v>
+        <v>15.7099294662476</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G281" t="n">
-        <v>15.6401081085205</v>
+        <v>15.6401071548462</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G283" t="n">
-        <v>15.1949939727783</v>
+        <v>15.194993019104</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G285" t="n">
-        <v>15.526650428772</v>
+        <v>15.526647567749</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G286" t="n">
-        <v>15.5091915130615</v>
+        <v>15.5091896057129</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>17.75</v>
       </c>
       <c r="G287" t="n">
-        <v>15.4917392730713</v>
+        <v>15.491735458374</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>15.5353736877441</v>
+        <v>15.5353755950928</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>15.5353736877441</v>
+        <v>15.5353755950928</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G292" t="n">
-        <v>15.526650428772</v>
+        <v>15.526647567749</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G293" t="n">
-        <v>15.7186584472656</v>
+        <v>15.718656539917</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>18</v>
       </c>
       <c r="G294" t="n">
-        <v>15.7099304199219</v>
+        <v>15.7099294662476</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>17.9300003051758</v>
       </c>
       <c r="G295" t="n">
-        <v>15.6488351821899</v>
+        <v>15.6488370895386</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G296" t="n">
-        <v>15.5964708328247</v>
+        <v>15.5964679718018</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G298" t="n">
-        <v>15.5179233551025</v>
+        <v>15.5179214477539</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G302" t="n">
-        <v>16.6787109375</v>
+        <v>16.6787090301514</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G303" t="n">
-        <v>16.8096237182617</v>
+        <v>16.8096218109131</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G304" t="n">
-        <v>16.8445339202881</v>
+        <v>16.8445358276367</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G305" t="n">
-        <v>16.8096237182617</v>
+        <v>16.8096218109131</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G307" t="n">
-        <v>17.0714588165283</v>
+        <v>17.0714569091797</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G314" t="n">
-        <v>17.5514850616455</v>
+        <v>17.5514812469482</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G315" t="n">
-        <v>17.5776672363281</v>
+        <v>17.5776634216309</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>20.5</v>
       </c>
       <c r="G319" t="n">
-        <v>17.89186668396</v>
+        <v>17.8918628692627</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>20.2299995422363</v>
       </c>
       <c r="G320" t="n">
-        <v>17.656213760376</v>
+        <v>17.6562175750732</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G321" t="n">
-        <v>17.7609462738037</v>
+        <v>17.7609519958496</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>18.3980751037598</v>
+        <v>18.3980731964111</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>21.4099998474121</v>
       </c>
       <c r="G325" t="n">
-        <v>18.6860904693604</v>
+        <v>18.6860885620117</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G329" t="n">
-        <v>19.0090179443359</v>
+        <v>19.0090160369873</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>21.3899993896484</v>
       </c>
       <c r="G331" t="n">
-        <v>18.6686325073242</v>
+        <v>18.6686305999756</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G332" t="n">
-        <v>18.7733688354492</v>
+        <v>18.7733669281006</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>21.75</v>
       </c>
       <c r="G333" t="n">
-        <v>18.9828338623047</v>
+        <v>18.9828319549561</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G334" t="n">
-        <v>19.1399345397949</v>
+        <v>19.1399326324463</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G336" t="n">
-        <v>19.0264663696289</v>
+        <v>19.0264682769775</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G338" t="n">
-        <v>19.6199550628662</v>
+        <v>19.6199569702148</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>22.75</v>
       </c>
       <c r="G339" t="n">
-        <v>19.8556041717529</v>
+        <v>19.8556060791016</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>23.5100002288818</v>
       </c>
       <c r="G343" t="n">
-        <v>20.518913269043</v>
+        <v>20.5189151763916</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G344" t="n">
-        <v>19.8992462158203</v>
+        <v>19.8992443084717</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>19.3319416046143</v>
+        <v>19.331937789917</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>22.25</v>
       </c>
       <c r="G348" t="n">
-        <v>19.4192218780518</v>
+        <v>19.4192199707031</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G349" t="n">
-        <v>19.3144836425781</v>
+        <v>19.3144855499268</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>19.3319416046143</v>
+        <v>19.331937789917</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G351" t="n">
-        <v>19.4279479980469</v>
+        <v>19.4279460906982</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>21.4099998474121</v>
       </c>
       <c r="G352" t="n">
-        <v>18.6860904693604</v>
+        <v>18.6860885620117</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>21.5900001525879</v>
       </c>
       <c r="G353" t="n">
-        <v>18.8431911468506</v>
+        <v>18.8431873321533</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>19.053092956543</v>
+        <v>19.0530910491943</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G358" t="n">
-        <v>18.938684463501</v>
+        <v>18.9386863708496</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G359" t="n">
-        <v>19.4491119384766</v>
+        <v>19.4491157531738</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G362" t="n">
-        <v>19.0794925689697</v>
+        <v>19.0794906616211</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G364" t="n">
-        <v>18.938684463501</v>
+        <v>18.9386863708496</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G366" t="n">
-        <v>18.3930530548096</v>
+        <v>18.3930511474609</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G367" t="n">
-        <v>18.4722595214844</v>
+        <v>18.4722576141357</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G370" t="n">
-        <v>18.0586357116699</v>
+        <v>18.0586338043213</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G371" t="n">
-        <v>18.305046081543</v>
+        <v>18.3050479888916</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G372" t="n">
-        <v>18.5866661071777</v>
+        <v>18.5866641998291</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G373" t="n">
-        <v>18.5074615478516</v>
+        <v>18.5074577331543</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G374" t="n">
-        <v>18.7978763580322</v>
+        <v>18.7978744506836</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G375" t="n">
-        <v>18.6834678649902</v>
+        <v>18.6834716796875</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G376" t="n">
-        <v>19.0618896484375</v>
+        <v>19.0618915557861</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G377" t="n">
-        <v>18.6746692657471</v>
+        <v>18.6746673583984</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G379" t="n">
-        <v>18.6042671203613</v>
+        <v>18.6042633056641</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G382" t="n">
-        <v>18.4106540679932</v>
+        <v>18.4106502532959</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G385" t="n">
-        <v>18.1114368438721</v>
+        <v>18.1114387512207</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>18.2786464691162</v>
+        <v>18.2786445617676</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>18.0850353240967</v>
+        <v>18.0850315093994</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>18.5690631866455</v>
+        <v>18.5690612792969</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G391" t="n">
-        <v>18.5866661071777</v>
+        <v>18.5866641998291</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G393" t="n">
-        <v>18.8330764770508</v>
+        <v>18.8330783843994</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>21.4300003051758</v>
       </c>
       <c r="G394" t="n">
-        <v>18.8594779968262</v>
+        <v>18.8594799041748</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G396" t="n">
-        <v>18.8858814239502</v>
+        <v>18.8858795166016</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G398" t="n">
-        <v>18.8858814239502</v>
+        <v>18.8858795166016</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G399" t="n">
-        <v>18.7274723052979</v>
+        <v>18.7274742126465</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G400" t="n">
-        <v>18.6570682525635</v>
+        <v>18.6570701599121</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>19.6691265106201</v>
+        <v>19.6691246032715</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G405" t="n">
-        <v>19.9771461486816</v>
+        <v>19.9771423339844</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G406" t="n">
-        <v>19.7835311889648</v>
+        <v>19.7835330963135</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>19.7571296691895</v>
+        <v>19.7571315765381</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>19.7571296691895</v>
+        <v>19.7571315765381</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>22.5</v>
       </c>
       <c r="G411" t="n">
-        <v>19.8011322021484</v>
+        <v>19.8011341094971</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G412" t="n">
-        <v>19.8275356292725</v>
+        <v>19.8275337219238</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>22.5</v>
       </c>
       <c r="G413" t="n">
-        <v>19.8011322021484</v>
+        <v>19.8011341094971</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G415" t="n">
-        <v>20.2587566375732</v>
+        <v>20.2587604522705</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>23.6100006103516</v>
       </c>
       <c r="G418" t="n">
-        <v>20.7779884338379</v>
+        <v>20.7779903411865</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>20.7691898345947</v>
+        <v>20.7691879272461</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G424" t="n">
-        <v>20.6107788085938</v>
+        <v>20.6107807159424</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G425" t="n">
-        <v>20.2851619720459</v>
+        <v>20.2851600646973</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G426" t="n">
-        <v>20.6723823547363</v>
+        <v>20.6723804473877</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>23.8700008392334</v>
       </c>
       <c r="G427" t="n">
-        <v>21.0068035125732</v>
+        <v>21.0068016052246</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>24.0699996948242</v>
       </c>
       <c r="G431" t="n">
-        <v>21.1828117370605</v>
+        <v>21.1828098297119</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G432" t="n">
-        <v>21.3764228820801</v>
+        <v>21.3764266967773</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>24.4699993133545</v>
       </c>
       <c r="G433" t="n">
-        <v>21.5348320007324</v>
+        <v>21.5348339080811</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>24.7700004577637</v>
       </c>
       <c r="G434" t="n">
-        <v>21.7988471984863</v>
+        <v>21.798849105835</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>21.7372436523438</v>
+        <v>21.7372417449951</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G437" t="n">
-        <v>21.7372436523438</v>
+        <v>21.7372417449951</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>24.9699993133545</v>
       </c>
       <c r="G438" t="n">
-        <v>21.9748554229736</v>
+        <v>21.974853515625</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G441" t="n">
-        <v>21.7548446655273</v>
+        <v>21.754846572876</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G442" t="n">
-        <v>21.6052341461182</v>
+        <v>21.6052379608154</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G443" t="n">
-        <v>21.5876388549805</v>
+        <v>21.5876369476318</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>24.5699996948242</v>
       </c>
       <c r="G444" t="n">
-        <v>21.6228351593018</v>
+        <v>21.6228370666504</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>24.25</v>
       </c>
       <c r="G445" t="n">
-        <v>21.3412227630615</v>
+        <v>21.3412189483643</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>24.3700008392334</v>
       </c>
       <c r="G447" t="n">
-        <v>21.4468269348145</v>
+        <v>21.4468288421631</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G448" t="n">
-        <v>21.4908275604248</v>
+        <v>21.4908294677734</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>24.7700004577637</v>
       </c>
       <c r="G450" t="n">
-        <v>21.7988471984863</v>
+        <v>21.798849105835</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G451" t="n">
-        <v>21.2268161773682</v>
+        <v>21.2268142700195</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G452" t="n">
-        <v>21.1388130187988</v>
+        <v>21.1388092041016</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>23.7099990844727</v>
       </c>
       <c r="G453" t="n">
-        <v>20.8659934997559</v>
+        <v>20.8659954071045</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>23.8700008392334</v>
       </c>
       <c r="G454" t="n">
-        <v>21.0068035125732</v>
+        <v>21.0068016052246</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G456" t="n">
-        <v>21.6492366790771</v>
+        <v>21.6492404937744</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G457" t="n">
-        <v>21.438024520874</v>
+        <v>21.4380264282227</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G458" t="n">
-        <v>21.6492366790771</v>
+        <v>21.6492404937744</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G459" t="n">
-        <v>21.6580390930176</v>
+        <v>21.6580410003662</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G460" t="n">
-        <v>21.7196426391602</v>
+        <v>21.7196407318115</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>24.2800006866455</v>
       </c>
       <c r="G462" t="n">
-        <v>21.3676223754883</v>
+        <v>21.3676242828369</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G463" t="n">
-        <v>21.8076496124268</v>
+        <v>21.8076477050781</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G464" t="n">
-        <v>21.7196426391602</v>
+        <v>21.7196407318115</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G466" t="n">
-        <v>21.7284412384033</v>
+        <v>21.7284450531006</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G468" t="n">
-        <v>21.3764228820801</v>
+        <v>21.3764266967773</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>24.25</v>
       </c>
       <c r="G469" t="n">
-        <v>21.3412227630615</v>
+        <v>21.3412189483643</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G470" t="n">
-        <v>21.4556255340576</v>
+        <v>21.4556293487549</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G471" t="n">
-        <v>21.7548446655273</v>
+        <v>21.754846572876</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G472" t="n">
-        <v>21.3852233886719</v>
+        <v>21.3852214813232</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G473" t="n">
-        <v>21.3236179351807</v>
+        <v>21.3236198425293</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G476" t="n">
-        <v>20.6723823547363</v>
+        <v>20.6723804473877</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>20.0651454925537</v>
+        <v>20.0651473999023</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G478" t="n">
-        <v>20.2851619720459</v>
+        <v>20.2851600646973</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>23.2600002288818</v>
       </c>
       <c r="G479" t="n">
-        <v>20.4699726104736</v>
+        <v>20.469970703125</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>22.8299999237061</v>
       </c>
       <c r="G481" t="n">
-        <v>20.0915470123291</v>
+        <v>20.0915489196777</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>22.9400005340576</v>
       </c>
       <c r="G482" t="n">
-        <v>20.1883563995361</v>
+        <v>20.1883544921875</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>22.8099994659424</v>
       </c>
       <c r="G483" t="n">
-        <v>20.0739498138428</v>
+        <v>20.0739517211914</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>20.5051727294922</v>
+        <v>20.5051746368408</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>23.2900009155273</v>
       </c>
       <c r="G486" t="n">
-        <v>20.496374130249</v>
+        <v>20.4963722229004</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G488" t="n">
-        <v>20.5403747558594</v>
+        <v>20.540376663208</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G489" t="n">
-        <v>20.5051727294922</v>
+        <v>20.5051746368408</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>23.2900009155273</v>
       </c>
       <c r="G490" t="n">
-        <v>20.496374130249</v>
+        <v>20.4963722229004</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>23.0300006866455</v>
       </c>
       <c r="G492" t="n">
-        <v>20.2675590515137</v>
+        <v>20.2675609588623</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G493" t="n">
-        <v>20.2147560119629</v>
+        <v>20.2147541046143</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>23.6700000762939</v>
       </c>
       <c r="G495" t="n">
-        <v>20.8307933807373</v>
+        <v>20.8307914733887</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G499" t="n">
-        <v>21.8780555725098</v>
+        <v>21.8780536651611</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>25.2700004577637</v>
       </c>
       <c r="G500" t="n">
-        <v>22.2388744354248</v>
+        <v>22.2388725280762</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G501" t="n">
-        <v>21.6052341461182</v>
+        <v>21.6052379608154</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G502" t="n">
-        <v>21.3764228820801</v>
+        <v>21.3764266967773</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>25.6800003051758</v>
       </c>
       <c r="G508" t="n">
-        <v>22.5996952056885</v>
+        <v>22.5996932983398</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G509" t="n">
-        <v>22.9869155883789</v>
+        <v>22.9869136810303</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G510" t="n">
-        <v>23.2333316802979</v>
+        <v>23.2333278656006</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>26.0799999237061</v>
       </c>
       <c r="G511" t="n">
-        <v>22.9517116546631</v>
+        <v>22.9517135620117</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G512" t="n">
-        <v>22.70530128479</v>
+        <v>22.7052974700928</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>22.5292911529541</v>
+        <v>22.5292892456055</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G514" t="n">
-        <v>22.9693145751953</v>
+        <v>22.9693164825439</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>25.9400005340576</v>
       </c>
       <c r="G515" t="n">
-        <v>22.8285064697266</v>
+        <v>22.8285083770752</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G517" t="n">
-        <v>22.9869155883789</v>
+        <v>22.9869136810303</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>25.4400005340576</v>
       </c>
       <c r="G521" t="n">
-        <v>22.3884792327881</v>
+        <v>22.3884811401367</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>27.0400009155273</v>
       </c>
       <c r="G525" t="n">
-        <v>23.7965621948242</v>
+        <v>23.7965641021729</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>26.7800006866455</v>
       </c>
       <c r="G526" t="n">
-        <v>23.5677471160889</v>
+        <v>23.5677490234375</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G527" t="n">
-        <v>23.690954208374</v>
+        <v>23.6909561157227</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>26.7800006866455</v>
       </c>
       <c r="G529" t="n">
-        <v>23.5677471160889</v>
+        <v>23.5677490234375</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G530" t="n">
-        <v>23.8317642211914</v>
+        <v>23.8317604064941</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G533" t="n">
-        <v>23.356538772583</v>
+        <v>23.3565349578857</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>26.7399997711182</v>
       </c>
       <c r="G534" t="n">
-        <v>23.5325450897217</v>
+        <v>23.5325469970703</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G535" t="n">
-        <v>22.8989124298096</v>
+        <v>22.8989086151123</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>22.5292911529541</v>
+        <v>22.5292892456055</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G539" t="n">
-        <v>22.9869155883789</v>
+        <v>22.9869136810303</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G540" t="n">
-        <v>22.634895324707</v>
+        <v>22.6348972320557</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>27.2299995422363</v>
       </c>
       <c r="G543" t="n">
-        <v>23.963773727417</v>
+        <v>23.9637718200684</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>25.0374317169189</v>
+        <v>25.0374298095703</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G546" t="n">
-        <v>24.7118129730225</v>
+        <v>24.7118148803711</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>28.25</v>
       </c>
       <c r="G548" t="n">
-        <v>24.8614253997803</v>
+        <v>24.8614234924316</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>28.1200008392334</v>
       </c>
       <c r="G549" t="n">
-        <v>24.7470188140869</v>
+        <v>24.7470149993896</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>28.3099994659424</v>
       </c>
       <c r="G551" t="n">
-        <v>24.9142246246338</v>
+        <v>24.9142284393311</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>28.8600006103516</v>
       </c>
       <c r="G552" t="n">
-        <v>25.3982563018799</v>
+        <v>25.3982524871826</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G553" t="n">
-        <v>25.2574462890625</v>
+        <v>25.2574481964111</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G554" t="n">
-        <v>24.6062068939209</v>
+        <v>24.6062088012695</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>28.3799991607666</v>
       </c>
       <c r="G556" t="n">
-        <v>24.9758243560791</v>
+        <v>24.975830078125</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>25.4774608612061</v>
+        <v>25.4774589538574</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G559" t="n">
-        <v>25.6622657775879</v>
+        <v>25.6622695922852</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G561" t="n">
-        <v>25.9174861907959</v>
+        <v>25.9174842834473</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>29.25</v>
       </c>
       <c r="G562" t="n">
-        <v>25.7414722442627</v>
+        <v>25.7414741516113</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>25.4774608612061</v>
+        <v>25.4774589538574</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>29.6100006103516</v>
       </c>
       <c r="G564" t="n">
-        <v>26.0582942962646</v>
+        <v>26.0582904815674</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>29.7700004577637</v>
       </c>
       <c r="G566" t="n">
-        <v>26.1991004943848</v>
+        <v>26.1991024017334</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>30.8600006103516</v>
       </c>
       <c r="G568" t="n">
-        <v>27.158353805542</v>
+        <v>27.1583557128906</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>30.6100006103516</v>
       </c>
       <c r="G570" t="n">
-        <v>26.9383392333984</v>
+        <v>26.9383411407471</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>30.8600006103516</v>
       </c>
       <c r="G572" t="n">
-        <v>27.158353805542</v>
+        <v>27.1583557128906</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>30.8299999237061</v>
       </c>
       <c r="G573" t="n">
-        <v>27.1319484710693</v>
+        <v>27.1319522857666</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>32.5</v>
       </c>
       <c r="G576" t="n">
-        <v>28.6016368865967</v>
+        <v>28.601634979248</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>32.9199981689453</v>
       </c>
       <c r="G577" t="n">
-        <v>28.9712543487549</v>
+        <v>28.9712581634521</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>33.3899993896484</v>
       </c>
       <c r="G579" t="n">
-        <v>29.3848781585693</v>
+        <v>29.3848819732666</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>33.0299987792969</v>
       </c>
       <c r="G580" t="n">
-        <v>29.0680637359619</v>
+        <v>29.0680599212646</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>33.75</v>
       </c>
       <c r="G581" t="n">
-        <v>29.7017002105713</v>
+        <v>29.7016983032227</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>33.75</v>
       </c>
       <c r="G582" t="n">
-        <v>29.7017002105713</v>
+        <v>29.7016983032227</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>34.0400009155273</v>
       </c>
       <c r="G583" t="n">
-        <v>29.956916809082</v>
+        <v>29.9569149017334</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>33.6599998474121</v>
       </c>
       <c r="G584" t="n">
-        <v>29.6224918365479</v>
+        <v>29.6224956512451</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>34.4599990844727</v>
       </c>
       <c r="G585" t="n">
-        <v>30.3265342712402</v>
+        <v>30.3265361785889</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>35.2299995422363</v>
       </c>
       <c r="G586" t="n">
-        <v>31.0041770935059</v>
+        <v>31.0041732788086</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>35.0200004577637</v>
       </c>
       <c r="G587" t="n">
-        <v>30.8193683624268</v>
+        <v>30.8193645477295</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>35.3600006103516</v>
       </c>
       <c r="G588" t="n">
-        <v>31.1185817718506</v>
+        <v>31.118579864502</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>36.0200004577637</v>
       </c>
       <c r="G590" t="n">
-        <v>31.6994190216064</v>
+        <v>31.6994132995605</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G591" t="n">
-        <v>31.7698211669922</v>
+        <v>31.7698173522949</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>37.439998626709</v>
       </c>
       <c r="G594" t="n">
-        <v>32.949089050293</v>
+        <v>32.9490814208984</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>38</v>
       </c>
       <c r="G595" t="n">
-        <v>33.4419136047363</v>
+        <v>33.4419174194336</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>36.5</v>
       </c>
       <c r="G596" t="n">
-        <v>32.1218376159668</v>
+        <v>32.1218452453613</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>35.6699981689453</v>
       </c>
       <c r="G597" t="n">
-        <v>31.3913993835449</v>
+        <v>31.3913898468018</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>36.4799995422363</v>
       </c>
       <c r="G599" t="n">
-        <v>32.1042404174805</v>
+        <v>32.1042327880859</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>32.7378730773926</v>
+        <v>32.7378768920898</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G604" t="n">
-        <v>33.1338958740234</v>
+        <v>33.1338996887207</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>37.9799995422363</v>
       </c>
       <c r="G605" t="n">
-        <v>33.42431640625</v>
+        <v>33.4243125915527</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>38.9099998474121</v>
       </c>
       <c r="G606" t="n">
-        <v>34.2427558898926</v>
+        <v>34.2427597045898</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>38.8600006103516</v>
       </c>
       <c r="G608" t="n">
-        <v>34.443531036377</v>
+        <v>34.4435348510742</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>37.8300018310547</v>
       </c>
       <c r="G611" t="n">
-        <v>33.530590057373</v>
+        <v>33.5305938720703</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>38.5499992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>34.1687622070312</v>
+        <v>34.1687660217285</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>39.2700004577637</v>
       </c>
       <c r="G616" t="n">
-        <v>34.8069381713867</v>
+        <v>34.8069343566895</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>39.8400001525879</v>
       </c>
       <c r="G618" t="n">
-        <v>35.3121528625488</v>
+        <v>35.3121566772461</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>41.3400001525879</v>
       </c>
       <c r="G619" t="n">
-        <v>36.6416816711426</v>
+        <v>36.6416854858398</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>40.8899993896484</v>
       </c>
       <c r="G620" t="n">
-        <v>36.2428169250488</v>
+        <v>36.2428207397461</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>39.8400001525879</v>
       </c>
       <c r="G621" t="n">
-        <v>35.3121528625488</v>
+        <v>35.3121566772461</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>39.75</v>
       </c>
       <c r="G622" t="n">
-        <v>35.2323875427246</v>
+        <v>35.2323837280273</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>41.2200012207031</v>
       </c>
       <c r="G624" t="n">
-        <v>36.5353202819824</v>
+        <v>36.5353240966797</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>42.060001373291</v>
       </c>
       <c r="G627" t="n">
-        <v>37.279857635498</v>
+        <v>37.2798538208008</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>41.4700012207031</v>
       </c>
       <c r="G628" t="n">
-        <v>36.756908416748</v>
+        <v>36.7569122314453</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>39.7799987792969</v>
       </c>
       <c r="G631" t="n">
-        <v>35.2589721679688</v>
+        <v>35.258975982666</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>39.5699996948242</v>
       </c>
       <c r="G632" t="n">
-        <v>35.0728378295898</v>
+        <v>35.0728416442871</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>38.8300018310547</v>
       </c>
       <c r="G633" t="n">
-        <v>34.4169464111328</v>
+        <v>34.4169425964355</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>38.810001373291</v>
       </c>
       <c r="G634" t="n">
-        <v>34.3992156982422</v>
+        <v>34.3992118835449</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>38.939998626709</v>
       </c>
       <c r="G635" t="n">
-        <v>34.5144424438477</v>
+        <v>34.5144348144531</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>38.4900016784668</v>
       </c>
       <c r="G636" t="n">
-        <v>34.1155853271484</v>
+        <v>34.1155891418457</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>39</v>
       </c>
       <c r="G637" t="n">
-        <v>34.567626953125</v>
+        <v>34.5676231384277</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>39.2700004577637</v>
       </c>
       <c r="G639" t="n">
-        <v>34.8069381713867</v>
+        <v>34.8069343566895</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>37.8499984741211</v>
       </c>
       <c r="G640" t="n">
-        <v>33.5483131408691</v>
+        <v>33.5483169555664</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>37</v>
       </c>
       <c r="G642" t="n">
-        <v>32.7949180603027</v>
+        <v>32.7949256896973</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G643" t="n">
-        <v>33.326732635498</v>
+        <v>33.3267288208008</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>33.8585433959961</v>
+        <v>33.8585395812988</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>39.0299987792969</v>
       </c>
       <c r="G647" t="n">
-        <v>34.5942153930664</v>
+        <v>34.5942115783691</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>38.5099983215332</v>
       </c>
       <c r="G648" t="n">
-        <v>34.1333084106445</v>
+        <v>34.1333045959473</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>39</v>
       </c>
       <c r="G650" t="n">
-        <v>34.567626953125</v>
+        <v>34.5676231384277</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>34.3903465270996</v>
+        <v>34.3903503417969</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G655" t="n">
-        <v>35.1437568664551</v>
+        <v>35.1437530517578</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>38.0400009155273</v>
       </c>
       <c r="G657" t="n">
-        <v>33.716724395752</v>
+        <v>33.7167282104492</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>37.5</v>
       </c>
       <c r="G660" t="n">
-        <v>33.2380981445312</v>
+        <v>33.2381019592285</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>38.5499992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>34.1687622070312</v>
+        <v>34.1687660217285</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>37.689998626709</v>
       </c>
       <c r="G665" t="n">
-        <v>33.4065017700195</v>
+        <v>33.4065055847168</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>37.9599990844727</v>
       </c>
       <c r="G669" t="n">
-        <v>33.6458206176758</v>
+        <v>33.645824432373</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G671" t="n">
-        <v>33.0608253479004</v>
+        <v>33.0608291625977</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>37.810001373291</v>
       </c>
       <c r="G673" t="n">
-        <v>33.512866973877</v>
+        <v>33.5128707885742</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>38.4900016784668</v>
       </c>
       <c r="G675" t="n">
-        <v>34.1155853271484</v>
+        <v>34.1155891418457</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>39.7099990844727</v>
       </c>
       <c r="G677" t="n">
-        <v>35.1969261169434</v>
+        <v>35.1969299316406</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>39.6399993896484</v>
       </c>
       <c r="G678" t="n">
-        <v>35.1348838806152</v>
+        <v>35.134880065918</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>39.7799987792969</v>
       </c>
       <c r="G680" t="n">
-        <v>35.2589721679688</v>
+        <v>35.258975982666</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>38.9300003051758</v>
       </c>
       <c r="G682" t="n">
-        <v>34.5055809020996</v>
+        <v>34.5055770874023</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G685" t="n">
-        <v>32.8835525512695</v>
+        <v>32.8835563659668</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>37.6100006103516</v>
       </c>
       <c r="G688" t="n">
-        <v>33.3355979919434</v>
+        <v>33.3356018066406</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>37.9300003051758</v>
       </c>
       <c r="G693" t="n">
-        <v>33.6192207336426</v>
+        <v>33.6192245483398</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>37.8499984741211</v>
       </c>
       <c r="G694" t="n">
-        <v>33.5483131408691</v>
+        <v>33.5483169555664</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>37.3699989318848</v>
       </c>
       <c r="G697" t="n">
-        <v>33.1228675842285</v>
+        <v>33.1228713989258</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>37.8300018310547</v>
       </c>
       <c r="G698" t="n">
-        <v>33.530590057373</v>
+        <v>33.5305938720703</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>37.7299995422363</v>
       </c>
       <c r="G699" t="n">
-        <v>33.4419555664062</v>
+        <v>33.4419593811035</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G701" t="n">
-        <v>32.8835525512695</v>
+        <v>32.8835563659668</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G702" t="n">
-        <v>34.3903465270996</v>
+        <v>34.3903503417969</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>38.6199989318848</v>
       </c>
       <c r="G703" t="n">
-        <v>34.2308082580566</v>
+        <v>34.2308120727539</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>36.1599998474121</v>
       </c>
       <c r="G705" t="n">
-        <v>32.0503883361816</v>
+        <v>32.0503921508789</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G707" t="n">
-        <v>30.9335899353027</v>
+        <v>30.9335880279541</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>31.7299995422363</v>
       </c>
       <c r="G709" t="n">
-        <v>28.1238613128662</v>
+        <v>28.1238632202148</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>31.2800006866455</v>
       </c>
       <c r="G710" t="n">
-        <v>27.7250080108643</v>
+        <v>27.725004196167</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G711" t="n">
-        <v>27.4059181213379</v>
+        <v>27.4059200286865</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>31.1399993896484</v>
       </c>
       <c r="G714" t="n">
-        <v>27.6009159088135</v>
+        <v>27.6009178161621</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>27.6540966033936</v>
+        <v>27.6540985107422</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>26.9450187683105</v>
+        <v>26.9450149536133</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>29.2299995422363</v>
       </c>
       <c r="G718" t="n">
-        <v>25.9079895019531</v>
+        <v>25.9079914093018</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G719" t="n">
-        <v>26.5018424987793</v>
+        <v>26.5018463134766</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>27.1222877502441</v>
+        <v>27.1222858428955</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>30.2299995422363</v>
       </c>
       <c r="G721" t="n">
-        <v>26.794340133667</v>
+        <v>26.7943382263184</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G723" t="n">
-        <v>26.7677516937256</v>
+        <v>26.767749786377</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>27.2109241485596</v>
+        <v>27.2109203338623</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G725" t="n">
-        <v>27.2995567321777</v>
+        <v>27.2995586395264</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>32.0099983215332</v>
       </c>
       <c r="G727" t="n">
-        <v>28.3720378875732</v>
+        <v>28.3720397949219</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>31.7700004577637</v>
       </c>
       <c r="G728" t="n">
-        <v>28.1593170166016</v>
+        <v>28.1593189239502</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G729" t="n">
-        <v>28.3099975585938</v>
+        <v>28.3099956512451</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>31.4599990844727</v>
       </c>
       <c r="G730" t="n">
-        <v>27.8845462799072</v>
+        <v>27.8845481872559</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>26.6791114807129</v>
+        <v>26.6791133880615</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G733" t="n">
-        <v>27.6540966033936</v>
+        <v>27.6540985107422</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G734" t="n">
-        <v>28.221363067627</v>
+        <v>28.2213611602783</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G738" t="n">
-        <v>25.5268611907959</v>
+        <v>25.5268573760986</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G739" t="n">
-        <v>26.0941219329834</v>
+        <v>26.094123840332</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>29.8299999237061</v>
       </c>
       <c r="G743" t="n">
-        <v>26.4398002624512</v>
+        <v>26.4397983551025</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G746" t="n">
-        <v>25.5091323852539</v>
+        <v>25.5091342926025</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>29.0699996948242</v>
       </c>
       <c r="G750" t="n">
-        <v>25.7661724090576</v>
+        <v>25.7661762237549</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>27.9400005340576</v>
       </c>
       <c r="G752" t="n">
-        <v>24.7646007537842</v>
+        <v>24.7645988464355</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>28.4599990844727</v>
       </c>
       <c r="G754" t="n">
-        <v>25.2254981994629</v>
+        <v>25.2255001068115</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>24.4189224243164</v>
+        <v>24.4189205169678</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G757" t="n">
-        <v>23.9491558074951</v>
+        <v>23.9491577148438</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G758" t="n">
-        <v>24.4632415771484</v>
+        <v>24.4632377624512</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G760" t="n">
-        <v>24.4366493225098</v>
+        <v>24.4366512298584</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>27.7900009155273</v>
       </c>
       <c r="G761" t="n">
-        <v>24.6316452026367</v>
+        <v>24.631649017334</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G762" t="n">
-        <v>24.862096786499</v>
+        <v>24.8620986938477</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>28.9300003051758</v>
       </c>
       <c r="G763" t="n">
-        <v>25.6420860290527</v>
+        <v>25.6420879364014</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G764" t="n">
-        <v>25.8459434509277</v>
+        <v>25.845947265625</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>30.6299991607666</v>
       </c>
       <c r="G768" t="n">
-        <v>27.1488800048828</v>
+        <v>27.1488780975342</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>30.0499992370605</v>
       </c>
       <c r="G775" t="n">
-        <v>26.6347942352295</v>
+        <v>26.6347961425781</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>30.0499992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>26.6347942352295</v>
+        <v>26.6347961425781</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>30.0200004577637</v>
       </c>
       <c r="G779" t="n">
-        <v>26.6082057952881</v>
+        <v>26.6082038879395</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>27.1222877502441</v>
+        <v>27.1222858428955</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>27.1666049957275</v>
+        <v>27.1666069030762</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>30.5699996948242</v>
       </c>
       <c r="G782" t="n">
-        <v>27.0956974029541</v>
+        <v>27.0956993103027</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>30.9599990844727</v>
       </c>
       <c r="G783" t="n">
-        <v>27.4413757324219</v>
+        <v>27.4413738250732</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G784" t="n">
-        <v>29.0722541809082</v>
+        <v>29.0722560882568</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G785" t="n">
-        <v>29.1608943939209</v>
+        <v>29.1608924865723</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G786" t="n">
-        <v>29.7370166778564</v>
+        <v>29.7370185852051</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>29.7370166778564</v>
+        <v>29.7370185852051</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>33.7700004577637</v>
       </c>
       <c r="G788" t="n">
-        <v>29.9320125579834</v>
+        <v>29.9320163726807</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>34.2099990844727</v>
       </c>
       <c r="G789" t="n">
-        <v>30.3220081329346</v>
+        <v>30.3220100402832</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>33.3800010681152</v>
       </c>
       <c r="G790" t="n">
-        <v>29.5863418579102</v>
+        <v>29.5863399505615</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G791" t="n">
-        <v>29.7813358306885</v>
+        <v>29.7813339233398</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G792" t="n">
-        <v>30.0649681091309</v>
+        <v>30.0649662017822</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>34.7599983215332</v>
       </c>
       <c r="G793" t="n">
-        <v>30.8094959259033</v>
+        <v>30.8094997406006</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>34.6500015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>30.7120037078857</v>
+        <v>30.7120056152344</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G796" t="n">
-        <v>30.4461002349854</v>
+        <v>30.4460983276367</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>34.8400001525879</v>
       </c>
       <c r="G798" t="n">
-        <v>30.880407333374</v>
+        <v>30.8804111480713</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G800" t="n">
-        <v>30.7563209533691</v>
+        <v>30.7563171386719</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>34.5099983215332</v>
       </c>
       <c r="G801" t="n">
-        <v>30.587911605835</v>
+        <v>30.5879173278809</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G802" t="n">
-        <v>31.0665416717529</v>
+        <v>31.0665435791016</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>34.9799995422363</v>
       </c>
       <c r="G803" t="n">
-        <v>31.0044956207275</v>
+        <v>31.0044994354248</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>34.2099990844727</v>
       </c>
       <c r="G804" t="n">
-        <v>30.3220081329346</v>
+        <v>30.3220100402832</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G808" t="n">
-        <v>31.9972133636475</v>
+        <v>31.9972095489502</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>36</v>
       </c>
       <c r="G809" t="n">
-        <v>31.9085750579834</v>
+        <v>31.9085788726807</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G810" t="n">
-        <v>31.7756195068359</v>
+        <v>31.7756233215332</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>35.560001373291</v>
       </c>
       <c r="G813" t="n">
-        <v>31.5185813903809</v>
+        <v>31.5185852050781</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>36.0900001525879</v>
       </c>
       <c r="G814" t="n">
-        <v>31.9883460998535</v>
+        <v>31.9883499145508</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>36.189998626709</v>
       </c>
       <c r="G815" t="n">
-        <v>32.076976776123</v>
+        <v>32.0769805908203</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>37</v>
       </c>
       <c r="G816" t="n">
-        <v>32.7949180603027</v>
+        <v>32.7949256896973</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>36.7599983215332</v>
       </c>
       <c r="G817" t="n">
-        <v>32.5821990966797</v>
+        <v>32.5821952819824</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G819" t="n">
-        <v>32.2631149291992</v>
+        <v>32.2631187438965</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>36</v>
       </c>
       <c r="G820" t="n">
-        <v>31.9085750579834</v>
+        <v>31.9085788726807</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>35.3400001525879</v>
       </c>
       <c r="G821" t="n">
-        <v>31.3235855102539</v>
+        <v>31.3235893249512</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G822" t="n">
-        <v>30.8449554443359</v>
+        <v>30.8449516296387</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>35.5699996948242</v>
       </c>
       <c r="G823" t="n">
-        <v>31.5274410247803</v>
+        <v>31.5274448394775</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>35.9199981689453</v>
       </c>
       <c r="G826" t="n">
-        <v>31.8376636505127</v>
+        <v>31.83766746521</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>36.7400016784668</v>
       </c>
       <c r="G827" t="n">
-        <v>32.5644721984863</v>
+        <v>32.5644760131836</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G828" t="n">
-        <v>32.6619758605957</v>
+        <v>32.6619720458984</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G830" t="n">
-        <v>32.9721946716309</v>
+        <v>32.9721984863281</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>36.7599983215332</v>
       </c>
       <c r="G832" t="n">
-        <v>32.5821990966797</v>
+        <v>32.5821952819824</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>35.9799995422363</v>
       </c>
       <c r="G833" t="n">
-        <v>31.89084815979</v>
+        <v>31.8908443450928</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>35.810001373291</v>
       </c>
       <c r="G834" t="n">
-        <v>31.7401676177979</v>
+        <v>31.7401714324951</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>36.4199981689453</v>
       </c>
       <c r="G835" t="n">
-        <v>32.2808456420898</v>
+        <v>32.2808380126953</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>36.2900009155273</v>
       </c>
       <c r="G837" t="n">
-        <v>32.1656150817871</v>
+        <v>32.1656188964844</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G838" t="n">
-        <v>32.4847030639648</v>
+        <v>32.4846992492676</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>36.310001373291</v>
       </c>
       <c r="G839" t="n">
-        <v>32.1833457946777</v>
+        <v>32.1833419799805</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>36.5200004577637</v>
       </c>
       <c r="G840" t="n">
-        <v>32.3694801330566</v>
+        <v>32.3694763183594</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>37</v>
       </c>
       <c r="G841" t="n">
-        <v>32.7949180603027</v>
+        <v>32.7949256896973</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>37.1399993896484</v>
       </c>
       <c r="G842" t="n">
-        <v>32.9190101623535</v>
+        <v>32.9190139770508</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>36.5699996948242</v>
       </c>
       <c r="G846" t="n">
-        <v>32.4137916564941</v>
+        <v>32.4137954711914</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>36.439998626709</v>
       </c>
       <c r="G847" t="n">
-        <v>32.2985649108887</v>
+        <v>32.2985687255859</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>36.3600006103516</v>
       </c>
       <c r="G849" t="n">
-        <v>32.2276573181152</v>
+        <v>32.227653503418</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>35.5699996948242</v>
       </c>
       <c r="G850" t="n">
-        <v>31.5274410247803</v>
+        <v>31.5274448394775</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>35.689998626709</v>
       </c>
       <c r="G851" t="n">
-        <v>31.6338024139404</v>
+        <v>31.6338062286377</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>35.5299987792969</v>
       </c>
       <c r="G852" t="n">
-        <v>31.4919910430908</v>
+        <v>31.4919872283936</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>35.8400001525879</v>
       </c>
       <c r="G856" t="n">
-        <v>31.7667598724365</v>
+        <v>31.7667560577393</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>35.2299995422363</v>
       </c>
       <c r="G857" t="n">
-        <v>31.2260875701904</v>
+        <v>31.2260837554932</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>31.6426658630371</v>
+        <v>31.6426696777344</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G861" t="n">
-        <v>31.9115905761719</v>
+        <v>31.9115829467773</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>34.5400009155273</v>
       </c>
       <c r="G862" t="n">
-        <v>30.9614124298096</v>
+        <v>30.9614086151123</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>34.9700012207031</v>
       </c>
       <c r="G863" t="n">
-        <v>31.3468608856201</v>
+        <v>31.3468570709229</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>35</v>
       </c>
       <c r="G864" t="n">
-        <v>31.3737525939941</v>
+        <v>31.3737487792969</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>34.4599990844727</v>
       </c>
       <c r="G865" t="n">
-        <v>30.8896942138672</v>
+        <v>30.8897018432617</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>33</v>
       </c>
       <c r="G868" t="n">
-        <v>29.5809688568115</v>
+        <v>29.5809669494629</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>33.7400016784668</v>
       </c>
       <c r="G870" t="n">
-        <v>30.2442970275879</v>
+        <v>30.2442989349365</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G873" t="n">
-        <v>31.1048316955566</v>
+        <v>31.1048355102539</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>34.3300018310547</v>
       </c>
       <c r="G874" t="n">
-        <v>30.77317237854</v>
+        <v>30.7731685638428</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>34.8199996948242</v>
       </c>
       <c r="G875" t="n">
-        <v>31.2124004364014</v>
+        <v>31.2123985290527</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>34.4900016784668</v>
       </c>
       <c r="G877" t="n">
-        <v>30.9165897369385</v>
+        <v>30.9165935516357</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G879" t="n">
-        <v>31.732307434082</v>
+        <v>31.7323112487793</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>36.6100006103516</v>
       </c>
       <c r="G881" t="n">
-        <v>32.8169403076172</v>
+        <v>32.8169441223145</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>37.6300010681152</v>
       </c>
       <c r="G882" t="n">
-        <v>33.7312622070312</v>
+        <v>33.7312660217285</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>37.4099998474121</v>
       </c>
       <c r="G883" t="n">
-        <v>33.5340614318848</v>
+        <v>33.5340576171875</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>36.3400001525879</v>
       </c>
       <c r="G886" t="n">
-        <v>32.5749206542969</v>
+        <v>32.5749168395996</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>37.1399993896484</v>
       </c>
       <c r="G887" t="n">
-        <v>33.2920379638672</v>
+        <v>33.2920341491699</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G888" t="n">
-        <v>33.7043762207031</v>
+        <v>33.7043724060059</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>38.25</v>
       </c>
       <c r="G895" t="n">
-        <v>34.2870254516602</v>
+        <v>34.2870292663574</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>38.4799995422363</v>
       </c>
       <c r="G898" t="n">
-        <v>34.4932022094727</v>
+        <v>34.4931983947754</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G905" t="n">
-        <v>34.6366195678711</v>
+        <v>34.6366233825684</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G906" t="n">
-        <v>34.9145088195801</v>
+        <v>34.9145050048828</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>39.0200004577637</v>
       </c>
       <c r="G907" t="n">
-        <v>34.9772491455078</v>
+        <v>34.9772529602051</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>37.6100006103516</v>
       </c>
       <c r="G910" t="n">
-        <v>33.7133369445801</v>
+        <v>33.7133407592773</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>37.1699981689453</v>
       </c>
       <c r="G911" t="n">
-        <v>33.3189239501953</v>
+        <v>33.318920135498</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>37.6300010681152</v>
       </c>
       <c r="G912" t="n">
-        <v>33.7312622070312</v>
+        <v>33.7312660217285</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>34.1100006103516</v>
       </c>
       <c r="G915" t="n">
-        <v>30.5759620666504</v>
+        <v>30.575963973999</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>34.0800018310547</v>
       </c>
       <c r="G916" t="n">
-        <v>30.5490741729736</v>
+        <v>30.549072265625</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>34.5099983215332</v>
       </c>
       <c r="G917" t="n">
-        <v>30.9345169067383</v>
+        <v>30.9345207214355</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G919" t="n">
-        <v>31.4992446899414</v>
+        <v>31.4992485046387</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>35.0699996948242</v>
       </c>
       <c r="G920" t="n">
-        <v>31.4365005493164</v>
+        <v>31.4364967346191</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>31.1048316955566</v>
+        <v>31.1048355102539</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>34.4199981689453</v>
       </c>
       <c r="G927" t="n">
-        <v>30.8538379669189</v>
+        <v>30.8538417816162</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>34.2099990844727</v>
       </c>
       <c r="G929" t="n">
-        <v>30.665599822998</v>
+        <v>30.6656017303467</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>33.7400016784668</v>
       </c>
       <c r="G934" t="n">
-        <v>30.2442970275879</v>
+        <v>30.2442989349365</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>35.9599990844727</v>
       </c>
       <c r="G937" t="n">
-        <v>32.2342872619629</v>
+        <v>32.2342834472656</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>35.3899993896484</v>
       </c>
       <c r="G941" t="n">
-        <v>31.7233428955078</v>
+        <v>31.7233467102051</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G943" t="n">
-        <v>30.7462730407715</v>
+        <v>30.7462768554688</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>32.4700012207031</v>
       </c>
       <c r="G946" t="n">
-        <v>29.1058788299561</v>
+        <v>29.1058769226074</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>32.6199989318848</v>
       </c>
       <c r="G947" t="n">
-        <v>29.2403354644775</v>
+        <v>29.2403335571289</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G948" t="n">
-        <v>28.7742118835449</v>
+        <v>28.7742080688477</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G953" t="n">
-        <v>29.3120460510254</v>
+        <v>29.312047958374</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>32.3400001525879</v>
       </c>
       <c r="G954" t="n">
-        <v>28.9893455505371</v>
+        <v>28.9893474578857</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>31.5900001525879</v>
       </c>
       <c r="G955" t="n">
-        <v>28.3170509338379</v>
+        <v>28.3170528411865</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G958" t="n">
-        <v>29.3479061126709</v>
+        <v>29.3479042053223</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>32.5800018310547</v>
       </c>
       <c r="G959" t="n">
-        <v>29.2044849395752</v>
+        <v>29.2044830322266</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>33.189998626709</v>
       </c>
       <c r="G960" t="n">
-        <v>29.7512798309326</v>
+        <v>29.751277923584</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>30.6566371917725</v>
+        <v>30.6566390991211</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>34.0699996948242</v>
       </c>
       <c r="G964" t="n">
-        <v>30.5401020050049</v>
+        <v>30.5401077270508</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>32.4900016784668</v>
       </c>
       <c r="G971" t="n">
-        <v>29.1238079071045</v>
+        <v>29.1238098144531</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>36.1699981689453</v>
       </c>
       <c r="G972" t="n">
-        <v>32.4225273132324</v>
+        <v>32.4225311279297</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>35.5</v>
       </c>
       <c r="G973" t="n">
-        <v>31.821949005127</v>
+        <v>31.8219451904297</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>34.6800003051758</v>
       </c>
       <c r="G975" t="n">
-        <v>31.0869064331055</v>
+        <v>31.0869026184082</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>34.5400009155273</v>
       </c>
       <c r="G976" t="n">
-        <v>30.9614124298096</v>
+        <v>30.9614086151123</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>35.1699981689453</v>
       </c>
       <c r="G977" t="n">
-        <v>31.5261383056641</v>
+        <v>31.5261421203613</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>35.0299987792969</v>
       </c>
       <c r="G979" t="n">
-        <v>31.4006443023682</v>
+        <v>31.4006404876709</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G980" t="n">
-        <v>31.732307434082</v>
+        <v>31.7323112487793</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>37.6399993896484</v>
       </c>
       <c r="G982" t="n">
-        <v>33.740234375</v>
+        <v>33.7402305603027</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>36.560001373291</v>
       </c>
       <c r="G987" t="n">
-        <v>32.7721214294434</v>
+        <v>32.7721252441406</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>38.7900009155273</v>
       </c>
       <c r="G998" t="n">
-        <v>34.7710800170898</v>
+        <v>34.7710838317871</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>38.8300018310547</v>
       </c>
       <c r="G1000" t="n">
-        <v>34.8069381713867</v>
+        <v>34.8069343566895</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>37.8277854919434</v>
+        <v>37.8277816772461</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>41.7900009155273</v>
       </c>
       <c r="G1003" t="n">
-        <v>37.460262298584</v>
+        <v>37.4602584838867</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1005" t="n">
-        <v>37.0210266113281</v>
+        <v>37.0210227966309</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>41</v>
       </c>
       <c r="G1006" t="n">
-        <v>36.7521133422852</v>
+        <v>36.7521095275879</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>40.439998626709</v>
       </c>
       <c r="G1009" t="n">
-        <v>36.2501258850098</v>
+        <v>36.250129699707</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>40.1599998474121</v>
       </c>
       <c r="G1010" t="n">
-        <v>35.9991416931152</v>
+        <v>35.999137878418</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>40.7900009155273</v>
       </c>
       <c r="G1013" t="n">
-        <v>36.5638694763184</v>
+        <v>36.5638656616211</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>40.6300010681152</v>
       </c>
       <c r="G1014" t="n">
-        <v>36.4204483032227</v>
+        <v>36.4204406738281</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>40.5900001525879</v>
       </c>
       <c r="G1016" t="n">
-        <v>36.3845901489258</v>
+        <v>36.384593963623</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>40.0900001525879</v>
       </c>
       <c r="G1017" t="n">
-        <v>35.936393737793</v>
+        <v>35.9363899230957</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>41.1599998474121</v>
       </c>
       <c r="G1020" t="n">
-        <v>36.8955307006836</v>
+        <v>36.8955345153809</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>41.1399993896484</v>
       </c>
       <c r="G1021" t="n">
-        <v>36.8776054382324</v>
+        <v>36.8776016235352</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G1023" t="n">
-        <v>36.572826385498</v>
+        <v>36.5728302001953</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>40.4300003051758</v>
       </c>
       <c r="G1029" t="n">
-        <v>36.2411613464355</v>
+        <v>36.2411651611328</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>40.3400001525879</v>
       </c>
       <c r="G1031" t="n">
-        <v>36.1604919433594</v>
+        <v>36.1604881286621</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>40.3699989318848</v>
       </c>
       <c r="G1035" t="n">
-        <v>36.187385559082</v>
+        <v>36.1873817443848</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>38.7099990844727</v>
       </c>
       <c r="G1042" t="n">
-        <v>34.6993637084961</v>
+        <v>34.6993675231934</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>39.7299995422363</v>
       </c>
       <c r="G1043" t="n">
-        <v>35.6136894226074</v>
+        <v>35.6136932373047</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>39.310001373291</v>
       </c>
       <c r="G1045" t="n">
-        <v>35.2372016906738</v>
+        <v>35.2372055053711</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1047" t="n">
-        <v>34.1525650024414</v>
+        <v>34.1525688171387</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>37.6399993896484</v>
       </c>
       <c r="G1049" t="n">
-        <v>33.740234375</v>
+        <v>33.7402305603027</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>39.0400009155273</v>
       </c>
       <c r="G1050" t="n">
-        <v>34.9951820373535</v>
+        <v>34.9951782226562</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>38.25</v>
       </c>
       <c r="G1051" t="n">
-        <v>34.2870254516602</v>
+        <v>34.2870292663574</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G1052" t="n">
-        <v>33.3009986877441</v>
+        <v>33.3010025024414</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>35.1300010681152</v>
       </c>
       <c r="G1054" t="n">
-        <v>31.4902877807617</v>
+        <v>31.4902839660645</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>35.2599983215332</v>
       </c>
       <c r="G1056" t="n">
-        <v>31.6068115234375</v>
+        <v>31.6068153381348</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>35.2200012207031</v>
       </c>
       <c r="G1057" t="n">
-        <v>31.5709571838379</v>
+        <v>31.5709609985352</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>35</v>
       </c>
       <c r="G1060" t="n">
-        <v>31.3737525939941</v>
+        <v>31.3737487792969</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>29.3600006103516</v>
       </c>
       <c r="G1065" t="n">
-        <v>26.3180980682373</v>
+        <v>26.3180961608887</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1067" t="n">
-        <v>26.6228733062744</v>
+        <v>26.6228694915771</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G1071" t="n">
-        <v>24.2205371856689</v>
+        <v>24.2205352783203</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>29.2700004577637</v>
       </c>
       <c r="G1072" t="n">
-        <v>26.2374210357666</v>
+        <v>26.237419128418</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G1074" t="n">
-        <v>29.0879497528076</v>
+        <v>29.0879516601562</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1075" t="n">
-        <v>30.5670013427734</v>
+        <v>30.5669975280762</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>33.2900009155273</v>
       </c>
       <c r="G1079" t="n">
-        <v>29.8409233093262</v>
+        <v>29.8409214019775</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>32.3899993896484</v>
       </c>
       <c r="G1080" t="n">
-        <v>29.0341663360596</v>
+        <v>29.0341644287109</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>27.8778190612793</v>
+        <v>27.8778209686279</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>33.25</v>
       </c>
       <c r="G1083" t="n">
-        <v>29.805061340332</v>
+        <v>29.8050651550293</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>33</v>
       </c>
       <c r="G1084" t="n">
-        <v>29.5809688568115</v>
+        <v>29.5809669494629</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>32.5800018310547</v>
       </c>
       <c r="G1095" t="n">
-        <v>29.2044849395752</v>
+        <v>29.2044830322266</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>34.1599998474121</v>
       </c>
       <c r="G1096" t="n">
-        <v>30.6207809448242</v>
+        <v>30.6207828521729</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G1097" t="n">
-        <v>30.8807373046875</v>
+        <v>30.8807334899902</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>34.6800003051758</v>
       </c>
       <c r="G1098" t="n">
-        <v>31.0869064331055</v>
+        <v>31.0869026184082</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1099" t="n">
-        <v>30.7462730407715</v>
+        <v>30.7462768554688</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>32.8199996948242</v>
       </c>
       <c r="G1100" t="n">
-        <v>29.4196166992188</v>
+        <v>29.4196147918701</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>33.2900009155273</v>
       </c>
       <c r="G1103" t="n">
-        <v>29.8409233093262</v>
+        <v>29.8409214019775</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>32.7799987792969</v>
       </c>
       <c r="G1104" t="n">
-        <v>29.3837585449219</v>
+        <v>29.3837623596191</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>32.2900009155273</v>
       </c>
       <c r="G1105" t="n">
-        <v>28.9445304870605</v>
+        <v>28.9445285797119</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>32.7700004577637</v>
       </c>
       <c r="G1106" t="n">
-        <v>29.3747959136963</v>
+        <v>29.3747940063477</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>31.8899993896484</v>
       </c>
       <c r="G1107" t="n">
-        <v>28.5859718322754</v>
+        <v>28.5859699249268</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1110" t="n">
-        <v>29.3120460510254</v>
+        <v>29.312047958374</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>32.2400016784668</v>
       </c>
       <c r="G1111" t="n">
-        <v>28.8997097015381</v>
+        <v>28.8997077941895</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>31.8899993896484</v>
       </c>
       <c r="G1113" t="n">
-        <v>28.5859718322754</v>
+        <v>28.5859699249268</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>33.3899993896484</v>
       </c>
       <c r="G1116" t="n">
-        <v>29.9305572509766</v>
+        <v>29.9305553436279</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G1117" t="n">
-        <v>29.5361499786377</v>
+        <v>29.5361480712891</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>33.689998626709</v>
       </c>
       <c r="G1120" t="n">
-        <v>30.1994781494141</v>
+        <v>30.1994743347168</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>34.6800003051758</v>
       </c>
       <c r="G1121" t="n">
-        <v>31.0869064331055</v>
+        <v>31.0869026184082</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>34.9700012207031</v>
       </c>
       <c r="G1122" t="n">
-        <v>31.3468608856201</v>
+        <v>31.3468570709229</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G1123" t="n">
-        <v>30.9972686767578</v>
+        <v>30.9972724914551</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>34.7299995422363</v>
       </c>
       <c r="G1125" t="n">
-        <v>31.1317272186279</v>
+        <v>31.1317234039307</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>34.1599998474121</v>
       </c>
       <c r="G1126" t="n">
-        <v>30.6207809448242</v>
+        <v>30.6207828521729</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1127" t="n">
-        <v>31.732307434082</v>
+        <v>31.7323112487793</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1128" t="n">
-        <v>30.1636199951172</v>
+        <v>30.1636257171631</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>34.0200004577637</v>
       </c>
       <c r="G1129" t="n">
-        <v>30.495288848877</v>
+        <v>30.4952850341797</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G1133" t="n">
-        <v>31.4992446899414</v>
+        <v>31.4992485046387</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>35.8400001525879</v>
       </c>
       <c r="G1136" t="n">
-        <v>32.1267166137695</v>
+        <v>32.1267204284668</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>34.7900009155273</v>
       </c>
       <c r="G1137" t="n">
-        <v>31.1855068206787</v>
+        <v>31.1855087280273</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>34.3899993896484</v>
       </c>
       <c r="G1138" t="n">
-        <v>30.8269500732422</v>
+        <v>30.8269481658936</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1139" t="n">
-        <v>30.7462730407715</v>
+        <v>30.7462768554688</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>34.2599983215332</v>
       </c>
       <c r="G1142" t="n">
-        <v>30.7104244232178</v>
+        <v>30.7104187011719</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>34.6399993896484</v>
       </c>
       <c r="G1143" t="n">
-        <v>31.0510482788086</v>
+        <v>31.0510559082031</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>34.1599998474121</v>
       </c>
       <c r="G1145" t="n">
-        <v>30.6207809448242</v>
+        <v>30.6207828521729</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>34.8199996948242</v>
       </c>
       <c r="G1146" t="n">
-        <v>31.2124004364014</v>
+        <v>31.2123985290527</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>34.5099983215332</v>
       </c>
       <c r="G1147" t="n">
-        <v>30.9345169067383</v>
+        <v>30.9345207214355</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>34.1599998474121</v>
       </c>
       <c r="G1148" t="n">
-        <v>30.6207809448242</v>
+        <v>30.6207828521729</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>34.1599998474121</v>
       </c>
       <c r="G1149" t="n">
-        <v>30.6207809448242</v>
+        <v>30.6207828521729</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G1152" t="n">
-        <v>30.9972686767578</v>
+        <v>30.9972724914551</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>33.9900016784668</v>
       </c>
       <c r="G1153" t="n">
-        <v>30.4683952331543</v>
+        <v>30.4683971405029</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>33.2299995422363</v>
       </c>
       <c r="G1154" t="n">
-        <v>29.7871322631836</v>
+        <v>29.7871360778809</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>33.6800003051758</v>
       </c>
       <c r="G1155" t="n">
-        <v>30.1905174255371</v>
+        <v>30.1905136108398</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>33.1699981689453</v>
       </c>
       <c r="G1163" t="n">
-        <v>29.7333507537842</v>
+        <v>29.7333526611328</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1164" t="n">
-        <v>29.2224082946777</v>
+        <v>29.2224102020264</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1171" t="n">
-        <v>29.3120460510254</v>
+        <v>29.312047958374</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G1173" t="n">
-        <v>30.0112342834473</v>
+        <v>30.0112361907959</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G1175" t="n">
-        <v>29.5361499786377</v>
+        <v>29.5361480712891</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>32.6100006103516</v>
       </c>
       <c r="G1176" t="n">
-        <v>29.2313747406006</v>
+        <v>29.231372833252</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>32.0400009155273</v>
       </c>
       <c r="G1179" t="n">
-        <v>28.7204284667969</v>
+        <v>28.7204265594482</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>32.3699989318848</v>
       </c>
       <c r="G1180" t="n">
-        <v>29.0162372589111</v>
+        <v>29.0162391662598</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>32.5299987792969</v>
       </c>
       <c r="G1181" t="n">
-        <v>29.1596603393555</v>
+        <v>29.1596584320068</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>32.6199989318848</v>
       </c>
       <c r="G1183" t="n">
-        <v>29.2403354644775</v>
+        <v>29.2403335571289</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1184" t="n">
-        <v>29.0431308746338</v>
+        <v>29.0431327819824</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G1185" t="n">
-        <v>29.0879497528076</v>
+        <v>29.0879516601562</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G1187" t="n">
-        <v>30.0112342834473</v>
+        <v>30.0112361907959</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>33.3899993896484</v>
       </c>
       <c r="G1188" t="n">
-        <v>29.9305572509766</v>
+        <v>29.9305553436279</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>34.4700012207031</v>
       </c>
       <c r="G1190" t="n">
-        <v>30.8986701965332</v>
+        <v>30.8986625671387</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1191" t="n">
-        <v>30.6566371917725</v>
+        <v>30.6566390991211</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>34.4700012207031</v>
       </c>
       <c r="G1192" t="n">
-        <v>30.8986701965332</v>
+        <v>30.8986625671387</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>36.7400016784668</v>
       </c>
       <c r="G1196" t="n">
-        <v>32.9334754943848</v>
+        <v>32.933479309082</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>37.9300003051758</v>
       </c>
       <c r="G1197" t="n">
-        <v>34.000186920166</v>
+        <v>34.0001831054688</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>36.5</v>
       </c>
       <c r="G1199" t="n">
-        <v>32.7183380126953</v>
+        <v>32.7183418273926</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>35.0699996948242</v>
       </c>
       <c r="G1200" t="n">
-        <v>31.4365005493164</v>
+        <v>31.4364967346191</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1202" t="n">
-        <v>31.553035736084</v>
+        <v>31.5530319213867</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1203" t="n">
-        <v>31.553035736084</v>
+        <v>31.5530319213867</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>35.4700012207031</v>
       </c>
       <c r="G1209" t="n">
-        <v>31.7950553894043</v>
+        <v>31.7950630187988</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>36.1699981689453</v>
       </c>
       <c r="G1210" t="n">
-        <v>32.4225273132324</v>
+        <v>32.4225311279297</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>36.7400016784668</v>
       </c>
       <c r="G1220" t="n">
-        <v>32.9334754943848</v>
+        <v>32.933479309082</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>37.8899993896484</v>
       </c>
       <c r="G1221" t="n">
-        <v>33.9643249511719</v>
+        <v>33.9643287658691</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>36</v>
       </c>
       <c r="G1231" t="n">
-        <v>32.2701454162598</v>
+        <v>32.270149230957</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>37.8199996948242</v>
       </c>
       <c r="G1233" t="n">
-        <v>33.9015808105469</v>
+        <v>33.9015769958496</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>39.7099990844727</v>
       </c>
       <c r="G1236" t="n">
-        <v>35.595760345459</v>
+        <v>35.5957641601562</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>39.689998626709</v>
       </c>
       <c r="G1238" t="n">
-        <v>35.5778350830078</v>
+        <v>35.5778312683105</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>41.0800018310547</v>
       </c>
       <c r="G1240" t="n">
-        <v>36.8238220214844</v>
+        <v>36.8238182067871</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>40.7799987792969</v>
       </c>
       <c r="G1242" t="n">
-        <v>36.5549011230469</v>
+        <v>36.5548973083496</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G1243" t="n">
-        <v>36.3935546875</v>
+        <v>36.3935508728027</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>41.1599998474121</v>
       </c>
       <c r="G1244" t="n">
-        <v>36.8955307006836</v>
+        <v>36.8955345153809</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G1247" t="n">
-        <v>37.5588607788086</v>
+        <v>37.5588645935059</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>41.1599998474121</v>
       </c>
       <c r="G1250" t="n">
-        <v>36.8955307006836</v>
+        <v>36.8955345153809</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>44.9000015258789</v>
       </c>
       <c r="G1256" t="n">
-        <v>40.248046875</v>
+        <v>40.2480430603027</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>46.4599990844727</v>
       </c>
       <c r="G1258" t="n">
-        <v>41.6464157104492</v>
+        <v>41.646411895752</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>48.7099990844727</v>
       </c>
       <c r="G1262" t="n">
-        <v>43.6632957458496</v>
+        <v>43.6632995605469</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>48.5</v>
       </c>
       <c r="G1264" t="n">
-        <v>43.4750595092773</v>
+        <v>43.4750556945801</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>48.3800010681152</v>
       </c>
       <c r="G1266" t="n">
-        <v>43.367488861084</v>
+        <v>43.3674926757812</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>48.2099990844727</v>
       </c>
       <c r="G1267" t="n">
-        <v>43.2151069641113</v>
+        <v>43.2150993347168</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>50.1399993896484</v>
       </c>
       <c r="G1270" t="n">
-        <v>44.945140838623</v>
+        <v>44.9451370239258</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>50</v>
       </c>
       <c r="G1271" t="n">
-        <v>44.8196487426758</v>
+        <v>44.8196411132812</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>48.060001373291</v>
       </c>
       <c r="G1275" t="n">
-        <v>43.0806427001953</v>
+        <v>43.0806465148926</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>48</v>
       </c>
       <c r="G1276" t="n">
-        <v>43.0268630981445</v>
+        <v>43.0268669128418</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1278" t="n">
-        <v>43.161319732666</v>
+        <v>43.1613235473633</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G1280" t="n">
-        <v>42.4442024230957</v>
+        <v>42.444206237793</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>47.6500015258789</v>
       </c>
       <c r="G1282" t="n">
-        <v>42.7131195068359</v>
+        <v>42.7131271362305</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>48.6699981689453</v>
       </c>
       <c r="G1283" t="n">
-        <v>43.62744140625</v>
+        <v>43.6274375915527</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>49.5900001525879</v>
       </c>
       <c r="G1284" t="n">
-        <v>44.4521217346191</v>
+        <v>44.4521255493164</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>48.6699981689453</v>
       </c>
       <c r="G1285" t="n">
-        <v>43.62744140625</v>
+        <v>43.6274375915527</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>47.3400001525879</v>
       </c>
       <c r="G1286" t="n">
-        <v>42.4352416992188</v>
+        <v>42.4352378845215</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1287" t="n">
-        <v>43.161319732666</v>
+        <v>43.1613235473633</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>47.2599983215332</v>
       </c>
       <c r="G1288" t="n">
-        <v>42.3635292053223</v>
+        <v>42.363525390625</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>47.9199981689453</v>
       </c>
       <c r="G1292" t="n">
-        <v>42.955150604248</v>
+        <v>42.9551467895508</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>47.9300003051758</v>
       </c>
       <c r="G1293" t="n">
-        <v>42.9641151428223</v>
+        <v>42.9641189575195</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>50.0200004577637</v>
       </c>
       <c r="G1294" t="n">
-        <v>44.837574005127</v>
+        <v>44.8375701904297</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>50.8400001525879</v>
       </c>
       <c r="G1295" t="n">
-        <v>45.5726203918457</v>
+        <v>45.5726127624512</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>52.1199989318848</v>
       </c>
       <c r="G1297" t="n">
-        <v>46.7200012207031</v>
+        <v>46.7199935913086</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>51.8199996948242</v>
       </c>
       <c r="G1302" t="n">
-        <v>46.4510803222656</v>
+        <v>46.4510765075684</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>50.6399993896484</v>
       </c>
       <c r="G1303" t="n">
-        <v>45.3933372497559</v>
+        <v>45.3933410644531</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>53.3199996948242</v>
       </c>
       <c r="G1305" t="n">
-        <v>47.7956733703613</v>
+        <v>47.7956695556641</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G1306" t="n">
-        <v>46.5227928161621</v>
+        <v>46.5227966308594</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>51.2200012207031</v>
       </c>
       <c r="G1307" t="n">
-        <v>45.9132461547852</v>
+        <v>45.9132423400879</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>51</v>
       </c>
       <c r="G1308" t="n">
-        <v>45.7160377502441</v>
+        <v>45.7160415649414</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>51.1399993896484</v>
       </c>
       <c r="G1309" t="n">
-        <v>45.8415374755859</v>
+        <v>45.8415336608887</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1310" t="n">
-        <v>45.9849548339844</v>
+        <v>45.9849586486816</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>52.1599998474121</v>
       </c>
       <c r="G1311" t="n">
-        <v>46.7558517456055</v>
+        <v>46.7558555603027</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>52.5400009155273</v>
       </c>
       <c r="G1312" t="n">
-        <v>47.0964813232422</v>
+        <v>47.0964851379395</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>50.5400009155273</v>
       </c>
       <c r="G1314" t="n">
-        <v>45.3036994934082</v>
+        <v>45.3036956787109</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>50.3199996948242</v>
       </c>
       <c r="G1317" t="n">
-        <v>45.1064834594727</v>
+        <v>45.1064910888672</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>51.8199996948242</v>
       </c>
       <c r="G1319" t="n">
-        <v>46.4510803222656</v>
+        <v>46.4510765075684</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>51.3199996948242</v>
       </c>
       <c r="G1321" t="n">
-        <v>46.0028839111328</v>
+        <v>46.0028877258301</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1324" t="n">
-        <v>44.9092826843262</v>
+        <v>44.9092864990234</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1326" t="n">
-        <v>44.1025352478027</v>
+        <v>44.1025314331055</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>47.9500007629395</v>
       </c>
       <c r="G1327" t="n">
-        <v>42.9820404052734</v>
+        <v>42.9820442199707</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>47.9500007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>42.9820404052734</v>
+        <v>42.9820442199707</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>50.8400001525879</v>
       </c>
       <c r="G1335" t="n">
-        <v>45.5726203918457</v>
+        <v>45.5726127624512</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>50.3600006103516</v>
       </c>
       <c r="G1337" t="n">
-        <v>45.1423454284668</v>
+        <v>45.1423416137695</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>50.3600006103516</v>
       </c>
       <c r="G1338" t="n">
-        <v>45.1423454284668</v>
+        <v>45.1423416137695</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1339" t="n">
-        <v>44.9092826843262</v>
+        <v>44.9092864990234</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>50.1399993896484</v>
       </c>
       <c r="G1340" t="n">
-        <v>44.945140838623</v>
+        <v>44.9451370239258</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>50.2200012207031</v>
       </c>
       <c r="G1345" t="n">
-        <v>45.0168495178223</v>
+        <v>45.0168533325195</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>52.3600006103516</v>
       </c>
       <c r="G1346" t="n">
-        <v>46.935131072998</v>
+        <v>46.9351348876953</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>53.5</v>
       </c>
       <c r="G1347" t="n">
-        <v>47.9570274353027</v>
+        <v>47.9570236206055</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>51</v>
       </c>
       <c r="G1350" t="n">
-        <v>45.7160377502441</v>
+        <v>45.7160415649414</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>50.9599990844727</v>
       </c>
       <c r="G1352" t="n">
-        <v>45.6801834106445</v>
+        <v>45.6801795959473</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>51.0200004577637</v>
       </c>
       <c r="G1353" t="n">
-        <v>45.7339668273926</v>
+        <v>45.7339706420898</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>51</v>
       </c>
       <c r="G1356" t="n">
-        <v>45.7160377502441</v>
+        <v>45.7160415649414</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>51.4199981689453</v>
       </c>
       <c r="G1357" t="n">
-        <v>46.0925254821777</v>
+        <v>46.0925216674805</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>51.2599983215332</v>
       </c>
       <c r="G1358" t="n">
-        <v>45.9491004943848</v>
+        <v>45.949104309082</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>51.7400016784668</v>
       </c>
       <c r="G1359" t="n">
-        <v>46.3793640136719</v>
+        <v>46.3793678283691</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>50.5400009155273</v>
       </c>
       <c r="G1360" t="n">
-        <v>45.3036994934082</v>
+        <v>45.3036956787109</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>50.939998626709</v>
       </c>
       <c r="G1361" t="n">
-        <v>45.6622505187988</v>
+        <v>45.6622543334961</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G1363" t="n">
-        <v>46.2538757324219</v>
+        <v>46.2538719177246</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>52.5</v>
       </c>
       <c r="G1366" t="n">
-        <v>47.0606231689453</v>
+        <v>47.0606269836426</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G1367" t="n">
-        <v>47.7777404785156</v>
+        <v>47.7777442932129</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>54.9599990844727</v>
       </c>
       <c r="G1370" t="n">
-        <v>49.6830215454102</v>
+        <v>49.6830253601074</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>55.5</v>
       </c>
       <c r="G1371" t="n">
-        <v>50.1711769104004</v>
+        <v>50.1711730957031</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>58.0400009155273</v>
       </c>
       <c r="G1373" t="n">
-        <v>52.4673042297363</v>
+        <v>52.4673004150391</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>57.6599998474121</v>
       </c>
       <c r="G1376" t="n">
-        <v>52.1237831115723</v>
+        <v>52.1237869262695</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G1378" t="n">
-        <v>52.702335357666</v>
+        <v>52.7023315429688</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>58.9199981689453</v>
       </c>
       <c r="G1380" t="n">
-        <v>53.2628021240234</v>
+        <v>53.2628059387207</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G1382" t="n">
-        <v>51.3463516235352</v>
+        <v>51.3463554382324</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G1387" t="n">
-        <v>52.9735298156738</v>
+        <v>52.9735260009766</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>58.2400016784668</v>
       </c>
       <c r="G1389" t="n">
-        <v>52.6480941772461</v>
+        <v>52.6480979919434</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>57.2200012207031</v>
       </c>
       <c r="G1391" t="n">
-        <v>51.7260284423828</v>
+        <v>51.7260322570801</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>57.2200012207031</v>
       </c>
       <c r="G1394" t="n">
-        <v>51.7260284423828</v>
+        <v>51.7260322570801</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>57.6199989318848</v>
       </c>
       <c r="G1395" t="n">
-        <v>52.0876274108887</v>
+        <v>52.0876235961914</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>56.7799987792969</v>
       </c>
       <c r="G1399" t="n">
-        <v>51.3282737731934</v>
+        <v>51.3282775878906</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>57.3400001525879</v>
       </c>
       <c r="G1401" t="n">
-        <v>51.8345146179199</v>
+        <v>51.8345108032227</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>57.2799987792969</v>
       </c>
       <c r="G1404" t="n">
-        <v>51.7802734375</v>
+        <v>51.7802696228027</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>57.1800003051758</v>
       </c>
       <c r="G1410" t="n">
-        <v>51.6898765563965</v>
+        <v>51.6898727416992</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>58.7200012207031</v>
       </c>
       <c r="G1412" t="n">
-        <v>53.0820121765137</v>
+        <v>53.0820083618164</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>59.5999984741211</v>
       </c>
       <c r="G1413" t="n">
-        <v>53.8775100708008</v>
+        <v>53.8775177001953</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>59.6599998474121</v>
       </c>
       <c r="G1415" t="n">
-        <v>53.9317512512207</v>
+        <v>53.9317588806152</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>58.7400016784668</v>
       </c>
       <c r="G1420" t="n">
-        <v>53.1000900268555</v>
+        <v>53.1000862121582</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G1421" t="n">
-        <v>53.1543273925781</v>
+        <v>53.1543235778809</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>58.7400016784668</v>
       </c>
       <c r="G1422" t="n">
-        <v>53.1000900268555</v>
+        <v>53.1000862121582</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>59.7599983215332</v>
       </c>
       <c r="G1424" t="n">
-        <v>54.0221519470215</v>
+        <v>54.0221557617188</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>62.060001373291</v>
       </c>
       <c r="G1427" t="n">
-        <v>56.1013221740723</v>
+        <v>56.1013259887695</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>61.8800010681152</v>
       </c>
       <c r="G1428" t="n">
-        <v>55.9385986328125</v>
+        <v>55.9386024475098</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>60.6599998474121</v>
       </c>
       <c r="G1429" t="n">
-        <v>54.8357429504395</v>
+        <v>54.8357391357422</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>58.4799995422363</v>
       </c>
       <c r="G1431" t="n">
-        <v>52.8650512695312</v>
+        <v>52.8650550842285</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>53.9199981689453</v>
       </c>
       <c r="G1433" t="n">
-        <v>48.7428779602051</v>
+        <v>48.7428741455078</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>55.5</v>
       </c>
       <c r="G1434" t="n">
-        <v>50.1711769104004</v>
+        <v>50.1711730957031</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>54.1800003051758</v>
       </c>
       <c r="G1437" t="n">
-        <v>48.9779167175293</v>
+        <v>48.9779205322266</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>54.3400001525879</v>
       </c>
       <c r="G1438" t="n">
-        <v>49.12255859375</v>
+        <v>49.1225509643555</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>54.8199996948242</v>
       </c>
       <c r="G1442" t="n">
-        <v>49.5564651489258</v>
+        <v>49.556468963623</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>54.0200004577637</v>
       </c>
       <c r="G1443" t="n">
-        <v>48.8332786560059</v>
+        <v>48.8332824707031</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>55.2599983215332</v>
       </c>
       <c r="G1446" t="n">
-        <v>49.954216003418</v>
+        <v>49.9542198181152</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>55.1800003051758</v>
       </c>
       <c r="G1447" t="n">
-        <v>49.881908416748</v>
+        <v>49.8819046020508</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>55.1800003051758</v>
       </c>
       <c r="G1448" t="n">
-        <v>49.881908416748</v>
+        <v>49.8819046020508</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>54.5999984741211</v>
       </c>
       <c r="G1450" t="n">
-        <v>49.3575859069824</v>
+        <v>49.3575897216797</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>51.7799987792969</v>
       </c>
       <c r="G1451" t="n">
-        <v>46.808349609375</v>
+        <v>46.8083534240723</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G1452" t="n">
-        <v>46.7360343933105</v>
+        <v>46.7360305786133</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>55.2400016784668</v>
       </c>
       <c r="G1457" t="n">
-        <v>49.9361419677734</v>
+        <v>49.9361457824707</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>52.939998626709</v>
       </c>
       <c r="G1461" t="n">
-        <v>47.8569717407227</v>
+        <v>47.8569679260254</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>54.8199996948242</v>
       </c>
       <c r="G1464" t="n">
-        <v>49.5564651489258</v>
+        <v>49.556468963623</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>56.9599990844727</v>
       </c>
       <c r="G1467" t="n">
-        <v>51.4909934997559</v>
+        <v>51.4909973144531</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>56.439998626709</v>
       </c>
       <c r="G1468" t="n">
-        <v>51.020923614502</v>
+        <v>51.0209197998047</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G1473" t="n">
-        <v>53.1543273925781</v>
+        <v>53.1543235778809</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>58.560001373291</v>
       </c>
       <c r="G1475" t="n">
-        <v>52.9373779296875</v>
+        <v>52.9373741149902</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>61.0200004577637</v>
       </c>
       <c r="G1478" t="n">
-        <v>55.1611709594727</v>
+        <v>55.1611747741699</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>60.1800003051758</v>
       </c>
       <c r="G1481" t="n">
-        <v>54.4018249511719</v>
+        <v>54.4018287658691</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G1485" t="n">
-        <v>56.860668182373</v>
+        <v>56.8606643676758</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>63.6800003051758</v>
       </c>
       <c r="G1486" t="n">
-        <v>57.5657730102539</v>
+        <v>57.5657768249512</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>66.2799987792969</v>
       </c>
       <c r="G1487" t="n">
-        <v>59.9161338806152</v>
+        <v>59.9161376953125</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>68.1600036621094</v>
       </c>
       <c r="G1489" t="n">
-        <v>61.6156387329102</v>
+        <v>61.6156311035156</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>65.3000030517578</v>
       </c>
       <c r="G1491" t="n">
-        <v>59.0302352905273</v>
+        <v>59.0302314758301</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>66.4599990844727</v>
       </c>
       <c r="G1492" t="n">
-        <v>60.0788459777832</v>
+        <v>60.078857421875</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>67.6600036621094</v>
       </c>
       <c r="G1493" t="n">
-        <v>61.1636352539062</v>
+        <v>61.1636390686035</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>69.0400009155273</v>
       </c>
       <c r="G1496" t="n">
-        <v>62.4111404418945</v>
+        <v>62.4111328125</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>66.5599975585938</v>
       </c>
       <c r="G1501" t="n">
-        <v>60.1692504882812</v>
+        <v>60.169246673584</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>64.0800018310547</v>
       </c>
       <c r="G1505" t="n">
-        <v>57.9273719787598</v>
+        <v>57.9273681640625</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>65.620002746582</v>
       </c>
       <c r="G1506" t="n">
-        <v>59.319507598877</v>
+        <v>59.3195114135742</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>65.5199966430664</v>
       </c>
       <c r="G1507" t="n">
-        <v>59.2290992736816</v>
+        <v>59.2291069030762</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>65.1399993896484</v>
       </c>
       <c r="G1508" t="n">
-        <v>58.8855934143066</v>
+        <v>58.8855972290039</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>66.8199996948242</v>
       </c>
       <c r="G1512" t="n">
-        <v>60.4042854309082</v>
+        <v>60.4042892456055</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>66.0599975585938</v>
       </c>
       <c r="G1513" t="n">
-        <v>59.7172584533691</v>
+        <v>59.7172546386719</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>65.1800003051758</v>
       </c>
       <c r="G1514" t="n">
-        <v>58.9217529296875</v>
+        <v>58.9217491149902</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>63.0800018310547</v>
       </c>
       <c r="G1515" t="n">
-        <v>57.0233879089355</v>
+        <v>57.0233840942383</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1516" t="n">
-        <v>58.4878387451172</v>
+        <v>58.4878425598145</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>63.1599998474121</v>
       </c>
       <c r="G1517" t="n">
-        <v>57.0956993103027</v>
+        <v>57.095703125</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>63.2200012207031</v>
       </c>
       <c r="G1518" t="n">
-        <v>57.1499443054199</v>
+        <v>57.1499481201172</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G1521" t="n">
-        <v>56.6798667907715</v>
+        <v>56.679874420166</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>62.9599990844727</v>
       </c>
       <c r="G1522" t="n">
-        <v>56.9149055480957</v>
+        <v>56.9149017333984</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>64.0800018310547</v>
       </c>
       <c r="G1523" t="n">
-        <v>57.9273719787598</v>
+        <v>57.9273681640625</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>59.9799995422363</v>
       </c>
       <c r="G1534" t="n">
-        <v>54.2210350036621</v>
+        <v>54.2210311889648</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>56.560001373291</v>
       </c>
       <c r="G1538" t="n">
-        <v>51.1294021606445</v>
+        <v>51.1293983459473</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>59.4199981689453</v>
       </c>
       <c r="G1549" t="n">
-        <v>53.7147979736328</v>
+        <v>53.7148017883301</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>57.8800010681152</v>
       </c>
       <c r="G1550" t="n">
-        <v>52.3226661682129</v>
+        <v>52.3226623535156</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>57.6199989318848</v>
       </c>
       <c r="G1552" t="n">
-        <v>52.0876274108887</v>
+        <v>52.0876235961914</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>57.1800003051758</v>
       </c>
       <c r="G1555" t="n">
-        <v>51.6898765563965</v>
+        <v>51.6898727416992</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>56.0400009155273</v>
       </c>
       <c r="G1558" t="n">
-        <v>50.6593284606934</v>
+        <v>50.6593322753906</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>55.0800018310547</v>
       </c>
       <c r="G1561" t="n">
-        <v>49.7915077209473</v>
+        <v>49.79150390625</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>54.7999992370605</v>
       </c>
       <c r="G1562" t="n">
-        <v>49.538387298584</v>
+        <v>49.5383834838867</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>54.7400016784668</v>
       </c>
       <c r="G1563" t="n">
-        <v>49.4841499328613</v>
+        <v>49.4841461181641</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G1564" t="n">
-        <v>49.4479866027832</v>
+        <v>49.4479904174805</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G1565" t="n">
-        <v>47.0976295471191</v>
+        <v>47.0976257324219</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G1566" t="n">
-        <v>49.4479866027832</v>
+        <v>49.4479904174805</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>54.1800003051758</v>
       </c>
       <c r="G1567" t="n">
-        <v>48.9779167175293</v>
+        <v>48.9779205322266</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>48.3199996948242</v>
       </c>
       <c r="G1570" t="n">
-        <v>43.6805648803711</v>
+        <v>43.6805610656738</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>45.310001373291</v>
       </c>
       <c r="G1572" t="n">
-        <v>40.9595718383789</v>
+        <v>40.9595680236816</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>44.6100006103516</v>
       </c>
       <c r="G1573" t="n">
-        <v>40.3267784118652</v>
+        <v>40.3267822265625</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>48.3499984741211</v>
       </c>
       <c r="G1574" t="n">
-        <v>43.7076835632324</v>
+        <v>43.7076797485352</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>47.9700012207031</v>
       </c>
       <c r="G1576" t="n">
-        <v>43.3641738891602</v>
+        <v>43.3641700744629</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G1581" t="n">
-        <v>46.1936416625977</v>
+        <v>46.1936454772949</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>49.7700004577637</v>
       </c>
       <c r="G1584" t="n">
-        <v>44.9913444519043</v>
+        <v>44.991340637207</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>49.2599983215332</v>
       </c>
       <c r="G1585" t="n">
-        <v>44.5303077697754</v>
+        <v>44.5303039550781</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>49.6699981689453</v>
       </c>
       <c r="G1586" t="n">
-        <v>44.9009399414062</v>
+        <v>44.900936126709</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>49.75</v>
       </c>
       <c r="G1587" t="n">
-        <v>44.973258972168</v>
+        <v>44.9732627868652</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G1589" t="n">
-        <v>47.0976295471191</v>
+        <v>47.0976257324219</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>50.7400016784668</v>
       </c>
       <c r="G1590" t="n">
-        <v>45.8682098388672</v>
+        <v>45.8682136535645</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G1592" t="n">
-        <v>47.549617767334</v>
+        <v>47.5496215820312</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>52.9799995422363</v>
       </c>
       <c r="G1593" t="n">
-        <v>47.8931350708008</v>
+        <v>47.8931312561035</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>49.4799995422363</v>
       </c>
       <c r="G1598" t="n">
-        <v>44.7291793823242</v>
+        <v>44.7291831970215</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>49.939998626709</v>
       </c>
       <c r="G1599" t="n">
-        <v>45.14501953125</v>
+        <v>45.1450157165527</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>50.560001373291</v>
       </c>
       <c r="G1600" t="n">
-        <v>45.7054901123047</v>
+        <v>45.705493927002</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>49.6500015258789</v>
       </c>
       <c r="G1601" t="n">
-        <v>44.882869720459</v>
+        <v>44.8828659057617</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>50.0200004577637</v>
       </c>
       <c r="G1604" t="n">
-        <v>45.217342376709</v>
+        <v>45.2173385620117</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>48.9900016784668</v>
       </c>
       <c r="G1610" t="n">
-        <v>44.2862358093262</v>
+        <v>44.2862319946289</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>47.2599983215332</v>
       </c>
       <c r="G1612" t="n">
-        <v>42.722339630127</v>
+        <v>42.7223358154297</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>41.8300018310547</v>
       </c>
       <c r="G1615" t="n">
-        <v>37.8137016296387</v>
+        <v>37.8137054443359</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>44.7400016784668</v>
       </c>
       <c r="G1617" t="n">
-        <v>40.4442939758301</v>
+        <v>40.4442977905273</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>45.3600006103516</v>
       </c>
       <c r="G1619" t="n">
-        <v>41.004768371582</v>
+        <v>41.0047645568848</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>45.2700004577637</v>
       </c>
       <c r="G1621" t="n">
-        <v>40.923412322998</v>
+        <v>40.9234085083008</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>43.7000007629395</v>
       </c>
       <c r="G1622" t="n">
-        <v>39.504150390625</v>
+        <v>39.5041542053223</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>40.8699989318848</v>
       </c>
       <c r="G1626" t="n">
-        <v>37.4779777526855</v>
+        <v>37.4779815673828</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1628" t="n">
-        <v>38.6975975036621</v>
+        <v>38.6975936889648</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>43.0900001525879</v>
       </c>
       <c r="G1629" t="n">
-        <v>39.513729095459</v>
+        <v>39.5137329101562</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>44.8899993896484</v>
       </c>
       <c r="G1630" t="n">
-        <v>41.1643371582031</v>
+        <v>41.1643333435059</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>44.8899993896484</v>
       </c>
       <c r="G1632" t="n">
-        <v>41.1643371582031</v>
+        <v>41.1643333435059</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>46.2599983215332</v>
       </c>
       <c r="G1633" t="n">
-        <v>42.4206275939941</v>
+        <v>42.4206314086914</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>45.8899993896484</v>
       </c>
       <c r="G1634" t="n">
-        <v>42.0813407897949</v>
+        <v>42.0813446044922</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>45.8199996948242</v>
       </c>
       <c r="G1636" t="n">
-        <v>42.0171546936035</v>
+        <v>42.0171508789062</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>39.7599983215332</v>
       </c>
       <c r="G1642" t="n">
-        <v>36.4601020812988</v>
+        <v>36.4601058959961</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>40.9300003051758</v>
       </c>
       <c r="G1653" t="n">
-        <v>37.5329971313477</v>
+        <v>37.5330009460449</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>40.3400001525879</v>
       </c>
       <c r="G1654" t="n">
-        <v>36.9919700622559</v>
+        <v>36.9919662475586</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>40.3400001525879</v>
       </c>
       <c r="G1655" t="n">
-        <v>36.9919700622559</v>
+        <v>36.9919662475586</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>41.2200012207031</v>
       </c>
       <c r="G1657" t="n">
-        <v>37.7989311218262</v>
+        <v>37.7989349365234</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>41.3899993896484</v>
       </c>
       <c r="G1658" t="n">
-        <v>37.9548225402832</v>
+        <v>37.9548187255859</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>40.2200012207031</v>
       </c>
       <c r="G1663" t="n">
-        <v>36.8819274902344</v>
+        <v>36.8819236755371</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>48.7299995422363</v>
       </c>
       <c r="G1675" t="n">
-        <v>44.6856384277344</v>
+        <v>44.6856346130371</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>47.7400016784668</v>
       </c>
       <c r="G1676" t="n">
-        <v>43.7778053283691</v>
+        <v>43.7778015136719</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>46.6599998474121</v>
       </c>
       <c r="G1689" t="n">
-        <v>42.7874412536621</v>
+        <v>42.7874374389648</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>47.5200004577637</v>
       </c>
       <c r="G1690" t="n">
-        <v>43.576057434082</v>
+        <v>43.5760612487793</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>47.9199981689453</v>
       </c>
       <c r="G1691" t="n">
-        <v>43.9428634643555</v>
+        <v>43.9428596496582</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>47.9799995422363</v>
       </c>
       <c r="G1692" t="n">
-        <v>43.9978828430176</v>
+        <v>43.9978790283203</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>43.5</v>
       </c>
       <c r="G1697" t="n">
-        <v>39.8896980285645</v>
+        <v>39.8897018432617</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>43.8699989318848</v>
       </c>
       <c r="G1701" t="n">
-        <v>40.2289924621582</v>
+        <v>40.2289962768555</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>44.5299987792969</v>
       </c>
       <c r="G1705" t="n">
-        <v>40.8342132568359</v>
+        <v>40.8342170715332</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>44.0499992370605</v>
       </c>
       <c r="G1707" t="n">
-        <v>40.3940505981445</v>
+        <v>40.3940544128418</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G1710" t="n">
-        <v>40.6233062744141</v>
+        <v>40.6233024597168</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1721" t="n">
-        <v>41.6320114135742</v>
+        <v>41.632007598877</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>44.3699989318848</v>
       </c>
       <c r="G1725" t="n">
-        <v>40.6874961853027</v>
+        <v>40.6875</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G1726" t="n">
-        <v>41.8154067993164</v>
+        <v>41.8154106140137</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>46.689998626709</v>
       </c>
       <c r="G1730" t="n">
-        <v>42.8149452209473</v>
+        <v>42.81494140625</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>47.3400001525879</v>
       </c>
       <c r="G1732" t="n">
-        <v>43.411003112793</v>
+        <v>43.4109992980957</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>46.0299987792969</v>
       </c>
       <c r="G1734" t="n">
-        <v>42.2097244262695</v>
+        <v>42.2097206115723</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>48.9300003051758</v>
       </c>
       <c r="G1735" t="n">
-        <v>44.8690338134766</v>
+        <v>44.8690376281738</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>43.689998626709</v>
       </c>
       <c r="G1739" t="n">
-        <v>40.0639305114746</v>
+        <v>40.0639343261719</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>42.2599983215332</v>
       </c>
       <c r="G1742" t="n">
-        <v>38.752613067627</v>
+        <v>38.7526092529297</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>46.4500007629395</v>
       </c>
       <c r="G1745" t="n">
-        <v>42.5948677062988</v>
+        <v>42.5948638916016</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>50.0200004577637</v>
       </c>
       <c r="G1751" t="n">
-        <v>45.8685722351074</v>
+        <v>45.8685684204102</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>49.8800010681152</v>
       </c>
       <c r="G1752" t="n">
-        <v>45.7401885986328</v>
+        <v>45.7401924133301</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>48.3600006103516</v>
       </c>
       <c r="G1754" t="n">
-        <v>44.3463439941406</v>
+        <v>44.3463478088379</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>48.1300010681152</v>
       </c>
       <c r="G1757" t="n">
-        <v>44.1354370117188</v>
+        <v>44.1354331970215</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>47.5</v>
       </c>
       <c r="G1759" t="n">
-        <v>43.5577201843262</v>
+        <v>43.5577163696289</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>49.8800010681152</v>
       </c>
       <c r="G1762" t="n">
-        <v>45.7401885986328</v>
+        <v>45.7401924133301</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>47.3400001525879</v>
       </c>
       <c r="G1766" t="n">
-        <v>43.411003112793</v>
+        <v>43.4109992980957</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>50.0800018310547</v>
       </c>
       <c r="G1769" t="n">
-        <v>45.9235954284668</v>
+        <v>45.9235916137695</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>51.6599998474121</v>
       </c>
       <c r="G1770" t="n">
-        <v>47.3724594116211</v>
+        <v>47.3724555969238</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G1778" t="n">
-        <v>44.1079216003418</v>
+        <v>44.1079177856445</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G1784" t="n">
-        <v>46.2170333862305</v>
+        <v>46.2170372009277</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>51.6599998474121</v>
       </c>
       <c r="G1786" t="n">
-        <v>47.3724594116211</v>
+        <v>47.3724555969238</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>53.5</v>
       </c>
       <c r="G1791" t="n">
-        <v>49.0597496032715</v>
+        <v>49.0597457885742</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>56.0400009155273</v>
       </c>
       <c r="G1794" t="n">
-        <v>51.3889389038086</v>
+        <v>51.3889427185059</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>56.0400009155273</v>
       </c>
       <c r="G1797" t="n">
-        <v>51.3889389038086</v>
+        <v>51.3889427185059</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>56.439998626709</v>
       </c>
       <c r="G1801" t="n">
-        <v>51.755744934082</v>
+        <v>51.7557411193848</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>57.7799987792969</v>
       </c>
       <c r="G1802" t="n">
-        <v>52.9845314025879</v>
+        <v>52.9845275878906</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>57.3199996948242</v>
       </c>
       <c r="G1803" t="n">
-        <v>52.5627059936523</v>
+        <v>52.5627098083496</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>58.5200004577637</v>
       </c>
       <c r="G1806" t="n">
-        <v>53.6631126403809</v>
+        <v>53.6631088256836</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>58.7599983215332</v>
       </c>
       <c r="G1807" t="n">
-        <v>53.8831901550293</v>
+        <v>53.883186340332</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>57.439998626709</v>
       </c>
       <c r="G1808" t="n">
-        <v>52.6727447509766</v>
+        <v>52.6727485656738</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>55.3199996948242</v>
       </c>
       <c r="G1812" t="n">
-        <v>50.7286987304688</v>
+        <v>50.7286949157715</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G1814" t="n">
-        <v>51.9941673278809</v>
+        <v>51.9941635131836</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>58.1599998474121</v>
       </c>
       <c r="G1816" t="n">
-        <v>53.3329887390137</v>
+        <v>53.3329925537109</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G1823" t="n">
-        <v>53.4613723754883</v>
+        <v>53.461368560791</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>60.560001373291</v>
       </c>
       <c r="G1828" t="n">
-        <v>55.533805847168</v>
+        <v>55.5338020324707</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G1830" t="n">
-        <v>55.5704765319824</v>
+        <v>55.5704803466797</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>60.939998626709</v>
       </c>
       <c r="G1839" t="n">
-        <v>55.8822593688965</v>
+        <v>55.8822631835938</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>60.560001373291</v>
       </c>
       <c r="G1844" t="n">
-        <v>55.533805847168</v>
+        <v>55.5338020324707</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>63.2599983215332</v>
       </c>
       <c r="G1851" t="n">
-        <v>58.0097122192383</v>
+        <v>58.009708404541</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>62.9799995422363</v>
       </c>
       <c r="G1853" t="n">
-        <v>57.7529487609863</v>
+        <v>57.7529525756836</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>65.7799987792969</v>
       </c>
       <c r="G1854" t="n">
-        <v>60.3205642700195</v>
+        <v>60.3205680847168</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>65.9400024414062</v>
       </c>
       <c r="G1855" t="n">
-        <v>60.46728515625</v>
+        <v>60.4672889709473</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>66.9199981689453</v>
       </c>
       <c r="G1859" t="n">
-        <v>61.3659477233887</v>
+        <v>61.3659515380859</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>67.1999969482422</v>
       </c>
       <c r="G1860" t="n">
-        <v>61.6227149963379</v>
+        <v>61.6227073669434</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>67.6800003051758</v>
       </c>
       <c r="G1861" t="n">
-        <v>62.0628776550293</v>
+        <v>62.062873840332</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>66.9199981689453</v>
       </c>
       <c r="G1863" t="n">
-        <v>61.3659477233887</v>
+        <v>61.3659515380859</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>67.1800003051758</v>
       </c>
       <c r="G1866" t="n">
-        <v>61.6043701171875</v>
+        <v>61.604377746582</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>68.5599975585938</v>
       </c>
       <c r="G1867" t="n">
-        <v>62.8698310852051</v>
+        <v>62.8698387145996</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>67.3000030517578</v>
       </c>
       <c r="G1868" t="n">
-        <v>61.714412689209</v>
+        <v>61.7144203186035</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>67.1800003051758</v>
       </c>
       <c r="G1869" t="n">
-        <v>61.6043701171875</v>
+        <v>61.604377746582</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1872" t="n">
-        <v>60.1555023193359</v>
+        <v>60.1554985046387</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>66.7799987792969</v>
       </c>
       <c r="G1873" t="n">
-        <v>61.2375717163086</v>
+        <v>61.2375679016113</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>66.6800003051758</v>
       </c>
       <c r="G1874" t="n">
-        <v>61.1458740234375</v>
+        <v>61.145866394043</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G1875" t="n">
-        <v>60.1555023193359</v>
+        <v>60.1554985046387</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>64.5</v>
       </c>
       <c r="G1878" t="n">
-        <v>59.1467971801758</v>
+        <v>59.146800994873</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>43.810001373291</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>928940</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>43.9199981689453</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>44.0900001525879</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>44.3199996948242</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>44.3199996948242</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>44.1699981689453</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>43.7900009155273</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>853018</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>44.0400009155273</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>43.3499984741211</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>44.0200004577637</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>44.0200004577637</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>43.5299987792969</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>1225516</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>43.5900001525879</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>42.7299995422363</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>43.3800010681152</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>43.3800010681152</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>43.2000007629395</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>805683</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>43.6599998474121</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>42.5900001525879</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>43.0900001525879</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>43.0900001525879</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>43.0099983215332</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>995661</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>44.3699989318848</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>43.2299995422363</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>43.2299995422363</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>967606</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>43.3899993896484</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>43.5999984741211</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>44.0900001525879</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -456,7 +456,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G3" t="n">
-        <v>10.6608629226685</v>
+        <v>10.6608648300171</v>
       </c>
       <c r="H3" t="n">
         <v>1649453</v>
@@ -485,7 +485,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G4" t="n">
-        <v>10.53981590271</v>
+        <v>10.5398149490356</v>
       </c>
       <c r="H4" t="n">
         <v>1682315</v>
@@ -514,7 +514,7 @@
         <v>12.25</v>
       </c>
       <c r="G5" t="n">
-        <v>10.5916938781738</v>
+        <v>10.5916929244995</v>
       </c>
       <c r="H5" t="n">
         <v>2789127</v>
@@ -543,7 +543,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G6" t="n">
-        <v>10.6781549453735</v>
+        <v>10.6781568527222</v>
       </c>
       <c r="H6" t="n">
         <v>1492468</v>
@@ -572,7 +572,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G7" t="n">
-        <v>10.8597269058228</v>
+        <v>10.8597297668457</v>
       </c>
       <c r="H7" t="n">
         <v>3085768</v>
@@ -601,7 +601,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G8" t="n">
-        <v>11.6205997467041</v>
+        <v>11.6206007003784</v>
       </c>
       <c r="H8" t="n">
         <v>3968372</v>
@@ -659,7 +659,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>11.1537017822266</v>
+        <v>11.1537027359009</v>
       </c>
       <c r="H10" t="n">
         <v>1611472</v>
@@ -688,7 +688,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G11" t="n">
-        <v>10.8424348831177</v>
+        <v>10.842435836792</v>
       </c>
       <c r="H11" t="n">
         <v>1753744</v>
@@ -746,7 +746,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G13" t="n">
-        <v>11.404444694519</v>
+        <v>11.4044427871704</v>
       </c>
       <c r="H13" t="n">
         <v>1474850</v>
@@ -775,7 +775,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G14" t="n">
-        <v>11.0845317840576</v>
+        <v>11.084529876709</v>
       </c>
       <c r="H14" t="n">
         <v>1462384</v>
@@ -804,7 +804,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G15" t="n">
-        <v>11.4909057617188</v>
+        <v>11.4909076690674</v>
       </c>
       <c r="H15" t="n">
         <v>1893243</v>
@@ -833,7 +833,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G16" t="n">
-        <v>11.7762327194214</v>
+        <v>11.7762336730957</v>
       </c>
       <c r="H16" t="n">
         <v>1616599</v>
@@ -891,7 +891,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G18" t="n">
-        <v>11.7848806381226</v>
+        <v>11.7848787307739</v>
       </c>
       <c r="H18" t="n">
         <v>1270858</v>
@@ -920,7 +920,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G19" t="n">
-        <v>11.7589426040649</v>
+        <v>11.7589416503906</v>
       </c>
       <c r="H19" t="n">
         <v>885954</v>
@@ -949,7 +949,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G20" t="n">
-        <v>11.3957977294922</v>
+        <v>11.3957967758179</v>
       </c>
       <c r="H20" t="n">
         <v>1253732</v>
@@ -978,7 +978,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G21" t="n">
-        <v>11.7502946853638</v>
+        <v>11.7502937316895</v>
       </c>
       <c r="H21" t="n">
         <v>1419181</v>
@@ -1065,7 +1065,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G24" t="n">
-        <v>11.430383682251</v>
+        <v>11.4303817749023</v>
       </c>
       <c r="H24" t="n">
         <v>1526683</v>
@@ -1094,7 +1094,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G25" t="n">
-        <v>11.5773687362671</v>
+        <v>11.5773706436157</v>
       </c>
       <c r="H25" t="n">
         <v>1223442</v>
@@ -1123,7 +1123,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G26" t="n">
-        <v>11.0931768417358</v>
+        <v>11.0931777954102</v>
       </c>
       <c r="H26" t="n">
         <v>1837554</v>
@@ -1152,7 +1152,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G27" t="n">
-        <v>10.9548387527466</v>
+        <v>10.9548358917236</v>
       </c>
       <c r="H27" t="n">
         <v>1958438</v>
@@ -1181,7 +1181,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G28" t="n">
-        <v>10.7300338745117</v>
+        <v>10.7300329208374</v>
       </c>
       <c r="H28" t="n">
         <v>2164227</v>
@@ -1210,7 +1210,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>10.9375429153442</v>
+        <v>10.9375448226929</v>
       </c>
       <c r="H29" t="n">
         <v>1215514</v>
@@ -1239,7 +1239,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>10.6349239349365</v>
+        <v>10.6349258422852</v>
       </c>
       <c r="H30" t="n">
         <v>2043322</v>
@@ -1297,7 +1297,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G32" t="n">
-        <v>11.3439197540283</v>
+        <v>11.343918800354</v>
       </c>
       <c r="H32" t="n">
         <v>1059726</v>
@@ -1326,7 +1326,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>11.5427846908569</v>
+        <v>11.5427837371826</v>
       </c>
       <c r="H33" t="n">
         <v>928566</v>
@@ -1355,7 +1355,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G34" t="n">
-        <v>12.061559677124</v>
+        <v>12.0615615844727</v>
       </c>
       <c r="H34" t="n">
         <v>1284802</v>
@@ -1471,7 +1471,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G38" t="n">
-        <v>11.7762327194214</v>
+        <v>11.7762336730957</v>
       </c>
       <c r="H38" t="n">
         <v>1423617</v>
@@ -1500,7 +1500,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G39" t="n">
-        <v>11.4649677276611</v>
+        <v>11.4649667739868</v>
       </c>
       <c r="H39" t="n">
         <v>1090792</v>
@@ -1529,7 +1529,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G40" t="n">
-        <v>11.8540496826172</v>
+        <v>11.8540515899658</v>
       </c>
       <c r="H40" t="n">
         <v>1276215</v>
@@ -1558,7 +1558,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G41" t="n">
-        <v>12.061559677124</v>
+        <v>12.0615615844727</v>
       </c>
       <c r="H41" t="n">
         <v>1147211</v>
@@ -1616,7 +1616,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G43" t="n">
-        <v>12.5976276397705</v>
+        <v>12.5976295471191</v>
       </c>
       <c r="H43" t="n">
         <v>1580398</v>
@@ -1645,7 +1645,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G44" t="n">
-        <v>12.5976276397705</v>
+        <v>12.5976295471191</v>
       </c>
       <c r="H44" t="n">
         <v>1551191</v>
@@ -1674,7 +1674,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G45" t="n">
-        <v>12.4074125289917</v>
+        <v>12.4074115753174</v>
       </c>
       <c r="H45" t="n">
         <v>1651102</v>
@@ -1703,7 +1703,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G46" t="n">
-        <v>12.8397264480591</v>
+        <v>12.8397274017334</v>
       </c>
       <c r="H46" t="n">
         <v>4767271</v>
@@ -1761,7 +1761,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G48" t="n">
-        <v>13.0991153717041</v>
+        <v>13.0991144180298</v>
       </c>
       <c r="H48" t="n">
         <v>1421650</v>
@@ -1848,7 +1848,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="G51" t="n">
-        <v>13.2374544143677</v>
+        <v>13.2374563217163</v>
       </c>
       <c r="H51" t="n">
         <v>1566708</v>
@@ -1877,7 +1877,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>13.323917388916</v>
+        <v>13.3239164352417</v>
       </c>
       <c r="H52" t="n">
         <v>732431</v>
@@ -1935,7 +1935,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G54" t="n">
-        <v>12.9607744216919</v>
+        <v>12.9607725143433</v>
       </c>
       <c r="H54" t="n">
         <v>851853</v>
@@ -1993,7 +1993,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G56" t="n">
-        <v>12.69273853302</v>
+        <v>12.692741394043</v>
       </c>
       <c r="H56" t="n">
         <v>924484</v>
@@ -2080,7 +2080,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G59" t="n">
-        <v>12.6495084762573</v>
+        <v>12.649507522583</v>
       </c>
       <c r="H59" t="n">
         <v>1096206</v>
@@ -2109,7 +2109,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G60" t="n">
-        <v>12.5803375244141</v>
+        <v>12.580340385437</v>
       </c>
       <c r="H60" t="n">
         <v>564761</v>
@@ -2167,7 +2167,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G62" t="n">
-        <v>13.1336984634399</v>
+        <v>13.1336994171143</v>
       </c>
       <c r="H62" t="n">
         <v>636895</v>
@@ -2196,7 +2196,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>12.8397264480591</v>
+        <v>12.8397274017334</v>
       </c>
       <c r="H63" t="n">
         <v>698980</v>
@@ -2225,7 +2225,7 @@
         <v>14.75</v>
       </c>
       <c r="G64" t="n">
-        <v>12.7532615661621</v>
+        <v>12.7532625198364</v>
       </c>
       <c r="H64" t="n">
         <v>735215</v>
@@ -2254,7 +2254,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G65" t="n">
-        <v>12.6149244308472</v>
+        <v>12.6149234771729</v>
       </c>
       <c r="H65" t="n">
         <v>563441</v>
@@ -2341,7 +2341,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>12.2344856262207</v>
+        <v>12.234486579895</v>
       </c>
       <c r="H68" t="n">
         <v>710495</v>
@@ -2457,7 +2457,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G72" t="n">
-        <v>12.6667995452881</v>
+        <v>12.6668004989624</v>
       </c>
       <c r="H72" t="n">
         <v>914198</v>
@@ -2515,7 +2515,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G74" t="n">
-        <v>12.5111684799194</v>
+        <v>12.5111675262451</v>
       </c>
       <c r="H74" t="n">
         <v>679585</v>
@@ -2544,7 +2544,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G75" t="n">
-        <v>12.779200553894</v>
+        <v>12.7792024612427</v>
       </c>
       <c r="H75" t="n">
         <v>998164</v>
@@ -2631,7 +2631,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>13.0126504898071</v>
+        <v>13.0126523971558</v>
       </c>
       <c r="H78" t="n">
         <v>1602045</v>
@@ -2660,7 +2660,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>12.7964954376221</v>
+        <v>12.7964944839478</v>
       </c>
       <c r="H79" t="n">
         <v>862991</v>
@@ -2718,7 +2718,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>12.4074125289917</v>
+        <v>12.4074115753174</v>
       </c>
       <c r="H81" t="n">
         <v>673927</v>
@@ -2747,7 +2747,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G82" t="n">
-        <v>12.3295955657959</v>
+        <v>12.3295965194702</v>
       </c>
       <c r="H82" t="n">
         <v>602545</v>
@@ -2776,7 +2776,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G83" t="n">
-        <v>12.1566715240479</v>
+        <v>12.1566696166992</v>
       </c>
       <c r="H83" t="n">
         <v>1080573</v>
@@ -2805,7 +2805,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G84" t="n">
-        <v>12.2431335449219</v>
+        <v>12.2431325912476</v>
       </c>
       <c r="H84" t="n">
         <v>878226</v>
@@ -2834,7 +2834,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G85" t="n">
-        <v>12.606276512146</v>
+        <v>12.6062755584717</v>
       </c>
       <c r="H85" t="n">
         <v>880454</v>
@@ -2892,7 +2892,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>12.8397264480591</v>
+        <v>12.8397274017334</v>
       </c>
       <c r="H87" t="n">
         <v>813600</v>
@@ -2921,7 +2921,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>12.6667995452881</v>
+        <v>12.6668004989624</v>
       </c>
       <c r="H88" t="n">
         <v>813115</v>
@@ -2979,7 +2979,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G90" t="n">
-        <v>12.6322145462036</v>
+        <v>12.6322154998779</v>
       </c>
       <c r="H90" t="n">
         <v>818561</v>
@@ -3008,7 +3008,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G91" t="n">
-        <v>12.9434823989868</v>
+        <v>12.9434814453125</v>
       </c>
       <c r="H91" t="n">
         <v>1500108</v>
@@ -3066,7 +3066,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>13.6611223220825</v>
+        <v>13.6611213684082</v>
       </c>
       <c r="H93" t="n">
         <v>1486350</v>
@@ -3095,7 +3095,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G94" t="n">
-        <v>13.6005983352661</v>
+        <v>13.6005973815918</v>
       </c>
       <c r="H94" t="n">
         <v>960559</v>
@@ -3124,7 +3124,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G95" t="n">
-        <v>13.5573673248291</v>
+        <v>13.5573682785034</v>
       </c>
       <c r="H95" t="n">
         <v>346697</v>
@@ -3182,7 +3182,7 @@
         <v>15.25</v>
       </c>
       <c r="G97" t="n">
-        <v>13.1855773925781</v>
+        <v>13.1855783462524</v>
       </c>
       <c r="H97" t="n">
         <v>724517</v>
@@ -3211,7 +3211,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G98" t="n">
-        <v>12.9867134094238</v>
+        <v>12.9867124557495</v>
       </c>
       <c r="H98" t="n">
         <v>1181840</v>
@@ -3240,7 +3240,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="n">
-        <v>12.9694213867188</v>
+        <v>12.9694194793701</v>
       </c>
       <c r="H99" t="n">
         <v>607656</v>
@@ -3269,7 +3269,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G100" t="n">
-        <v>12.8559598922729</v>
+        <v>12.8559589385986</v>
       </c>
       <c r="H100" t="n">
         <v>894076</v>
@@ -3298,7 +3298,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G101" t="n">
-        <v>13.1788854598999</v>
+        <v>13.1788864135742</v>
       </c>
       <c r="H101" t="n">
         <v>1204794</v>
@@ -3385,7 +3385,7 @@
         <v>15</v>
       </c>
       <c r="G104" t="n">
-        <v>13.0916090011597</v>
+        <v>13.0916080474854</v>
       </c>
       <c r="H104" t="n">
         <v>606719</v>
@@ -3414,7 +3414,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G105" t="n">
-        <v>13.2137966156006</v>
+        <v>13.2137975692749</v>
       </c>
       <c r="H105" t="n">
         <v>358747</v>
@@ -3472,7 +3472,7 @@
         <v>15</v>
       </c>
       <c r="G107" t="n">
-        <v>13.0916090011597</v>
+        <v>13.0916080474854</v>
       </c>
       <c r="H107" t="n">
         <v>430117</v>
@@ -3530,7 +3530,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G109" t="n">
-        <v>12.9868755340576</v>
+        <v>12.9868764877319</v>
       </c>
       <c r="H109" t="n">
         <v>547891</v>
@@ -3617,7 +3617,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G112" t="n">
-        <v>13.3447132110596</v>
+        <v>13.3447113037109</v>
       </c>
       <c r="H112" t="n">
         <v>536219</v>
@@ -3646,7 +3646,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G113" t="n">
-        <v>13.3534421920776</v>
+        <v>13.3534393310547</v>
       </c>
       <c r="H113" t="n">
         <v>559424</v>
@@ -3675,7 +3675,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G114" t="n">
-        <v>12.92578125</v>
+        <v>12.9257822036743</v>
       </c>
       <c r="H114" t="n">
         <v>615351</v>
@@ -3733,7 +3733,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G116" t="n">
-        <v>12.367205619812</v>
+        <v>12.3672065734863</v>
       </c>
       <c r="H116" t="n">
         <v>976492</v>
@@ -3762,7 +3762,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G117" t="n">
-        <v>12.8385028839111</v>
+        <v>12.8385047912598</v>
       </c>
       <c r="H117" t="n">
         <v>623004</v>
@@ -3791,7 +3791,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G118" t="n">
-        <v>12.4981212615967</v>
+        <v>12.498122215271</v>
       </c>
       <c r="H118" t="n">
         <v>692977</v>
@@ -3820,7 +3820,7 @@
         <v>15</v>
       </c>
       <c r="G119" t="n">
-        <v>13.0916090011597</v>
+        <v>13.0916080474854</v>
       </c>
       <c r="H119" t="n">
         <v>1468595</v>
@@ -3849,7 +3849,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G120" t="n">
-        <v>13.4232606887817</v>
+        <v>13.4232635498047</v>
       </c>
       <c r="H120" t="n">
         <v>818235</v>
@@ -3878,7 +3878,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G121" t="n">
-        <v>13.2923460006714</v>
+        <v>13.2923450469971</v>
       </c>
       <c r="H121" t="n">
         <v>549643</v>
@@ -3907,7 +3907,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G122" t="n">
-        <v>13.4669017791748</v>
+        <v>13.4669008255005</v>
       </c>
       <c r="H122" t="n">
         <v>753655</v>
@@ -3936,7 +3936,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G123" t="n">
-        <v>13.8247375488281</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H123" t="n">
         <v>1071384</v>
@@ -4023,7 +4023,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G126" t="n">
-        <v>12.3410224914551</v>
+        <v>12.3410234451294</v>
       </c>
       <c r="H126" t="n">
         <v>1032859</v>
@@ -4052,7 +4052,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G127" t="n">
-        <v>12.367205619812</v>
+        <v>12.3672065734863</v>
       </c>
       <c r="H127" t="n">
         <v>1000036</v>
@@ -4081,7 +4081,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G128" t="n">
-        <v>12.3410224914551</v>
+        <v>12.3410234451294</v>
       </c>
       <c r="H128" t="n">
         <v>1265115</v>
@@ -4110,7 +4110,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G129" t="n">
-        <v>12.7774095535278</v>
+        <v>12.7774105072021</v>
       </c>
       <c r="H129" t="n">
         <v>1186863</v>
@@ -4168,7 +4168,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G131" t="n">
-        <v>12.3410224914551</v>
+        <v>12.3410234451294</v>
       </c>
       <c r="H131" t="n">
         <v>797500</v>
@@ -4197,7 +4197,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G132" t="n">
-        <v>12.2624731063843</v>
+        <v>12.2624740600586</v>
       </c>
       <c r="H132" t="n">
         <v>1039453</v>
@@ -4226,7 +4226,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G133" t="n">
-        <v>12.4893951416016</v>
+        <v>12.4893941879272</v>
       </c>
       <c r="H133" t="n">
         <v>1308654</v>
@@ -4255,7 +4255,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G134" t="n">
-        <v>12.5155773162842</v>
+        <v>12.5155782699585</v>
       </c>
       <c r="H134" t="n">
         <v>932643</v>
@@ -4284,7 +4284,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G135" t="n">
-        <v>12.6028547286987</v>
+        <v>12.6028537750244</v>
       </c>
       <c r="H135" t="n">
         <v>793285</v>
@@ -4313,7 +4313,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G136" t="n">
-        <v>12.5592164993286</v>
+        <v>12.5592155456543</v>
       </c>
       <c r="H136" t="n">
         <v>818852</v>
@@ -4400,7 +4400,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G139" t="n">
-        <v>12.594126701355</v>
+        <v>12.5941276550293</v>
       </c>
       <c r="H139" t="n">
         <v>922665</v>
@@ -4429,7 +4429,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G140" t="n">
-        <v>12.5853996276855</v>
+        <v>12.5853986740112</v>
       </c>
       <c r="H140" t="n">
         <v>815278</v>
@@ -4458,7 +4458,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G141" t="n">
-        <v>12.4108457565308</v>
+        <v>12.4108438491821</v>
       </c>
       <c r="H141" t="n">
         <v>770225</v>
@@ -4487,7 +4487,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G142" t="n">
-        <v>12.9694213867188</v>
+        <v>12.9694194793701</v>
       </c>
       <c r="H142" t="n">
         <v>1026377</v>
@@ -4516,7 +4516,7 @@
         <v>15</v>
       </c>
       <c r="G143" t="n">
-        <v>13.0916090011597</v>
+        <v>13.0916080474854</v>
       </c>
       <c r="H143" t="n">
         <v>733886</v>
@@ -4574,7 +4574,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G145" t="n">
-        <v>13.7723712921143</v>
+        <v>13.7723722457886</v>
       </c>
       <c r="H145" t="n">
         <v>1113472</v>
@@ -4603,7 +4603,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G146" t="n">
-        <v>13.6676406860352</v>
+        <v>13.6676387786865</v>
       </c>
       <c r="H146" t="n">
         <v>943572</v>
@@ -4632,7 +4632,7 @@
         <v>16</v>
       </c>
       <c r="G147" t="n">
-        <v>13.9643831253052</v>
+        <v>13.9643812179565</v>
       </c>
       <c r="H147" t="n">
         <v>1380522</v>
@@ -4661,7 +4661,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G148" t="n">
-        <v>13.6676406860352</v>
+        <v>13.6676387786865</v>
       </c>
       <c r="H148" t="n">
         <v>2107652</v>
@@ -4690,7 +4690,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G149" t="n">
-        <v>13.6850938796997</v>
+        <v>13.685094833374</v>
       </c>
       <c r="H149" t="n">
         <v>1049960</v>
@@ -4719,7 +4719,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G150" t="n">
-        <v>13.5629062652588</v>
+        <v>13.5629072189331</v>
       </c>
       <c r="H150" t="n">
         <v>1035867</v>
@@ -4806,7 +4806,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>13.3534421920776</v>
+        <v>13.3534393310547</v>
       </c>
       <c r="H153" t="n">
         <v>726750</v>
@@ -4864,7 +4864,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G155" t="n">
-        <v>13.6327285766602</v>
+        <v>13.6327276229858</v>
       </c>
       <c r="H155" t="n">
         <v>1014631</v>
@@ -4951,7 +4951,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G158" t="n">
-        <v>13.6501846313477</v>
+        <v>13.650182723999</v>
       </c>
       <c r="H158" t="n">
         <v>378632</v>
@@ -5038,7 +5038,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G161" t="n">
-        <v>13.4232606887817</v>
+        <v>13.4232635498047</v>
       </c>
       <c r="H161" t="n">
         <v>459541</v>
@@ -5067,7 +5067,7 @@
         <v>15.5</v>
       </c>
       <c r="G162" t="n">
-        <v>13.5279960632324</v>
+        <v>13.5279970169067</v>
       </c>
       <c r="H162" t="n">
         <v>324617</v>
@@ -5183,7 +5183,7 @@
         <v>15.5900001525879</v>
       </c>
       <c r="G166" t="n">
-        <v>13.6065454483032</v>
+        <v>13.6065435409546</v>
       </c>
       <c r="H166" t="n">
         <v>728887</v>
@@ -5212,7 +5212,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G167" t="n">
-        <v>13.3708963394165</v>
+        <v>13.3708953857422</v>
       </c>
       <c r="H167" t="n">
         <v>437224</v>
@@ -5241,7 +5241,7 @@
         <v>15.25</v>
       </c>
       <c r="G168" t="n">
-        <v>13.3098011016846</v>
+        <v>13.3098020553589</v>
       </c>
       <c r="H168" t="n">
         <v>546583</v>
@@ -5270,7 +5270,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G169" t="n">
-        <v>13.2050685882568</v>
+        <v>13.2050676345825</v>
       </c>
       <c r="H169" t="n">
         <v>490869</v>
@@ -5299,7 +5299,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G170" t="n">
-        <v>13.1439762115479</v>
+        <v>13.1439752578735</v>
       </c>
       <c r="H170" t="n">
         <v>758859</v>
@@ -5328,7 +5328,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G171" t="n">
-        <v>12.9781484603882</v>
+        <v>12.9781475067139</v>
       </c>
       <c r="H171" t="n">
         <v>563248</v>
@@ -5357,7 +5357,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G172" t="n">
-        <v>13.0392427444458</v>
+        <v>13.0392417907715</v>
       </c>
       <c r="H172" t="n">
         <v>865182</v>
@@ -5531,7 +5531,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G178" t="n">
-        <v>13.2137966156006</v>
+        <v>13.2137975692749</v>
       </c>
       <c r="H178" t="n">
         <v>613140</v>
@@ -5560,7 +5560,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>13.3534421920776</v>
+        <v>13.3534393310547</v>
       </c>
       <c r="H179" t="n">
         <v>1294130</v>
@@ -5589,7 +5589,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G180" t="n">
-        <v>13.5192680358887</v>
+        <v>13.5192670822144</v>
       </c>
       <c r="H180" t="n">
         <v>1280281</v>
@@ -5618,7 +5618,7 @@
         <v>15.25</v>
       </c>
       <c r="G181" t="n">
-        <v>13.3098011016846</v>
+        <v>13.3098020553589</v>
       </c>
       <c r="H181" t="n">
         <v>739721</v>
@@ -5647,7 +5647,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G182" t="n">
-        <v>13.8247375488281</v>
+        <v>13.8247394561768</v>
       </c>
       <c r="H182" t="n">
         <v>1956264</v>
@@ -5792,7 +5792,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G187" t="n">
-        <v>13.6327285766602</v>
+        <v>13.6327276229858</v>
       </c>
       <c r="H187" t="n">
         <v>872087</v>
@@ -5879,7 +5879,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G190" t="n">
-        <v>13.0741519927979</v>
+        <v>13.0741529464722</v>
       </c>
       <c r="H190" t="n">
         <v>1511981</v>
@@ -5908,7 +5908,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G191" t="n">
-        <v>13.2661628723145</v>
+        <v>13.2661619186401</v>
       </c>
       <c r="H191" t="n">
         <v>1036074</v>
@@ -5966,7 +5966,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G193" t="n">
-        <v>13.257435798645</v>
+        <v>13.2574329376221</v>
       </c>
       <c r="H193" t="n">
         <v>1437271</v>
@@ -6082,7 +6082,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G197" t="n">
-        <v>13.3970794677734</v>
+        <v>13.3970813751221</v>
       </c>
       <c r="H197" t="n">
         <v>1055119</v>
@@ -6111,7 +6111,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G198" t="n">
-        <v>13.1003370285034</v>
+        <v>13.1003360748291</v>
       </c>
       <c r="H198" t="n">
         <v>977738</v>
@@ -6140,7 +6140,7 @@
         <v>15.25</v>
       </c>
       <c r="G199" t="n">
-        <v>13.3098011016846</v>
+        <v>13.3098020553589</v>
       </c>
       <c r="H199" t="n">
         <v>759071</v>
@@ -6169,7 +6169,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G200" t="n">
-        <v>13.4494457244873</v>
+        <v>13.4494466781616</v>
       </c>
       <c r="H200" t="n">
         <v>1067668</v>
@@ -6198,7 +6198,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G201" t="n">
-        <v>13.3970794677734</v>
+        <v>13.3970813751221</v>
       </c>
       <c r="H201" t="n">
         <v>644615</v>
@@ -6227,7 +6227,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>13.1788854598999</v>
+        <v>13.1788864135742</v>
       </c>
       <c r="H202" t="n">
         <v>1049363</v>
@@ -6256,7 +6256,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G203" t="n">
-        <v>13.3534421920776</v>
+        <v>13.3534393310547</v>
       </c>
       <c r="H203" t="n">
         <v>987488</v>
@@ -6285,7 +6285,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G204" t="n">
-        <v>13.4669017791748</v>
+        <v>13.4669008255005</v>
       </c>
       <c r="H204" t="n">
         <v>583464</v>
@@ -6314,7 +6314,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G205" t="n">
-        <v>13.7025508880615</v>
+        <v>13.7025499343872</v>
       </c>
       <c r="H205" t="n">
         <v>1121332</v>
@@ -6430,7 +6430,7 @@
         <v>15.5</v>
       </c>
       <c r="G209" t="n">
-        <v>13.5279960632324</v>
+        <v>13.5279970169067</v>
       </c>
       <c r="H209" t="n">
         <v>858588</v>
@@ -6546,7 +6546,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G213" t="n">
-        <v>13.4058074951172</v>
+        <v>13.4058065414429</v>
       </c>
       <c r="H213" t="n">
         <v>718789</v>
@@ -6633,7 +6633,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G216" t="n">
-        <v>12.9694213867188</v>
+        <v>12.9694194793701</v>
       </c>
       <c r="H216" t="n">
         <v>796342</v>
@@ -6691,7 +6691,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G218" t="n">
-        <v>13.0130577087402</v>
+        <v>13.0130596160889</v>
       </c>
       <c r="H218" t="n">
         <v>873594</v>
@@ -6720,7 +6720,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G219" t="n">
-        <v>12.7774095535278</v>
+        <v>12.7774105072021</v>
       </c>
       <c r="H219" t="n">
         <v>1250147</v>
@@ -6749,7 +6749,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G220" t="n">
-        <v>12.9694213867188</v>
+        <v>12.9694194793701</v>
       </c>
       <c r="H220" t="n">
         <v>944460</v>
@@ -6807,7 +6807,7 @@
         <v>15</v>
       </c>
       <c r="G222" t="n">
-        <v>13.0916090011597</v>
+        <v>13.0916080474854</v>
       </c>
       <c r="H222" t="n">
         <v>981759</v>
@@ -6836,7 +6836,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G223" t="n">
-        <v>12.9694213867188</v>
+        <v>12.9694194793701</v>
       </c>
       <c r="H223" t="n">
         <v>595855</v>
@@ -6923,7 +6923,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G226" t="n">
-        <v>12.9868755340576</v>
+        <v>12.9868764877319</v>
       </c>
       <c r="H226" t="n">
         <v>721836</v>
@@ -6952,7 +6952,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G227" t="n">
-        <v>13.1439762115479</v>
+        <v>13.1439752578735</v>
       </c>
       <c r="H227" t="n">
         <v>521608</v>
@@ -7039,7 +7039,7 @@
         <v>15.25</v>
       </c>
       <c r="G230" t="n">
-        <v>13.3098011016846</v>
+        <v>13.3098020553589</v>
       </c>
       <c r="H230" t="n">
         <v>518076</v>
@@ -7097,7 +7097,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G232" t="n">
-        <v>13.1003370285034</v>
+        <v>13.1003360748291</v>
       </c>
       <c r="H232" t="n">
         <v>428003</v>
@@ -7126,7 +7126,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>13.1788854598999</v>
+        <v>13.1788864135742</v>
       </c>
       <c r="H233" t="n">
         <v>316602</v>
@@ -7155,7 +7155,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G234" t="n">
-        <v>12.9519653320312</v>
+        <v>12.9519643783569</v>
       </c>
       <c r="H234" t="n">
         <v>601686</v>
@@ -7184,7 +7184,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G235" t="n">
-        <v>13.2923460006714</v>
+        <v>13.2923450469971</v>
       </c>
       <c r="H235" t="n">
         <v>641282</v>
@@ -7213,7 +7213,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G236" t="n">
-        <v>13.3883504867554</v>
+        <v>13.388352394104</v>
       </c>
       <c r="H236" t="n">
         <v>638406</v>
@@ -7271,7 +7271,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G238" t="n">
-        <v>13.3883504867554</v>
+        <v>13.388352394104</v>
       </c>
       <c r="H238" t="n">
         <v>1152236</v>
@@ -7300,7 +7300,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G239" t="n">
-        <v>13.6589107513428</v>
+        <v>13.6589117050171</v>
       </c>
       <c r="H239" t="n">
         <v>1908155</v>
@@ -7358,7 +7358,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>14.2262144088745</v>
+        <v>14.2262134552002</v>
       </c>
       <c r="H241" t="n">
         <v>1730095</v>
@@ -7387,7 +7387,7 @@
         <v>16.6100006103516</v>
       </c>
       <c r="G242" t="n">
-        <v>14.4967765808105</v>
+        <v>14.4967746734619</v>
       </c>
       <c r="H242" t="n">
         <v>1500151</v>
@@ -7416,7 +7416,7 @@
         <v>16.8099994659424</v>
       </c>
       <c r="G243" t="n">
-        <v>14.671329498291</v>
+        <v>14.6713285446167</v>
       </c>
       <c r="H243" t="n">
         <v>1336897</v>
@@ -7445,7 +7445,7 @@
         <v>16.75</v>
       </c>
       <c r="G244" t="n">
-        <v>14.6189622879028</v>
+        <v>14.6189641952515</v>
       </c>
       <c r="H244" t="n">
         <v>993746</v>
@@ -7474,7 +7474,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G245" t="n">
-        <v>14.4793176651001</v>
+        <v>14.4793195724487</v>
       </c>
       <c r="H245" t="n">
         <v>1162278</v>
@@ -7503,7 +7503,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>14.1389379501343</v>
+        <v>14.13893699646</v>
       </c>
       <c r="H246" t="n">
         <v>3408964</v>
@@ -7561,7 +7561,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G248" t="n">
-        <v>14.3571290969849</v>
+        <v>14.3571310043335</v>
       </c>
       <c r="H248" t="n">
         <v>1359703</v>
@@ -7590,7 +7590,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G249" t="n">
-        <v>14.4531345367432</v>
+        <v>14.4531335830688</v>
       </c>
       <c r="H249" t="n">
         <v>812808</v>
@@ -7619,7 +7619,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G250" t="n">
-        <v>14.4793176651001</v>
+        <v>14.4793195724487</v>
       </c>
       <c r="H250" t="n">
         <v>680184</v>
@@ -7648,7 +7648,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G251" t="n">
-        <v>14.374587059021</v>
+        <v>14.3745822906494</v>
       </c>
       <c r="H251" t="n">
         <v>659941</v>
@@ -7677,7 +7677,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G252" t="n">
-        <v>14.2436685562134</v>
+        <v>14.243670463562</v>
       </c>
       <c r="H252" t="n">
         <v>505924</v>
@@ -7706,7 +7706,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G253" t="n">
-        <v>14.2698545455933</v>
+        <v>14.2698535919189</v>
       </c>
       <c r="H253" t="n">
         <v>555130</v>
@@ -7735,7 +7735,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>14.2698545455933</v>
+        <v>14.2698535919189</v>
       </c>
       <c r="H254" t="n">
         <v>353288</v>
@@ -7793,7 +7793,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G256" t="n">
-        <v>14.4531345367432</v>
+        <v>14.4531335830688</v>
       </c>
       <c r="H256" t="n">
         <v>713480</v>
@@ -7822,7 +7822,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G257" t="n">
-        <v>14.4269514083862</v>
+        <v>14.4269523620605</v>
       </c>
       <c r="H257" t="n">
         <v>386993</v>
@@ -7851,7 +7851,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>14.6626005172729</v>
+        <v>14.6626024246216</v>
       </c>
       <c r="H258" t="n">
         <v>644667</v>
@@ -7880,7 +7880,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G259" t="n">
-        <v>14.5491418838501</v>
+        <v>14.5491409301758</v>
       </c>
       <c r="H259" t="n">
         <v>711449</v>
@@ -7938,7 +7938,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G261" t="n">
-        <v>14.2611255645752</v>
+        <v>14.2611246109009</v>
       </c>
       <c r="H261" t="n">
         <v>927406</v>
@@ -7967,7 +7967,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G262" t="n">
-        <v>14.4793176651001</v>
+        <v>14.4793195724487</v>
       </c>
       <c r="H262" t="n">
         <v>720832</v>
@@ -7996,7 +7996,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G263" t="n">
-        <v>14.2436685562134</v>
+        <v>14.243670463562</v>
       </c>
       <c r="H263" t="n">
         <v>725960</v>
@@ -8025,7 +8025,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>14.531683921814</v>
+        <v>14.5316858291626</v>
       </c>
       <c r="H264" t="n">
         <v>719045</v>
@@ -8054,7 +8054,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G265" t="n">
-        <v>15.0029821395874</v>
+        <v>15.002984046936</v>
       </c>
       <c r="H265" t="n">
         <v>2064736</v>
@@ -8083,7 +8083,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G266" t="n">
-        <v>15.0378942489624</v>
+        <v>15.0378913879395</v>
       </c>
       <c r="H266" t="n">
         <v>1402402</v>
@@ -8112,7 +8112,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G267" t="n">
-        <v>15.2473592758179</v>
+        <v>15.2473611831665</v>
       </c>
       <c r="H267" t="n">
         <v>907647</v>
@@ -8141,7 +8141,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G268" t="n">
-        <v>15.2822694778442</v>
+        <v>15.2822732925415</v>
       </c>
       <c r="H268" t="n">
         <v>1019197</v>
@@ -8170,7 +8170,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G269" t="n">
-        <v>15.0466222763062</v>
+        <v>15.0466213226318</v>
       </c>
       <c r="H269" t="n">
         <v>656150</v>
@@ -8228,7 +8228,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G271" t="n">
-        <v>15.6401090621948</v>
+        <v>15.6401100158691</v>
       </c>
       <c r="H271" t="n">
         <v>1420539</v>
@@ -8257,7 +8257,7 @@
         <v>18</v>
       </c>
       <c r="G272" t="n">
-        <v>15.7099294662476</v>
+        <v>15.7099304199219</v>
       </c>
       <c r="H272" t="n">
         <v>1880234</v>
@@ -8286,7 +8286,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G273" t="n">
-        <v>15.7448425292969</v>
+        <v>15.7448415756226</v>
       </c>
       <c r="H273" t="n">
         <v>1202755</v>
@@ -8315,7 +8315,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G274" t="n">
-        <v>15.7361154556274</v>
+        <v>15.7361116409302</v>
       </c>
       <c r="H274" t="n">
         <v>851879</v>
@@ -8344,7 +8344,7 @@
         <v>18.0900001525879</v>
       </c>
       <c r="G275" t="n">
-        <v>15.7884798049927</v>
+        <v>15.7884788513184</v>
       </c>
       <c r="H275" t="n">
         <v>1122628</v>
@@ -8373,7 +8373,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G276" t="n">
-        <v>15.6575651168823</v>
+        <v>15.6575622558594</v>
       </c>
       <c r="H276" t="n">
         <v>643911</v>
@@ -8402,7 +8402,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G277" t="n">
-        <v>15.7361154556274</v>
+        <v>15.7361116409302</v>
       </c>
       <c r="H277" t="n">
         <v>775083</v>
@@ -8431,7 +8431,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>15.5790138244629</v>
+        <v>15.5790147781372</v>
       </c>
       <c r="H278" t="n">
         <v>1068639</v>
@@ -8460,7 +8460,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>15.5353765487671</v>
+        <v>15.5353746414185</v>
       </c>
       <c r="H279" t="n">
         <v>1289110</v>
@@ -8489,7 +8489,7 @@
         <v>18</v>
       </c>
       <c r="G280" t="n">
-        <v>15.7099294662476</v>
+        <v>15.7099304199219</v>
       </c>
       <c r="H280" t="n">
         <v>1252469</v>
@@ -8518,7 +8518,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G281" t="n">
-        <v>15.6401090621948</v>
+        <v>15.6401100158691</v>
       </c>
       <c r="H281" t="n">
         <v>608226</v>
@@ -8547,7 +8547,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G282" t="n">
-        <v>15.4655513763428</v>
+        <v>15.4655542373657</v>
       </c>
       <c r="H282" t="n">
         <v>1266777</v>
@@ -8576,7 +8576,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G283" t="n">
-        <v>15.1949949264526</v>
+        <v>15.1949939727783</v>
       </c>
       <c r="H283" t="n">
         <v>969335</v>
@@ -8605,7 +8605,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G284" t="n">
-        <v>15.4830093383789</v>
+        <v>15.4830102920532</v>
       </c>
       <c r="H284" t="n">
         <v>860181</v>
@@ -8663,7 +8663,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G286" t="n">
-        <v>15.5091943740845</v>
+        <v>15.5091934204102</v>
       </c>
       <c r="H286" t="n">
         <v>687555</v>
@@ -8692,7 +8692,7 @@
         <v>17.75</v>
       </c>
       <c r="G287" t="n">
-        <v>15.4917373657227</v>
+        <v>15.491735458374</v>
       </c>
       <c r="H287" t="n">
         <v>1064175</v>
@@ -8721,7 +8721,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>15.5353765487671</v>
+        <v>15.5353746414185</v>
       </c>
       <c r="H288" t="n">
         <v>585881</v>
@@ -8750,7 +8750,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>15.5353765487671</v>
+        <v>15.5353746414185</v>
       </c>
       <c r="H289" t="n">
         <v>700554</v>
@@ -8779,7 +8779,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G290" t="n">
-        <v>15.4393711090088</v>
+        <v>15.4393692016602</v>
       </c>
       <c r="H290" t="n">
         <v>670079</v>
@@ -8808,7 +8808,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G291" t="n">
-        <v>15.4655513763428</v>
+        <v>15.4655542373657</v>
       </c>
       <c r="H291" t="n">
         <v>633998</v>
@@ -8866,7 +8866,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G293" t="n">
-        <v>15.7186574935913</v>
+        <v>15.7186555862427</v>
       </c>
       <c r="H293" t="n">
         <v>363621</v>
@@ -8895,7 +8895,7 @@
         <v>18</v>
       </c>
       <c r="G294" t="n">
-        <v>15.7099294662476</v>
+        <v>15.7099304199219</v>
       </c>
       <c r="H294" t="n">
         <v>752656</v>
@@ -8924,7 +8924,7 @@
         <v>17.9300003051758</v>
       </c>
       <c r="G295" t="n">
-        <v>15.6488351821899</v>
+        <v>15.6488370895386</v>
       </c>
       <c r="H295" t="n">
         <v>500672</v>
@@ -8953,7 +8953,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G296" t="n">
-        <v>15.5964698791504</v>
+        <v>15.5964689254761</v>
       </c>
       <c r="H296" t="n">
         <v>417107</v>
@@ -8982,7 +8982,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>15.4481010437012</v>
+        <v>15.4481000900269</v>
       </c>
       <c r="H297" t="n">
         <v>818808</v>
@@ -9040,7 +9040,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G299" t="n">
-        <v>15.7273845672607</v>
+        <v>15.7273874282837</v>
       </c>
       <c r="H299" t="n">
         <v>1566803</v>
@@ -9069,7 +9069,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G300" t="n">
-        <v>16.617618560791</v>
+        <v>16.6176147460938</v>
       </c>
       <c r="H300" t="n">
         <v>7363241</v>
@@ -9127,7 +9127,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G302" t="n">
-        <v>16.6787071228027</v>
+        <v>16.6787109375</v>
       </c>
       <c r="H302" t="n">
         <v>1467071</v>
@@ -9185,7 +9185,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G304" t="n">
-        <v>16.8445377349854</v>
+        <v>16.8445339202881</v>
       </c>
       <c r="H304" t="n">
         <v>1139004</v>
@@ -9243,7 +9243,7 @@
         <v>19.5</v>
       </c>
       <c r="G306" t="n">
-        <v>17.0190925598145</v>
+        <v>17.0190906524658</v>
       </c>
       <c r="H306" t="n">
         <v>1146962</v>
@@ -9330,7 +9330,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G309" t="n">
-        <v>17.1063690185547</v>
+        <v>17.1063671112061</v>
       </c>
       <c r="H309" t="n">
         <v>828283</v>
@@ -9359,7 +9359,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G310" t="n">
-        <v>17.3507423400879</v>
+        <v>17.3507442474365</v>
       </c>
       <c r="H310" t="n">
         <v>932865</v>
@@ -9417,7 +9417,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G312" t="n">
-        <v>17.6649475097656</v>
+        <v>17.6649417877197</v>
       </c>
       <c r="H312" t="n">
         <v>2795629</v>
@@ -9504,7 +9504,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G315" t="n">
-        <v>17.5776653289795</v>
+        <v>17.5776672363281</v>
       </c>
       <c r="H315" t="n">
         <v>879344</v>
@@ -9533,7 +9533,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>17.8045845031738</v>
+        <v>17.8045883178711</v>
       </c>
       <c r="H316" t="n">
         <v>669451</v>
@@ -9562,7 +9562,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G317" t="n">
-        <v>17.75221824646</v>
+        <v>17.7522220611572</v>
       </c>
       <c r="H317" t="n">
         <v>768865</v>
@@ -9707,7 +9707,7 @@
         <v>20.5300006866455</v>
       </c>
       <c r="G322" t="n">
-        <v>17.9180488586426</v>
+        <v>17.9180469512939</v>
       </c>
       <c r="H322" t="n">
         <v>790238</v>
@@ -9736,7 +9736,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G323" t="n">
-        <v>18.092601776123</v>
+        <v>18.0926036834717</v>
       </c>
       <c r="H323" t="n">
         <v>1723222</v>
@@ -9765,7 +9765,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>18.3980751037598</v>
+        <v>18.3980712890625</v>
       </c>
       <c r="H324" t="n">
         <v>1303495</v>
@@ -9794,7 +9794,7 @@
         <v>21.4099998474121</v>
       </c>
       <c r="G325" t="n">
-        <v>18.686092376709</v>
+        <v>18.6860885620117</v>
       </c>
       <c r="H325" t="n">
         <v>1372973</v>
@@ -9823,7 +9823,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G326" t="n">
-        <v>18.6948204040527</v>
+        <v>18.6948146820068</v>
       </c>
       <c r="H326" t="n">
         <v>785335</v>
@@ -9852,7 +9852,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G327" t="n">
-        <v>18.6599082946777</v>
+        <v>18.6599063873291</v>
       </c>
       <c r="H327" t="n">
         <v>1093693</v>
@@ -9939,7 +9939,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G330" t="n">
-        <v>18.5726299285889</v>
+        <v>18.5726318359375</v>
       </c>
       <c r="H330" t="n">
         <v>1304009</v>
@@ -10026,7 +10026,7 @@
         <v>21.75</v>
       </c>
       <c r="G333" t="n">
-        <v>18.9828338623047</v>
+        <v>18.9828357696533</v>
       </c>
       <c r="H333" t="n">
         <v>1285458</v>
@@ -10084,7 +10084,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G335" t="n">
-        <v>18.9130096435547</v>
+        <v>18.9130115509033</v>
       </c>
       <c r="H335" t="n">
         <v>1050359</v>
@@ -10113,7 +10113,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G336" t="n">
-        <v>19.0264682769775</v>
+        <v>19.0264701843262</v>
       </c>
       <c r="H336" t="n">
         <v>1460378</v>
@@ -10229,7 +10229,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G340" t="n">
-        <v>19.7770576477051</v>
+        <v>19.7770557403564</v>
       </c>
       <c r="H340" t="n">
         <v>980376</v>
@@ -10258,7 +10258,7 @@
         <v>23.0100002288818</v>
       </c>
       <c r="G341" t="n">
-        <v>20.0825252532959</v>
+        <v>20.0825271606445</v>
       </c>
       <c r="H341" t="n">
         <v>1419124</v>
@@ -10345,7 +10345,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G344" t="n">
-        <v>19.8992481231689</v>
+        <v>19.8992462158203</v>
       </c>
       <c r="H344" t="n">
         <v>3314939</v>
@@ -10374,7 +10374,7 @@
         <v>22.0300006866455</v>
       </c>
       <c r="G345" t="n">
-        <v>19.2272090911865</v>
+        <v>19.2272071838379</v>
       </c>
       <c r="H345" t="n">
         <v>3104687</v>
@@ -10403,7 +10403,7 @@
         <v>22.2700004577637</v>
       </c>
       <c r="G346" t="n">
-        <v>19.436674118042</v>
+        <v>19.4366760253906</v>
       </c>
       <c r="H346" t="n">
         <v>1239971</v>
@@ -10432,7 +10432,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>19.3319416046143</v>
+        <v>19.3319435119629</v>
       </c>
       <c r="H347" t="n">
         <v>1708988</v>
@@ -10461,7 +10461,7 @@
         <v>22.25</v>
       </c>
       <c r="G348" t="n">
-        <v>19.4192218780518</v>
+        <v>19.4192161560059</v>
       </c>
       <c r="H348" t="n">
         <v>1129055</v>
@@ -10490,7 +10490,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G349" t="n">
-        <v>19.3144836425781</v>
+        <v>19.3144855499268</v>
       </c>
       <c r="H349" t="n">
         <v>680641</v>
@@ -10519,7 +10519,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>19.3319416046143</v>
+        <v>19.3319435119629</v>
       </c>
       <c r="H350" t="n">
         <v>591698</v>
@@ -10577,7 +10577,7 @@
         <v>21.4099998474121</v>
       </c>
       <c r="G352" t="n">
-        <v>18.686092376709</v>
+        <v>18.6860885620117</v>
       </c>
       <c r="H352" t="n">
         <v>1115090</v>
@@ -10606,7 +10606,7 @@
         <v>21.5900001525879</v>
       </c>
       <c r="G353" t="n">
-        <v>18.8431911468506</v>
+        <v>18.843189239502</v>
       </c>
       <c r="H353" t="n">
         <v>1400646</v>
@@ -10635,7 +10635,7 @@
         <v>21.7700004577637</v>
       </c>
       <c r="G354" t="n">
-        <v>19.0002861022949</v>
+        <v>19.0002899169922</v>
       </c>
       <c r="H354" t="n">
         <v>742088</v>
@@ -10664,7 +10664,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G355" t="n">
-        <v>19.0970916748047</v>
+        <v>19.0970935821533</v>
       </c>
       <c r="H355" t="n">
         <v>598941</v>
@@ -10693,7 +10693,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G356" t="n">
-        <v>19.1674995422363</v>
+        <v>19.1674976348877</v>
       </c>
       <c r="H356" t="n">
         <v>506402</v>
@@ -10722,7 +10722,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>19.0530891418457</v>
+        <v>19.0530910491943</v>
       </c>
       <c r="H357" t="n">
         <v>594084</v>
@@ -10809,7 +10809,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G360" t="n">
-        <v>18.6922702789307</v>
+        <v>18.6922721862793</v>
       </c>
       <c r="H360" t="n">
         <v>819552</v>
@@ -10838,7 +10838,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G361" t="n">
-        <v>19.1674995422363</v>
+        <v>19.1674976348877</v>
       </c>
       <c r="H361" t="n">
         <v>781455</v>
@@ -10867,7 +10867,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G362" t="n">
-        <v>19.0794906616211</v>
+        <v>19.0794925689697</v>
       </c>
       <c r="H362" t="n">
         <v>1232561</v>
@@ -10896,7 +10896,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G363" t="n">
-        <v>19.1498966217041</v>
+        <v>19.1498947143555</v>
       </c>
       <c r="H363" t="n">
         <v>760309</v>
@@ -10954,7 +10954,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G365" t="n">
-        <v>18.736270904541</v>
+        <v>18.7362728118896</v>
       </c>
       <c r="H365" t="n">
         <v>535127</v>
@@ -10983,7 +10983,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G366" t="n">
-        <v>18.3930530548096</v>
+        <v>18.3930511474609</v>
       </c>
       <c r="H366" t="n">
         <v>900255</v>
@@ -11041,7 +11041,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G368" t="n">
-        <v>18.4370594024658</v>
+        <v>18.4370574951172</v>
       </c>
       <c r="H368" t="n">
         <v>580990</v>
@@ -11070,7 +11070,7 @@
         <v>21.0699996948242</v>
       </c>
       <c r="G369" t="n">
-        <v>18.5426616668701</v>
+        <v>18.5426597595215</v>
       </c>
       <c r="H369" t="n">
         <v>478532</v>
@@ -11099,7 +11099,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G370" t="n">
-        <v>18.0586357116699</v>
+        <v>18.0586338043213</v>
       </c>
       <c r="H370" t="n">
         <v>518850</v>
@@ -11157,7 +11157,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G372" t="n">
-        <v>18.5866641998291</v>
+        <v>18.5866603851318</v>
       </c>
       <c r="H372" t="n">
         <v>746226</v>
@@ -11186,7 +11186,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G373" t="n">
-        <v>18.5074596405029</v>
+        <v>18.5074577331543</v>
       </c>
       <c r="H373" t="n">
         <v>1047383</v>
@@ -11215,7 +11215,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G374" t="n">
-        <v>18.7978763580322</v>
+        <v>18.7978782653809</v>
       </c>
       <c r="H374" t="n">
         <v>1374327</v>
@@ -11244,7 +11244,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G375" t="n">
-        <v>18.6834697723389</v>
+        <v>18.6834659576416</v>
       </c>
       <c r="H375" t="n">
         <v>732330</v>
@@ -11302,7 +11302,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G377" t="n">
-        <v>18.6746654510498</v>
+        <v>18.6746711730957</v>
       </c>
       <c r="H377" t="n">
         <v>1742350</v>
@@ -11331,7 +11331,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G378" t="n">
-        <v>18.6130657196045</v>
+        <v>18.6130638122559</v>
       </c>
       <c r="H378" t="n">
         <v>588378</v>
@@ -11360,7 +11360,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G379" t="n">
-        <v>18.6042633056641</v>
+        <v>18.6042652130127</v>
       </c>
       <c r="H379" t="n">
         <v>443070</v>
@@ -11389,7 +11389,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G380" t="n">
-        <v>18.7802753448486</v>
+        <v>18.7802791595459</v>
       </c>
       <c r="H380" t="n">
         <v>474690</v>
@@ -11418,7 +11418,7 @@
         <v>21.0699996948242</v>
       </c>
       <c r="G381" t="n">
-        <v>18.5426616668701</v>
+        <v>18.5426597595215</v>
       </c>
       <c r="H381" t="n">
         <v>626229</v>
@@ -11447,7 +11447,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G382" t="n">
-        <v>18.4106540679932</v>
+        <v>18.4106559753418</v>
       </c>
       <c r="H382" t="n">
         <v>627183</v>
@@ -11476,7 +11476,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G383" t="n">
-        <v>17.85622215271</v>
+        <v>17.8562240600586</v>
       </c>
       <c r="H383" t="n">
         <v>1090391</v>
@@ -11505,7 +11505,7 @@
         <v>20.5</v>
       </c>
       <c r="G384" t="n">
-        <v>18.0410308837891</v>
+        <v>18.0410327911377</v>
       </c>
       <c r="H384" t="n">
         <v>949467</v>
@@ -11563,7 +11563,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G386" t="n">
-        <v>18.0762348175049</v>
+        <v>18.0762386322021</v>
       </c>
       <c r="H386" t="n">
         <v>635176</v>
@@ -11592,7 +11592,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>18.2786445617676</v>
+        <v>18.2786464691162</v>
       </c>
       <c r="H387" t="n">
         <v>945753</v>
@@ -11621,7 +11621,7 @@
         <v>20.6900005340576</v>
       </c>
       <c r="G388" t="n">
-        <v>18.2082443237305</v>
+        <v>18.2082405090332</v>
       </c>
       <c r="H388" t="n">
         <v>708178</v>
@@ -11650,7 +11650,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>18.0850372314453</v>
+        <v>18.0850353240967</v>
       </c>
       <c r="H389" t="n">
         <v>653573</v>
@@ -11708,7 +11708,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G391" t="n">
-        <v>18.5866641998291</v>
+        <v>18.5866603851318</v>
       </c>
       <c r="H391" t="n">
         <v>648000</v>
@@ -11737,7 +11737,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>18.7450695037842</v>
+        <v>18.7450771331787</v>
       </c>
       <c r="H392" t="n">
         <v>567176</v>
@@ -11824,7 +11824,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G395" t="n">
-        <v>18.9034805297852</v>
+        <v>18.9034824371338</v>
       </c>
       <c r="H395" t="n">
         <v>758952</v>
@@ -11882,7 +11882,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G397" t="n">
-        <v>18.7802753448486</v>
+        <v>18.7802791595459</v>
       </c>
       <c r="H397" t="n">
         <v>744363</v>
@@ -11940,7 +11940,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G399" t="n">
-        <v>18.7274723052979</v>
+        <v>18.7274742126465</v>
       </c>
       <c r="H399" t="n">
         <v>713077</v>
@@ -11998,7 +11998,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G401" t="n">
-        <v>18.9034805297852</v>
+        <v>18.9034824371338</v>
       </c>
       <c r="H401" t="n">
         <v>404465</v>
@@ -12027,7 +12027,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G402" t="n">
-        <v>18.736270904541</v>
+        <v>18.7362728118896</v>
       </c>
       <c r="H402" t="n">
         <v>480284</v>
@@ -12056,7 +12056,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>19.6691265106201</v>
+        <v>19.6691246032715</v>
       </c>
       <c r="H403" t="n">
         <v>2201726</v>
@@ -12172,7 +12172,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G407" t="n">
-        <v>19.6867256164551</v>
+        <v>19.6867237091064</v>
       </c>
       <c r="H407" t="n">
         <v>501188</v>
@@ -12230,7 +12230,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>19.7571315765381</v>
+        <v>19.7571334838867</v>
       </c>
       <c r="H409" t="n">
         <v>480941</v>
@@ -12259,7 +12259,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>19.7571315765381</v>
+        <v>19.7571334838867</v>
       </c>
       <c r="H410" t="n">
         <v>399927</v>
@@ -12317,7 +12317,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G412" t="n">
-        <v>19.8275337219238</v>
+        <v>19.8275375366211</v>
       </c>
       <c r="H412" t="n">
         <v>514863</v>
@@ -12375,7 +12375,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G414" t="n">
-        <v>19.7747325897217</v>
+        <v>19.774730682373</v>
       </c>
       <c r="H414" t="n">
         <v>841500</v>
@@ -12404,7 +12404,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G415" t="n">
-        <v>20.2587623596191</v>
+        <v>20.2587585449219</v>
       </c>
       <c r="H415" t="n">
         <v>763275</v>
@@ -12433,7 +12433,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G416" t="n">
-        <v>20.5491771697998</v>
+        <v>20.5491790771484</v>
       </c>
       <c r="H416" t="n">
         <v>829041</v>
@@ -12462,7 +12462,7 @@
         <v>23.7900009155273</v>
       </c>
       <c r="G417" t="n">
-        <v>20.9363975524902</v>
+        <v>20.9363994598389</v>
       </c>
       <c r="H417" t="n">
         <v>843683</v>
@@ -12491,7 +12491,7 @@
         <v>23.6100006103516</v>
       </c>
       <c r="G418" t="n">
-        <v>20.7779922485352</v>
+        <v>20.7779903411865</v>
       </c>
       <c r="H418" t="n">
         <v>801781</v>
@@ -12520,7 +12520,7 @@
         <v>23.5699996948242</v>
       </c>
       <c r="G419" t="n">
-        <v>20.7427845001221</v>
+        <v>20.7427864074707</v>
       </c>
       <c r="H419" t="n">
         <v>492258</v>
@@ -12578,7 +12578,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>20.7691879272461</v>
+        <v>20.7691860198975</v>
       </c>
       <c r="H421" t="n">
         <v>631950</v>
@@ -12607,7 +12607,7 @@
         <v>23.5699996948242</v>
       </c>
       <c r="G422" t="n">
-        <v>20.7427845001221</v>
+        <v>20.7427864074707</v>
       </c>
       <c r="H422" t="n">
         <v>599968</v>
@@ -12636,7 +12636,7 @@
         <v>23.5</v>
       </c>
       <c r="G423" t="n">
-        <v>20.6811809539795</v>
+        <v>20.6811847686768</v>
       </c>
       <c r="H423" t="n">
         <v>438055</v>
@@ -12694,7 +12694,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G425" t="n">
-        <v>20.2851600646973</v>
+        <v>20.2851581573486</v>
       </c>
       <c r="H425" t="n">
         <v>939305</v>
@@ -12723,7 +12723,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G426" t="n">
-        <v>20.672384262085</v>
+        <v>20.6723823547363</v>
       </c>
       <c r="H426" t="n">
         <v>549649</v>
@@ -12752,7 +12752,7 @@
         <v>23.8700008392334</v>
       </c>
       <c r="G427" t="n">
-        <v>21.0068035125732</v>
+        <v>21.0068016052246</v>
       </c>
       <c r="H427" t="n">
         <v>643160</v>
@@ -12781,7 +12781,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G428" t="n">
-        <v>21.2796173095703</v>
+        <v>21.2796192169189</v>
       </c>
       <c r="H428" t="n">
         <v>824280</v>
@@ -12839,7 +12839,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G430" t="n">
-        <v>21.2796173095703</v>
+        <v>21.2796192169189</v>
       </c>
       <c r="H430" t="n">
         <v>835828</v>
@@ -12955,7 +12955,7 @@
         <v>24.7700004577637</v>
       </c>
       <c r="G434" t="n">
-        <v>21.798849105835</v>
+        <v>21.7988452911377</v>
       </c>
       <c r="H434" t="n">
         <v>599662</v>
@@ -13071,7 +13071,7 @@
         <v>24.9699993133545</v>
       </c>
       <c r="G438" t="n">
-        <v>21.9748592376709</v>
+        <v>21.9748573303223</v>
       </c>
       <c r="H438" t="n">
         <v>1108014</v>
@@ -13100,7 +13100,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>21.8692531585693</v>
+        <v>21.8692512512207</v>
       </c>
       <c r="H439" t="n">
         <v>807660</v>
@@ -13245,7 +13245,7 @@
         <v>24.5699996948242</v>
       </c>
       <c r="G444" t="n">
-        <v>21.622838973999</v>
+        <v>21.6228370666504</v>
       </c>
       <c r="H444" t="n">
         <v>438750</v>
@@ -13303,7 +13303,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G446" t="n">
-        <v>21.2092113494873</v>
+        <v>21.2092132568359</v>
       </c>
       <c r="H446" t="n">
         <v>1077693</v>
@@ -13332,7 +13332,7 @@
         <v>24.3700008392334</v>
       </c>
       <c r="G447" t="n">
-        <v>21.4468269348145</v>
+        <v>21.4468307495117</v>
       </c>
       <c r="H447" t="n">
         <v>656480</v>
@@ -13419,7 +13419,7 @@
         <v>24.7700004577637</v>
       </c>
       <c r="G450" t="n">
-        <v>21.798849105835</v>
+        <v>21.7988452911377</v>
       </c>
       <c r="H450" t="n">
         <v>570303</v>
@@ -13448,7 +13448,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G451" t="n">
-        <v>21.2268180847168</v>
+        <v>21.2268161773682</v>
       </c>
       <c r="H451" t="n">
         <v>1286800</v>
@@ -13477,7 +13477,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G452" t="n">
-        <v>21.1388092041016</v>
+        <v>21.1388111114502</v>
       </c>
       <c r="H452" t="n">
         <v>720527</v>
@@ -13506,7 +13506,7 @@
         <v>23.7099990844727</v>
       </c>
       <c r="G453" t="n">
-        <v>20.8659915924072</v>
+        <v>20.8659934997559</v>
       </c>
       <c r="H453" t="n">
         <v>713778</v>
@@ -13535,7 +13535,7 @@
         <v>23.8700008392334</v>
       </c>
       <c r="G454" t="n">
-        <v>21.0068035125732</v>
+        <v>21.0068016052246</v>
       </c>
       <c r="H454" t="n">
         <v>432897</v>
@@ -13564,7 +13564,7 @@
         <v>24.4599990844727</v>
       </c>
       <c r="G455" t="n">
-        <v>21.5260334014893</v>
+        <v>21.5260314941406</v>
       </c>
       <c r="H455" t="n">
         <v>810344</v>
@@ -13593,7 +13593,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G456" t="n">
-        <v>21.6492404937744</v>
+        <v>21.649242401123</v>
       </c>
       <c r="H456" t="n">
         <v>608555</v>
@@ -13622,7 +13622,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G457" t="n">
-        <v>21.4380264282227</v>
+        <v>21.438024520874</v>
       </c>
       <c r="H457" t="n">
         <v>691134</v>
@@ -13651,7 +13651,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G458" t="n">
-        <v>21.6492404937744</v>
+        <v>21.649242401123</v>
       </c>
       <c r="H458" t="n">
         <v>928554</v>
@@ -13854,7 +13854,7 @@
         <v>24.9099998474121</v>
       </c>
       <c r="G465" t="n">
-        <v>21.9220542907715</v>
+        <v>21.9220523834229</v>
       </c>
       <c r="H465" t="n">
         <v>1308526</v>
@@ -13883,7 +13883,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G466" t="n">
-        <v>21.7284450531006</v>
+        <v>21.728443145752</v>
       </c>
       <c r="H466" t="n">
         <v>2224743</v>
@@ -14086,7 +14086,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G473" t="n">
-        <v>21.3236217498779</v>
+        <v>21.3236198425293</v>
       </c>
       <c r="H473" t="n">
         <v>795656</v>
@@ -14115,7 +14115,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G474" t="n">
-        <v>21.2356128692627</v>
+        <v>21.2356147766113</v>
       </c>
       <c r="H474" t="n">
         <v>731965</v>
@@ -14144,7 +14144,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G475" t="n">
-        <v>21.1564121246338</v>
+        <v>21.1564102172852</v>
       </c>
       <c r="H475" t="n">
         <v>691656</v>
@@ -14173,7 +14173,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G476" t="n">
-        <v>20.672384262085</v>
+        <v>20.6723823547363</v>
       </c>
       <c r="H476" t="n">
         <v>1149844</v>
@@ -14202,7 +14202,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>20.0651473999023</v>
+        <v>20.065149307251</v>
       </c>
       <c r="H477" t="n">
         <v>1679544</v>
@@ -14231,7 +14231,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G478" t="n">
-        <v>20.2851600646973</v>
+        <v>20.2851581573486</v>
       </c>
       <c r="H478" t="n">
         <v>1186716</v>
@@ -14318,7 +14318,7 @@
         <v>22.8299999237061</v>
       </c>
       <c r="G481" t="n">
-        <v>20.0915470123291</v>
+        <v>20.091552734375</v>
       </c>
       <c r="H481" t="n">
         <v>1192351</v>
@@ -14347,7 +14347,7 @@
         <v>22.9400005340576</v>
       </c>
       <c r="G482" t="n">
-        <v>20.1883544921875</v>
+        <v>20.1883583068848</v>
       </c>
       <c r="H482" t="n">
         <v>709541</v>
@@ -14376,7 +14376,7 @@
         <v>22.8099994659424</v>
       </c>
       <c r="G483" t="n">
-        <v>20.0739498138428</v>
+        <v>20.0739479064941</v>
       </c>
       <c r="H483" t="n">
         <v>511071</v>
@@ -14405,7 +14405,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>20.5051746368408</v>
+        <v>20.5051708221436</v>
       </c>
       <c r="H484" t="n">
         <v>875959</v>
@@ -14434,7 +14434,7 @@
         <v>23.5</v>
       </c>
       <c r="G485" t="n">
-        <v>20.6811809539795</v>
+        <v>20.6811847686768</v>
       </c>
       <c r="H485" t="n">
         <v>826917</v>
@@ -14463,7 +14463,7 @@
         <v>23.2900009155273</v>
       </c>
       <c r="G486" t="n">
-        <v>20.4963722229004</v>
+        <v>20.496374130249</v>
       </c>
       <c r="H486" t="n">
         <v>581964</v>
@@ -14492,7 +14492,7 @@
         <v>23.5699996948242</v>
       </c>
       <c r="G487" t="n">
-        <v>20.7427845001221</v>
+        <v>20.7427864074707</v>
       </c>
       <c r="H487" t="n">
         <v>431355</v>
@@ -14521,7 +14521,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G488" t="n">
-        <v>20.540376663208</v>
+        <v>20.5403747558594</v>
       </c>
       <c r="H488" t="n">
         <v>537404</v>
@@ -14550,7 +14550,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G489" t="n">
-        <v>20.5051746368408</v>
+        <v>20.5051708221436</v>
       </c>
       <c r="H489" t="n">
         <v>630087</v>
@@ -14579,7 +14579,7 @@
         <v>23.2900009155273</v>
       </c>
       <c r="G490" t="n">
-        <v>20.4963722229004</v>
+        <v>20.496374130249</v>
       </c>
       <c r="H490" t="n">
         <v>634554</v>
@@ -14608,7 +14608,7 @@
         <v>23</v>
       </c>
       <c r="G491" t="n">
-        <v>20.2411575317383</v>
+        <v>20.2411594390869</v>
       </c>
       <c r="H491" t="n">
         <v>817345</v>
@@ -14637,7 +14637,7 @@
         <v>23.0300006866455</v>
       </c>
       <c r="G492" t="n">
-        <v>20.2675628662109</v>
+        <v>20.2675590515137</v>
       </c>
       <c r="H492" t="n">
         <v>1005663</v>
@@ -14695,7 +14695,7 @@
         <v>23.0599994659424</v>
       </c>
       <c r="G494" t="n">
-        <v>20.2939605712891</v>
+        <v>20.2939624786377</v>
       </c>
       <c r="H494" t="n">
         <v>461715</v>
@@ -14753,7 +14753,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>20.8131923675537</v>
+        <v>20.8131904602051</v>
       </c>
       <c r="H496" t="n">
         <v>870293</v>
@@ -14782,7 +14782,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G497" t="n">
-        <v>21.3324203491211</v>
+        <v>21.3324222564697</v>
       </c>
       <c r="H497" t="n">
         <v>1075786</v>
@@ -14811,7 +14811,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G498" t="n">
-        <v>21.8340454101562</v>
+        <v>21.8340492248535</v>
       </c>
       <c r="H498" t="n">
         <v>1202133</v>
@@ -14840,7 +14840,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G499" t="n">
-        <v>21.8780555725098</v>
+        <v>21.8780517578125</v>
       </c>
       <c r="H499" t="n">
         <v>650044</v>
@@ -14869,7 +14869,7 @@
         <v>25.2700004577637</v>
       </c>
       <c r="G500" t="n">
-        <v>22.2388706207275</v>
+        <v>22.2388744354248</v>
       </c>
       <c r="H500" t="n">
         <v>1226430</v>
@@ -14956,7 +14956,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>21.6932392120361</v>
+        <v>21.6932411193848</v>
       </c>
       <c r="H503" t="n">
         <v>1280680</v>
@@ -14985,7 +14985,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G504" t="n">
-        <v>22.1860656738281</v>
+        <v>22.1860675811768</v>
       </c>
       <c r="H504" t="n">
         <v>1426844</v>
@@ -15043,7 +15043,7 @@
         <v>25.1900005340576</v>
       </c>
       <c r="G506" t="n">
-        <v>22.1684703826904</v>
+        <v>22.1684684753418</v>
       </c>
       <c r="H506" t="n">
         <v>833635</v>
@@ -15072,7 +15072,7 @@
         <v>25.5</v>
       </c>
       <c r="G507" t="n">
-        <v>22.4412860870361</v>
+        <v>22.4412841796875</v>
       </c>
       <c r="H507" t="n">
         <v>673865</v>
@@ -15101,7 +15101,7 @@
         <v>25.6800003051758</v>
       </c>
       <c r="G508" t="n">
-        <v>22.5996952056885</v>
+        <v>22.5996971130371</v>
       </c>
       <c r="H508" t="n">
         <v>795151</v>
@@ -15130,7 +15130,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G509" t="n">
-        <v>22.9869136810303</v>
+        <v>22.9869155883789</v>
       </c>
       <c r="H509" t="n">
         <v>885647</v>
@@ -15159,7 +15159,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G510" t="n">
-        <v>23.2333316802979</v>
+        <v>23.2333297729492</v>
       </c>
       <c r="H510" t="n">
         <v>964323</v>
@@ -15188,7 +15188,7 @@
         <v>26.0799999237061</v>
       </c>
       <c r="G511" t="n">
-        <v>22.9517135620117</v>
+        <v>22.9517097473145</v>
       </c>
       <c r="H511" t="n">
         <v>466610</v>
@@ -15217,7 +15217,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G512" t="n">
-        <v>22.7052993774414</v>
+        <v>22.70530128479</v>
       </c>
       <c r="H512" t="n">
         <v>620738</v>
@@ -15275,7 +15275,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G514" t="n">
-        <v>22.9693183898926</v>
+        <v>22.9693145751953</v>
       </c>
       <c r="H514" t="n">
         <v>802020</v>
@@ -15333,7 +15333,7 @@
         <v>26</v>
       </c>
       <c r="G516" t="n">
-        <v>22.881311416626</v>
+        <v>22.8813095092773</v>
       </c>
       <c r="H516" t="n">
         <v>935527</v>
@@ -15362,7 +15362,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G517" t="n">
-        <v>22.9869136810303</v>
+        <v>22.9869155883789</v>
       </c>
       <c r="H517" t="n">
         <v>618837</v>
@@ -15391,7 +15391,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G518" t="n">
-        <v>22.5468883514404</v>
+        <v>22.5468921661377</v>
       </c>
       <c r="H518" t="n">
         <v>1003197</v>
@@ -15449,7 +15449,7 @@
         <v>25.1599998474121</v>
       </c>
       <c r="G520" t="n">
-        <v>22.1420650482178</v>
+        <v>22.1420669555664</v>
       </c>
       <c r="H520" t="n">
         <v>976002</v>
@@ -15478,7 +15478,7 @@
         <v>25.4400005340576</v>
       </c>
       <c r="G521" t="n">
-        <v>22.3884792327881</v>
+        <v>22.3884811401367</v>
       </c>
       <c r="H521" t="n">
         <v>579102</v>
@@ -15507,7 +15507,7 @@
         <v>25.5</v>
       </c>
       <c r="G522" t="n">
-        <v>22.4412860870361</v>
+        <v>22.4412841796875</v>
       </c>
       <c r="H522" t="n">
         <v>541546</v>
@@ -15623,7 +15623,7 @@
         <v>26.7800006866455</v>
       </c>
       <c r="G526" t="n">
-        <v>23.5677490234375</v>
+        <v>23.5677471160889</v>
       </c>
       <c r="H526" t="n">
         <v>1061315</v>
@@ -15652,7 +15652,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G527" t="n">
-        <v>23.690954208374</v>
+        <v>23.6909561157227</v>
       </c>
       <c r="H527" t="n">
         <v>628987</v>
@@ -15681,7 +15681,7 @@
         <v>27.0599994659424</v>
       </c>
       <c r="G528" t="n">
-        <v>23.8141593933105</v>
+        <v>23.8141632080078</v>
       </c>
       <c r="H528" t="n">
         <v>897350</v>
@@ -15710,7 +15710,7 @@
         <v>26.7800006866455</v>
       </c>
       <c r="G529" t="n">
-        <v>23.5677490234375</v>
+        <v>23.5677471160889</v>
       </c>
       <c r="H529" t="n">
         <v>1027867</v>
@@ -15739,7 +15739,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G530" t="n">
-        <v>23.8317642211914</v>
+        <v>23.83176612854</v>
       </c>
       <c r="H530" t="n">
         <v>772402</v>
@@ -15797,7 +15797,7 @@
         <v>26.6299991607666</v>
       </c>
       <c r="G532" t="n">
-        <v>23.4357414245605</v>
+        <v>23.4357395172119</v>
       </c>
       <c r="H532" t="n">
         <v>658220</v>
@@ -15826,7 +15826,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G533" t="n">
-        <v>23.3565349578857</v>
+        <v>23.3565368652344</v>
       </c>
       <c r="H533" t="n">
         <v>1001892</v>
@@ -15855,7 +15855,7 @@
         <v>26.7399997711182</v>
       </c>
       <c r="G534" t="n">
-        <v>23.5325489044189</v>
+        <v>23.5325469970703</v>
       </c>
       <c r="H534" t="n">
         <v>658257</v>
@@ -15884,7 +15884,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G535" t="n">
-        <v>22.8989124298096</v>
+        <v>22.8989105224609</v>
       </c>
       <c r="H535" t="n">
         <v>532342</v>
@@ -15971,7 +15971,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G538" t="n">
-        <v>23.6733551025391</v>
+        <v>23.6733531951904</v>
       </c>
       <c r="H538" t="n">
         <v>1322304</v>
@@ -16000,7 +16000,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G539" t="n">
-        <v>22.9869136810303</v>
+        <v>22.9869155883789</v>
       </c>
       <c r="H539" t="n">
         <v>1035265</v>
@@ -16029,7 +16029,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G540" t="n">
-        <v>22.6348934173584</v>
+        <v>22.634895324707</v>
       </c>
       <c r="H540" t="n">
         <v>1326975</v>
@@ -16116,7 +16116,7 @@
         <v>27.2299995422363</v>
       </c>
       <c r="G543" t="n">
-        <v>23.9637718200684</v>
+        <v>23.9637699127197</v>
       </c>
       <c r="H543" t="n">
         <v>1056186</v>
@@ -16145,7 +16145,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G544" t="n">
-        <v>24.949426651001</v>
+        <v>24.9494285583496</v>
       </c>
       <c r="H544" t="n">
         <v>1953200</v>
@@ -16203,7 +16203,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G546" t="n">
-        <v>24.7118148803711</v>
+        <v>24.7118167877197</v>
       </c>
       <c r="H546" t="n">
         <v>1021909</v>
@@ -16232,7 +16232,7 @@
         <v>28.2299995422363</v>
       </c>
       <c r="G547" t="n">
-        <v>24.8438205718994</v>
+        <v>24.843822479248</v>
       </c>
       <c r="H547" t="n">
         <v>1406010</v>
@@ -16261,7 +16261,7 @@
         <v>28.25</v>
       </c>
       <c r="G548" t="n">
-        <v>24.861421585083</v>
+        <v>24.8614234924316</v>
       </c>
       <c r="H548" t="n">
         <v>958804</v>
@@ -16290,7 +16290,7 @@
         <v>28.1200008392334</v>
       </c>
       <c r="G549" t="n">
-        <v>24.7470169067383</v>
+        <v>24.7470188140869</v>
       </c>
       <c r="H549" t="n">
         <v>792339</v>
@@ -16319,7 +16319,7 @@
         <v>28.0400009155273</v>
       </c>
       <c r="G550" t="n">
-        <v>24.6766147613525</v>
+        <v>24.6766128540039</v>
       </c>
       <c r="H550" t="n">
         <v>888530</v>
@@ -16348,7 +16348,7 @@
         <v>28.3099994659424</v>
       </c>
       <c r="G551" t="n">
-        <v>24.9142265319824</v>
+        <v>24.9142284393311</v>
       </c>
       <c r="H551" t="n">
         <v>3273175</v>
@@ -16377,7 +16377,7 @@
         <v>28.8600006103516</v>
       </c>
       <c r="G552" t="n">
-        <v>25.3982524871826</v>
+        <v>25.3982543945312</v>
       </c>
       <c r="H552" t="n">
         <v>2501270</v>
@@ -16464,7 +16464,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>24.5534038543701</v>
+        <v>24.5534019470215</v>
       </c>
       <c r="H555" t="n">
         <v>1211066</v>
@@ -16493,7 +16493,7 @@
         <v>28.3799991607666</v>
       </c>
       <c r="G556" t="n">
-        <v>24.975830078125</v>
+        <v>24.9758281707764</v>
       </c>
       <c r="H556" t="n">
         <v>1231907</v>
@@ -16522,7 +16522,7 @@
         <v>28.2399997711182</v>
       </c>
       <c r="G557" t="n">
-        <v>24.8526191711426</v>
+        <v>24.8526210784912</v>
       </c>
       <c r="H557" t="n">
         <v>798613</v>
@@ -16551,7 +16551,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>25.4774589538574</v>
+        <v>25.4774570465088</v>
       </c>
       <c r="H558" t="n">
         <v>1163365</v>
@@ -16638,7 +16638,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G561" t="n">
-        <v>25.9174823760986</v>
+        <v>25.9174861907959</v>
       </c>
       <c r="H561" t="n">
         <v>1040116</v>
@@ -16667,7 +16667,7 @@
         <v>29.25</v>
       </c>
       <c r="G562" t="n">
-        <v>25.7414722442627</v>
+        <v>25.7414703369141</v>
       </c>
       <c r="H562" t="n">
         <v>966757</v>
@@ -16696,7 +16696,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>25.4774589538574</v>
+        <v>25.4774570465088</v>
       </c>
       <c r="H563" t="n">
         <v>761601</v>
@@ -16725,7 +16725,7 @@
         <v>29.6100006103516</v>
       </c>
       <c r="G564" t="n">
-        <v>26.0582904815674</v>
+        <v>26.058292388916</v>
       </c>
       <c r="H564" t="n">
         <v>887659</v>
@@ -16754,7 +16754,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G565" t="n">
-        <v>25.9966869354248</v>
+        <v>25.9966888427734</v>
       </c>
       <c r="H565" t="n">
         <v>1686155</v>
@@ -16783,7 +16783,7 @@
         <v>29.7700004577637</v>
       </c>
       <c r="G566" t="n">
-        <v>26.1990966796875</v>
+        <v>26.1991024017334</v>
       </c>
       <c r="H566" t="n">
         <v>958755</v>
@@ -16841,7 +16841,7 @@
         <v>30.8600006103516</v>
       </c>
       <c r="G568" t="n">
-        <v>27.1583557128906</v>
+        <v>27.158353805542</v>
       </c>
       <c r="H568" t="n">
         <v>1311717</v>
@@ -16899,7 +16899,7 @@
         <v>30.6100006103516</v>
       </c>
       <c r="G570" t="n">
-        <v>26.9383430480957</v>
+        <v>26.9383392333984</v>
       </c>
       <c r="H570" t="n">
         <v>1168580</v>
@@ -16928,7 +16928,7 @@
         <v>30.5599994659424</v>
       </c>
       <c r="G571" t="n">
-        <v>26.8943386077881</v>
+        <v>26.8943367004395</v>
       </c>
       <c r="H571" t="n">
         <v>830320</v>
@@ -16957,7 +16957,7 @@
         <v>30.8600006103516</v>
       </c>
       <c r="G572" t="n">
-        <v>27.1583557128906</v>
+        <v>27.158353805542</v>
       </c>
       <c r="H572" t="n">
         <v>1443817</v>
@@ -16986,7 +16986,7 @@
         <v>30.8299999237061</v>
       </c>
       <c r="G573" t="n">
-        <v>27.1319561004639</v>
+        <v>27.1319522857666</v>
       </c>
       <c r="H573" t="n">
         <v>995555</v>
@@ -17015,7 +17015,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>27.1935577392578</v>
+        <v>27.1935539245605</v>
       </c>
       <c r="H574" t="n">
         <v>942142</v>
@@ -17044,7 +17044,7 @@
         <v>32.8699989318848</v>
       </c>
       <c r="G575" t="n">
-        <v>28.9272575378418</v>
+        <v>28.9272556304932</v>
       </c>
       <c r="H575" t="n">
         <v>4195540</v>
@@ -17073,7 +17073,7 @@
         <v>32.5</v>
       </c>
       <c r="G576" t="n">
-        <v>28.601634979248</v>
+        <v>28.6016387939453</v>
       </c>
       <c r="H576" t="n">
         <v>1611053</v>
@@ -17102,7 +17102,7 @@
         <v>32.9199981689453</v>
       </c>
       <c r="G577" t="n">
-        <v>28.9712562561035</v>
+        <v>28.9712581634521</v>
       </c>
       <c r="H577" t="n">
         <v>2075439</v>
@@ -17131,7 +17131,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G578" t="n">
-        <v>29.3056735992432</v>
+        <v>29.3056774139404</v>
       </c>
       <c r="H578" t="n">
         <v>1355277</v>
@@ -17160,7 +17160,7 @@
         <v>33.3899993896484</v>
       </c>
       <c r="G579" t="n">
-        <v>29.3848838806152</v>
+        <v>29.3848819732666</v>
       </c>
       <c r="H579" t="n">
         <v>1397575</v>
@@ -17189,7 +17189,7 @@
         <v>33.0299987792969</v>
       </c>
       <c r="G580" t="n">
-        <v>29.068058013916</v>
+        <v>29.0680637359619</v>
       </c>
       <c r="H580" t="n">
         <v>1597550</v>
@@ -17218,7 +17218,7 @@
         <v>33.75</v>
       </c>
       <c r="G581" t="n">
-        <v>29.7017002105713</v>
+        <v>29.7016983032227</v>
       </c>
       <c r="H581" t="n">
         <v>1401063</v>
@@ -17247,7 +17247,7 @@
         <v>33.75</v>
       </c>
       <c r="G582" t="n">
-        <v>29.7017002105713</v>
+        <v>29.7016983032227</v>
       </c>
       <c r="H582" t="n">
         <v>1363549</v>
@@ -17276,7 +17276,7 @@
         <v>34.0400009155273</v>
       </c>
       <c r="G583" t="n">
-        <v>29.956916809082</v>
+        <v>29.9569149017334</v>
       </c>
       <c r="H583" t="n">
         <v>1366041</v>
@@ -17305,7 +17305,7 @@
         <v>33.6599998474121</v>
       </c>
       <c r="G584" t="n">
-        <v>29.6224956512451</v>
+        <v>29.6224975585938</v>
       </c>
       <c r="H584" t="n">
         <v>2010222</v>
@@ -17334,7 +17334,7 @@
         <v>34.4599990844727</v>
       </c>
       <c r="G585" t="n">
-        <v>30.3265361785889</v>
+        <v>30.326530456543</v>
       </c>
       <c r="H585" t="n">
         <v>1696501</v>
@@ -17363,7 +17363,7 @@
         <v>35.2299995422363</v>
       </c>
       <c r="G586" t="n">
-        <v>31.0041770935059</v>
+        <v>31.0041751861572</v>
       </c>
       <c r="H586" t="n">
         <v>2160276</v>
@@ -17392,7 +17392,7 @@
         <v>35.0200004577637</v>
       </c>
       <c r="G587" t="n">
-        <v>30.8193645477295</v>
+        <v>30.8193683624268</v>
       </c>
       <c r="H587" t="n">
         <v>2202729</v>
@@ -17421,7 +17421,7 @@
         <v>35.3600006103516</v>
       </c>
       <c r="G588" t="n">
-        <v>31.1185779571533</v>
+        <v>31.118579864502</v>
       </c>
       <c r="H588" t="n">
         <v>1508373</v>
@@ -17450,7 +17450,7 @@
         <v>35.25</v>
       </c>
       <c r="G589" t="n">
-        <v>31.0217723846436</v>
+        <v>31.0217742919922</v>
       </c>
       <c r="H589" t="n">
         <v>1091262</v>
@@ -17479,7 +17479,7 @@
         <v>36.0200004577637</v>
       </c>
       <c r="G590" t="n">
-        <v>31.6994171142578</v>
+        <v>31.6994094848633</v>
       </c>
       <c r="H590" t="n">
         <v>1503377</v>
@@ -17508,7 +17508,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G591" t="n">
-        <v>31.769811630249</v>
+        <v>31.7698135375977</v>
       </c>
       <c r="H591" t="n">
         <v>1358065</v>
@@ -17537,7 +17537,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G592" t="n">
-        <v>32.0338363647461</v>
+        <v>32.0338249206543</v>
       </c>
       <c r="H592" t="n">
         <v>1074472</v>
@@ -17566,7 +17566,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>32.5178642272949</v>
+        <v>32.5178604125977</v>
       </c>
       <c r="H593" t="n">
         <v>1243389</v>
@@ -17653,7 +17653,7 @@
         <v>36.5</v>
       </c>
       <c r="G596" t="n">
-        <v>32.1218414306641</v>
+        <v>32.1218376159668</v>
       </c>
       <c r="H596" t="n">
         <v>2985277</v>
@@ -17711,7 +17711,7 @@
         <v>35.25</v>
       </c>
       <c r="G598" t="n">
-        <v>31.0217723846436</v>
+        <v>31.0217742919922</v>
       </c>
       <c r="H598" t="n">
         <v>2947165</v>
@@ -17740,7 +17740,7 @@
         <v>36.4799995422363</v>
       </c>
       <c r="G599" t="n">
-        <v>32.1042366027832</v>
+        <v>32.1042327880859</v>
       </c>
       <c r="H599" t="n">
         <v>1602446</v>
@@ -17769,7 +17769,7 @@
         <v>36.5299987792969</v>
       </c>
       <c r="G600" t="n">
-        <v>32.1482391357422</v>
+        <v>32.1482353210449</v>
       </c>
       <c r="H600" t="n">
         <v>1348380</v>
@@ -17798,7 +17798,7 @@
         <v>36.7900009155273</v>
       </c>
       <c r="G601" t="n">
-        <v>32.3770561218262</v>
+        <v>32.3770523071289</v>
       </c>
       <c r="H601" t="n">
         <v>1404087</v>
@@ -17827,7 +17827,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>32.7378730773926</v>
+        <v>32.7378768920898</v>
       </c>
       <c r="H602" t="n">
         <v>881437</v>
@@ -17885,7 +17885,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G604" t="n">
-        <v>33.1338996887207</v>
+        <v>33.1338958740234</v>
       </c>
       <c r="H604" t="n">
         <v>1818450</v>
@@ -17943,7 +17943,7 @@
         <v>38.9099998474121</v>
       </c>
       <c r="G606" t="n">
-        <v>34.2427597045898</v>
+        <v>34.2427558898926</v>
       </c>
       <c r="H606" t="n">
         <v>1852426</v>
@@ -17972,7 +17972,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G607" t="n">
-        <v>34.6739883422852</v>
+        <v>34.6739845275879</v>
       </c>
       <c r="H607" t="n">
         <v>2017540</v>
@@ -18001,7 +18001,7 @@
         <v>38.8600006103516</v>
       </c>
       <c r="G608" t="n">
-        <v>34.4435348510742</v>
+        <v>34.443531036377</v>
       </c>
       <c r="H608" t="n">
         <v>1119804</v>
@@ -18088,7 +18088,7 @@
         <v>37.8300018310547</v>
       </c>
       <c r="G611" t="n">
-        <v>33.5305938720703</v>
+        <v>33.5305976867676</v>
       </c>
       <c r="H611" t="n">
         <v>1649342</v>
@@ -18117,7 +18117,7 @@
         <v>39.2599983215332</v>
       </c>
       <c r="G612" t="n">
-        <v>34.7980690002441</v>
+        <v>34.7980651855469</v>
       </c>
       <c r="H612" t="n">
         <v>2416786</v>
@@ -18146,7 +18146,7 @@
         <v>39.4799995422363</v>
       </c>
       <c r="G613" t="n">
-        <v>34.9930648803711</v>
+        <v>34.9930686950684</v>
       </c>
       <c r="H613" t="n">
         <v>1676560</v>
@@ -18204,7 +18204,7 @@
         <v>38.5499992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>34.1687622070312</v>
+        <v>34.1687660217285</v>
       </c>
       <c r="H615" t="n">
         <v>2341279</v>
@@ -18233,7 +18233,7 @@
         <v>39.2700004577637</v>
       </c>
       <c r="G616" t="n">
-        <v>34.8069343566895</v>
+        <v>34.8069381713867</v>
       </c>
       <c r="H616" t="n">
         <v>18139790</v>
@@ -18262,7 +18262,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G617" t="n">
-        <v>34.8335227966309</v>
+        <v>34.8335266113281</v>
       </c>
       <c r="H617" t="n">
         <v>1879244</v>
@@ -18407,7 +18407,7 @@
         <v>39.75</v>
       </c>
       <c r="G622" t="n">
-        <v>35.2323875427246</v>
+        <v>35.2323837280273</v>
       </c>
       <c r="H622" t="n">
         <v>1264800</v>
@@ -18436,7 +18436,7 @@
         <v>40.8699989318848</v>
       </c>
       <c r="G623" t="n">
-        <v>36.2250938415527</v>
+        <v>36.2250900268555</v>
       </c>
       <c r="H623" t="n">
         <v>879167</v>
@@ -18494,7 +18494,7 @@
         <v>41.560001373291</v>
       </c>
       <c r="G625" t="n">
-        <v>36.8366775512695</v>
+        <v>36.8366737365723</v>
       </c>
       <c r="H625" t="n">
         <v>920031</v>
@@ -18523,7 +18523,7 @@
         <v>42.1800003051758</v>
       </c>
       <c r="G626" t="n">
-        <v>37.3862075805664</v>
+        <v>37.3862113952637</v>
       </c>
       <c r="H626" t="n">
         <v>1460626</v>
@@ -18581,7 +18581,7 @@
         <v>41.4700012207031</v>
       </c>
       <c r="G628" t="n">
-        <v>36.7569046020508</v>
+        <v>36.756908416748</v>
       </c>
       <c r="H628" t="n">
         <v>821599</v>
@@ -18610,7 +18610,7 @@
         <v>40.189998626709</v>
       </c>
       <c r="G629" t="n">
-        <v>35.6223793029785</v>
+        <v>35.6223754882812</v>
       </c>
       <c r="H629" t="n">
         <v>1546782</v>
@@ -18668,7 +18668,7 @@
         <v>39.7799987792969</v>
       </c>
       <c r="G631" t="n">
-        <v>35.258975982666</v>
+        <v>35.2589721679688</v>
       </c>
       <c r="H631" t="n">
         <v>993775</v>
@@ -18697,7 +18697,7 @@
         <v>39.5699996948242</v>
       </c>
       <c r="G632" t="n">
-        <v>35.0728378295898</v>
+        <v>35.0728416442871</v>
       </c>
       <c r="H632" t="n">
         <v>629661</v>
@@ -18726,7 +18726,7 @@
         <v>38.8300018310547</v>
       </c>
       <c r="G633" t="n">
-        <v>34.4169464111328</v>
+        <v>34.4169425964355</v>
       </c>
       <c r="H633" t="n">
         <v>912183</v>
@@ -18755,7 +18755,7 @@
         <v>38.810001373291</v>
       </c>
       <c r="G634" t="n">
-        <v>34.3992156982422</v>
+        <v>34.3992195129395</v>
       </c>
       <c r="H634" t="n">
         <v>1259802</v>
@@ -18784,7 +18784,7 @@
         <v>38.939998626709</v>
       </c>
       <c r="G635" t="n">
-        <v>34.5144424438477</v>
+        <v>34.5144348144531</v>
       </c>
       <c r="H635" t="n">
         <v>1183997</v>
@@ -18842,7 +18842,7 @@
         <v>39</v>
       </c>
       <c r="G637" t="n">
-        <v>34.5676193237305</v>
+        <v>34.5676231384277</v>
       </c>
       <c r="H637" t="n">
         <v>854719</v>
@@ -18871,7 +18871,7 @@
         <v>38.7599983215332</v>
       </c>
       <c r="G638" t="n">
-        <v>34.3548965454102</v>
+        <v>34.3548927307129</v>
       </c>
       <c r="H638" t="n">
         <v>1297277</v>
@@ -18900,7 +18900,7 @@
         <v>39.2700004577637</v>
       </c>
       <c r="G639" t="n">
-        <v>34.8069343566895</v>
+        <v>34.8069381713867</v>
       </c>
       <c r="H639" t="n">
         <v>875723</v>
@@ -19016,7 +19016,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G643" t="n">
-        <v>33.3267364501953</v>
+        <v>33.326732635498</v>
       </c>
       <c r="H643" t="n">
         <v>960730</v>
@@ -19045,7 +19045,7 @@
         <v>38.439998626709</v>
       </c>
       <c r="G644" t="n">
-        <v>34.0712661743164</v>
+        <v>34.0712623596191</v>
       </c>
       <c r="H644" t="n">
         <v>929686</v>
@@ -19074,7 +19074,7 @@
         <v>37.4799995422363</v>
       </c>
       <c r="G645" t="n">
-        <v>33.2203712463379</v>
+        <v>33.2203750610352</v>
       </c>
       <c r="H645" t="n">
         <v>828797</v>
@@ -19103,7 +19103,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>33.8585472106934</v>
+        <v>33.8585433959961</v>
       </c>
       <c r="H646" t="n">
         <v>669484</v>
@@ -19132,7 +19132,7 @@
         <v>39.0299987792969</v>
       </c>
       <c r="G647" t="n">
-        <v>34.5942077636719</v>
+        <v>34.5942115783691</v>
       </c>
       <c r="H647" t="n">
         <v>822041</v>
@@ -19161,7 +19161,7 @@
         <v>38.5099983215332</v>
       </c>
       <c r="G648" t="n">
-        <v>34.1333084106445</v>
+        <v>34.1333122253418</v>
       </c>
       <c r="H648" t="n">
         <v>539255</v>
@@ -19219,7 +19219,7 @@
         <v>39</v>
       </c>
       <c r="G650" t="n">
-        <v>34.5676193237305</v>
+        <v>34.5676231384277</v>
       </c>
       <c r="H650" t="n">
         <v>662049</v>
@@ -19248,7 +19248,7 @@
         <v>38.8899993896484</v>
       </c>
       <c r="G651" t="n">
-        <v>34.4701232910156</v>
+        <v>34.4701271057129</v>
       </c>
       <c r="H651" t="n">
         <v>570119</v>
@@ -19277,7 +19277,7 @@
         <v>38.8899993896484</v>
       </c>
       <c r="G652" t="n">
-        <v>34.4701232910156</v>
+        <v>34.4701271057129</v>
       </c>
       <c r="H652" t="n">
         <v>626702</v>
@@ -19335,7 +19335,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G654" t="n">
-        <v>34.2485389709473</v>
+        <v>34.24853515625</v>
       </c>
       <c r="H654" t="n">
         <v>721570</v>
@@ -19393,7 +19393,7 @@
         <v>38.25</v>
       </c>
       <c r="G656" t="n">
-        <v>33.9028663635254</v>
+        <v>33.9028625488281</v>
       </c>
       <c r="H656" t="n">
         <v>3921763</v>
@@ -19480,7 +19480,7 @@
         <v>37.7200012207031</v>
       </c>
       <c r="G659" t="n">
-        <v>33.4331016540527</v>
+        <v>33.4330978393555</v>
       </c>
       <c r="H659" t="n">
         <v>880738</v>
@@ -19596,7 +19596,7 @@
         <v>37.5699996948242</v>
       </c>
       <c r="G663" t="n">
-        <v>33.3001441955566</v>
+        <v>33.3001403808594</v>
       </c>
       <c r="H663" t="n">
         <v>655079</v>
@@ -19625,7 +19625,7 @@
         <v>38.5499992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>34.1687622070312</v>
+        <v>34.1687660217285</v>
       </c>
       <c r="H664" t="n">
         <v>851691</v>
@@ -19654,7 +19654,7 @@
         <v>37.689998626709</v>
       </c>
       <c r="G665" t="n">
-        <v>33.4065093994141</v>
+        <v>33.4065055847168</v>
       </c>
       <c r="H665" t="n">
         <v>599833</v>
@@ -19915,7 +19915,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G674" t="n">
-        <v>33.8142280578613</v>
+        <v>33.8142242431641</v>
       </c>
       <c r="H674" t="n">
         <v>498965</v>
@@ -19973,7 +19973,7 @@
         <v>39.0099983215332</v>
       </c>
       <c r="G676" t="n">
-        <v>34.5764808654785</v>
+        <v>34.5764846801758</v>
       </c>
       <c r="H676" t="n">
         <v>720063</v>
@@ -20002,7 +20002,7 @@
         <v>39.7099990844727</v>
       </c>
       <c r="G677" t="n">
-        <v>35.1969299316406</v>
+        <v>35.1969375610352</v>
       </c>
       <c r="H677" t="n">
         <v>498198</v>
@@ -20060,7 +20060,7 @@
         <v>39.8199996948242</v>
       </c>
       <c r="G679" t="n">
-        <v>35.2944259643555</v>
+        <v>35.29443359375</v>
       </c>
       <c r="H679" t="n">
         <v>437405</v>
@@ -20089,7 +20089,7 @@
         <v>39.7799987792969</v>
       </c>
       <c r="G680" t="n">
-        <v>35.258975982666</v>
+        <v>35.2589721679688</v>
       </c>
       <c r="H680" t="n">
         <v>555816</v>
@@ -20118,7 +20118,7 @@
         <v>38.9599990844727</v>
       </c>
       <c r="G681" t="n">
-        <v>34.5321655273438</v>
+        <v>34.532169342041</v>
       </c>
       <c r="H681" t="n">
         <v>887023</v>
@@ -20321,7 +20321,7 @@
         <v>37.6100006103516</v>
       </c>
       <c r="G688" t="n">
-        <v>33.3356018066406</v>
+        <v>33.3355979919434</v>
       </c>
       <c r="H688" t="n">
         <v>775565</v>
@@ -20379,7 +20379,7 @@
         <v>37.2599983215332</v>
       </c>
       <c r="G690" t="n">
-        <v>33.0253715515137</v>
+        <v>33.0253753662109</v>
       </c>
       <c r="H690" t="n">
         <v>749361</v>
@@ -20437,7 +20437,7 @@
         <v>37.7400016784668</v>
       </c>
       <c r="G692" t="n">
-        <v>33.4508247375488</v>
+        <v>33.4508171081543</v>
       </c>
       <c r="H692" t="n">
         <v>1047439</v>
@@ -20611,7 +20611,7 @@
         <v>37.8300018310547</v>
       </c>
       <c r="G698" t="n">
-        <v>33.5305938720703</v>
+        <v>33.5305976867676</v>
       </c>
       <c r="H698" t="n">
         <v>655566</v>
@@ -20669,7 +20669,7 @@
         <v>38.0099983215332</v>
       </c>
       <c r="G700" t="n">
-        <v>33.6901359558105</v>
+        <v>33.6901321411133</v>
       </c>
       <c r="H700" t="n">
         <v>534553</v>
@@ -20930,7 +20930,7 @@
         <v>31.7299995422363</v>
       </c>
       <c r="G709" t="n">
-        <v>28.1238632202148</v>
+        <v>28.1238613128662</v>
       </c>
       <c r="H709" t="n">
         <v>3800188</v>
@@ -20988,7 +20988,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G711" t="n">
-        <v>27.4059200286865</v>
+        <v>27.4059219360352</v>
       </c>
       <c r="H711" t="n">
         <v>1484801</v>
@@ -21017,7 +21017,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G712" t="n">
-        <v>26.8741130828857</v>
+        <v>26.8741111755371</v>
       </c>
       <c r="H712" t="n">
         <v>1948918</v>
@@ -21075,7 +21075,7 @@
         <v>31.1399993896484</v>
       </c>
       <c r="G714" t="n">
-        <v>27.6009178161621</v>
+        <v>27.6009159088135</v>
       </c>
       <c r="H714" t="n">
         <v>2190535</v>
@@ -21220,7 +21220,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G719" t="n">
-        <v>26.5018424987793</v>
+        <v>26.5018444061279</v>
       </c>
       <c r="H719" t="n">
         <v>2071083</v>
@@ -21249,7 +21249,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>27.1222877502441</v>
+        <v>27.1222858428955</v>
       </c>
       <c r="H720" t="n">
         <v>3234856</v>
@@ -21365,7 +21365,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>27.2109241485596</v>
+        <v>27.2109260559082</v>
       </c>
       <c r="H724" t="n">
         <v>1719539</v>
@@ -21481,7 +21481,7 @@
         <v>31.7700004577637</v>
       </c>
       <c r="G728" t="n">
-        <v>28.1593170166016</v>
+        <v>28.1593151092529</v>
       </c>
       <c r="H728" t="n">
         <v>924294</v>
@@ -21539,7 +21539,7 @@
         <v>31.4599990844727</v>
       </c>
       <c r="G730" t="n">
-        <v>27.8845500946045</v>
+        <v>27.8845481872559</v>
       </c>
       <c r="H730" t="n">
         <v>820783</v>
@@ -21568,7 +21568,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G731" t="n">
-        <v>26.8741130828857</v>
+        <v>26.8741111755371</v>
       </c>
       <c r="H731" t="n">
         <v>1286620</v>
@@ -21655,7 +21655,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G734" t="n">
-        <v>28.221363067627</v>
+        <v>28.2213611602783</v>
       </c>
       <c r="H734" t="n">
         <v>1625490</v>
@@ -21800,7 +21800,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G739" t="n">
-        <v>26.0941219329834</v>
+        <v>26.094123840332</v>
       </c>
       <c r="H739" t="n">
         <v>977330</v>
@@ -21829,7 +21829,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G740" t="n">
-        <v>26.0586700439453</v>
+        <v>26.0586681365967</v>
       </c>
       <c r="H740" t="n">
         <v>682615</v>
@@ -21916,7 +21916,7 @@
         <v>29.8299999237061</v>
       </c>
       <c r="G743" t="n">
-        <v>26.4398002624512</v>
+        <v>26.4397983551025</v>
       </c>
       <c r="H743" t="n">
         <v>1169165</v>
@@ -22003,7 +22003,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G746" t="n">
-        <v>25.5091342926025</v>
+        <v>25.5091323852539</v>
       </c>
       <c r="H746" t="n">
         <v>2134397</v>
@@ -22061,7 +22061,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>26.0143508911133</v>
+        <v>26.0143527984619</v>
       </c>
       <c r="H748" t="n">
         <v>1130216</v>
@@ -22119,7 +22119,7 @@
         <v>29.0699996948242</v>
       </c>
       <c r="G750" t="n">
-        <v>25.7661743164062</v>
+        <v>25.7661724090576</v>
       </c>
       <c r="H750" t="n">
         <v>1146861</v>
@@ -22148,7 +22148,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G751" t="n">
-        <v>26.1029872894287</v>
+        <v>26.1029891967773</v>
       </c>
       <c r="H751" t="n">
         <v>881315</v>
@@ -22177,7 +22177,7 @@
         <v>27.9400005340576</v>
       </c>
       <c r="G752" t="n">
-        <v>24.7645988464355</v>
+        <v>24.7645969390869</v>
       </c>
       <c r="H752" t="n">
         <v>1188153</v>
@@ -22235,7 +22235,7 @@
         <v>28.4599990844727</v>
       </c>
       <c r="G754" t="n">
-        <v>25.2255001068115</v>
+        <v>25.2255020141602</v>
       </c>
       <c r="H754" t="n">
         <v>881877</v>
@@ -22264,7 +22264,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G755" t="n">
-        <v>24.9418697357178</v>
+        <v>24.9418716430664</v>
       </c>
       <c r="H755" t="n">
         <v>1014117</v>
@@ -22351,7 +22351,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G758" t="n">
-        <v>24.4632396697998</v>
+        <v>24.4632377624512</v>
       </c>
       <c r="H758" t="n">
         <v>1620255</v>
@@ -22380,7 +22380,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G759" t="n">
-        <v>24.9773235321045</v>
+        <v>24.9773254394531</v>
       </c>
       <c r="H759" t="n">
         <v>1167669</v>
@@ -22467,7 +22467,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G762" t="n">
-        <v>24.8620986938477</v>
+        <v>24.862096786499</v>
       </c>
       <c r="H762" t="n">
         <v>1125794</v>
@@ -22496,7 +22496,7 @@
         <v>28.9300003051758</v>
       </c>
       <c r="G763" t="n">
-        <v>25.6420841217041</v>
+        <v>25.6420860290527</v>
       </c>
       <c r="H763" t="n">
         <v>922395</v>
@@ -22525,7 +22525,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G764" t="n">
-        <v>25.8459434509277</v>
+        <v>25.8459453582764</v>
       </c>
       <c r="H764" t="n">
         <v>767016</v>
@@ -22583,7 +22583,7 @@
         <v>29.0200004577637</v>
       </c>
       <c r="G766" t="n">
-        <v>25.7218570709229</v>
+        <v>25.7218589782715</v>
       </c>
       <c r="H766" t="n">
         <v>1425551</v>
@@ -22699,7 +22699,7 @@
         <v>30.8600006103516</v>
       </c>
       <c r="G770" t="n">
-        <v>27.3527412414551</v>
+        <v>27.3527393341064</v>
       </c>
       <c r="H770" t="n">
         <v>1430045</v>
@@ -22757,7 +22757,7 @@
         <v>29.6700000762939</v>
       </c>
       <c r="G772" t="n">
-        <v>26.2979850769043</v>
+        <v>26.2979831695557</v>
       </c>
       <c r="H772" t="n">
         <v>1076322</v>
@@ -22815,7 +22815,7 @@
         <v>29.9699993133545</v>
       </c>
       <c r="G774" t="n">
-        <v>26.5638885498047</v>
+        <v>26.5638866424561</v>
       </c>
       <c r="H774" t="n">
         <v>991815</v>
@@ -22989,7 +22989,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>27.1222877502441</v>
+        <v>27.1222858428955</v>
       </c>
       <c r="H780" t="n">
         <v>1098776</v>
@@ -23134,7 +23134,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G785" t="n">
-        <v>29.1608963012695</v>
+        <v>29.1608924865723</v>
       </c>
       <c r="H785" t="n">
         <v>1615118</v>
@@ -23163,7 +23163,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G786" t="n">
-        <v>29.7370166778564</v>
+        <v>29.7370204925537</v>
       </c>
       <c r="H786" t="n">
         <v>1741406</v>
@@ -23192,7 +23192,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>29.7370166778564</v>
+        <v>29.7370204925537</v>
       </c>
       <c r="H787" t="n">
         <v>1067159</v>
@@ -23250,7 +23250,7 @@
         <v>34.2099990844727</v>
       </c>
       <c r="G789" t="n">
-        <v>30.3220100402832</v>
+        <v>30.3220081329346</v>
       </c>
       <c r="H789" t="n">
         <v>1701124</v>
@@ -23308,7 +23308,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G791" t="n">
-        <v>29.7813339233398</v>
+        <v>29.7813377380371</v>
       </c>
       <c r="H791" t="n">
         <v>926123</v>
@@ -23337,7 +23337,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G792" t="n">
-        <v>30.0649681091309</v>
+        <v>30.0649662017822</v>
       </c>
       <c r="H792" t="n">
         <v>850712</v>
@@ -23366,7 +23366,7 @@
         <v>34.7599983215332</v>
       </c>
       <c r="G793" t="n">
-        <v>30.809497833252</v>
+        <v>30.8094997406006</v>
       </c>
       <c r="H793" t="n">
         <v>1670028</v>
@@ -23395,7 +23395,7 @@
         <v>34.9900016784668</v>
       </c>
       <c r="G794" t="n">
-        <v>31.0133647918701</v>
+        <v>31.0133686065674</v>
       </c>
       <c r="H794" t="n">
         <v>1207749</v>
@@ -23424,7 +23424,7 @@
         <v>34.6500015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>30.7120018005371</v>
+        <v>30.7120056152344</v>
       </c>
       <c r="H795" t="n">
         <v>1435515</v>
@@ -23453,7 +23453,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G796" t="n">
-        <v>30.4460983276367</v>
+        <v>30.4460964202881</v>
       </c>
       <c r="H796" t="n">
         <v>1441009</v>
@@ -23482,7 +23482,7 @@
         <v>34.8800010681152</v>
       </c>
       <c r="G797" t="n">
-        <v>30.915864944458</v>
+        <v>30.9158630371094</v>
       </c>
       <c r="H797" t="n">
         <v>659300</v>
@@ -23540,7 +23540,7 @@
         <v>34.7099990844727</v>
       </c>
       <c r="G799" t="n">
-        <v>30.7651863098145</v>
+        <v>30.7651824951172</v>
       </c>
       <c r="H799" t="n">
         <v>823941</v>
@@ -23569,7 +23569,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G800" t="n">
-        <v>30.7563247680664</v>
+        <v>30.7563209533691</v>
       </c>
       <c r="H800" t="n">
         <v>1405682</v>
@@ -23598,7 +23598,7 @@
         <v>34.5099983215332</v>
       </c>
       <c r="G801" t="n">
-        <v>30.5879135131836</v>
+        <v>30.587911605835</v>
       </c>
       <c r="H801" t="n">
         <v>920024</v>
@@ -23627,7 +23627,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G802" t="n">
-        <v>31.0665416717529</v>
+        <v>31.0665454864502</v>
       </c>
       <c r="H802" t="n">
         <v>962131</v>
@@ -23685,7 +23685,7 @@
         <v>34.2099990844727</v>
       </c>
       <c r="G804" t="n">
-        <v>30.3220100402832</v>
+        <v>30.3220081329346</v>
       </c>
       <c r="H804" t="n">
         <v>1006399</v>
@@ -23743,7 +23743,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G806" t="n">
-        <v>33.1937866210938</v>
+        <v>33.1937828063965</v>
       </c>
       <c r="H806" t="n">
         <v>5810745</v>
@@ -23772,7 +23772,7 @@
         <v>37.0499992370605</v>
       </c>
       <c r="G807" t="n">
-        <v>32.8392448425293</v>
+        <v>32.839241027832</v>
       </c>
       <c r="H807" t="n">
         <v>1765923</v>
@@ -23801,7 +23801,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G808" t="n">
-        <v>31.9972076416016</v>
+        <v>31.9972057342529</v>
       </c>
       <c r="H808" t="n">
         <v>1604293</v>
@@ -23830,7 +23830,7 @@
         <v>36</v>
       </c>
       <c r="G809" t="n">
-        <v>31.9085712432861</v>
+        <v>31.9085750579834</v>
       </c>
       <c r="H809" t="n">
         <v>1045374</v>
@@ -23859,7 +23859,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G810" t="n">
-        <v>31.7756214141846</v>
+        <v>31.7756175994873</v>
       </c>
       <c r="H810" t="n">
         <v>1116850</v>
@@ -23888,7 +23888,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>31.5983581542969</v>
+        <v>31.5983543395996</v>
       </c>
       <c r="H811" t="n">
         <v>809991</v>
@@ -23946,7 +23946,7 @@
         <v>35.560001373291</v>
       </c>
       <c r="G813" t="n">
-        <v>31.5185775756836</v>
+        <v>31.5185852050781</v>
       </c>
       <c r="H813" t="n">
         <v>434769</v>
@@ -24004,7 +24004,7 @@
         <v>36.189998626709</v>
       </c>
       <c r="G815" t="n">
-        <v>32.076976776123</v>
+        <v>32.0769805908203</v>
       </c>
       <c r="H815" t="n">
         <v>969213</v>
@@ -24091,7 +24091,7 @@
         <v>37.0499992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>32.8392448425293</v>
+        <v>32.839241027832</v>
       </c>
       <c r="H818" t="n">
         <v>661527</v>
@@ -24120,7 +24120,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G819" t="n">
-        <v>32.263111114502</v>
+        <v>32.2631072998047</v>
       </c>
       <c r="H819" t="n">
         <v>2337735</v>
@@ -24149,7 +24149,7 @@
         <v>36</v>
       </c>
       <c r="G820" t="n">
-        <v>31.9085712432861</v>
+        <v>31.9085750579834</v>
       </c>
       <c r="H820" t="n">
         <v>1016518</v>
@@ -24178,7 +24178,7 @@
         <v>35.3400001525879</v>
       </c>
       <c r="G821" t="n">
-        <v>31.3235855102539</v>
+        <v>31.3235816955566</v>
       </c>
       <c r="H821" t="n">
         <v>1262625</v>
@@ -24207,7 +24207,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G822" t="n">
-        <v>30.8449535369873</v>
+        <v>30.8449554443359</v>
       </c>
       <c r="H822" t="n">
         <v>1377576</v>
@@ -24236,7 +24236,7 @@
         <v>35.5699996948242</v>
       </c>
       <c r="G823" t="n">
-        <v>31.5274410247803</v>
+        <v>31.5274448394775</v>
       </c>
       <c r="H823" t="n">
         <v>1008251</v>
@@ -24265,7 +24265,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G824" t="n">
-        <v>31.5983581542969</v>
+        <v>31.5983543395996</v>
       </c>
       <c r="H824" t="n">
         <v>896495</v>
@@ -24294,7 +24294,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G825" t="n">
-        <v>31.5983581542969</v>
+        <v>31.5983543395996</v>
       </c>
       <c r="H825" t="n">
         <v>699585</v>
@@ -24323,7 +24323,7 @@
         <v>35.9199981689453</v>
       </c>
       <c r="G826" t="n">
-        <v>31.8376693725586</v>
+        <v>31.8376655578613</v>
       </c>
       <c r="H826" t="n">
         <v>884296</v>
@@ -24352,7 +24352,7 @@
         <v>36.7400016784668</v>
       </c>
       <c r="G827" t="n">
-        <v>32.5644760131836</v>
+        <v>32.5644721984863</v>
       </c>
       <c r="H827" t="n">
         <v>1157500</v>
@@ -24410,7 +24410,7 @@
         <v>37.4199981689453</v>
       </c>
       <c r="G829" t="n">
-        <v>33.1671905517578</v>
+        <v>33.1671867370605</v>
       </c>
       <c r="H829" t="n">
         <v>1468450</v>
@@ -24439,7 +24439,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G830" t="n">
-        <v>32.9721946716309</v>
+        <v>32.9721984863281</v>
       </c>
       <c r="H830" t="n">
         <v>781643</v>
@@ -24468,7 +24468,7 @@
         <v>37.1300010681152</v>
       </c>
       <c r="G831" t="n">
-        <v>32.9101524353027</v>
+        <v>32.9101486206055</v>
       </c>
       <c r="H831" t="n">
         <v>854359</v>
@@ -24526,7 +24526,7 @@
         <v>35.9799995422363</v>
       </c>
       <c r="G833" t="n">
-        <v>31.8908386230469</v>
+        <v>31.8908424377441</v>
       </c>
       <c r="H833" t="n">
         <v>924927</v>
@@ -24584,7 +24584,7 @@
         <v>36.4199981689453</v>
       </c>
       <c r="G835" t="n">
-        <v>32.2808380126953</v>
+        <v>32.2808418273926</v>
       </c>
       <c r="H835" t="n">
         <v>1102237</v>
@@ -24613,7 +24613,7 @@
         <v>36.5</v>
       </c>
       <c r="G836" t="n">
-        <v>32.3517532348633</v>
+        <v>32.351749420166</v>
       </c>
       <c r="H836" t="n">
         <v>603024</v>
@@ -24642,7 +24642,7 @@
         <v>36.2900009155273</v>
       </c>
       <c r="G837" t="n">
-        <v>32.1656150817871</v>
+        <v>32.1656112670898</v>
       </c>
       <c r="H837" t="n">
         <v>693862</v>
@@ -24671,7 +24671,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G838" t="n">
-        <v>32.4847030639648</v>
+        <v>32.4846992492676</v>
       </c>
       <c r="H838" t="n">
         <v>764909</v>
@@ -24816,7 +24816,7 @@
         <v>36.9300003051758</v>
       </c>
       <c r="G843" t="n">
-        <v>32.7328796386719</v>
+        <v>32.7328834533691</v>
       </c>
       <c r="H843" t="n">
         <v>420685</v>
@@ -24845,7 +24845,7 @@
         <v>36.25</v>
       </c>
       <c r="G844" t="n">
-        <v>32.1301574707031</v>
+        <v>32.1301612854004</v>
       </c>
       <c r="H844" t="n">
         <v>666434</v>
@@ -24903,7 +24903,7 @@
         <v>36.5699996948242</v>
       </c>
       <c r="G846" t="n">
-        <v>32.4137916564941</v>
+        <v>32.4137954711914</v>
       </c>
       <c r="H846" t="n">
         <v>597301</v>
@@ -24961,7 +24961,7 @@
         <v>37.189998626709</v>
       </c>
       <c r="G848" t="n">
-        <v>32.9633293151855</v>
+        <v>32.9633255004883</v>
       </c>
       <c r="H848" t="n">
         <v>662987</v>
@@ -24990,7 +24990,7 @@
         <v>36.3600006103516</v>
       </c>
       <c r="G849" t="n">
-        <v>32.2276649475098</v>
+        <v>32.2276611328125</v>
       </c>
       <c r="H849" t="n">
         <v>560045</v>
@@ -25019,7 +25019,7 @@
         <v>35.5699996948242</v>
       </c>
       <c r="G850" t="n">
-        <v>31.5274410247803</v>
+        <v>31.5274448394775</v>
       </c>
       <c r="H850" t="n">
         <v>985193</v>
@@ -25077,7 +25077,7 @@
         <v>35.5299987792969</v>
       </c>
       <c r="G852" t="n">
-        <v>31.4919891357422</v>
+        <v>31.4919853210449</v>
       </c>
       <c r="H852" t="n">
         <v>1325314</v>
@@ -25164,7 +25164,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G855" t="n">
-        <v>31.5983581542969</v>
+        <v>31.5983543395996</v>
       </c>
       <c r="H855" t="n">
         <v>833148</v>
@@ -25193,7 +25193,7 @@
         <v>35.8400001525879</v>
       </c>
       <c r="G856" t="n">
-        <v>31.7667579650879</v>
+        <v>31.7667617797852</v>
       </c>
       <c r="H856" t="n">
         <v>937200</v>
@@ -25222,7 +25222,7 @@
         <v>35.2299995422363</v>
       </c>
       <c r="G857" t="n">
-        <v>31.2260894775391</v>
+        <v>31.2260856628418</v>
       </c>
       <c r="H857" t="n">
         <v>1038179</v>
@@ -25309,7 +25309,7 @@
         <v>34.5699996948242</v>
       </c>
       <c r="G860" t="n">
-        <v>30.9883041381836</v>
+        <v>30.988302230835</v>
       </c>
       <c r="H860" t="n">
         <v>723455</v>
@@ -25367,7 +25367,7 @@
         <v>34.5400009155273</v>
       </c>
       <c r="G862" t="n">
-        <v>30.9614124298096</v>
+        <v>30.9614105224609</v>
       </c>
       <c r="H862" t="n">
         <v>797919</v>
@@ -25425,7 +25425,7 @@
         <v>35</v>
       </c>
       <c r="G864" t="n">
-        <v>31.3737545013428</v>
+        <v>31.3737506866455</v>
       </c>
       <c r="H864" t="n">
         <v>317879</v>
@@ -25454,7 +25454,7 @@
         <v>34.4599990844727</v>
       </c>
       <c r="G865" t="n">
-        <v>30.8896999359131</v>
+        <v>30.8896961212158</v>
       </c>
       <c r="H865" t="n">
         <v>939244</v>
@@ -25541,7 +25541,7 @@
         <v>33</v>
       </c>
       <c r="G868" t="n">
-        <v>29.5809650421143</v>
+        <v>29.5809669494629</v>
       </c>
       <c r="H868" t="n">
         <v>848788</v>
@@ -25599,7 +25599,7 @@
         <v>33.7400016784668</v>
       </c>
       <c r="G870" t="n">
-        <v>30.2442970275879</v>
+        <v>30.2443008422852</v>
       </c>
       <c r="H870" t="n">
         <v>1312714</v>
@@ -25628,7 +25628,7 @@
         <v>34.5</v>
       </c>
       <c r="G871" t="n">
-        <v>30.9255561828613</v>
+        <v>30.9255523681641</v>
       </c>
       <c r="H871" t="n">
         <v>939585</v>
@@ -25657,7 +25657,7 @@
         <v>34.5</v>
       </c>
       <c r="G872" t="n">
-        <v>30.9255561828613</v>
+        <v>30.9255523681641</v>
       </c>
       <c r="H872" t="n">
         <v>651824</v>
@@ -25686,7 +25686,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G873" t="n">
-        <v>31.1048374176025</v>
+        <v>31.1048336029053</v>
       </c>
       <c r="H873" t="n">
         <v>701678</v>
@@ -25715,7 +25715,7 @@
         <v>34.3300018310547</v>
       </c>
       <c r="G874" t="n">
-        <v>30.7731685638428</v>
+        <v>30.7731666564941</v>
       </c>
       <c r="H874" t="n">
         <v>432588</v>
@@ -25744,7 +25744,7 @@
         <v>34.8199996948242</v>
       </c>
       <c r="G875" t="n">
-        <v>31.2123985290527</v>
+        <v>31.2124004364014</v>
       </c>
       <c r="H875" t="n">
         <v>974474</v>
@@ -25773,7 +25773,7 @@
         <v>34.4099998474121</v>
       </c>
       <c r="G876" t="n">
-        <v>30.8448791503906</v>
+        <v>30.844877243042</v>
       </c>
       <c r="H876" t="n">
         <v>644732</v>
@@ -25802,7 +25802,7 @@
         <v>34.4900016784668</v>
       </c>
       <c r="G877" t="n">
-        <v>30.9165916442871</v>
+        <v>30.9165897369385</v>
       </c>
       <c r="H877" t="n">
         <v>661919</v>
@@ -25831,7 +25831,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>31.4185695648193</v>
+        <v>31.4185733795166</v>
       </c>
       <c r="H878" t="n">
         <v>548985</v>
@@ -25860,7 +25860,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G879" t="n">
-        <v>31.732307434082</v>
+        <v>31.7323150634766</v>
       </c>
       <c r="H879" t="n">
         <v>523035</v>
@@ -25889,7 +25889,7 @@
         <v>36.4799995422363</v>
       </c>
       <c r="G880" t="n">
-        <v>32.7004127502441</v>
+        <v>32.7004089355469</v>
       </c>
       <c r="H880" t="n">
         <v>1084955</v>
@@ -25918,7 +25918,7 @@
         <v>36.6100006103516</v>
       </c>
       <c r="G881" t="n">
-        <v>32.8169441223145</v>
+        <v>32.8169403076172</v>
       </c>
       <c r="H881" t="n">
         <v>635069</v>
@@ -25976,7 +25976,7 @@
         <v>37.4099998474121</v>
       </c>
       <c r="G883" t="n">
-        <v>33.5340576171875</v>
+        <v>33.5340614318848</v>
       </c>
       <c r="H883" t="n">
         <v>1426261</v>
@@ -26063,7 +26063,7 @@
         <v>36.3400001525879</v>
       </c>
       <c r="G886" t="n">
-        <v>32.5749206542969</v>
+        <v>32.5749168395996</v>
       </c>
       <c r="H886" t="n">
         <v>617440</v>
@@ -26121,7 +26121,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G888" t="n">
-        <v>33.7043762207031</v>
+        <v>33.7043724060059</v>
       </c>
       <c r="H888" t="n">
         <v>675996</v>
@@ -26237,7 +26237,7 @@
         <v>38.6100006103516</v>
       </c>
       <c r="G892" t="n">
-        <v>34.6097297668457</v>
+        <v>34.609733581543</v>
       </c>
       <c r="H892" t="n">
         <v>484443</v>
@@ -26266,7 +26266,7 @@
         <v>38.5099983215332</v>
       </c>
       <c r="G893" t="n">
-        <v>34.5200881958008</v>
+        <v>34.520092010498</v>
       </c>
       <c r="H893" t="n">
         <v>536386</v>
@@ -26324,7 +26324,7 @@
         <v>38.25</v>
       </c>
       <c r="G895" t="n">
-        <v>34.2870330810547</v>
+        <v>34.2870292663574</v>
       </c>
       <c r="H895" t="n">
         <v>505280</v>
@@ -26353,7 +26353,7 @@
         <v>38.3300018310547</v>
       </c>
       <c r="G896" t="n">
-        <v>34.3587455749512</v>
+        <v>34.3587379455566</v>
       </c>
       <c r="H896" t="n">
         <v>545003</v>
@@ -26411,7 +26411,7 @@
         <v>38.4799995422363</v>
       </c>
       <c r="G898" t="n">
-        <v>34.4931945800781</v>
+        <v>34.4931983947754</v>
       </c>
       <c r="H898" t="n">
         <v>479500</v>
@@ -26440,7 +26440,7 @@
         <v>37.9900016784668</v>
       </c>
       <c r="G899" t="n">
-        <v>34.0539665222168</v>
+        <v>34.0539703369141</v>
       </c>
       <c r="H899" t="n">
         <v>520720</v>
@@ -26498,7 +26498,7 @@
         <v>38.0900001525879</v>
       </c>
       <c r="G901" t="n">
-        <v>34.1436080932617</v>
+        <v>34.1436042785645</v>
       </c>
       <c r="H901" t="n">
         <v>580225</v>
@@ -26527,7 +26527,7 @@
         <v>38.189998626709</v>
       </c>
       <c r="G902" t="n">
-        <v>34.2332420349121</v>
+        <v>34.2332458496094</v>
       </c>
       <c r="H902" t="n">
         <v>495278</v>
@@ -26585,7 +26585,7 @@
         <v>38.6599998474121</v>
       </c>
       <c r="G904" t="n">
-        <v>34.6545486450195</v>
+        <v>34.6545524597168</v>
       </c>
       <c r="H904" t="n">
         <v>350895</v>
@@ -26614,7 +26614,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G905" t="n">
-        <v>34.6366233825684</v>
+        <v>34.6366195678711</v>
       </c>
       <c r="H905" t="n">
         <v>593778</v>
@@ -26672,7 +26672,7 @@
         <v>39.0200004577637</v>
       </c>
       <c r="G907" t="n">
-        <v>34.9772529602051</v>
+        <v>34.9772491455078</v>
       </c>
       <c r="H907" t="n">
         <v>2171192</v>
@@ -26730,7 +26730,7 @@
         <v>38.6100006103516</v>
       </c>
       <c r="G909" t="n">
-        <v>34.6097297668457</v>
+        <v>34.609733581543</v>
       </c>
       <c r="H909" t="n">
         <v>433378</v>
@@ -26759,7 +26759,7 @@
         <v>37.6100006103516</v>
       </c>
       <c r="G910" t="n">
-        <v>33.7133407592773</v>
+        <v>33.7133369445801</v>
       </c>
       <c r="H910" t="n">
         <v>700142</v>
@@ -26788,7 +26788,7 @@
         <v>37.1699981689453</v>
       </c>
       <c r="G911" t="n">
-        <v>33.318920135498</v>
+        <v>33.3189277648926</v>
       </c>
       <c r="H911" t="n">
         <v>773735</v>
@@ -26875,7 +26875,7 @@
         <v>34.4099998474121</v>
       </c>
       <c r="G914" t="n">
-        <v>30.8448791503906</v>
+        <v>30.844877243042</v>
       </c>
       <c r="H914" t="n">
         <v>1764920</v>
@@ -26962,7 +26962,7 @@
         <v>34.5099983215332</v>
       </c>
       <c r="G917" t="n">
-        <v>30.9345188140869</v>
+        <v>30.9345169067383</v>
       </c>
       <c r="H917" t="n">
         <v>654596</v>
@@ -26991,7 +26991,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G918" t="n">
-        <v>31.6426696777344</v>
+        <v>31.6426658630371</v>
       </c>
       <c r="H918" t="n">
         <v>1446790</v>
@@ -27078,7 +27078,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G921" t="n">
-        <v>30.6118183135986</v>
+        <v>30.6118202209473</v>
       </c>
       <c r="H921" t="n">
         <v>892985</v>
@@ -27107,7 +27107,7 @@
         <v>33.8600006103516</v>
       </c>
       <c r="G922" t="n">
-        <v>30.3518676757812</v>
+        <v>30.3518600463867</v>
       </c>
       <c r="H922" t="n">
         <v>941134</v>
@@ -27136,7 +27136,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G923" t="n">
-        <v>30.8628044128418</v>
+        <v>30.8628063201904</v>
       </c>
       <c r="H923" t="n">
         <v>572622</v>
@@ -27165,7 +27165,7 @@
         <v>34.3600006103516</v>
       </c>
       <c r="G924" t="n">
-        <v>30.8000564575195</v>
+        <v>30.8000640869141</v>
       </c>
       <c r="H924" t="n">
         <v>541714</v>
@@ -27223,7 +27223,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>31.1048374176025</v>
+        <v>31.1048336029053</v>
       </c>
       <c r="H926" t="n">
         <v>520663</v>
@@ -27252,7 +27252,7 @@
         <v>34.4199981689453</v>
       </c>
       <c r="G927" t="n">
-        <v>30.8538417816162</v>
+        <v>30.8538436889648</v>
       </c>
       <c r="H927" t="n">
         <v>554924</v>
@@ -27310,7 +27310,7 @@
         <v>34.2099990844727</v>
       </c>
       <c r="G929" t="n">
-        <v>30.6656017303467</v>
+        <v>30.665599822998</v>
       </c>
       <c r="H929" t="n">
         <v>931359</v>
@@ -27339,7 +27339,7 @@
         <v>34</v>
       </c>
       <c r="G930" t="n">
-        <v>30.4773616790771</v>
+        <v>30.4773597717285</v>
       </c>
       <c r="H930" t="n">
         <v>944307</v>
@@ -27368,7 +27368,7 @@
         <v>33.939998626709</v>
       </c>
       <c r="G931" t="n">
-        <v>30.4235725402832</v>
+        <v>30.4235706329346</v>
       </c>
       <c r="H931" t="n">
         <v>687996</v>
@@ -27397,7 +27397,7 @@
         <v>34.0900001525879</v>
       </c>
       <c r="G932" t="n">
-        <v>30.5580348968506</v>
+        <v>30.558032989502</v>
       </c>
       <c r="H932" t="n">
         <v>744539</v>
@@ -27426,7 +27426,7 @@
         <v>34.310001373291</v>
       </c>
       <c r="G933" t="n">
-        <v>30.7552394866943</v>
+        <v>30.7552433013916</v>
       </c>
       <c r="H933" t="n">
         <v>537870</v>
@@ -27455,7 +27455,7 @@
         <v>33.7400016784668</v>
       </c>
       <c r="G934" t="n">
-        <v>30.2442970275879</v>
+        <v>30.2443008422852</v>
       </c>
       <c r="H934" t="n">
         <v>608650</v>
@@ -27513,7 +27513,7 @@
         <v>35.8600006103516</v>
       </c>
       <c r="G936" t="n">
-        <v>32.1446495056152</v>
+        <v>32.1446533203125</v>
       </c>
       <c r="H936" t="n">
         <v>1146587</v>
@@ -27542,7 +27542,7 @@
         <v>35.9599990844727</v>
       </c>
       <c r="G937" t="n">
-        <v>32.2342872619629</v>
+        <v>32.2342910766602</v>
       </c>
       <c r="H937" t="n">
         <v>1052656</v>
@@ -27571,7 +27571,7 @@
         <v>35.4900016784668</v>
       </c>
       <c r="G938" t="n">
-        <v>31.8129844665527</v>
+        <v>31.81298828125</v>
       </c>
       <c r="H938" t="n">
         <v>1403485</v>
@@ -27629,7 +27629,7 @@
         <v>35.3699989318848</v>
       </c>
       <c r="G940" t="n">
-        <v>31.7054138183594</v>
+        <v>31.7054214477539</v>
       </c>
       <c r="H940" t="n">
         <v>486465</v>
@@ -27658,7 +27658,7 @@
         <v>35.3899993896484</v>
       </c>
       <c r="G941" t="n">
-        <v>31.7233467102051</v>
+        <v>31.7233428955078</v>
       </c>
       <c r="H941" t="n">
         <v>889173</v>
@@ -27716,7 +27716,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G943" t="n">
-        <v>30.7462768554688</v>
+        <v>30.7462730407715</v>
       </c>
       <c r="H943" t="n">
         <v>916782</v>
@@ -27774,7 +27774,7 @@
         <v>31.7399997711182</v>
       </c>
       <c r="G945" t="n">
-        <v>28.451509475708</v>
+        <v>28.4515113830566</v>
       </c>
       <c r="H945" t="n">
         <v>4200368</v>
@@ -27803,7 +27803,7 @@
         <v>32.4700012207031</v>
       </c>
       <c r="G946" t="n">
-        <v>29.1058788299561</v>
+        <v>29.1058807373047</v>
       </c>
       <c r="H946" t="n">
         <v>2161504</v>
@@ -27832,7 +27832,7 @@
         <v>32.6199989318848</v>
       </c>
       <c r="G947" t="n">
-        <v>29.2403373718262</v>
+        <v>29.2403354644775</v>
       </c>
       <c r="H947" t="n">
         <v>1413678</v>
@@ -27890,7 +27890,7 @@
         <v>32.2299995422363</v>
       </c>
       <c r="G949" t="n">
-        <v>28.8907413482666</v>
+        <v>28.8907451629639</v>
       </c>
       <c r="H949" t="n">
         <v>619789</v>
@@ -27919,7 +27919,7 @@
         <v>32.1399993896484</v>
       </c>
       <c r="G950" t="n">
-        <v>28.8100700378418</v>
+        <v>28.8100681304932</v>
       </c>
       <c r="H950" t="n">
         <v>758436</v>
@@ -27948,7 +27948,7 @@
         <v>32.3600006103516</v>
       </c>
       <c r="G951" t="n">
-        <v>29.0072727203369</v>
+        <v>29.0072746276855</v>
       </c>
       <c r="H951" t="n">
         <v>627632</v>
@@ -27977,7 +27977,7 @@
         <v>32.8899993896484</v>
       </c>
       <c r="G952" t="n">
-        <v>29.482364654541</v>
+        <v>29.4823627471924</v>
       </c>
       <c r="H952" t="n">
         <v>1008886</v>
@@ -28006,7 +28006,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G953" t="n">
-        <v>29.3120498657227</v>
+        <v>29.312047958374</v>
       </c>
       <c r="H953" t="n">
         <v>774471</v>
@@ -28035,7 +28035,7 @@
         <v>32.3400001525879</v>
       </c>
       <c r="G954" t="n">
-        <v>28.9893455505371</v>
+        <v>28.9893474578857</v>
       </c>
       <c r="H954" t="n">
         <v>963022</v>
@@ -28064,7 +28064,7 @@
         <v>31.5900001525879</v>
       </c>
       <c r="G955" t="n">
-        <v>28.3170509338379</v>
+        <v>28.3170528411865</v>
       </c>
       <c r="H955" t="n">
         <v>1094474</v>
@@ -28180,7 +28180,7 @@
         <v>32.5800018310547</v>
       </c>
       <c r="G959" t="n">
-        <v>29.2044830322266</v>
+        <v>29.2044849395752</v>
       </c>
       <c r="H959" t="n">
         <v>960553</v>
@@ -28209,7 +28209,7 @@
         <v>33.189998626709</v>
       </c>
       <c r="G960" t="n">
-        <v>29.7512760162354</v>
+        <v>29.7512798309326</v>
       </c>
       <c r="H960" t="n">
         <v>1071453</v>
@@ -28267,7 +28267,7 @@
         <v>34.4799995422363</v>
       </c>
       <c r="G962" t="n">
-        <v>30.9076251983643</v>
+        <v>30.9076271057129</v>
       </c>
       <c r="H962" t="n">
         <v>1438118</v>
@@ -28325,7 +28325,7 @@
         <v>34.0699996948242</v>
       </c>
       <c r="G964" t="n">
-        <v>30.5401058197021</v>
+        <v>30.5401077270508</v>
       </c>
       <c r="H964" t="n">
         <v>1036844</v>
@@ -28354,7 +28354,7 @@
         <v>33.6399993896484</v>
       </c>
       <c r="G965" t="n">
-        <v>30.1546573638916</v>
+        <v>30.154655456543</v>
       </c>
       <c r="H965" t="n">
         <v>712337</v>
@@ -28383,7 +28383,7 @@
         <v>33.310001373291</v>
       </c>
       <c r="G966" t="n">
-        <v>29.858850479126</v>
+        <v>29.8588466644287</v>
       </c>
       <c r="H966" t="n">
         <v>980773</v>
@@ -28412,7 +28412,7 @@
         <v>32.1699981689453</v>
       </c>
       <c r="G967" t="n">
-        <v>28.8369579315186</v>
+        <v>28.8369598388672</v>
       </c>
       <c r="H967" t="n">
         <v>1772518</v>
@@ -28441,7 +28441,7 @@
         <v>32.5</v>
       </c>
       <c r="G968" t="n">
-        <v>29.1327686309814</v>
+        <v>29.1327724456787</v>
       </c>
       <c r="H968" t="n">
         <v>884906</v>
@@ -28470,7 +28470,7 @@
         <v>32.2799987792969</v>
       </c>
       <c r="G969" t="n">
-        <v>28.9355640411377</v>
+        <v>28.9355621337891</v>
       </c>
       <c r="H969" t="n">
         <v>720055</v>
@@ -28499,7 +28499,7 @@
         <v>32.189998626709</v>
       </c>
       <c r="G970" t="n">
-        <v>28.854887008667</v>
+        <v>28.8548889160156</v>
       </c>
       <c r="H970" t="n">
         <v>823867</v>
@@ -28528,7 +28528,7 @@
         <v>32.4900016784668</v>
       </c>
       <c r="G971" t="n">
-        <v>29.1238098144531</v>
+        <v>29.1238059997559</v>
       </c>
       <c r="H971" t="n">
         <v>1098341</v>
@@ -28586,7 +28586,7 @@
         <v>35.5</v>
       </c>
       <c r="G973" t="n">
-        <v>31.821949005127</v>
+        <v>31.8219451904297</v>
       </c>
       <c r="H973" t="n">
         <v>1816453</v>
@@ -28644,7 +28644,7 @@
         <v>34.6800003051758</v>
       </c>
       <c r="G975" t="n">
-        <v>31.0869102478027</v>
+        <v>31.0869064331055</v>
       </c>
       <c r="H975" t="n">
         <v>945737</v>
@@ -28673,7 +28673,7 @@
         <v>34.5400009155273</v>
       </c>
       <c r="G976" t="n">
-        <v>30.9614124298096</v>
+        <v>30.9614105224609</v>
       </c>
       <c r="H976" t="n">
         <v>782683</v>
@@ -28731,7 +28731,7 @@
         <v>35.2900009155273</v>
       </c>
       <c r="G978" t="n">
-        <v>31.6337051391602</v>
+        <v>31.6337089538574</v>
       </c>
       <c r="H978" t="n">
         <v>977368</v>
@@ -28789,7 +28789,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G980" t="n">
-        <v>31.732307434082</v>
+        <v>31.7323150634766</v>
       </c>
       <c r="H980" t="n">
         <v>711442</v>
@@ -28818,7 +28818,7 @@
         <v>37.1100006103516</v>
       </c>
       <c r="G981" t="n">
-        <v>33.2651443481445</v>
+        <v>33.2651405334473</v>
       </c>
       <c r="H981" t="n">
         <v>2209113</v>
@@ -28847,7 +28847,7 @@
         <v>37.6399993896484</v>
       </c>
       <c r="G982" t="n">
-        <v>33.7402305603027</v>
+        <v>33.740234375</v>
       </c>
       <c r="H982" t="n">
         <v>3080867</v>
@@ -28876,7 +28876,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G983" t="n">
-        <v>33.345817565918</v>
+        <v>33.3458213806152</v>
       </c>
       <c r="H983" t="n">
         <v>1012398</v>
@@ -29079,7 +29079,7 @@
         <v>37.75</v>
       </c>
       <c r="G990" t="n">
-        <v>33.8388328552246</v>
+        <v>33.8388366699219</v>
       </c>
       <c r="H990" t="n">
         <v>1387769</v>
@@ -29108,7 +29108,7 @@
         <v>37.4300003051758</v>
       </c>
       <c r="G991" t="n">
-        <v>33.5519905090332</v>
+        <v>33.5519866943359</v>
       </c>
       <c r="H991" t="n">
         <v>1053129</v>
@@ -29195,7 +29195,7 @@
         <v>39.0800018310547</v>
       </c>
       <c r="G994" t="n">
-        <v>35.0310325622559</v>
+        <v>35.0310401916504</v>
       </c>
       <c r="H994" t="n">
         <v>1804382</v>
@@ -29224,7 +29224,7 @@
         <v>39.189998626709</v>
       </c>
       <c r="G995" t="n">
-        <v>35.1296348571777</v>
+        <v>35.129638671875</v>
       </c>
       <c r="H995" t="n">
         <v>1135892</v>
@@ -29311,7 +29311,7 @@
         <v>38.7900009155273</v>
       </c>
       <c r="G998" t="n">
-        <v>34.7710800170898</v>
+        <v>34.7710762023926</v>
       </c>
       <c r="H998" t="n">
         <v>1542216</v>
@@ -29340,7 +29340,7 @@
         <v>38.6800003051758</v>
       </c>
       <c r="G999" t="n">
-        <v>34.672477722168</v>
+        <v>34.6724739074707</v>
       </c>
       <c r="H999" t="n">
         <v>1289775</v>
@@ -29369,7 +29369,7 @@
         <v>38.8300018310547</v>
       </c>
       <c r="G1000" t="n">
-        <v>34.806941986084</v>
+        <v>34.8069343566895</v>
       </c>
       <c r="H1000" t="n">
         <v>954282</v>
@@ -29456,7 +29456,7 @@
         <v>41.7900009155273</v>
       </c>
       <c r="G1003" t="n">
-        <v>37.460262298584</v>
+        <v>37.4602584838867</v>
       </c>
       <c r="H1003" t="n">
         <v>1615928</v>
@@ -29514,7 +29514,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1005" t="n">
-        <v>37.0210266113281</v>
+        <v>37.0210227966309</v>
       </c>
       <c r="H1005" t="n">
         <v>2188303</v>
@@ -29630,7 +29630,7 @@
         <v>40.439998626709</v>
       </c>
       <c r="G1009" t="n">
-        <v>36.250129699707</v>
+        <v>36.2501258850098</v>
       </c>
       <c r="H1009" t="n">
         <v>1743456</v>
@@ -29688,7 +29688,7 @@
         <v>40.3199996948242</v>
       </c>
       <c r="G1011" t="n">
-        <v>36.1425590515137</v>
+        <v>36.1425628662109</v>
       </c>
       <c r="H1011" t="n">
         <v>894769</v>
@@ -29775,7 +29775,7 @@
         <v>40.6300010681152</v>
       </c>
       <c r="G1014" t="n">
-        <v>36.4204483032227</v>
+        <v>36.4204444885254</v>
       </c>
       <c r="H1014" t="n">
         <v>552800</v>
@@ -29804,7 +29804,7 @@
         <v>40.0699996948242</v>
       </c>
       <c r="G1015" t="n">
-        <v>35.9184684753418</v>
+        <v>35.9184608459473</v>
       </c>
       <c r="H1015" t="n">
         <v>736786</v>
@@ -29862,7 +29862,7 @@
         <v>40.0900001525879</v>
       </c>
       <c r="G1017" t="n">
-        <v>35.9363975524902</v>
+        <v>35.936393737793</v>
       </c>
       <c r="H1017" t="n">
         <v>616330</v>
@@ -29891,7 +29891,7 @@
         <v>40.0699996948242</v>
       </c>
       <c r="G1018" t="n">
-        <v>35.9184684753418</v>
+        <v>35.9184608459473</v>
       </c>
       <c r="H1018" t="n">
         <v>918334</v>
@@ -29920,7 +29920,7 @@
         <v>40.2700004577637</v>
       </c>
       <c r="G1019" t="n">
-        <v>36.0977401733398</v>
+        <v>36.0977439880371</v>
       </c>
       <c r="H1019" t="n">
         <v>732903</v>
@@ -30007,7 +30007,7 @@
         <v>40.7099990844727</v>
       </c>
       <c r="G1022" t="n">
-        <v>36.4921569824219</v>
+        <v>36.4921531677246</v>
       </c>
       <c r="H1022" t="n">
         <v>616889</v>
@@ -30036,7 +30036,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G1023" t="n">
-        <v>36.572826385498</v>
+        <v>36.5728302001953</v>
       </c>
       <c r="H1023" t="n">
         <v>593054</v>
@@ -30123,7 +30123,7 @@
         <v>42.6800003051758</v>
       </c>
       <c r="G1026" t="n">
-        <v>38.2580490112305</v>
+        <v>38.258056640625</v>
       </c>
       <c r="H1026" t="n">
         <v>911034</v>
@@ -30239,7 +30239,7 @@
         <v>41.4900016784668</v>
       </c>
       <c r="G1030" t="n">
-        <v>37.1913375854492</v>
+        <v>37.1913414001465</v>
       </c>
       <c r="H1030" t="n">
         <v>1079239</v>
@@ -30297,7 +30297,7 @@
         <v>40.5499992370605</v>
       </c>
       <c r="G1032" t="n">
-        <v>36.3487358093262</v>
+        <v>36.3487319946289</v>
       </c>
       <c r="H1032" t="n">
         <v>790008</v>
@@ -30326,7 +30326,7 @@
         <v>38.8600006103516</v>
       </c>
       <c r="G1033" t="n">
-        <v>34.8338279724121</v>
+        <v>34.8338241577148</v>
       </c>
       <c r="H1033" t="n">
         <v>2285540</v>
@@ -30355,7 +30355,7 @@
         <v>40.0699996948242</v>
       </c>
       <c r="G1034" t="n">
-        <v>35.9184684753418</v>
+        <v>35.9184608459473</v>
       </c>
       <c r="H1034" t="n">
         <v>1420294</v>
@@ -30384,7 +30384,7 @@
         <v>40.3699989318848</v>
       </c>
       <c r="G1035" t="n">
-        <v>36.1873817443848</v>
+        <v>36.187385559082</v>
       </c>
       <c r="H1035" t="n">
         <v>943157</v>
@@ -30413,7 +30413,7 @@
         <v>39.560001373291</v>
       </c>
       <c r="G1036" t="n">
-        <v>35.4612998962402</v>
+        <v>35.4613037109375</v>
       </c>
       <c r="H1036" t="n">
         <v>1121921</v>
@@ -30442,7 +30442,7 @@
         <v>39</v>
       </c>
       <c r="G1037" t="n">
-        <v>34.9593200683594</v>
+        <v>34.9593238830566</v>
       </c>
       <c r="H1037" t="n">
         <v>1455263</v>
@@ -30529,7 +30529,7 @@
         <v>40.4099998474121</v>
       </c>
       <c r="G1040" t="n">
-        <v>36.2232360839844</v>
+        <v>36.2232398986816</v>
       </c>
       <c r="H1040" t="n">
         <v>1074543</v>
@@ -30587,7 +30587,7 @@
         <v>38.7099990844727</v>
       </c>
       <c r="G1042" t="n">
-        <v>34.6993713378906</v>
+        <v>34.6993637084961</v>
       </c>
       <c r="H1042" t="n">
         <v>1594270</v>
@@ -30616,7 +30616,7 @@
         <v>39.7299995422363</v>
       </c>
       <c r="G1043" t="n">
-        <v>35.6136932373047</v>
+        <v>35.6136856079102</v>
       </c>
       <c r="H1043" t="n">
         <v>1401681</v>
@@ -30761,7 +30761,7 @@
         <v>38.2599983215332</v>
       </c>
       <c r="G1048" t="n">
-        <v>34.2959899902344</v>
+        <v>34.2959938049316</v>
       </c>
       <c r="H1048" t="n">
         <v>854544</v>
@@ -30790,7 +30790,7 @@
         <v>37.6399993896484</v>
       </c>
       <c r="G1049" t="n">
-        <v>33.7402305603027</v>
+        <v>33.740234375</v>
       </c>
       <c r="H1049" t="n">
         <v>1048207</v>
@@ -30819,7 +30819,7 @@
         <v>39.0400009155273</v>
       </c>
       <c r="G1050" t="n">
-        <v>34.9951782226562</v>
+        <v>34.9951820373535</v>
       </c>
       <c r="H1050" t="n">
         <v>1650260</v>
@@ -30848,7 +30848,7 @@
         <v>38.25</v>
       </c>
       <c r="G1051" t="n">
-        <v>34.2870330810547</v>
+        <v>34.2870292663574</v>
       </c>
       <c r="H1051" t="n">
         <v>1244274</v>
@@ -30877,7 +30877,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G1052" t="n">
-        <v>33.3009948730469</v>
+        <v>33.3010025024414</v>
       </c>
       <c r="H1052" t="n">
         <v>1277454</v>
@@ -30906,7 +30906,7 @@
         <v>35.1599998474121</v>
       </c>
       <c r="G1053" t="n">
-        <v>31.5171699523926</v>
+        <v>31.5171737670898</v>
       </c>
       <c r="H1053" t="n">
         <v>2416909</v>
@@ -30993,7 +30993,7 @@
         <v>35.2599983215332</v>
       </c>
       <c r="G1056" t="n">
-        <v>31.606819152832</v>
+        <v>31.6068153381348</v>
       </c>
       <c r="H1056" t="n">
         <v>1857517</v>
@@ -31022,7 +31022,7 @@
         <v>35.2200012207031</v>
       </c>
       <c r="G1057" t="n">
-        <v>31.5709609985352</v>
+        <v>31.5709571838379</v>
       </c>
       <c r="H1057" t="n">
         <v>2535243</v>
@@ -31051,7 +31051,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G1058" t="n">
-        <v>30.8628044128418</v>
+        <v>30.8628063201904</v>
       </c>
       <c r="H1058" t="n">
         <v>1881974</v>
@@ -31080,7 +31080,7 @@
         <v>34.5</v>
       </c>
       <c r="G1059" t="n">
-        <v>30.9255561828613</v>
+        <v>30.9255523681641</v>
       </c>
       <c r="H1059" t="n">
         <v>1559647</v>
@@ -31109,7 +31109,7 @@
         <v>35</v>
       </c>
       <c r="G1060" t="n">
-        <v>31.3737545013428</v>
+        <v>31.3737506866455</v>
       </c>
       <c r="H1060" t="n">
         <v>1434536</v>
@@ -31196,7 +31196,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G1063" t="n">
-        <v>27.35791015625</v>
+        <v>27.3579120635986</v>
       </c>
       <c r="H1063" t="n">
         <v>3525053</v>
@@ -31283,7 +31283,7 @@
         <v>26</v>
       </c>
       <c r="G1066" t="n">
-        <v>23.3062171936035</v>
+        <v>23.3062152862549</v>
       </c>
       <c r="H1066" t="n">
         <v>3728488</v>
@@ -31312,7 +31312,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1067" t="n">
-        <v>26.6228713989258</v>
+        <v>26.6228694915771</v>
       </c>
       <c r="H1067" t="n">
         <v>4220010</v>
@@ -31341,7 +31341,7 @@
         <v>27.3899993896484</v>
       </c>
       <c r="G1068" t="n">
-        <v>24.5522003173828</v>
+        <v>24.5521984100342</v>
       </c>
       <c r="H1068" t="n">
         <v>2828873</v>
@@ -31486,7 +31486,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>25.6368389129639</v>
+        <v>25.6368370056152</v>
       </c>
       <c r="H1073" t="n">
         <v>1307772</v>
@@ -31544,7 +31544,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1075" t="n">
-        <v>30.5670013427734</v>
+        <v>30.5669975280762</v>
       </c>
       <c r="H1075" t="n">
         <v>1666454</v>
@@ -31631,7 +31631,7 @@
         <v>34</v>
       </c>
       <c r="G1078" t="n">
-        <v>30.4773616790771</v>
+        <v>30.4773597717285</v>
       </c>
       <c r="H1078" t="n">
         <v>964218</v>
@@ -31660,7 +31660,7 @@
         <v>33.2900009155273</v>
       </c>
       <c r="G1079" t="n">
-        <v>29.8409214019775</v>
+        <v>29.8409194946289</v>
       </c>
       <c r="H1079" t="n">
         <v>1159294</v>
@@ -31689,7 +31689,7 @@
         <v>32.3899993896484</v>
       </c>
       <c r="G1080" t="n">
-        <v>29.0341644287109</v>
+        <v>29.0341663360596</v>
       </c>
       <c r="H1080" t="n">
         <v>802534</v>
@@ -31718,7 +31718,7 @@
         <v>32</v>
       </c>
       <c r="G1081" t="n">
-        <v>28.6845741271973</v>
+        <v>28.6845722198486</v>
       </c>
       <c r="H1081" t="n">
         <v>680782</v>
@@ -31747,7 +31747,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>27.8778209686279</v>
+        <v>27.8778190612793</v>
       </c>
       <c r="H1082" t="n">
         <v>752004</v>
@@ -31776,7 +31776,7 @@
         <v>33.25</v>
       </c>
       <c r="G1083" t="n">
-        <v>29.805061340332</v>
+        <v>29.8050632476807</v>
       </c>
       <c r="H1083" t="n">
         <v>814010</v>
@@ -31805,7 +31805,7 @@
         <v>33</v>
       </c>
       <c r="G1084" t="n">
-        <v>29.5809650421143</v>
+        <v>29.5809669494629</v>
       </c>
       <c r="H1084" t="n">
         <v>1199533</v>
@@ -31834,7 +31834,7 @@
         <v>32.6399993896484</v>
       </c>
       <c r="G1085" t="n">
-        <v>29.2582626342773</v>
+        <v>29.258264541626</v>
       </c>
       <c r="H1085" t="n">
         <v>638911</v>
@@ -31863,7 +31863,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G1086" t="n">
-        <v>29.4465045928955</v>
+        <v>29.4465065002441</v>
       </c>
       <c r="H1086" t="n">
         <v>604539</v>
@@ -31892,7 +31892,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1087" t="n">
-        <v>30.2084426879883</v>
+        <v>30.2084407806396</v>
       </c>
       <c r="H1087" t="n">
         <v>830697</v>
@@ -31921,7 +31921,7 @@
         <v>33.2099990844727</v>
       </c>
       <c r="G1088" t="n">
-        <v>29.7692050933838</v>
+        <v>29.7692070007324</v>
       </c>
       <c r="H1088" t="n">
         <v>1565453</v>
@@ -31950,7 +31950,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G1089" t="n">
-        <v>29.4465045928955</v>
+        <v>29.4465065002441</v>
       </c>
       <c r="H1089" t="n">
         <v>854571</v>
@@ -31979,7 +31979,7 @@
         <v>34.5200004577637</v>
       </c>
       <c r="G1090" t="n">
-        <v>30.9434852600098</v>
+        <v>30.9434833526611</v>
       </c>
       <c r="H1090" t="n">
         <v>943023</v>
@@ -32037,7 +32037,7 @@
         <v>34</v>
       </c>
       <c r="G1092" t="n">
-        <v>30.4773616790771</v>
+        <v>30.4773597717285</v>
       </c>
       <c r="H1092" t="n">
         <v>795448</v>
@@ -32095,7 +32095,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G1094" t="n">
-        <v>29.7154273986816</v>
+        <v>29.7154235839844</v>
       </c>
       <c r="H1094" t="n">
         <v>731600</v>
@@ -32124,7 +32124,7 @@
         <v>32.5800018310547</v>
       </c>
       <c r="G1095" t="n">
-        <v>29.2044830322266</v>
+        <v>29.2044849395752</v>
       </c>
       <c r="H1095" t="n">
         <v>548993</v>
@@ -32153,7 +32153,7 @@
         <v>34.1599998474121</v>
       </c>
       <c r="G1096" t="n">
-        <v>30.620777130127</v>
+        <v>30.6207809448242</v>
       </c>
       <c r="H1096" t="n">
         <v>676509</v>
@@ -32182,7 +32182,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G1097" t="n">
-        <v>30.8807353973389</v>
+        <v>30.8807373046875</v>
       </c>
       <c r="H1097" t="n">
         <v>596149</v>
@@ -32211,7 +32211,7 @@
         <v>34.6800003051758</v>
       </c>
       <c r="G1098" t="n">
-        <v>31.0869102478027</v>
+        <v>31.0869064331055</v>
       </c>
       <c r="H1098" t="n">
         <v>578868</v>
@@ -32240,7 +32240,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1099" t="n">
-        <v>30.7462768554688</v>
+        <v>30.7462730407715</v>
       </c>
       <c r="H1099" t="n">
         <v>886071</v>
@@ -32269,7 +32269,7 @@
         <v>32.8199996948242</v>
       </c>
       <c r="G1100" t="n">
-        <v>29.4196186065674</v>
+        <v>29.4196166992188</v>
       </c>
       <c r="H1100" t="n">
         <v>691332</v>
@@ -32298,7 +32298,7 @@
         <v>33.3600006103516</v>
       </c>
       <c r="G1101" t="n">
-        <v>29.9036674499512</v>
+        <v>29.9036693572998</v>
       </c>
       <c r="H1101" t="n">
         <v>328634</v>
@@ -32327,7 +32327,7 @@
         <v>32.4300003051758</v>
       </c>
       <c r="G1102" t="n">
-        <v>29.0700206756592</v>
+        <v>29.0700225830078</v>
       </c>
       <c r="H1102" t="n">
         <v>561855</v>
@@ -32356,7 +32356,7 @@
         <v>33.2900009155273</v>
       </c>
       <c r="G1103" t="n">
-        <v>29.8409214019775</v>
+        <v>29.8409194946289</v>
       </c>
       <c r="H1103" t="n">
         <v>1188345</v>
@@ -32385,7 +32385,7 @@
         <v>32.7799987792969</v>
       </c>
       <c r="G1104" t="n">
-        <v>29.3837604522705</v>
+        <v>29.3837566375732</v>
       </c>
       <c r="H1104" t="n">
         <v>516266</v>
@@ -32414,7 +32414,7 @@
         <v>32.2900009155273</v>
       </c>
       <c r="G1105" t="n">
-        <v>28.9445304870605</v>
+        <v>28.9445285797119</v>
       </c>
       <c r="H1105" t="n">
         <v>939635</v>
@@ -32559,7 +32559,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1110" t="n">
-        <v>29.3120498657227</v>
+        <v>29.312047958374</v>
       </c>
       <c r="H1110" t="n">
         <v>656885</v>
@@ -32617,7 +32617,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1112" t="n">
-        <v>29.025203704834</v>
+        <v>29.0252056121826</v>
       </c>
       <c r="H1112" t="n">
         <v>712773</v>
@@ -32704,7 +32704,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G1115" t="n">
-        <v>28.5411510467529</v>
+        <v>28.5411491394043</v>
       </c>
       <c r="H1115" t="n">
         <v>781900</v>
@@ -32733,7 +32733,7 @@
         <v>33.3899993896484</v>
       </c>
       <c r="G1116" t="n">
-        <v>29.9305610656738</v>
+        <v>29.9305591583252</v>
       </c>
       <c r="H1116" t="n">
         <v>1107671</v>
@@ -32762,7 +32762,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G1117" t="n">
-        <v>29.5361461639404</v>
+        <v>29.5361499786377</v>
       </c>
       <c r="H1117" t="n">
         <v>791926</v>
@@ -32791,7 +32791,7 @@
         <v>34.8699989318848</v>
       </c>
       <c r="G1118" t="n">
-        <v>31.2572154998779</v>
+        <v>31.2572212219238</v>
       </c>
       <c r="H1118" t="n">
         <v>1316171</v>
@@ -32820,7 +32820,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G1119" t="n">
-        <v>29.9843444824219</v>
+        <v>29.9843425750732</v>
       </c>
       <c r="H1119" t="n">
         <v>2062579</v>
@@ -32849,7 +32849,7 @@
         <v>33.689998626709</v>
       </c>
       <c r="G1120" t="n">
-        <v>30.1994762420654</v>
+        <v>30.1994781494141</v>
       </c>
       <c r="H1120" t="n">
         <v>713925</v>
@@ -32878,7 +32878,7 @@
         <v>34.6800003051758</v>
       </c>
       <c r="G1121" t="n">
-        <v>31.0869102478027</v>
+        <v>31.0869064331055</v>
       </c>
       <c r="H1121" t="n">
         <v>1028412</v>
@@ -32936,7 +32936,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G1123" t="n">
-        <v>30.9972686767578</v>
+        <v>30.9972705841064</v>
       </c>
       <c r="H1123" t="n">
         <v>863955</v>
@@ -32994,7 +32994,7 @@
         <v>34.7299995422363</v>
       </c>
       <c r="G1125" t="n">
-        <v>31.131721496582</v>
+        <v>31.1317234039307</v>
       </c>
       <c r="H1125" t="n">
         <v>1136308</v>
@@ -33023,7 +33023,7 @@
         <v>34.1599998474121</v>
       </c>
       <c r="G1126" t="n">
-        <v>30.620777130127</v>
+        <v>30.6207809448242</v>
       </c>
       <c r="H1126" t="n">
         <v>889828</v>
@@ -33052,7 +33052,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1127" t="n">
-        <v>31.732307434082</v>
+        <v>31.7323150634766</v>
       </c>
       <c r="H1127" t="n">
         <v>1456634</v>
@@ -33081,7 +33081,7 @@
         <v>33.6500015258789</v>
       </c>
       <c r="G1128" t="n">
-        <v>30.1636219024658</v>
+        <v>30.1636238098145</v>
       </c>
       <c r="H1128" t="n">
         <v>1147152</v>
@@ -33139,7 +33139,7 @@
         <v>33.8699989318848</v>
       </c>
       <c r="G1130" t="n">
-        <v>30.3608245849609</v>
+        <v>30.3608303070068</v>
       </c>
       <c r="H1130" t="n">
         <v>1036556</v>
@@ -33168,7 +33168,7 @@
         <v>34.6599998474121</v>
       </c>
       <c r="G1131" t="n">
-        <v>31.0689811706543</v>
+        <v>31.0689792633057</v>
       </c>
       <c r="H1131" t="n">
         <v>891042</v>
@@ -33255,7 +33255,7 @@
         <v>35.2299995422363</v>
       </c>
       <c r="G1134" t="n">
-        <v>31.5799255371094</v>
+        <v>31.5799217224121</v>
       </c>
       <c r="H1134" t="n">
         <v>1177999</v>
@@ -33284,7 +33284,7 @@
         <v>35.5200004577637</v>
       </c>
       <c r="G1135" t="n">
-        <v>31.8398780822754</v>
+        <v>31.8398818969727</v>
       </c>
       <c r="H1135" t="n">
         <v>629000</v>
@@ -33313,7 +33313,7 @@
         <v>35.8400001525879</v>
       </c>
       <c r="G1136" t="n">
-        <v>32.1267204284668</v>
+        <v>32.1267242431641</v>
       </c>
       <c r="H1136" t="n">
         <v>1106671</v>
@@ -33400,7 +33400,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1139" t="n">
-        <v>30.7462768554688</v>
+        <v>30.7462730407715</v>
       </c>
       <c r="H1139" t="n">
         <v>852356</v>
@@ -33429,7 +33429,7 @@
         <v>34.8300018310547</v>
       </c>
       <c r="G1140" t="n">
-        <v>31.2213687896729</v>
+        <v>31.2213668823242</v>
       </c>
       <c r="H1140" t="n">
         <v>576778</v>
@@ -33487,7 +33487,7 @@
         <v>34.2599983215332</v>
       </c>
       <c r="G1142" t="n">
-        <v>30.7104187011719</v>
+        <v>30.7104206085205</v>
       </c>
       <c r="H1142" t="n">
         <v>897900</v>
@@ -33545,7 +33545,7 @@
         <v>33.8899993896484</v>
       </c>
       <c r="G1144" t="n">
-        <v>30.378755569458</v>
+        <v>30.3787574768066</v>
       </c>
       <c r="H1144" t="n">
         <v>688704</v>
@@ -33574,7 +33574,7 @@
         <v>34.1599998474121</v>
       </c>
       <c r="G1145" t="n">
-        <v>30.620777130127</v>
+        <v>30.6207809448242</v>
       </c>
       <c r="H1145" t="n">
         <v>455854</v>
@@ -33603,7 +33603,7 @@
         <v>34.8199996948242</v>
       </c>
       <c r="G1146" t="n">
-        <v>31.2123985290527</v>
+        <v>31.2124004364014</v>
       </c>
       <c r="H1146" t="n">
         <v>726482</v>
@@ -33632,7 +33632,7 @@
         <v>34.5099983215332</v>
       </c>
       <c r="G1147" t="n">
-        <v>30.9345188140869</v>
+        <v>30.9345169067383</v>
       </c>
       <c r="H1147" t="n">
         <v>523660</v>
@@ -33661,7 +33661,7 @@
         <v>34.1599998474121</v>
       </c>
       <c r="G1148" t="n">
-        <v>30.620777130127</v>
+        <v>30.6207809448242</v>
       </c>
       <c r="H1148" t="n">
         <v>594488</v>
@@ -33690,7 +33690,7 @@
         <v>34.1599998474121</v>
       </c>
       <c r="G1149" t="n">
-        <v>30.620777130127</v>
+        <v>30.6207809448242</v>
       </c>
       <c r="H1149" t="n">
         <v>475182</v>
@@ -33719,7 +33719,7 @@
         <v>34.6500015258789</v>
       </c>
       <c r="G1150" t="n">
-        <v>31.0600128173828</v>
+        <v>31.0600166320801</v>
       </c>
       <c r="H1150" t="n">
         <v>494968</v>
@@ -33777,7 +33777,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G1152" t="n">
-        <v>30.9972686767578</v>
+        <v>30.9972705841064</v>
       </c>
       <c r="H1152" t="n">
         <v>836843</v>
@@ -33806,7 +33806,7 @@
         <v>33.9900016784668</v>
       </c>
       <c r="G1153" t="n">
-        <v>30.4683990478516</v>
+        <v>30.4683952331543</v>
       </c>
       <c r="H1153" t="n">
         <v>921541</v>
@@ -33835,7 +33835,7 @@
         <v>33.2299995422363</v>
       </c>
       <c r="G1154" t="n">
-        <v>29.7871360778809</v>
+        <v>29.7871341705322</v>
       </c>
       <c r="H1154" t="n">
         <v>1032463</v>
@@ -33864,7 +33864,7 @@
         <v>33.6800003051758</v>
       </c>
       <c r="G1155" t="n">
-        <v>30.1905155181885</v>
+        <v>30.1905174255371</v>
       </c>
       <c r="H1155" t="n">
         <v>795795</v>
@@ -33893,7 +33893,7 @@
         <v>34.5</v>
       </c>
       <c r="G1156" t="n">
-        <v>30.9255561828613</v>
+        <v>30.9255523681641</v>
       </c>
       <c r="H1156" t="n">
         <v>1491319</v>
@@ -34038,7 +34038,7 @@
         <v>32.8899993896484</v>
       </c>
       <c r="G1161" t="n">
-        <v>29.482364654541</v>
+        <v>29.4823627471924</v>
       </c>
       <c r="H1161" t="n">
         <v>1732469</v>
@@ -34096,7 +34096,7 @@
         <v>33.1699981689453</v>
       </c>
       <c r="G1163" t="n">
-        <v>29.7333526611328</v>
+        <v>29.7333507537842</v>
       </c>
       <c r="H1163" t="n">
         <v>951695</v>
@@ -34125,7 +34125,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1164" t="n">
-        <v>29.2224082946777</v>
+        <v>29.2224063873291</v>
       </c>
       <c r="H1164" t="n">
         <v>521076</v>
@@ -34154,7 +34154,7 @@
         <v>32.6300010681152</v>
       </c>
       <c r="G1165" t="n">
-        <v>29.2493019104004</v>
+        <v>29.249303817749</v>
       </c>
       <c r="H1165" t="n">
         <v>711512</v>
@@ -34183,7 +34183,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1166" t="n">
-        <v>28.5949306488037</v>
+        <v>28.5949325561523</v>
       </c>
       <c r="H1166" t="n">
         <v>856225</v>
@@ -34212,7 +34212,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1167" t="n">
-        <v>29.025203704834</v>
+        <v>29.0252056121826</v>
       </c>
       <c r="H1167" t="n">
         <v>768051</v>
@@ -34241,7 +34241,7 @@
         <v>32.0699996948242</v>
       </c>
       <c r="G1168" t="n">
-        <v>28.7473201751709</v>
+        <v>28.7473182678223</v>
       </c>
       <c r="H1168" t="n">
         <v>1018271</v>
@@ -34270,7 +34270,7 @@
         <v>32.2799987792969</v>
       </c>
       <c r="G1169" t="n">
-        <v>28.9355640411377</v>
+        <v>28.9355621337891</v>
       </c>
       <c r="H1169" t="n">
         <v>483869</v>
@@ -34299,7 +34299,7 @@
         <v>31.9699993133545</v>
       </c>
       <c r="G1170" t="n">
-        <v>28.6576805114746</v>
+        <v>28.6576824188232</v>
       </c>
       <c r="H1170" t="n">
         <v>376907</v>
@@ -34328,7 +34328,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1171" t="n">
-        <v>29.3120498657227</v>
+        <v>29.312047958374</v>
       </c>
       <c r="H1171" t="n">
         <v>960546</v>
@@ -34357,7 +34357,7 @@
         <v>33.8899993896484</v>
       </c>
       <c r="G1172" t="n">
-        <v>30.378755569458</v>
+        <v>30.3787574768066</v>
       </c>
       <c r="H1172" t="n">
         <v>814774</v>
@@ -34386,7 +34386,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G1173" t="n">
-        <v>30.0112361907959</v>
+        <v>30.0112323760986</v>
       </c>
       <c r="H1173" t="n">
         <v>506274</v>
@@ -34415,7 +34415,7 @@
         <v>32.8800010681152</v>
       </c>
       <c r="G1174" t="n">
-        <v>29.4734020233154</v>
+        <v>29.4733982086182</v>
       </c>
       <c r="H1174" t="n">
         <v>689163</v>
@@ -34444,7 +34444,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G1175" t="n">
-        <v>29.5361461639404</v>
+        <v>29.5361499786377</v>
       </c>
       <c r="H1175" t="n">
         <v>432772</v>
@@ -34502,7 +34502,7 @@
         <v>32.2299995422363</v>
       </c>
       <c r="G1177" t="n">
-        <v>28.8907413482666</v>
+        <v>28.8907451629639</v>
       </c>
       <c r="H1177" t="n">
         <v>558791</v>
@@ -34531,7 +34531,7 @@
         <v>32.0200004577637</v>
       </c>
       <c r="G1178" t="n">
-        <v>28.7024993896484</v>
+        <v>28.7025032043457</v>
       </c>
       <c r="H1178" t="n">
         <v>507381</v>
@@ -34560,7 +34560,7 @@
         <v>32.0400009155273</v>
       </c>
       <c r="G1179" t="n">
-        <v>28.7204303741455</v>
+        <v>28.7204284667969</v>
       </c>
       <c r="H1179" t="n">
         <v>514051</v>
@@ -34647,7 +34647,7 @@
         <v>33.1599998474121</v>
       </c>
       <c r="G1182" t="n">
-        <v>29.7243881225586</v>
+        <v>29.7243900299072</v>
       </c>
       <c r="H1182" t="n">
         <v>424634</v>
@@ -34676,7 +34676,7 @@
         <v>32.6199989318848</v>
       </c>
       <c r="G1183" t="n">
-        <v>29.2403373718262</v>
+        <v>29.2403354644775</v>
       </c>
       <c r="H1183" t="n">
         <v>685213</v>
@@ -34763,7 +34763,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G1186" t="n">
-        <v>29.1148414611816</v>
+        <v>29.1148433685303</v>
       </c>
       <c r="H1186" t="n">
         <v>560790</v>
@@ -34792,7 +34792,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G1187" t="n">
-        <v>30.0112361907959</v>
+        <v>30.0112323760986</v>
       </c>
       <c r="H1187" t="n">
         <v>1548768</v>
@@ -34821,7 +34821,7 @@
         <v>33.3899993896484</v>
       </c>
       <c r="G1188" t="n">
-        <v>29.9305610656738</v>
+        <v>29.9305591583252</v>
       </c>
       <c r="H1188" t="n">
         <v>940955</v>
@@ -34879,7 +34879,7 @@
         <v>34.4700012207031</v>
       </c>
       <c r="G1190" t="n">
-        <v>30.8986625671387</v>
+        <v>30.8986663818359</v>
       </c>
       <c r="H1190" t="n">
         <v>689525</v>
@@ -34937,7 +34937,7 @@
         <v>34.4700012207031</v>
       </c>
       <c r="G1192" t="n">
-        <v>30.8986625671387</v>
+        <v>30.8986663818359</v>
       </c>
       <c r="H1192" t="n">
         <v>988286</v>
@@ -34966,7 +34966,7 @@
         <v>34.310001373291</v>
       </c>
       <c r="G1193" t="n">
-        <v>30.7552394866943</v>
+        <v>30.7552433013916</v>
       </c>
       <c r="H1193" t="n">
         <v>612049</v>
@@ -34995,7 +34995,7 @@
         <v>34.8899993896484</v>
       </c>
       <c r="G1194" t="n">
-        <v>31.2751445770264</v>
+        <v>31.2751483917236</v>
       </c>
       <c r="H1194" t="n">
         <v>816452</v>
@@ -35053,7 +35053,7 @@
         <v>36.7400016784668</v>
       </c>
       <c r="G1196" t="n">
-        <v>32.933479309082</v>
+        <v>32.9334754943848</v>
       </c>
       <c r="H1196" t="n">
         <v>1499655</v>
@@ -35111,7 +35111,7 @@
         <v>37.2200012207031</v>
       </c>
       <c r="G1198" t="n">
-        <v>33.3637428283691</v>
+        <v>33.3637466430664</v>
       </c>
       <c r="H1198" t="n">
         <v>648519</v>
@@ -35140,7 +35140,7 @@
         <v>36.5</v>
       </c>
       <c r="G1199" t="n">
-        <v>32.7183456420898</v>
+        <v>32.7183418273926</v>
       </c>
       <c r="H1199" t="n">
         <v>1511426</v>
@@ -35198,7 +35198,7 @@
         <v>34.5200004577637</v>
       </c>
       <c r="G1201" t="n">
-        <v>30.9434852600098</v>
+        <v>30.9434833526611</v>
       </c>
       <c r="H1201" t="n">
         <v>665853</v>
@@ -35285,7 +35285,7 @@
         <v>34.7400016784668</v>
       </c>
       <c r="G1204" t="n">
-        <v>31.1406860351562</v>
+        <v>31.1406898498535</v>
       </c>
       <c r="H1204" t="n">
         <v>608760</v>
@@ -35314,7 +35314,7 @@
         <v>35.1800003051758</v>
       </c>
       <c r="G1205" t="n">
-        <v>31.5351028442383</v>
+        <v>31.5351066589355</v>
       </c>
       <c r="H1205" t="n">
         <v>518246</v>
@@ -35343,7 +35343,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G1206" t="n">
-        <v>31.4185695648193</v>
+        <v>31.4185733795166</v>
       </c>
       <c r="H1206" t="n">
         <v>439769</v>
@@ -35488,7 +35488,7 @@
         <v>36.4300003051758</v>
       </c>
       <c r="G1211" t="n">
-        <v>32.6555938720703</v>
+        <v>32.655590057373</v>
       </c>
       <c r="H1211" t="n">
         <v>635833</v>
@@ -35546,7 +35546,7 @@
         <v>36.0200004577637</v>
       </c>
       <c r="G1213" t="n">
-        <v>32.2880706787109</v>
+        <v>32.2880668640137</v>
       </c>
       <c r="H1213" t="n">
         <v>835340</v>
@@ -35575,7 +35575,7 @@
         <v>36.3899993896484</v>
       </c>
       <c r="G1214" t="n">
-        <v>32.6197357177734</v>
+        <v>32.6197395324707</v>
       </c>
       <c r="H1214" t="n">
         <v>695087</v>
@@ -35720,7 +35720,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1219" t="n">
-        <v>32.9872550964355</v>
+        <v>32.9872589111328</v>
       </c>
       <c r="H1219" t="n">
         <v>1280510</v>
@@ -35749,7 +35749,7 @@
         <v>36.7400016784668</v>
       </c>
       <c r="G1220" t="n">
-        <v>32.933479309082</v>
+        <v>32.9334754943848</v>
       </c>
       <c r="H1220" t="n">
         <v>487502</v>
@@ -35778,7 +35778,7 @@
         <v>37.8899993896484</v>
       </c>
       <c r="G1221" t="n">
-        <v>33.9643287658691</v>
+        <v>33.9643249511719</v>
       </c>
       <c r="H1221" t="n">
         <v>956555</v>
@@ -35807,7 +35807,7 @@
         <v>37.4300003051758</v>
       </c>
       <c r="G1222" t="n">
-        <v>33.5519905090332</v>
+        <v>33.5519866943359</v>
       </c>
       <c r="H1222" t="n">
         <v>941124</v>
@@ -35865,7 +35865,7 @@
         <v>38.939998626709</v>
       </c>
       <c r="G1224" t="n">
-        <v>34.9055404663086</v>
+        <v>34.9055328369141</v>
       </c>
       <c r="H1224" t="n">
         <v>1643016</v>
@@ -36010,7 +36010,7 @@
         <v>34.3600006103516</v>
       </c>
       <c r="G1229" t="n">
-        <v>30.8000564575195</v>
+        <v>30.8000640869141</v>
       </c>
       <c r="H1229" t="n">
         <v>684958</v>
@@ -36039,7 +36039,7 @@
         <v>35.1199989318848</v>
       </c>
       <c r="G1230" t="n">
-        <v>31.4813232421875</v>
+        <v>31.481315612793</v>
       </c>
       <c r="H1230" t="n">
         <v>708133</v>
@@ -36068,7 +36068,7 @@
         <v>36</v>
       </c>
       <c r="G1231" t="n">
-        <v>32.2701416015625</v>
+        <v>32.2701454162598</v>
       </c>
       <c r="H1231" t="n">
         <v>837191</v>
@@ -36097,7 +36097,7 @@
         <v>36.3699989318848</v>
       </c>
       <c r="G1232" t="n">
-        <v>32.6018104553223</v>
+        <v>32.6018028259277</v>
       </c>
       <c r="H1232" t="n">
         <v>1092932</v>
@@ -36126,7 +36126,7 @@
         <v>37.8199996948242</v>
       </c>
       <c r="G1233" t="n">
-        <v>33.9015808105469</v>
+        <v>33.9015769958496</v>
       </c>
       <c r="H1233" t="n">
         <v>1181186</v>
@@ -36213,7 +36213,7 @@
         <v>39.7099990844727</v>
       </c>
       <c r="G1236" t="n">
-        <v>35.595760345459</v>
+        <v>35.5957679748535</v>
       </c>
       <c r="H1236" t="n">
         <v>1206949</v>
@@ -36242,7 +36242,7 @@
         <v>40.4900016784668</v>
       </c>
       <c r="G1237" t="n">
-        <v>36.2949523925781</v>
+        <v>36.2949485778809</v>
       </c>
       <c r="H1237" t="n">
         <v>882600</v>
@@ -36271,7 +36271,7 @@
         <v>39.689998626709</v>
       </c>
       <c r="G1238" t="n">
-        <v>35.5778312683105</v>
+        <v>35.5778350830078</v>
       </c>
       <c r="H1238" t="n">
         <v>712135</v>
@@ -36300,7 +36300,7 @@
         <v>39.810001373291</v>
       </c>
       <c r="G1239" t="n">
-        <v>35.6854057312012</v>
+        <v>35.6853981018066</v>
       </c>
       <c r="H1239" t="n">
         <v>525261</v>
@@ -36329,7 +36329,7 @@
         <v>41.0800018310547</v>
       </c>
       <c r="G1240" t="n">
-        <v>36.8238220214844</v>
+        <v>36.8238258361816</v>
       </c>
       <c r="H1240" t="n">
         <v>944829</v>
@@ -36358,7 +36358,7 @@
         <v>41.060001373291</v>
       </c>
       <c r="G1241" t="n">
-        <v>36.8058929443359</v>
+        <v>36.8058891296387</v>
       </c>
       <c r="H1241" t="n">
         <v>651551</v>
@@ -36416,7 +36416,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G1243" t="n">
-        <v>36.3935546875</v>
+        <v>36.3935508728027</v>
       </c>
       <c r="H1243" t="n">
         <v>559053</v>
@@ -36474,7 +36474,7 @@
         <v>41.689998626709</v>
       </c>
       <c r="G1245" t="n">
-        <v>37.3706207275391</v>
+        <v>37.3706169128418</v>
       </c>
       <c r="H1245" t="n">
         <v>790759</v>
@@ -36561,7 +36561,7 @@
         <v>41.4599990844727</v>
       </c>
       <c r="G1248" t="n">
-        <v>37.1644477844238</v>
+        <v>37.1644515991211</v>
       </c>
       <c r="H1248" t="n">
         <v>617185</v>
@@ -36590,7 +36590,7 @@
         <v>41.0099983215332</v>
       </c>
       <c r="G1249" t="n">
-        <v>36.7610740661621</v>
+        <v>36.7610702514648</v>
       </c>
       <c r="H1249" t="n">
         <v>659023</v>
@@ -36706,7 +36706,7 @@
         <v>42.5900001525879</v>
       </c>
       <c r="G1253" t="n">
-        <v>38.177375793457</v>
+        <v>38.1773719787598</v>
       </c>
       <c r="H1253" t="n">
         <v>934680</v>
@@ -36735,7 +36735,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1254" t="n">
-        <v>38.7241744995117</v>
+        <v>38.724178314209</v>
       </c>
       <c r="H1254" t="n">
         <v>930793</v>
@@ -36764,7 +36764,7 @@
         <v>44</v>
       </c>
       <c r="G1255" t="n">
-        <v>39.4412879943848</v>
+        <v>39.441291809082</v>
       </c>
       <c r="H1255" t="n">
         <v>2134898</v>
@@ -36793,7 +36793,7 @@
         <v>44.9000015258789</v>
       </c>
       <c r="G1256" t="n">
-        <v>40.2480430603027</v>
+        <v>40.248046875</v>
       </c>
       <c r="H1256" t="n">
         <v>1092806</v>
@@ -36822,7 +36822,7 @@
         <v>46.6100006103516</v>
       </c>
       <c r="G1257" t="n">
-        <v>41.7808723449707</v>
+        <v>41.780876159668</v>
       </c>
       <c r="H1257" t="n">
         <v>1623869</v>
@@ -36880,7 +36880,7 @@
         <v>47.5800018310547</v>
       </c>
       <c r="G1259" t="n">
-        <v>42.6503715515137</v>
+        <v>42.6503753662109</v>
       </c>
       <c r="H1259" t="n">
         <v>1094182</v>
@@ -36909,7 +36909,7 @@
         <v>47.8800010681152</v>
       </c>
       <c r="G1260" t="n">
-        <v>42.9193000793457</v>
+        <v>42.9192924499512</v>
       </c>
       <c r="H1260" t="n">
         <v>793172</v>
@@ -36967,7 +36967,7 @@
         <v>48.7099990844727</v>
       </c>
       <c r="G1262" t="n">
-        <v>43.6632957458496</v>
+        <v>43.6632995605469</v>
       </c>
       <c r="H1262" t="n">
         <v>968756</v>
@@ -37025,7 +37025,7 @@
         <v>48.5</v>
       </c>
       <c r="G1264" t="n">
-        <v>43.4750556945801</v>
+        <v>43.4750595092773</v>
       </c>
       <c r="H1264" t="n">
         <v>1163548</v>
@@ -37112,7 +37112,7 @@
         <v>48.2099990844727</v>
       </c>
       <c r="G1267" t="n">
-        <v>43.2150993347168</v>
+        <v>43.2151031494141</v>
       </c>
       <c r="H1267" t="n">
         <v>405890</v>
@@ -37141,7 +37141,7 @@
         <v>49.7299995422363</v>
       </c>
       <c r="G1268" t="n">
-        <v>44.5776176452637</v>
+        <v>44.5776214599609</v>
       </c>
       <c r="H1268" t="n">
         <v>601188</v>
@@ -37170,7 +37170,7 @@
         <v>50.2999992370605</v>
       </c>
       <c r="G1269" t="n">
-        <v>45.0885581970215</v>
+        <v>45.0885620117188</v>
       </c>
       <c r="H1269" t="n">
         <v>658618</v>
@@ -37199,7 +37199,7 @@
         <v>50.1399993896484</v>
       </c>
       <c r="G1270" t="n">
-        <v>44.9451370239258</v>
+        <v>44.945140838623</v>
       </c>
       <c r="H1270" t="n">
         <v>353603</v>
@@ -37228,7 +37228,7 @@
         <v>50</v>
       </c>
       <c r="G1271" t="n">
-        <v>44.8196411132812</v>
+        <v>44.8196449279785</v>
       </c>
       <c r="H1271" t="n">
         <v>623046</v>
@@ -37373,7 +37373,7 @@
         <v>48</v>
       </c>
       <c r="G1276" t="n">
-        <v>43.0268592834473</v>
+        <v>43.0268630981445</v>
       </c>
       <c r="H1276" t="n">
         <v>779555</v>
@@ -37431,7 +37431,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1278" t="n">
-        <v>43.1613235473633</v>
+        <v>43.161319732666</v>
       </c>
       <c r="H1278" t="n">
         <v>859462</v>
@@ -37460,7 +37460,7 @@
         <v>47.7799987792969</v>
       </c>
       <c r="G1279" t="n">
-        <v>42.8296546936035</v>
+        <v>42.8296508789062</v>
       </c>
       <c r="H1279" t="n">
         <v>657222</v>
@@ -37489,7 +37489,7 @@
         <v>47.3499984741211</v>
       </c>
       <c r="G1280" t="n">
-        <v>42.444206237793</v>
+        <v>42.4442024230957</v>
       </c>
       <c r="H1280" t="n">
         <v>485197</v>
@@ -37518,7 +37518,7 @@
         <v>48.4300003051758</v>
       </c>
       <c r="G1281" t="n">
-        <v>43.4123115539551</v>
+        <v>43.4123077392578</v>
       </c>
       <c r="H1281" t="n">
         <v>523491</v>
@@ -37576,7 +37576,7 @@
         <v>48.6699981689453</v>
       </c>
       <c r="G1283" t="n">
-        <v>43.6274375915527</v>
+        <v>43.62744140625</v>
       </c>
       <c r="H1283" t="n">
         <v>695817</v>
@@ -37605,7 +37605,7 @@
         <v>49.5900001525879</v>
       </c>
       <c r="G1284" t="n">
-        <v>44.4521217346191</v>
+        <v>44.4521255493164</v>
       </c>
       <c r="H1284" t="n">
         <v>737426</v>
@@ -37634,7 +37634,7 @@
         <v>48.6699981689453</v>
       </c>
       <c r="G1285" t="n">
-        <v>43.6274375915527</v>
+        <v>43.62744140625</v>
       </c>
       <c r="H1285" t="n">
         <v>592520</v>
@@ -37663,7 +37663,7 @@
         <v>47.3400001525879</v>
       </c>
       <c r="G1286" t="n">
-        <v>42.4352378845215</v>
+        <v>42.4352416992188</v>
       </c>
       <c r="H1286" t="n">
         <v>547777</v>
@@ -37692,7 +37692,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1287" t="n">
-        <v>43.1613235473633</v>
+        <v>43.161319732666</v>
       </c>
       <c r="H1287" t="n">
         <v>571676</v>
@@ -37721,7 +37721,7 @@
         <v>47.2599983215332</v>
       </c>
       <c r="G1288" t="n">
-        <v>42.363525390625</v>
+        <v>42.3635292053223</v>
       </c>
       <c r="H1288" t="n">
         <v>893943</v>
@@ -37750,7 +37750,7 @@
         <v>48.0900001525879</v>
       </c>
       <c r="G1289" t="n">
-        <v>43.1075325012207</v>
+        <v>43.107536315918</v>
       </c>
       <c r="H1289" t="n">
         <v>554005</v>
@@ -37779,7 +37779,7 @@
         <v>46.6100006103516</v>
       </c>
       <c r="G1290" t="n">
-        <v>41.7808723449707</v>
+        <v>41.780876159668</v>
       </c>
       <c r="H1290" t="n">
         <v>648354</v>
@@ -37866,7 +37866,7 @@
         <v>47.9300003051758</v>
       </c>
       <c r="G1293" t="n">
-        <v>42.9641189575195</v>
+        <v>42.9641151428223</v>
       </c>
       <c r="H1293" t="n">
         <v>606640</v>
@@ -37895,7 +37895,7 @@
         <v>50.0200004577637</v>
       </c>
       <c r="G1294" t="n">
-        <v>44.8375701904297</v>
+        <v>44.837574005127</v>
       </c>
       <c r="H1294" t="n">
         <v>1070314</v>
@@ -37953,7 +37953,7 @@
         <v>51.5800018310547</v>
       </c>
       <c r="G1296" t="n">
-        <v>46.2359504699707</v>
+        <v>46.2359466552734</v>
       </c>
       <c r="H1296" t="n">
         <v>755439</v>
@@ -37982,7 +37982,7 @@
         <v>52.1199989318848</v>
       </c>
       <c r="G1297" t="n">
-        <v>46.7200012207031</v>
+        <v>46.7199974060059</v>
       </c>
       <c r="H1297" t="n">
         <v>657479</v>
@@ -38011,7 +38011,7 @@
         <v>51.6599998474121</v>
       </c>
       <c r="G1298" t="n">
-        <v>46.3076553344727</v>
+        <v>46.3076591491699</v>
       </c>
       <c r="H1298" t="n">
         <v>615630</v>
@@ -38069,7 +38069,7 @@
         <v>51.2400016784668</v>
       </c>
       <c r="G1300" t="n">
-        <v>45.9311714172363</v>
+        <v>45.9311752319336</v>
       </c>
       <c r="H1300" t="n">
         <v>566259</v>
@@ -38214,7 +38214,7 @@
         <v>53.3199996948242</v>
       </c>
       <c r="G1305" t="n">
-        <v>47.7956695556641</v>
+        <v>47.7956733703613</v>
       </c>
       <c r="H1305" t="n">
         <v>2189364</v>
@@ -38359,7 +38359,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1310" t="n">
-        <v>45.9849548339844</v>
+        <v>45.9849586486816</v>
       </c>
       <c r="H1310" t="n">
         <v>818219</v>
@@ -38388,7 +38388,7 @@
         <v>52.1599998474121</v>
       </c>
       <c r="G1311" t="n">
-        <v>46.7558555603027</v>
+        <v>46.7558479309082</v>
       </c>
       <c r="H1311" t="n">
         <v>702040</v>
@@ -38417,7 +38417,7 @@
         <v>52.5400009155273</v>
       </c>
       <c r="G1312" t="n">
-        <v>47.0964851379395</v>
+        <v>47.0964813232422</v>
       </c>
       <c r="H1312" t="n">
         <v>604331</v>
@@ -38446,7 +38446,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G1313" t="n">
-        <v>46.3435096740723</v>
+        <v>46.3435134887695</v>
       </c>
       <c r="H1313" t="n">
         <v>647143</v>
@@ -38504,7 +38504,7 @@
         <v>49.5499992370605</v>
       </c>
       <c r="G1315" t="n">
-        <v>44.4162712097168</v>
+        <v>44.4162635803223</v>
       </c>
       <c r="H1315" t="n">
         <v>574645</v>
@@ -38591,7 +38591,7 @@
         <v>49.6100006103516</v>
       </c>
       <c r="G1318" t="n">
-        <v>44.4700508117676</v>
+        <v>44.4700546264648</v>
       </c>
       <c r="H1318" t="n">
         <v>1612873</v>
@@ -38649,7 +38649,7 @@
         <v>52.0400009155273</v>
       </c>
       <c r="G1320" t="n">
-        <v>46.6482925415039</v>
+        <v>46.6482887268066</v>
       </c>
       <c r="H1320" t="n">
         <v>501531</v>
@@ -38678,7 +38678,7 @@
         <v>51.3199996948242</v>
       </c>
       <c r="G1321" t="n">
-        <v>46.0028877258301</v>
+        <v>46.0028839111328</v>
       </c>
       <c r="H1321" t="n">
         <v>672676</v>
@@ -38765,7 +38765,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1324" t="n">
-        <v>44.9092826843262</v>
+        <v>44.9092864990234</v>
       </c>
       <c r="H1324" t="n">
         <v>827275</v>
@@ -38823,7 +38823,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1326" t="n">
-        <v>44.1025314331055</v>
+        <v>44.1025352478027</v>
       </c>
       <c r="H1326" t="n">
         <v>421369</v>
@@ -38852,7 +38852,7 @@
         <v>47.9500007629395</v>
       </c>
       <c r="G1327" t="n">
-        <v>42.9820442199707</v>
+        <v>42.982048034668</v>
       </c>
       <c r="H1327" t="n">
         <v>1034091</v>
@@ -38939,7 +38939,7 @@
         <v>47.9500007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>42.9820442199707</v>
+        <v>42.982048034668</v>
       </c>
       <c r="H1330" t="n">
         <v>610263</v>
@@ -38997,7 +38997,7 @@
         <v>49.2099990844727</v>
       </c>
       <c r="G1332" t="n">
-        <v>44.1114921569824</v>
+        <v>44.1114959716797</v>
       </c>
       <c r="H1332" t="n">
         <v>824033</v>
@@ -39026,7 +39026,7 @@
         <v>48.8699989318848</v>
       </c>
       <c r="G1333" t="n">
-        <v>43.8067207336426</v>
+        <v>43.8067169189453</v>
       </c>
       <c r="H1333" t="n">
         <v>664214</v>
@@ -39055,7 +39055,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G1334" t="n">
-        <v>44.5507316589355</v>
+        <v>44.5507278442383</v>
       </c>
       <c r="H1334" t="n">
         <v>574721</v>
@@ -39142,7 +39142,7 @@
         <v>50.3600006103516</v>
       </c>
       <c r="G1337" t="n">
-        <v>45.1423492431641</v>
+        <v>45.1423454284668</v>
       </c>
       <c r="H1337" t="n">
         <v>749848</v>
@@ -39171,7 +39171,7 @@
         <v>50.3600006103516</v>
       </c>
       <c r="G1338" t="n">
-        <v>45.1423492431641</v>
+        <v>45.1423454284668</v>
       </c>
       <c r="H1338" t="n">
         <v>694097</v>
@@ -39200,7 +39200,7 @@
         <v>50.0999984741211</v>
       </c>
       <c r="G1339" t="n">
-        <v>44.9092826843262</v>
+        <v>44.9092864990234</v>
       </c>
       <c r="H1339" t="n">
         <v>439395</v>
@@ -39229,7 +39229,7 @@
         <v>50.1399993896484</v>
       </c>
       <c r="G1340" t="n">
-        <v>44.9451370239258</v>
+        <v>44.945140838623</v>
       </c>
       <c r="H1340" t="n">
         <v>515025</v>
@@ -39287,7 +39287,7 @@
         <v>50.439998626709</v>
       </c>
       <c r="G1342" t="n">
-        <v>45.2140502929688</v>
+        <v>45.214054107666</v>
       </c>
       <c r="H1342" t="n">
         <v>501711</v>
@@ -39316,7 +39316,7 @@
         <v>51.5</v>
       </c>
       <c r="G1343" t="n">
-        <v>46.1642379760742</v>
+        <v>46.164234161377</v>
       </c>
       <c r="H1343" t="n">
         <v>771133</v>
@@ -39374,7 +39374,7 @@
         <v>50.2200012207031</v>
       </c>
       <c r="G1345" t="n">
-        <v>45.0168495178223</v>
+        <v>45.0168533325195</v>
       </c>
       <c r="H1345" t="n">
         <v>641825</v>
@@ -39403,7 +39403,7 @@
         <v>52.3600006103516</v>
       </c>
       <c r="G1346" t="n">
-        <v>46.9351272583008</v>
+        <v>46.935131072998</v>
       </c>
       <c r="H1346" t="n">
         <v>919141</v>
@@ -39432,7 +39432,7 @@
         <v>53.5</v>
       </c>
       <c r="G1347" t="n">
-        <v>47.9570159912109</v>
+        <v>47.9570236206055</v>
       </c>
       <c r="H1347" t="n">
         <v>755027</v>
@@ -39490,7 +39490,7 @@
         <v>51.5</v>
       </c>
       <c r="G1349" t="n">
-        <v>46.1642379760742</v>
+        <v>46.164234161377</v>
       </c>
       <c r="H1349" t="n">
         <v>955263</v>
@@ -39577,7 +39577,7 @@
         <v>50.9599990844727</v>
       </c>
       <c r="G1352" t="n">
-        <v>45.6801834106445</v>
+        <v>45.6801872253418</v>
       </c>
       <c r="H1352" t="n">
         <v>748447</v>
@@ -39606,7 +39606,7 @@
         <v>51.0200004577637</v>
       </c>
       <c r="G1353" t="n">
-        <v>45.7339630126953</v>
+        <v>45.7339668273926</v>
       </c>
       <c r="H1353" t="n">
         <v>558678</v>
@@ -39635,7 +39635,7 @@
         <v>51.4799995422363</v>
       </c>
       <c r="G1354" t="n">
-        <v>46.1463088989258</v>
+        <v>46.1463050842285</v>
       </c>
       <c r="H1354" t="n">
         <v>428571</v>
@@ -39722,7 +39722,7 @@
         <v>51.4199981689453</v>
       </c>
       <c r="G1357" t="n">
-        <v>46.0925254821777</v>
+        <v>46.0925216674805</v>
       </c>
       <c r="H1357" t="n">
         <v>557261</v>
@@ -39780,7 +39780,7 @@
         <v>51.7400016784668</v>
       </c>
       <c r="G1359" t="n">
-        <v>46.3793716430664</v>
+        <v>46.3793678283691</v>
       </c>
       <c r="H1359" t="n">
         <v>421221</v>
@@ -39838,7 +39838,7 @@
         <v>50.939998626709</v>
       </c>
       <c r="G1361" t="n">
-        <v>45.6622581481934</v>
+        <v>45.6622543334961</v>
       </c>
       <c r="H1361" t="n">
         <v>555578</v>
@@ -39867,7 +39867,7 @@
         <v>51.5800018310547</v>
       </c>
       <c r="G1362" t="n">
-        <v>46.2359504699707</v>
+        <v>46.2359466552734</v>
       </c>
       <c r="H1362" t="n">
         <v>590820</v>
@@ -39954,7 +39954,7 @@
         <v>52.7599983215332</v>
       </c>
       <c r="G1365" t="n">
-        <v>47.2936859130859</v>
+        <v>47.2936897277832</v>
       </c>
       <c r="H1365" t="n">
         <v>746402</v>
@@ -39983,7 +39983,7 @@
         <v>52.5</v>
       </c>
       <c r="G1366" t="n">
-        <v>47.0606231689453</v>
+        <v>47.0606269836426</v>
       </c>
       <c r="H1366" t="n">
         <v>628114</v>
@@ -40041,7 +40041,7 @@
         <v>53.5800018310547</v>
       </c>
       <c r="G1368" t="n">
-        <v>48.0287322998047</v>
+        <v>48.0287399291992</v>
       </c>
       <c r="H1368" t="n">
         <v>863105</v>
@@ -40099,7 +40099,7 @@
         <v>54.9599990844727</v>
       </c>
       <c r="G1370" t="n">
-        <v>49.6830253601074</v>
+        <v>49.6830215454102</v>
       </c>
       <c r="H1370" t="n">
         <v>687075</v>
@@ -40128,7 +40128,7 @@
         <v>55.5</v>
       </c>
       <c r="G1371" t="n">
-        <v>50.1711807250977</v>
+        <v>50.1711769104004</v>
       </c>
       <c r="H1371" t="n">
         <v>616936</v>
@@ -40186,7 +40186,7 @@
         <v>58.0400009155273</v>
       </c>
       <c r="G1373" t="n">
-        <v>52.4673004150391</v>
+        <v>52.4673042297363</v>
       </c>
       <c r="H1373" t="n">
         <v>625541</v>
@@ -40273,7 +40273,7 @@
         <v>57.6599998474121</v>
       </c>
       <c r="G1376" t="n">
-        <v>52.1237869262695</v>
+        <v>52.1237831115723</v>
       </c>
       <c r="H1376" t="n">
         <v>459845</v>
@@ -40331,7 +40331,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G1378" t="n">
-        <v>52.7023277282715</v>
+        <v>52.702335357666</v>
       </c>
       <c r="H1378" t="n">
         <v>509502</v>
@@ -40360,7 +40360,7 @@
         <v>59.2400016784668</v>
       </c>
       <c r="G1379" t="n">
-        <v>53.5520820617676</v>
+        <v>53.5520782470703</v>
       </c>
       <c r="H1379" t="n">
         <v>696599</v>
@@ -40418,7 +40418,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1381" t="n">
-        <v>52.0695419311523</v>
+        <v>52.0695457458496</v>
       </c>
       <c r="H1381" t="n">
         <v>659000</v>
@@ -40447,7 +40447,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G1382" t="n">
-        <v>51.3463554382324</v>
+        <v>51.3463516235352</v>
       </c>
       <c r="H1382" t="n">
         <v>706838</v>
@@ -40476,7 +40476,7 @@
         <v>56.8400001525879</v>
       </c>
       <c r="G1383" t="n">
-        <v>51.3825187683105</v>
+        <v>51.3825149536133</v>
       </c>
       <c r="H1383" t="n">
         <v>486048</v>
@@ -40592,7 +40592,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G1387" t="n">
-        <v>52.9735260009766</v>
+        <v>52.9735298156738</v>
       </c>
       <c r="H1387" t="n">
         <v>501161</v>
@@ -40650,7 +40650,7 @@
         <v>58.2400016784668</v>
       </c>
       <c r="G1389" t="n">
-        <v>52.6480979919434</v>
+        <v>52.6480941772461</v>
       </c>
       <c r="H1389" t="n">
         <v>469111</v>
@@ -40679,7 +40679,7 @@
         <v>58.2799987792969</v>
       </c>
       <c r="G1390" t="n">
-        <v>52.6842575073242</v>
+        <v>52.684253692627</v>
       </c>
       <c r="H1390" t="n">
         <v>403713</v>
@@ -40766,7 +40766,7 @@
         <v>57.7200012207031</v>
       </c>
       <c r="G1393" t="n">
-        <v>52.1780281066895</v>
+        <v>52.1780242919922</v>
       </c>
       <c r="H1393" t="n">
         <v>350259</v>
@@ -40853,7 +40853,7 @@
         <v>57.060001373291</v>
       </c>
       <c r="G1396" t="n">
-        <v>51.5813941955566</v>
+        <v>51.5813980102539</v>
       </c>
       <c r="H1396" t="n">
         <v>394733</v>
@@ -40940,7 +40940,7 @@
         <v>56.7799987792969</v>
       </c>
       <c r="G1399" t="n">
-        <v>51.3282737731934</v>
+        <v>51.3282775878906</v>
       </c>
       <c r="H1399" t="n">
         <v>256552</v>
@@ -41056,7 +41056,7 @@
         <v>56.3600006103516</v>
       </c>
       <c r="G1403" t="n">
-        <v>50.948600769043</v>
+        <v>50.9486045837402</v>
       </c>
       <c r="H1403" t="n">
         <v>545358</v>
@@ -41114,7 +41114,7 @@
         <v>57.7599983215332</v>
       </c>
       <c r="G1405" t="n">
-        <v>52.2141799926758</v>
+        <v>52.214183807373</v>
       </c>
       <c r="H1405" t="n">
         <v>332441</v>
@@ -41172,7 +41172,7 @@
         <v>57.7599983215332</v>
       </c>
       <c r="G1407" t="n">
-        <v>52.2141799926758</v>
+        <v>52.214183807373</v>
       </c>
       <c r="H1407" t="n">
         <v>391722</v>
@@ -41317,7 +41317,7 @@
         <v>58.7200012207031</v>
       </c>
       <c r="G1412" t="n">
-        <v>53.0820083618164</v>
+        <v>53.0820121765137</v>
       </c>
       <c r="H1412" t="n">
         <v>256902</v>
@@ -41375,7 +41375,7 @@
         <v>59.939998626709</v>
       </c>
       <c r="G1414" t="n">
-        <v>54.1848754882812</v>
+        <v>54.1848678588867</v>
       </c>
       <c r="H1414" t="n">
         <v>449464</v>
@@ -41404,7 +41404,7 @@
         <v>59.6599998474121</v>
       </c>
       <c r="G1415" t="n">
-        <v>53.931755065918</v>
+        <v>53.9317512512207</v>
       </c>
       <c r="H1415" t="n">
         <v>679790</v>
@@ -41491,7 +41491,7 @@
         <v>58</v>
       </c>
       <c r="G1418" t="n">
-        <v>52.4311408996582</v>
+        <v>52.4311370849609</v>
       </c>
       <c r="H1418" t="n">
         <v>650785</v>
@@ -41520,7 +41520,7 @@
         <v>58.2799987792969</v>
       </c>
       <c r="G1419" t="n">
-        <v>52.6842575073242</v>
+        <v>52.684253692627</v>
       </c>
       <c r="H1419" t="n">
         <v>481348</v>
@@ -41578,7 +41578,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G1421" t="n">
-        <v>53.1543312072754</v>
+        <v>53.1543273925781</v>
       </c>
       <c r="H1421" t="n">
         <v>362702</v>
@@ -41636,7 +41636,7 @@
         <v>58.6199989318848</v>
       </c>
       <c r="G1423" t="n">
-        <v>52.9916076660156</v>
+        <v>52.9916114807129</v>
       </c>
       <c r="H1423" t="n">
         <v>686976</v>
@@ -41723,7 +41723,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1426" t="n">
-        <v>55.6854820251465</v>
+        <v>55.6854782104492</v>
       </c>
       <c r="H1426" t="n">
         <v>574434</v>
@@ -41752,7 +41752,7 @@
         <v>62.060001373291</v>
       </c>
       <c r="G1427" t="n">
-        <v>56.101318359375</v>
+        <v>56.1013221740723</v>
       </c>
       <c r="H1427" t="n">
         <v>490738</v>
@@ -41781,7 +41781,7 @@
         <v>61.8800010681152</v>
       </c>
       <c r="G1428" t="n">
-        <v>55.938606262207</v>
+        <v>55.9385986328125</v>
       </c>
       <c r="H1428" t="n">
         <v>392477</v>
@@ -41839,7 +41839,7 @@
         <v>60.060001373291</v>
       </c>
       <c r="G1430" t="n">
-        <v>54.2933502197266</v>
+        <v>54.2933540344238</v>
       </c>
       <c r="H1430" t="n">
         <v>351504</v>
@@ -41868,7 +41868,7 @@
         <v>58.4799995422363</v>
       </c>
       <c r="G1431" t="n">
-        <v>52.8650550842285</v>
+        <v>52.8650512695312</v>
       </c>
       <c r="H1431" t="n">
         <v>830898</v>
@@ -41926,7 +41926,7 @@
         <v>53.9199981689453</v>
       </c>
       <c r="G1433" t="n">
-        <v>48.7428741455078</v>
+        <v>48.7428779602051</v>
       </c>
       <c r="H1433" t="n">
         <v>1189356</v>
@@ -41955,7 +41955,7 @@
         <v>55.5</v>
       </c>
       <c r="G1434" t="n">
-        <v>50.1711807250977</v>
+        <v>50.1711769104004</v>
       </c>
       <c r="H1434" t="n">
         <v>787081</v>
@@ -41984,7 +41984,7 @@
         <v>54.6599998474121</v>
       </c>
       <c r="G1435" t="n">
-        <v>49.4118309020996</v>
+        <v>49.4118270874023</v>
       </c>
       <c r="H1435" t="n">
         <v>671471</v>
@@ -42100,7 +42100,7 @@
         <v>54.6199989318848</v>
       </c>
       <c r="G1439" t="n">
-        <v>49.3756713867188</v>
+        <v>49.3756675720215</v>
       </c>
       <c r="H1439" t="n">
         <v>293784</v>
@@ -42129,7 +42129,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>48.9959983825684</v>
+        <v>48.9959945678711</v>
       </c>
       <c r="H1440" t="n">
         <v>1707186</v>
@@ -42187,7 +42187,7 @@
         <v>54.8199996948242</v>
       </c>
       <c r="G1442" t="n">
-        <v>49.556468963623</v>
+        <v>49.5564651489258</v>
       </c>
       <c r="H1442" t="n">
         <v>359198</v>
@@ -42216,7 +42216,7 @@
         <v>54.0200004577637</v>
       </c>
       <c r="G1443" t="n">
-        <v>48.8332824707031</v>
+        <v>48.8332786560059</v>
       </c>
       <c r="H1443" t="n">
         <v>584736</v>
@@ -42245,7 +42245,7 @@
         <v>54.939998626709</v>
       </c>
       <c r="G1444" t="n">
-        <v>49.6649436950684</v>
+        <v>49.6649398803711</v>
       </c>
       <c r="H1444" t="n">
         <v>534288</v>
@@ -42274,7 +42274,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1445" t="n">
-        <v>50.2615737915039</v>
+        <v>50.2615776062012</v>
       </c>
       <c r="H1445" t="n">
         <v>651684</v>
@@ -42477,7 +42477,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G1452" t="n">
-        <v>46.7360305786133</v>
+        <v>46.7360343933105</v>
       </c>
       <c r="H1452" t="n">
         <v>908760</v>
@@ -42535,7 +42535,7 @@
         <v>51.6599998474121</v>
       </c>
       <c r="G1454" t="n">
-        <v>46.6998748779297</v>
+        <v>46.6998710632324</v>
       </c>
       <c r="H1454" t="n">
         <v>696284</v>
@@ -42593,7 +42593,7 @@
         <v>54.3600006103516</v>
       </c>
       <c r="G1456" t="n">
-        <v>49.1406364440918</v>
+        <v>49.1406326293945</v>
       </c>
       <c r="H1456" t="n">
         <v>835925</v>
@@ -42651,7 +42651,7 @@
         <v>55</v>
       </c>
       <c r="G1458" t="n">
-        <v>49.719181060791</v>
+        <v>49.7191848754883</v>
       </c>
       <c r="H1458" t="n">
         <v>615681</v>
@@ -42738,7 +42738,7 @@
         <v>52.939998626709</v>
       </c>
       <c r="G1461" t="n">
-        <v>47.8569679260254</v>
+        <v>47.8569717407227</v>
       </c>
       <c r="H1461" t="n">
         <v>371331</v>
@@ -42796,7 +42796,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G1463" t="n">
-        <v>48.9959983825684</v>
+        <v>48.9959945678711</v>
       </c>
       <c r="H1463" t="n">
         <v>846158</v>
@@ -42825,7 +42825,7 @@
         <v>54.8199996948242</v>
       </c>
       <c r="G1464" t="n">
-        <v>49.556468963623</v>
+        <v>49.5564651489258</v>
       </c>
       <c r="H1464" t="n">
         <v>856152</v>
@@ -42941,7 +42941,7 @@
         <v>56.439998626709</v>
       </c>
       <c r="G1468" t="n">
-        <v>51.0209159851074</v>
+        <v>51.020923614502</v>
       </c>
       <c r="H1468" t="n">
         <v>339395</v>
@@ -43086,7 +43086,7 @@
         <v>58.7999992370605</v>
       </c>
       <c r="G1473" t="n">
-        <v>53.1543312072754</v>
+        <v>53.1543273925781</v>
       </c>
       <c r="H1473" t="n">
         <v>467472</v>
@@ -43115,7 +43115,7 @@
         <v>58.2799987792969</v>
       </c>
       <c r="G1474" t="n">
-        <v>52.6842575073242</v>
+        <v>52.684253692627</v>
       </c>
       <c r="H1474" t="n">
         <v>634098</v>
@@ -43173,7 +43173,7 @@
         <v>59.7400016784668</v>
       </c>
       <c r="G1476" t="n">
-        <v>54.0040702819824</v>
+        <v>54.0040740966797</v>
       </c>
       <c r="H1476" t="n">
         <v>649440</v>
@@ -43231,7 +43231,7 @@
         <v>61.0200004577637</v>
       </c>
       <c r="G1478" t="n">
-        <v>55.1611785888672</v>
+        <v>55.1611709594727</v>
       </c>
       <c r="H1478" t="n">
         <v>603050</v>
@@ -43289,7 +43289,7 @@
         <v>60.6199989318848</v>
       </c>
       <c r="G1480" t="n">
-        <v>54.7995758056641</v>
+        <v>54.7995834350586</v>
       </c>
       <c r="H1480" t="n">
         <v>579896</v>
@@ -43318,7 +43318,7 @@
         <v>60.1800003051758</v>
       </c>
       <c r="G1481" t="n">
-        <v>54.4018287658691</v>
+        <v>54.4018249511719</v>
       </c>
       <c r="H1481" t="n">
         <v>623963</v>
@@ -43347,7 +43347,7 @@
         <v>61.2200012207031</v>
       </c>
       <c r="G1482" t="n">
-        <v>55.3419723510742</v>
+        <v>55.3419761657715</v>
       </c>
       <c r="H1482" t="n">
         <v>637932</v>
@@ -43550,7 +43550,7 @@
         <v>68.1600036621094</v>
       </c>
       <c r="G1489" t="n">
-        <v>61.6156349182129</v>
+        <v>61.6156387329102</v>
       </c>
       <c r="H1489" t="n">
         <v>747874</v>
@@ -43637,7 +43637,7 @@
         <v>66.4599990844727</v>
       </c>
       <c r="G1492" t="n">
-        <v>60.078857421875</v>
+        <v>60.0788459777832</v>
       </c>
       <c r="H1492" t="n">
         <v>723413</v>
@@ -43782,7 +43782,7 @@
         <v>68.3399963378906</v>
       </c>
       <c r="G1497" t="n">
-        <v>61.7783470153809</v>
+        <v>61.7783432006836</v>
       </c>
       <c r="H1497" t="n">
         <v>1103847</v>
@@ -43811,7 +43811,7 @@
         <v>67.8000030517578</v>
       </c>
       <c r="G1498" t="n">
-        <v>61.2901954650879</v>
+        <v>61.2901992797852</v>
       </c>
       <c r="H1498" t="n">
         <v>898555</v>
@@ -43840,7 +43840,7 @@
         <v>68.7600021362305</v>
       </c>
       <c r="G1499" t="n">
-        <v>62.1580238342285</v>
+        <v>62.1580200195312</v>
       </c>
       <c r="H1499" t="n">
         <v>642088</v>
@@ -43869,7 +43869,7 @@
         <v>66.1600036621094</v>
       </c>
       <c r="G1500" t="n">
-        <v>59.8076629638672</v>
+        <v>59.8076667785645</v>
       </c>
       <c r="H1500" t="n">
         <v>1062917</v>
@@ -43898,7 +43898,7 @@
         <v>66.5599975585938</v>
       </c>
       <c r="G1501" t="n">
-        <v>60.169246673584</v>
+        <v>60.1692504882812</v>
       </c>
       <c r="H1501" t="n">
         <v>552520</v>
@@ -43956,7 +43956,7 @@
         <v>62.7200012207031</v>
       </c>
       <c r="G1503" t="n">
-        <v>56.6979560852051</v>
+        <v>56.6979484558105</v>
       </c>
       <c r="H1503" t="n">
         <v>1201347</v>
@@ -44043,7 +44043,7 @@
         <v>65.620002746582</v>
       </c>
       <c r="G1506" t="n">
-        <v>59.319507598877</v>
+        <v>59.3195037841797</v>
       </c>
       <c r="H1506" t="n">
         <v>803677</v>
@@ -44072,7 +44072,7 @@
         <v>65.5199966430664</v>
       </c>
       <c r="G1507" t="n">
-        <v>59.2290992736816</v>
+        <v>59.2291030883789</v>
       </c>
       <c r="H1507" t="n">
         <v>642706</v>
@@ -44130,7 +44130,7 @@
         <v>66.3199996948242</v>
       </c>
       <c r="G1509" t="n">
-        <v>59.9522972106934</v>
+        <v>59.9522933959961</v>
       </c>
       <c r="H1509" t="n">
         <v>470818</v>
@@ -44217,7 +44217,7 @@
         <v>66.8199996948242</v>
       </c>
       <c r="G1512" t="n">
-        <v>60.4042892456055</v>
+        <v>60.4042854309082</v>
       </c>
       <c r="H1512" t="n">
         <v>463060</v>
@@ -44246,7 +44246,7 @@
         <v>66.0599975585938</v>
       </c>
       <c r="G1513" t="n">
-        <v>59.7172546386719</v>
+        <v>59.7172584533691</v>
       </c>
       <c r="H1513" t="n">
         <v>575102</v>
@@ -44333,7 +44333,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1516" t="n">
-        <v>58.4878425598145</v>
+        <v>58.4878387451172</v>
       </c>
       <c r="H1516" t="n">
         <v>666887</v>
@@ -44478,7 +44478,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G1521" t="n">
-        <v>56.679874420166</v>
+        <v>56.6798706054688</v>
       </c>
       <c r="H1521" t="n">
         <v>312156</v>
@@ -44565,7 +44565,7 @@
         <v>64.2399978637695</v>
       </c>
       <c r="G1524" t="n">
-        <v>58.0720062255859</v>
+        <v>58.0720024108887</v>
       </c>
       <c r="H1524" t="n">
         <v>265608</v>
@@ -44797,7 +44797,7 @@
         <v>60.6199989318848</v>
       </c>
       <c r="G1532" t="n">
-        <v>54.7995758056641</v>
+        <v>54.7995834350586</v>
       </c>
       <c r="H1532" t="n">
         <v>717719</v>
@@ -44826,7 +44826,7 @@
         <v>60.3800010681152</v>
       </c>
       <c r="G1533" t="n">
-        <v>54.5826225280762</v>
+        <v>54.5826263427734</v>
       </c>
       <c r="H1533" t="n">
         <v>655214</v>
@@ -44942,7 +44942,7 @@
         <v>57.7400016784668</v>
       </c>
       <c r="G1537" t="n">
-        <v>52.196102142334</v>
+        <v>52.1961059570312</v>
       </c>
       <c r="H1537" t="n">
         <v>615447</v>
@@ -44971,7 +44971,7 @@
         <v>56.560001373291</v>
       </c>
       <c r="G1538" t="n">
-        <v>51.1294059753418</v>
+        <v>51.1293983459473</v>
       </c>
       <c r="H1538" t="n">
         <v>825603</v>
@@ -45029,7 +45029,7 @@
         <v>58.4199981689453</v>
       </c>
       <c r="G1540" t="n">
-        <v>52.8108139038086</v>
+        <v>52.8108100891113</v>
       </c>
       <c r="H1540" t="n">
         <v>801918</v>
@@ -45087,7 +45087,7 @@
         <v>55.5800018310547</v>
       </c>
       <c r="G1542" t="n">
-        <v>50.2434959411621</v>
+        <v>50.2434997558594</v>
       </c>
       <c r="H1542" t="n">
         <v>745435</v>
@@ -45116,7 +45116,7 @@
         <v>55.1199989318848</v>
       </c>
       <c r="G1543" t="n">
-        <v>49.8276634216309</v>
+        <v>49.8276596069336</v>
       </c>
       <c r="H1543" t="n">
         <v>766368</v>
@@ -45174,7 +45174,7 @@
         <v>56.4799995422363</v>
       </c>
       <c r="G1545" t="n">
-        <v>51.0570869445801</v>
+        <v>51.0570831298828</v>
       </c>
       <c r="H1545" t="n">
         <v>723919</v>
@@ -45203,7 +45203,7 @@
         <v>55.439998626709</v>
       </c>
       <c r="G1546" t="n">
-        <v>50.1169357299805</v>
+        <v>50.1169395446777</v>
       </c>
       <c r="H1546" t="n">
         <v>892110</v>
@@ -45261,7 +45261,7 @@
         <v>59.0200004577637</v>
       </c>
       <c r="G1548" t="n">
-        <v>53.3532028198242</v>
+        <v>53.3532066345215</v>
       </c>
       <c r="H1548" t="n">
         <v>1181627</v>
@@ -45290,7 +45290,7 @@
         <v>59.4199981689453</v>
       </c>
       <c r="G1549" t="n">
-        <v>53.7147979736328</v>
+        <v>53.7147941589355</v>
       </c>
       <c r="H1549" t="n">
         <v>770651</v>
@@ -45319,7 +45319,7 @@
         <v>57.8800010681152</v>
       </c>
       <c r="G1550" t="n">
-        <v>52.3226623535156</v>
+        <v>52.3226661682129</v>
       </c>
       <c r="H1550" t="n">
         <v>707003</v>
@@ -45348,7 +45348,7 @@
         <v>58</v>
       </c>
       <c r="G1551" t="n">
-        <v>52.4311408996582</v>
+        <v>52.4311370849609</v>
       </c>
       <c r="H1551" t="n">
         <v>784948</v>
@@ -45406,7 +45406,7 @@
         <v>56.8400001525879</v>
       </c>
       <c r="G1553" t="n">
-        <v>51.3825187683105</v>
+        <v>51.3825149536133</v>
       </c>
       <c r="H1553" t="n">
         <v>399743</v>
@@ -45435,7 +45435,7 @@
         <v>58.1599998474121</v>
       </c>
       <c r="G1554" t="n">
-        <v>52.5757751464844</v>
+        <v>52.5757789611816</v>
       </c>
       <c r="H1554" t="n">
         <v>399952</v>
@@ -45493,7 +45493,7 @@
         <v>55.5200004577637</v>
       </c>
       <c r="G1556" t="n">
-        <v>50.1892509460449</v>
+        <v>50.1892547607422</v>
       </c>
       <c r="H1556" t="n">
         <v>639440</v>
@@ -45696,7 +45696,7 @@
         <v>54.7400016784668</v>
       </c>
       <c r="G1563" t="n">
-        <v>49.4841499328613</v>
+        <v>49.4841537475586</v>
       </c>
       <c r="H1563" t="n">
         <v>625013</v>
@@ -45725,7 +45725,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G1564" t="n">
-        <v>49.4479866027832</v>
+        <v>49.4479904174805</v>
       </c>
       <c r="H1564" t="n">
         <v>679546</v>
@@ -45783,7 +45783,7 @@
         <v>54.7000007629395</v>
       </c>
       <c r="G1566" t="n">
-        <v>49.4479866027832</v>
+        <v>49.4479904174805</v>
       </c>
       <c r="H1566" t="n">
         <v>1509389</v>
@@ -45841,7 +45841,7 @@
         <v>49.2400016784668</v>
       </c>
       <c r="G1568" t="n">
-        <v>44.5122299194336</v>
+        <v>44.5122337341309</v>
       </c>
       <c r="H1568" t="n">
         <v>1499119</v>
@@ -45899,7 +45899,7 @@
         <v>48.3199996948242</v>
       </c>
       <c r="G1570" t="n">
-        <v>43.6805610656738</v>
+        <v>43.6805648803711</v>
       </c>
       <c r="H1570" t="n">
         <v>906670</v>
@@ -45957,7 +45957,7 @@
         <v>45.310001373291</v>
       </c>
       <c r="G1572" t="n">
-        <v>40.9595756530762</v>
+        <v>40.9595718383789</v>
       </c>
       <c r="H1572" t="n">
         <v>1434836</v>
@@ -46015,7 +46015,7 @@
         <v>48.3499984741211</v>
       </c>
       <c r="G1574" t="n">
-        <v>43.7076835632324</v>
+        <v>43.7076797485352</v>
       </c>
       <c r="H1574" t="n">
         <v>1336574</v>
@@ -46102,7 +46102,7 @@
         <v>48</v>
       </c>
       <c r="G1577" t="n">
-        <v>43.3912887573242</v>
+        <v>43.3912925720215</v>
       </c>
       <c r="H1577" t="n">
         <v>713950</v>
@@ -46131,7 +46131,7 @@
         <v>46.4900016784668</v>
       </c>
       <c r="G1578" t="n">
-        <v>42.0262756347656</v>
+        <v>42.0262718200684</v>
       </c>
       <c r="H1578" t="n">
         <v>1241906</v>
@@ -46160,7 +46160,7 @@
         <v>49.1399993896484</v>
       </c>
       <c r="G1579" t="n">
-        <v>44.4218254089355</v>
+        <v>44.4218292236328</v>
       </c>
       <c r="H1579" t="n">
         <v>1113127</v>
@@ -46247,7 +46247,7 @@
         <v>50.6399993896484</v>
       </c>
       <c r="G1582" t="n">
-        <v>45.7778091430664</v>
+        <v>45.7778015136719</v>
       </c>
       <c r="H1582" t="n">
         <v>538124</v>
@@ -46305,7 +46305,7 @@
         <v>49.7700004577637</v>
       </c>
       <c r="G1584" t="n">
-        <v>44.9913444519043</v>
+        <v>44.991340637207</v>
       </c>
       <c r="H1584" t="n">
         <v>533956</v>
@@ -46392,7 +46392,7 @@
         <v>49.75</v>
       </c>
       <c r="G1587" t="n">
-        <v>44.9732551574707</v>
+        <v>44.973258972168</v>
       </c>
       <c r="H1587" t="n">
         <v>459316</v>
@@ -46421,7 +46421,7 @@
         <v>52.5400009155273</v>
       </c>
       <c r="G1588" t="n">
-        <v>47.4953804016113</v>
+        <v>47.4953842163086</v>
       </c>
       <c r="H1588" t="n">
         <v>844588</v>
@@ -46479,7 +46479,7 @@
         <v>50.7400016784668</v>
       </c>
       <c r="G1590" t="n">
-        <v>45.8682098388672</v>
+        <v>45.8682060241699</v>
       </c>
       <c r="H1590" t="n">
         <v>602730</v>
@@ -46595,7 +46595,7 @@
         <v>50.4799995422363</v>
       </c>
       <c r="G1594" t="n">
-        <v>45.633171081543</v>
+        <v>45.6331672668457</v>
       </c>
       <c r="H1594" t="n">
         <v>737895</v>
@@ -46624,7 +46624,7 @@
         <v>49.439998626709</v>
       </c>
       <c r="G1595" t="n">
-        <v>44.6930236816406</v>
+        <v>44.6930274963379</v>
       </c>
       <c r="H1595" t="n">
         <v>562356</v>
@@ -46653,7 +46653,7 @@
         <v>51</v>
       </c>
       <c r="G1596" t="n">
-        <v>46.1032409667969</v>
+        <v>46.1032447814941</v>
       </c>
       <c r="H1596" t="n">
         <v>616704</v>
@@ -46682,7 +46682,7 @@
         <v>48.5499992370605</v>
       </c>
       <c r="G1597" t="n">
-        <v>43.888484954834</v>
+        <v>43.8884811401367</v>
       </c>
       <c r="H1597" t="n">
         <v>1102782</v>
@@ -46740,7 +46740,7 @@
         <v>49.939998626709</v>
       </c>
       <c r="G1599" t="n">
-        <v>45.14501953125</v>
+        <v>45.1450233459473</v>
       </c>
       <c r="H1599" t="n">
         <v>977874</v>
@@ -46856,7 +46856,7 @@
         <v>51.1599998474121</v>
       </c>
       <c r="G1603" t="n">
-        <v>46.2478828430176</v>
+        <v>46.2478790283203</v>
       </c>
       <c r="H1603" t="n">
         <v>625029</v>
@@ -46885,7 +46885,7 @@
         <v>50.0200004577637</v>
       </c>
       <c r="G1604" t="n">
-        <v>45.2173385620117</v>
+        <v>45.217342376709</v>
       </c>
       <c r="H1604" t="n">
         <v>1027627</v>
@@ -46972,7 +46972,7 @@
         <v>48.8400001525879</v>
       </c>
       <c r="G1607" t="n">
-        <v>44.1506309509277</v>
+        <v>44.150634765625</v>
       </c>
       <c r="H1607" t="n">
         <v>731703</v>
@@ -47030,7 +47030,7 @@
         <v>50.2799987792969</v>
       </c>
       <c r="G1609" t="n">
-        <v>45.4523696899414</v>
+        <v>45.4523735046387</v>
       </c>
       <c r="H1609" t="n">
         <v>582414</v>
@@ -47088,7 +47088,7 @@
         <v>47.9599990844727</v>
       </c>
       <c r="G1611" t="n">
-        <v>43.3551292419434</v>
+        <v>43.3551254272461</v>
       </c>
       <c r="H1611" t="n">
         <v>641246</v>
@@ -47117,7 +47117,7 @@
         <v>47.2599983215332</v>
       </c>
       <c r="G1612" t="n">
-        <v>42.7223358154297</v>
+        <v>42.722339630127</v>
       </c>
       <c r="H1612" t="n">
         <v>991991</v>
@@ -47146,7 +47146,7 @@
         <v>44.5999984741211</v>
       </c>
       <c r="G1613" t="n">
-        <v>40.3177375793457</v>
+        <v>40.3177337646484</v>
       </c>
       <c r="H1613" t="n">
         <v>1511817</v>
@@ -47204,7 +47204,7 @@
         <v>41.8300018310547</v>
       </c>
       <c r="G1615" t="n">
-        <v>37.8137016296387</v>
+        <v>37.8136978149414</v>
       </c>
       <c r="H1615" t="n">
         <v>778010</v>
@@ -47262,7 +47262,7 @@
         <v>44.7400016784668</v>
       </c>
       <c r="G1617" t="n">
-        <v>40.4443016052246</v>
+        <v>40.4442939758301</v>
       </c>
       <c r="H1617" t="n">
         <v>1032613</v>
@@ -47378,7 +47378,7 @@
         <v>45.2700004577637</v>
       </c>
       <c r="G1621" t="n">
-        <v>40.9234046936035</v>
+        <v>40.923412322998</v>
       </c>
       <c r="H1621" t="n">
         <v>524847</v>
@@ -47436,7 +47436,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G1623" t="n">
-        <v>38.9617538452148</v>
+        <v>38.9617614746094</v>
       </c>
       <c r="H1623" t="n">
         <v>934998</v>
@@ -47494,7 +47494,7 @@
         <v>42.2799987792969</v>
       </c>
       <c r="G1625" t="n">
-        <v>38.7709503173828</v>
+        <v>38.7709541320801</v>
       </c>
       <c r="H1625" t="n">
         <v>657342</v>
@@ -47581,7 +47581,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1628" t="n">
-        <v>38.6975936889648</v>
+        <v>38.6975975036621</v>
       </c>
       <c r="H1628" t="n">
         <v>1055847</v>
@@ -47610,7 +47610,7 @@
         <v>43.0900001525879</v>
       </c>
       <c r="G1629" t="n">
-        <v>39.5137329101562</v>
+        <v>39.513729095459</v>
       </c>
       <c r="H1629" t="n">
         <v>907088</v>
@@ -47639,7 +47639,7 @@
         <v>44.8899993896484</v>
       </c>
       <c r="G1630" t="n">
-        <v>41.1643371582031</v>
+        <v>41.1643333435059</v>
       </c>
       <c r="H1630" t="n">
         <v>961465</v>
@@ -47668,7 +47668,7 @@
         <v>44.7000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>40.990104675293</v>
+        <v>40.9901084899902</v>
       </c>
       <c r="H1631" t="n">
         <v>1574338</v>
@@ -47697,7 +47697,7 @@
         <v>44.8899993896484</v>
       </c>
       <c r="G1632" t="n">
-        <v>41.1643371582031</v>
+        <v>41.1643333435059</v>
       </c>
       <c r="H1632" t="n">
         <v>743616</v>
@@ -47755,7 +47755,7 @@
         <v>45.8899993896484</v>
       </c>
       <c r="G1634" t="n">
-        <v>42.0813407897949</v>
+        <v>42.0813446044922</v>
       </c>
       <c r="H1634" t="n">
         <v>572132</v>
@@ -47842,7 +47842,7 @@
         <v>44.6300010681152</v>
       </c>
       <c r="G1637" t="n">
-        <v>40.9259223937988</v>
+        <v>40.9259185791016</v>
       </c>
       <c r="H1637" t="n">
         <v>548854</v>
@@ -47929,7 +47929,7 @@
         <v>39.439998626709</v>
       </c>
       <c r="G1640" t="n">
-        <v>36.1666564941406</v>
+        <v>36.1666603088379</v>
       </c>
       <c r="H1640" t="n">
         <v>658135</v>
@@ -48016,7 +48016,7 @@
         <v>37.4900016784668</v>
       </c>
       <c r="G1643" t="n">
-        <v>34.3785018920898</v>
+        <v>34.3785057067871</v>
       </c>
       <c r="H1643" t="n">
         <v>826231</v>
@@ -48045,7 +48045,7 @@
         <v>37.189998626709</v>
       </c>
       <c r="G1644" t="n">
-        <v>34.103401184082</v>
+        <v>34.1033973693848</v>
       </c>
       <c r="H1644" t="n">
         <v>1414667</v>
@@ -48103,7 +48103,7 @@
         <v>37.0900001525879</v>
       </c>
       <c r="G1646" t="n">
-        <v>34.0117034912109</v>
+        <v>34.0117073059082</v>
       </c>
       <c r="H1646" t="n">
         <v>560768</v>
@@ -48190,7 +48190,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G1649" t="n">
-        <v>36.4050827026367</v>
+        <v>36.405086517334</v>
       </c>
       <c r="H1649" t="n">
         <v>901918</v>
@@ -48219,7 +48219,7 @@
         <v>39.9599990844727</v>
       </c>
       <c r="G1650" t="n">
-        <v>36.6435012817383</v>
+        <v>36.6435050964355</v>
       </c>
       <c r="H1650" t="n">
         <v>885566</v>
@@ -48422,7 +48422,7 @@
         <v>41.2200012207031</v>
       </c>
       <c r="G1657" t="n">
-        <v>37.7989349365234</v>
+        <v>37.7989311218262</v>
       </c>
       <c r="H1657" t="n">
         <v>526824</v>
@@ -48480,7 +48480,7 @@
         <v>41.4799995422363</v>
       </c>
       <c r="G1659" t="n">
-        <v>38.037353515625</v>
+        <v>38.0373497009277</v>
       </c>
       <c r="H1659" t="n">
         <v>424091</v>
@@ -48509,7 +48509,7 @@
         <v>40.8300018310547</v>
       </c>
       <c r="G1660" t="n">
-        <v>37.4412956237793</v>
+        <v>37.4412994384766</v>
       </c>
       <c r="H1660" t="n">
         <v>307116</v>
@@ -48567,7 +48567,7 @@
         <v>40.9799995422363</v>
       </c>
       <c r="G1662" t="n">
-        <v>37.5788497924805</v>
+        <v>37.5788459777832</v>
       </c>
       <c r="H1662" t="n">
         <v>533084</v>
@@ -48625,7 +48625,7 @@
         <v>40.0900001525879</v>
       </c>
       <c r="G1664" t="n">
-        <v>36.7627182006836</v>
+        <v>36.7627143859863</v>
       </c>
       <c r="H1664" t="n">
         <v>604033</v>
@@ -48683,7 +48683,7 @@
         <v>42.560001373291</v>
       </c>
       <c r="G1666" t="n">
-        <v>39.0277214050293</v>
+        <v>39.027717590332</v>
       </c>
       <c r="H1666" t="n">
         <v>473754</v>
@@ -48770,7 +48770,7 @@
         <v>43.6100006103516</v>
       </c>
       <c r="G1669" t="n">
-        <v>39.9905738830566</v>
+        <v>39.9905700683594</v>
       </c>
       <c r="H1669" t="n">
         <v>476741</v>
@@ -48799,7 +48799,7 @@
         <v>44.0400009155273</v>
       </c>
       <c r="G1670" t="n">
-        <v>40.3848838806152</v>
+        <v>40.3848876953125</v>
       </c>
       <c r="H1670" t="n">
         <v>398887</v>
@@ -48828,7 +48828,7 @@
         <v>42.0299987792969</v>
       </c>
       <c r="G1671" t="n">
-        <v>38.5417022705078</v>
+        <v>38.5417060852051</v>
       </c>
       <c r="H1671" t="n">
         <v>675725</v>
@@ -48857,7 +48857,7 @@
         <v>43.1599998474121</v>
       </c>
       <c r="G1672" t="n">
-        <v>39.5779190063477</v>
+        <v>39.5779228210449</v>
       </c>
       <c r="H1672" t="n">
         <v>652068</v>
@@ -48915,7 +48915,7 @@
         <v>48.6699981689453</v>
       </c>
       <c r="G1674" t="n">
-        <v>44.6306114196777</v>
+        <v>44.630615234375</v>
       </c>
       <c r="H1674" t="n">
         <v>1448455</v>
@@ -48973,7 +48973,7 @@
         <v>47.7400016784668</v>
       </c>
       <c r="G1676" t="n">
-        <v>43.7778015136719</v>
+        <v>43.7778053283691</v>
       </c>
       <c r="H1676" t="n">
         <v>1024710</v>
@@ -49002,7 +49002,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G1677" t="n">
-        <v>44.062068939209</v>
+        <v>44.0620727539062</v>
       </c>
       <c r="H1677" t="n">
         <v>385128</v>
@@ -49089,7 +49089,7 @@
         <v>49.2799987792969</v>
       </c>
       <c r="G1680" t="n">
-        <v>45.1899871826172</v>
+        <v>45.1899909973145</v>
       </c>
       <c r="H1680" t="n">
         <v>339827</v>
@@ -49147,7 +49147,7 @@
         <v>49.5099983215332</v>
       </c>
       <c r="G1682" t="n">
-        <v>45.4008979797363</v>
+        <v>45.4008941650391</v>
       </c>
       <c r="H1682" t="n">
         <v>375934</v>
@@ -49176,7 +49176,7 @@
         <v>49.7599983215332</v>
       </c>
       <c r="G1683" t="n">
-        <v>45.6301498413086</v>
+        <v>45.6301536560059</v>
       </c>
       <c r="H1683" t="n">
         <v>400898</v>
@@ -49263,7 +49263,7 @@
         <v>48.7599983215332</v>
       </c>
       <c r="G1686" t="n">
-        <v>44.7131462097168</v>
+        <v>44.7131423950195</v>
       </c>
       <c r="H1686" t="n">
         <v>411955</v>
@@ -49350,7 +49350,7 @@
         <v>46.6599998474121</v>
       </c>
       <c r="G1689" t="n">
-        <v>42.7874336242676</v>
+        <v>42.7874374389648</v>
       </c>
       <c r="H1689" t="n">
         <v>563509</v>
@@ -49408,7 +49408,7 @@
         <v>47.9199981689453</v>
       </c>
       <c r="G1691" t="n">
-        <v>43.9428634643555</v>
+        <v>43.9428596496582</v>
       </c>
       <c r="H1691" t="n">
         <v>243165</v>
@@ -49437,7 +49437,7 @@
         <v>47.9799995422363</v>
       </c>
       <c r="G1692" t="n">
-        <v>43.9978866577148</v>
+        <v>43.9978828430176</v>
       </c>
       <c r="H1692" t="n">
         <v>304849</v>
@@ -49495,7 +49495,7 @@
         <v>44.6699981689453</v>
       </c>
       <c r="G1694" t="n">
-        <v>40.9625930786133</v>
+        <v>40.9625968933105</v>
       </c>
       <c r="H1694" t="n">
         <v>512613</v>
@@ -49524,7 +49524,7 @@
         <v>44.8400001525879</v>
       </c>
       <c r="G1695" t="n">
-        <v>41.1184883117676</v>
+        <v>41.1184844970703</v>
       </c>
       <c r="H1695" t="n">
         <v>420782</v>
@@ -49611,7 +49611,7 @@
         <v>44.75</v>
       </c>
       <c r="G1698" t="n">
-        <v>41.0359535217285</v>
+        <v>41.0359573364258</v>
       </c>
       <c r="H1698" t="n">
         <v>441045</v>
@@ -49669,7 +49669,7 @@
         <v>43.6399993896484</v>
       </c>
       <c r="G1700" t="n">
-        <v>40.0180778503418</v>
+        <v>40.0180816650391</v>
       </c>
       <c r="H1700" t="n">
         <v>373850</v>
@@ -49698,7 +49698,7 @@
         <v>43.8699989318848</v>
       </c>
       <c r="G1701" t="n">
-        <v>40.2289886474609</v>
+        <v>40.2289924621582</v>
       </c>
       <c r="H1701" t="n">
         <v>362220</v>
@@ -49756,7 +49756,7 @@
         <v>45.0099983215332</v>
       </c>
       <c r="G1703" t="n">
-        <v>41.2743759155273</v>
+        <v>41.2743797302246</v>
       </c>
       <c r="H1703" t="n">
         <v>558865</v>
@@ -49785,7 +49785,7 @@
         <v>45.5699996948242</v>
       </c>
       <c r="G1704" t="n">
-        <v>41.787899017334</v>
+        <v>41.7879028320312</v>
       </c>
       <c r="H1704" t="n">
         <v>473241</v>
@@ -49814,7 +49814,7 @@
         <v>44.5299987792969</v>
       </c>
       <c r="G1705" t="n">
-        <v>40.8342170715332</v>
+        <v>40.8342132568359</v>
       </c>
       <c r="H1705" t="n">
         <v>596099</v>
@@ -49843,7 +49843,7 @@
         <v>45.2700004577637</v>
       </c>
       <c r="G1706" t="n">
-        <v>41.5127983093262</v>
+        <v>41.5128021240234</v>
       </c>
       <c r="H1706" t="n">
         <v>581315</v>
@@ -49959,7 +49959,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G1710" t="n">
-        <v>40.6233024597168</v>
+        <v>40.6233062744141</v>
       </c>
       <c r="H1710" t="n">
         <v>557779</v>
@@ -50046,7 +50046,7 @@
         <v>41.6100006103516</v>
       </c>
       <c r="G1713" t="n">
-        <v>38.1565589904785</v>
+        <v>38.1565628051758</v>
       </c>
       <c r="H1713" t="n">
         <v>811954</v>
@@ -50075,7 +50075,7 @@
         <v>43.0499992370605</v>
       </c>
       <c r="G1714" t="n">
-        <v>39.4770469665527</v>
+        <v>39.47705078125</v>
       </c>
       <c r="H1714" t="n">
         <v>805678</v>
@@ -50336,7 +50336,7 @@
         <v>44.4799995422363</v>
       </c>
       <c r="G1723" t="n">
-        <v>40.7883682250977</v>
+        <v>40.7883644104004</v>
       </c>
       <c r="H1723" t="n">
         <v>607719</v>
@@ -50394,7 +50394,7 @@
         <v>44.3699989318848</v>
       </c>
       <c r="G1725" t="n">
-        <v>40.6875</v>
+        <v>40.6874961853027</v>
       </c>
       <c r="H1725" t="n">
         <v>650692</v>
@@ -50423,7 +50423,7 @@
         <v>45.5999984741211</v>
       </c>
       <c r="G1726" t="n">
-        <v>41.8154067993164</v>
+        <v>41.8154106140137</v>
       </c>
       <c r="H1726" t="n">
         <v>959182</v>
@@ -50452,7 +50452,7 @@
         <v>45.2000007629395</v>
       </c>
       <c r="G1727" t="n">
-        <v>41.448616027832</v>
+        <v>41.4486122131348</v>
       </c>
       <c r="H1727" t="n">
         <v>1009032</v>
@@ -50510,7 +50510,7 @@
         <v>46.4199981689453</v>
       </c>
       <c r="G1729" t="n">
-        <v>42.5673561096191</v>
+        <v>42.5673522949219</v>
       </c>
       <c r="H1729" t="n">
         <v>747030</v>
@@ -50539,7 +50539,7 @@
         <v>46.689998626709</v>
       </c>
       <c r="G1730" t="n">
-        <v>42.8149452209473</v>
+        <v>42.8149490356445</v>
       </c>
       <c r="H1730" t="n">
         <v>673135</v>
@@ -50597,7 +50597,7 @@
         <v>47.3400001525879</v>
       </c>
       <c r="G1732" t="n">
-        <v>43.4109992980957</v>
+        <v>43.411003112793</v>
       </c>
       <c r="H1732" t="n">
         <v>1120303</v>
@@ -50626,7 +50626,7 @@
         <v>45.9500007629395</v>
       </c>
       <c r="G1733" t="n">
-        <v>42.1363639831543</v>
+        <v>42.1363677978516</v>
       </c>
       <c r="H1733" t="n">
         <v>915604</v>
@@ -50655,7 +50655,7 @@
         <v>46.0299987792969</v>
       </c>
       <c r="G1734" t="n">
-        <v>42.2097244262695</v>
+        <v>42.2097206115723</v>
       </c>
       <c r="H1734" t="n">
         <v>881810</v>
@@ -50713,7 +50713,7 @@
         <v>48.4000015258789</v>
       </c>
       <c r="G1736" t="n">
-        <v>44.3830299377441</v>
+        <v>44.3830261230469</v>
       </c>
       <c r="H1736" t="n">
         <v>779016</v>
@@ -50800,7 +50800,7 @@
         <v>43.689998626709</v>
       </c>
       <c r="G1739" t="n">
-        <v>40.0639343261719</v>
+        <v>40.0639305114746</v>
       </c>
       <c r="H1739" t="n">
         <v>929757</v>
@@ -50829,7 +50829,7 @@
         <v>44.1800003051758</v>
       </c>
       <c r="G1740" t="n">
-        <v>40.5132598876953</v>
+        <v>40.5132637023926</v>
       </c>
       <c r="H1740" t="n">
         <v>758077</v>
@@ -50916,7 +50916,7 @@
         <v>45.3899993896484</v>
       </c>
       <c r="G1743" t="n">
-        <v>41.6228408813477</v>
+        <v>41.6228370666504</v>
       </c>
       <c r="H1743" t="n">
         <v>1690841</v>
@@ -50974,7 +50974,7 @@
         <v>46.4500007629395</v>
       </c>
       <c r="G1745" t="n">
-        <v>42.5948638916016</v>
+        <v>42.5948677062988</v>
       </c>
       <c r="H1745" t="n">
         <v>649635</v>
@@ -51003,7 +51003,7 @@
         <v>46.7200012207031</v>
       </c>
       <c r="G1746" t="n">
-        <v>42.842456817627</v>
+        <v>42.8424606323242</v>
       </c>
       <c r="H1746" t="n">
         <v>503971</v>
@@ -51032,7 +51032,7 @@
         <v>49.5699996948242</v>
       </c>
       <c r="G1747" t="n">
-        <v>45.4559211730957</v>
+        <v>45.4559173583984</v>
       </c>
       <c r="H1747" t="n">
         <v>1170063</v>
@@ -51177,7 +51177,7 @@
         <v>49.8800010681152</v>
       </c>
       <c r="G1752" t="n">
-        <v>45.7401962280273</v>
+        <v>45.7401885986328</v>
       </c>
       <c r="H1752" t="n">
         <v>615979</v>
@@ -51293,7 +51293,7 @@
         <v>48.2900009155273</v>
       </c>
       <c r="G1756" t="n">
-        <v>44.282154083252</v>
+        <v>44.2821502685547</v>
       </c>
       <c r="H1756" t="n">
         <v>557018</v>
@@ -51380,7 +51380,7 @@
         <v>47.5</v>
       </c>
       <c r="G1759" t="n">
-        <v>43.5577201843262</v>
+        <v>43.5577239990234</v>
       </c>
       <c r="H1759" t="n">
         <v>564456</v>
@@ -51467,7 +51467,7 @@
         <v>49.8800010681152</v>
       </c>
       <c r="G1762" t="n">
-        <v>45.7401962280273</v>
+        <v>45.7401885986328</v>
       </c>
       <c r="H1762" t="n">
         <v>803165</v>
@@ -51583,7 +51583,7 @@
         <v>47.3400001525879</v>
       </c>
       <c r="G1766" t="n">
-        <v>43.4109992980957</v>
+        <v>43.411003112793</v>
       </c>
       <c r="H1766" t="n">
         <v>493981</v>
@@ -51641,7 +51641,7 @@
         <v>49.3699989318848</v>
       </c>
       <c r="G1768" t="n">
-        <v>45.2725219726562</v>
+        <v>45.272518157959</v>
       </c>
       <c r="H1768" t="n">
         <v>779194</v>
@@ -51757,7 +51757,7 @@
         <v>49.4199981689453</v>
       </c>
       <c r="G1772" t="n">
-        <v>45.3183670043945</v>
+        <v>45.3183708190918</v>
       </c>
       <c r="H1772" t="n">
         <v>1043622</v>
@@ -51873,7 +51873,7 @@
         <v>48.9099998474121</v>
       </c>
       <c r="G1776" t="n">
-        <v>44.8506965637207</v>
+        <v>44.8506927490234</v>
       </c>
       <c r="H1776" t="n">
         <v>548697</v>
@@ -51902,7 +51902,7 @@
         <v>48.4000015258789</v>
       </c>
       <c r="G1777" t="n">
-        <v>44.3830299377441</v>
+        <v>44.3830261230469</v>
       </c>
       <c r="H1777" t="n">
         <v>443168</v>
@@ -51931,7 +51931,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G1778" t="n">
-        <v>44.1079177856445</v>
+        <v>44.1079216003418</v>
       </c>
       <c r="H1778" t="n">
         <v>332804</v>
@@ -52076,7 +52076,7 @@
         <v>50.6599998474121</v>
       </c>
       <c r="G1783" t="n">
-        <v>46.4554557800293</v>
+        <v>46.455451965332</v>
       </c>
       <c r="H1783" t="n">
         <v>434995</v>
@@ -52395,7 +52395,7 @@
         <v>56.0400009155273</v>
       </c>
       <c r="G1794" t="n">
-        <v>51.3889427185059</v>
+        <v>51.3889389038086</v>
       </c>
       <c r="H1794" t="n">
         <v>626436</v>
@@ -52453,7 +52453,7 @@
         <v>55.0200004577637</v>
       </c>
       <c r="G1796" t="n">
-        <v>50.4535980224609</v>
+        <v>50.4535942077637</v>
       </c>
       <c r="H1796" t="n">
         <v>748242</v>
@@ -52482,7 +52482,7 @@
         <v>56.0400009155273</v>
       </c>
       <c r="G1797" t="n">
-        <v>51.3889427185059</v>
+        <v>51.3889389038086</v>
       </c>
       <c r="H1797" t="n">
         <v>460398</v>
@@ -52627,7 +52627,7 @@
         <v>57.7799987792969</v>
       </c>
       <c r="G1802" t="n">
-        <v>52.9845237731934</v>
+        <v>52.9845314025879</v>
       </c>
       <c r="H1802" t="n">
         <v>1014541</v>
@@ -52830,7 +52830,7 @@
         <v>57.2599983215332</v>
       </c>
       <c r="G1809" t="n">
-        <v>52.5076866149902</v>
+        <v>52.507682800293</v>
       </c>
       <c r="H1809" t="n">
         <v>454977</v>
@@ -52975,7 +52975,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G1814" t="n">
-        <v>51.9941596984863</v>
+        <v>51.9941673278809</v>
       </c>
       <c r="H1814" t="n">
         <v>543033</v>
@@ -53062,7 +53062,7 @@
         <v>57.6599998474121</v>
       </c>
       <c r="G1817" t="n">
-        <v>52.8744888305664</v>
+        <v>52.8744850158691</v>
       </c>
       <c r="H1817" t="n">
         <v>591017</v>
@@ -53120,7 +53120,7 @@
         <v>58.6599998474121</v>
       </c>
       <c r="G1819" t="n">
-        <v>53.7914886474609</v>
+        <v>53.7914924621582</v>
       </c>
       <c r="H1819" t="n">
         <v>721037</v>
@@ -53149,7 +53149,7 @@
         <v>58.6199989318848</v>
       </c>
       <c r="G1820" t="n">
-        <v>53.754810333252</v>
+        <v>53.7548141479492</v>
       </c>
       <c r="H1820" t="n">
         <v>619799</v>
@@ -53178,7 +53178,7 @@
         <v>58.2599983215332</v>
       </c>
       <c r="G1821" t="n">
-        <v>53.4246864318848</v>
+        <v>53.424690246582</v>
       </c>
       <c r="H1821" t="n">
         <v>598781</v>
@@ -53207,7 +53207,7 @@
         <v>57.7200012207031</v>
       </c>
       <c r="G1822" t="n">
-        <v>52.9295120239258</v>
+        <v>52.9295082092285</v>
       </c>
       <c r="H1822" t="n">
         <v>1020334</v>
@@ -53236,7 +53236,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G1823" t="n">
-        <v>53.4613647460938</v>
+        <v>53.461368560791</v>
       </c>
       <c r="H1823" t="n">
         <v>513225</v>
@@ -53265,7 +53265,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G1824" t="n">
-        <v>53.0028686523438</v>
+        <v>53.002872467041</v>
       </c>
       <c r="H1824" t="n">
         <v>1011884</v>
@@ -53323,7 +53323,7 @@
         <v>60.3600006103516</v>
       </c>
       <c r="G1826" t="n">
-        <v>55.350399017334</v>
+        <v>55.3504028320312</v>
       </c>
       <c r="H1826" t="n">
         <v>1362141</v>
@@ -53352,7 +53352,7 @@
         <v>60.7799987792969</v>
       </c>
       <c r="G1827" t="n">
-        <v>55.7355422973633</v>
+        <v>55.735538482666</v>
       </c>
       <c r="H1827" t="n">
         <v>590944</v>
@@ -53381,7 +53381,7 @@
         <v>60.560001373291</v>
       </c>
       <c r="G1828" t="n">
-        <v>55.5337982177734</v>
+        <v>55.533805847168</v>
       </c>
       <c r="H1828" t="n">
         <v>510846</v>
@@ -53758,7 +53758,7 @@
         <v>61.6199989318848</v>
       </c>
       <c r="G1841" t="n">
-        <v>56.5058250427246</v>
+        <v>56.5058212280273</v>
       </c>
       <c r="H1841" t="n">
         <v>384125</v>
@@ -53787,7 +53787,7 @@
         <v>60.6399993896484</v>
       </c>
       <c r="G1842" t="n">
-        <v>55.6071624755859</v>
+        <v>55.6071586608887</v>
       </c>
       <c r="H1842" t="n">
         <v>537257</v>
@@ -53845,7 +53845,7 @@
         <v>60.560001373291</v>
       </c>
       <c r="G1844" t="n">
-        <v>55.5337982177734</v>
+        <v>55.533805847168</v>
       </c>
       <c r="H1844" t="n">
         <v>268343</v>
@@ -53874,7 +53874,7 @@
         <v>62.439998626709</v>
       </c>
       <c r="G1845" t="n">
-        <v>57.2577705383301</v>
+        <v>57.2577743530273</v>
       </c>
       <c r="H1845" t="n">
         <v>961724</v>
@@ -53932,7 +53932,7 @@
         <v>63.5400009155273</v>
       </c>
       <c r="G1847" t="n">
-        <v>58.2664756774902</v>
+        <v>58.266471862793</v>
       </c>
       <c r="H1847" t="n">
         <v>697418</v>
@@ -53961,7 +53961,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G1848" t="n">
-        <v>58.413200378418</v>
+        <v>58.4131965637207</v>
       </c>
       <c r="H1848" t="n">
         <v>982460</v>
@@ -53990,7 +53990,7 @@
         <v>63.5999984741211</v>
       </c>
       <c r="G1849" t="n">
-        <v>58.3214912414551</v>
+        <v>58.3214950561523</v>
       </c>
       <c r="H1849" t="n">
         <v>485886</v>
@@ -54048,7 +54048,7 @@
         <v>63.2599983215332</v>
       </c>
       <c r="G1851" t="n">
-        <v>58.0097122192383</v>
+        <v>58.0097160339355</v>
       </c>
       <c r="H1851" t="n">
         <v>522060</v>
@@ -54106,7 +54106,7 @@
         <v>62.9799995422363</v>
       </c>
       <c r="G1853" t="n">
-        <v>57.7529525756836</v>
+        <v>57.7529487609863</v>
       </c>
       <c r="H1853" t="n">
         <v>415409</v>
@@ -54135,7 +54135,7 @@
         <v>65.7799987792969</v>
       </c>
       <c r="G1854" t="n">
-        <v>60.3205642700195</v>
+        <v>60.3205604553223</v>
       </c>
       <c r="H1854" t="n">
         <v>1108560</v>
@@ -54164,7 +54164,7 @@
         <v>65.9400024414062</v>
       </c>
       <c r="G1855" t="n">
-        <v>60.4672927856445</v>
+        <v>60.46728515625</v>
       </c>
       <c r="H1855" t="n">
         <v>606943</v>
@@ -54193,7 +54193,7 @@
         <v>64.6399993896484</v>
       </c>
       <c r="G1856" t="n">
-        <v>59.2751808166504</v>
+        <v>59.2751770019531</v>
       </c>
       <c r="H1856" t="n">
         <v>446302</v>
@@ -54222,7 +54222,7 @@
         <v>65.5</v>
       </c>
       <c r="G1857" t="n">
-        <v>60.0638008117676</v>
+        <v>60.0638046264648</v>
       </c>
       <c r="H1857" t="n">
         <v>470065</v>
@@ -54251,7 +54251,7 @@
         <v>65.9199981689453</v>
       </c>
       <c r="G1858" t="n">
-        <v>60.4489479064941</v>
+        <v>60.4489440917969</v>
       </c>
       <c r="H1858" t="n">
         <v>404022</v>
@@ -54280,7 +54280,7 @@
         <v>66.9199981689453</v>
       </c>
       <c r="G1859" t="n">
-        <v>61.3659477233887</v>
+        <v>61.3659439086914</v>
       </c>
       <c r="H1859" t="n">
         <v>691068</v>
@@ -54309,7 +54309,7 @@
         <v>67.1999969482422</v>
       </c>
       <c r="G1860" t="n">
-        <v>61.6227073669434</v>
+        <v>61.6227149963379</v>
       </c>
       <c r="H1860" t="n">
         <v>592611</v>
@@ -54338,7 +54338,7 @@
         <v>67.6800003051758</v>
       </c>
       <c r="G1861" t="n">
-        <v>62.062873840332</v>
+        <v>62.0628776550293</v>
       </c>
       <c r="H1861" t="n">
         <v>425527</v>
@@ -54396,7 +54396,7 @@
         <v>66.9199981689453</v>
       </c>
       <c r="G1863" t="n">
-        <v>61.3659477233887</v>
+        <v>61.3659439086914</v>
       </c>
       <c r="H1863" t="n">
         <v>649507</v>
@@ -54425,7 +54425,7 @@
         <v>67.8199996948242</v>
       </c>
       <c r="G1864" t="n">
-        <v>62.1912574768066</v>
+        <v>62.1912536621094</v>
       </c>
       <c r="H1864" t="n">
         <v>687705</v>
@@ -54454,7 +54454,7 @@
         <v>67.1600036621094</v>
       </c>
       <c r="G1865" t="n">
-        <v>61.5860328674316</v>
+        <v>61.5860404968262</v>
       </c>
       <c r="H1865" t="n">
         <v>467718</v>
@@ -54483,7 +54483,7 @@
         <v>67.1800003051758</v>
       </c>
       <c r="G1866" t="n">
-        <v>61.6043701171875</v>
+        <v>61.6043739318848</v>
       </c>
       <c r="H1866" t="n">
         <v>536988</v>
@@ -54512,7 +54512,7 @@
         <v>68.5599975585938</v>
       </c>
       <c r="G1867" t="n">
-        <v>62.8698387145996</v>
+        <v>62.8698310852051</v>
       </c>
       <c r="H1867" t="n">
         <v>750394</v>
@@ -54570,7 +54570,7 @@
         <v>67.1800003051758</v>
       </c>
       <c r="G1869" t="n">
-        <v>61.6043701171875</v>
+        <v>61.6043739318848</v>
       </c>
       <c r="H1869" t="n">
         <v>1122045</v>
@@ -54599,7 +54599,7 @@
         <v>66.7600021362305</v>
       </c>
       <c r="G1870" t="n">
-        <v>61.2192306518555</v>
+        <v>61.2192268371582</v>
       </c>
       <c r="H1870" t="n">
         <v>431390</v>
@@ -54628,7 +54628,7 @@
         <v>66.1999969482422</v>
       </c>
       <c r="G1871" t="n">
-        <v>60.7057037353516</v>
+        <v>60.7056999206543</v>
       </c>
       <c r="H1871" t="n">
         <v>483579</v>
@@ -54686,7 +54686,7 @@
         <v>66.7799987792969</v>
       </c>
       <c r="G1873" t="n">
-        <v>61.2375679016113</v>
+        <v>61.2375717163086</v>
       </c>
       <c r="H1873" t="n">
         <v>545710</v>
@@ -54831,7 +54831,7 @@
         <v>64.5</v>
       </c>
       <c r="G1878" t="n">
-        <v>59.146800994873</v>
+        <v>59.1467971801758</v>
       </c>
       <c r="H1878" t="n">
         <v>555303</v>
@@ -79951,6 +79951,64 @@
         <v>2199455</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>42.9700012207031</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>43.0900001525879</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>42.0999984741211</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>1281957</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>42.9900016784668</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>43.2400016784668</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>42.2000007629395</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>42.3800010681152</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>42.3800010681152</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>934993</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MONC.MI.xlsx
+++ b/data/MONC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>10.7646179199219</v>
+        <v>10.7646198272705</v>
       </c>
       <c r="H2" t="n">
         <v>2223179</v>
@@ -514,7 +514,7 @@
         <v>12.25</v>
       </c>
       <c r="G5" t="n">
-        <v>10.5916938781738</v>
+        <v>10.5916929244995</v>
       </c>
       <c r="H5" t="n">
         <v>2789127</v>
@@ -543,7 +543,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G6" t="n">
-        <v>10.6781578063965</v>
+        <v>10.6781568527222</v>
       </c>
       <c r="H6" t="n">
         <v>1492468</v>
@@ -601,7 +601,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G8" t="n">
-        <v>11.6206016540527</v>
+        <v>11.6205997467041</v>
       </c>
       <c r="H8" t="n">
         <v>3968372</v>
@@ -630,7 +630,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G9" t="n">
-        <v>11.3006887435913</v>
+        <v>11.3006896972656</v>
       </c>
       <c r="H9" t="n">
         <v>2273754</v>
@@ -659,7 +659,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>11.1537008285522</v>
+        <v>11.1537027359009</v>
       </c>
       <c r="H10" t="n">
         <v>1611472</v>
@@ -688,7 +688,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G11" t="n">
-        <v>10.8424348831177</v>
+        <v>10.842435836792</v>
       </c>
       <c r="H11" t="n">
         <v>1753744</v>
@@ -717,7 +717,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G12" t="n">
-        <v>11.2228717803955</v>
+        <v>11.2228698730469</v>
       </c>
       <c r="H12" t="n">
         <v>1902069</v>
@@ -775,7 +775,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G14" t="n">
-        <v>11.0845317840576</v>
+        <v>11.0845308303833</v>
       </c>
       <c r="H14" t="n">
         <v>1462384</v>
@@ -833,7 +833,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G16" t="n">
-        <v>11.7762336730957</v>
+        <v>11.77623462677</v>
       </c>
       <c r="H16" t="n">
         <v>1616599</v>
@@ -862,7 +862,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G17" t="n">
-        <v>11.6638307571411</v>
+        <v>11.6638317108154</v>
       </c>
       <c r="H17" t="n">
         <v>850284</v>
@@ -891,7 +891,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G18" t="n">
-        <v>11.7848815917969</v>
+        <v>11.7848806381226</v>
       </c>
       <c r="H18" t="n">
         <v>1270858</v>
@@ -978,7 +978,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G21" t="n">
-        <v>11.7502937316895</v>
+        <v>11.7502946853638</v>
       </c>
       <c r="H21" t="n">
         <v>1419181</v>
@@ -1007,7 +1007,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G22" t="n">
-        <v>11.6119537353516</v>
+        <v>11.6119546890259</v>
       </c>
       <c r="H22" t="n">
         <v>669707</v>
@@ -1036,7 +1036,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G23" t="n">
-        <v>11.5600748062134</v>
+        <v>11.5600757598877</v>
       </c>
       <c r="H23" t="n">
         <v>1555247</v>
@@ -1094,7 +1094,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G25" t="n">
-        <v>11.5773696899414</v>
+        <v>11.5773687362671</v>
       </c>
       <c r="H25" t="n">
         <v>1223442</v>
@@ -1152,7 +1152,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G27" t="n">
-        <v>10.9548349380493</v>
+        <v>10.9548368453979</v>
       </c>
       <c r="H27" t="n">
         <v>1958438</v>
@@ -1181,7 +1181,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G28" t="n">
-        <v>10.7300329208374</v>
+        <v>10.730034828186</v>
       </c>
       <c r="H28" t="n">
         <v>2164227</v>
@@ -1210,7 +1210,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>10.9375438690186</v>
+        <v>10.9375448226929</v>
       </c>
       <c r="H29" t="n">
         <v>1215514</v>
@@ -1268,7 +1268,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>10.9807767868042</v>
+        <v>10.9807758331299</v>
       </c>
       <c r="H31" t="n">
         <v>1611286</v>
@@ -1355,7 +1355,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G34" t="n">
-        <v>12.061559677124</v>
+        <v>12.0615606307983</v>
       </c>
       <c r="H34" t="n">
         <v>1284802</v>
@@ -1442,7 +1442,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>12.0529136657715</v>
+        <v>12.0529146194458</v>
       </c>
       <c r="H37" t="n">
         <v>827636</v>
@@ -1471,7 +1471,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G38" t="n">
-        <v>11.7762336730957</v>
+        <v>11.77623462677</v>
       </c>
       <c r="H38" t="n">
         <v>1423617</v>
@@ -1500,7 +1500,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G39" t="n">
-        <v>11.4649677276611</v>
+        <v>11.4649686813354</v>
       </c>
       <c r="H39" t="n">
         <v>1090792</v>
@@ -1529,7 +1529,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G40" t="n">
-        <v>11.8540515899658</v>
+        <v>11.8540496826172</v>
       </c>
       <c r="H40" t="n">
         <v>1276215</v>
@@ -1558,7 +1558,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G41" t="n">
-        <v>12.061559677124</v>
+        <v>12.0615606307983</v>
       </c>
       <c r="H41" t="n">
         <v>1147211</v>
@@ -1587,7 +1587,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G42" t="n">
-        <v>12.3814735412598</v>
+        <v>12.3814725875854</v>
       </c>
       <c r="H42" t="n">
         <v>1343675</v>
@@ -1616,7 +1616,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G43" t="n">
-        <v>12.5976305007935</v>
+        <v>12.5976285934448</v>
       </c>
       <c r="H43" t="n">
         <v>1580398</v>
@@ -1645,7 +1645,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G44" t="n">
-        <v>12.5976305007935</v>
+        <v>12.5976285934448</v>
       </c>
       <c r="H44" t="n">
         <v>1551191</v>
@@ -1674,7 +1674,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G45" t="n">
-        <v>12.4074125289917</v>
+        <v>12.407413482666</v>
       </c>
       <c r="H45" t="n">
         <v>1651102</v>
@@ -1732,7 +1732,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G47" t="n">
-        <v>13.0299444198608</v>
+        <v>13.0299434661865</v>
       </c>
       <c r="H47" t="n">
         <v>2341101</v>
@@ -1819,7 +1819,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G50" t="n">
-        <v>13.0731754302979</v>
+        <v>13.0731763839722</v>
       </c>
       <c r="H50" t="n">
         <v>2267421</v>
@@ -1877,7 +1877,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G52" t="n">
-        <v>13.3239183425903</v>
+        <v>13.323917388916</v>
       </c>
       <c r="H52" t="n">
         <v>732431</v>
@@ -1906,7 +1906,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G53" t="n">
-        <v>13.0731754302979</v>
+        <v>13.0731763839722</v>
       </c>
       <c r="H53" t="n">
         <v>988061</v>
@@ -1935,7 +1935,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G54" t="n">
-        <v>12.9607734680176</v>
+        <v>12.9607744216919</v>
       </c>
       <c r="H54" t="n">
         <v>851853</v>
@@ -1964,7 +1964,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G55" t="n">
-        <v>12.6754455566406</v>
+        <v>12.6754465103149</v>
       </c>
       <c r="H55" t="n">
         <v>982899</v>
@@ -1993,7 +1993,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G56" t="n">
-        <v>12.6927404403687</v>
+        <v>12.6927375793457</v>
       </c>
       <c r="H56" t="n">
         <v>924484</v>
@@ -2080,7 +2080,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G59" t="n">
-        <v>12.649510383606</v>
+        <v>12.6495084762573</v>
       </c>
       <c r="H59" t="n">
         <v>1096206</v>
@@ -2138,7 +2138,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G61" t="n">
-        <v>12.7273244857788</v>
+        <v>12.7273235321045</v>
       </c>
       <c r="H61" t="n">
         <v>700829</v>
@@ -2167,7 +2167,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G62" t="n">
-        <v>13.1336994171143</v>
+        <v>13.1337003707886</v>
       </c>
       <c r="H62" t="n">
         <v>636895</v>
@@ -2225,7 +2225,7 @@
         <v>14.75</v>
       </c>
       <c r="G64" t="n">
-        <v>12.7532625198364</v>
+        <v>12.7532634735107</v>
       </c>
       <c r="H64" t="n">
         <v>735215</v>
@@ -2254,7 +2254,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G65" t="n">
-        <v>12.6149244308472</v>
+        <v>12.6149225234985</v>
       </c>
       <c r="H65" t="n">
         <v>563441</v>
@@ -2283,7 +2283,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G66" t="n">
-        <v>12.5630445480347</v>
+        <v>12.563045501709</v>
       </c>
       <c r="H66" t="n">
         <v>1439447</v>
@@ -2341,7 +2341,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>12.2344856262207</v>
+        <v>12.234486579895</v>
       </c>
       <c r="H68" t="n">
         <v>710495</v>
@@ -2399,7 +2399,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G70" t="n">
-        <v>12.4679355621338</v>
+        <v>12.4679365158081</v>
       </c>
       <c r="H70" t="n">
         <v>583921</v>
@@ -2428,7 +2428,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G71" t="n">
-        <v>12.4679355621338</v>
+        <v>12.4679365158081</v>
       </c>
       <c r="H71" t="n">
         <v>955960</v>
@@ -2544,7 +2544,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G75" t="n">
-        <v>12.7791996002197</v>
+        <v>12.7792024612427</v>
       </c>
       <c r="H75" t="n">
         <v>998164</v>
@@ -2573,7 +2573,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G76" t="n">
-        <v>13.0731754302979</v>
+        <v>13.0731763839722</v>
       </c>
       <c r="H76" t="n">
         <v>1175190</v>
@@ -2602,7 +2602,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G77" t="n">
-        <v>12.8310813903809</v>
+        <v>12.8310794830322</v>
       </c>
       <c r="H77" t="n">
         <v>912055</v>
@@ -2718,7 +2718,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>12.4074125289917</v>
+        <v>12.407413482666</v>
       </c>
       <c r="H81" t="n">
         <v>673927</v>
@@ -2747,7 +2747,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G82" t="n">
-        <v>12.3295965194702</v>
+        <v>12.3295955657959</v>
       </c>
       <c r="H82" t="n">
         <v>602545</v>
@@ -2776,7 +2776,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G83" t="n">
-        <v>12.1566705703735</v>
+        <v>12.1566715240479</v>
       </c>
       <c r="H83" t="n">
         <v>1080573</v>
@@ -2805,7 +2805,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G84" t="n">
-        <v>12.2431335449219</v>
+        <v>12.2431316375732</v>
       </c>
       <c r="H84" t="n">
         <v>878226</v>
@@ -2834,7 +2834,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G85" t="n">
-        <v>12.606276512146</v>
+        <v>12.6062784194946</v>
       </c>
       <c r="H85" t="n">
         <v>880454</v>
@@ -2863,7 +2863,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G86" t="n">
-        <v>12.7273244857788</v>
+        <v>12.7273235321045</v>
       </c>
       <c r="H86" t="n">
         <v>1053335</v>
@@ -3008,7 +3008,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G91" t="n">
-        <v>12.9434814453125</v>
+        <v>12.9434823989868</v>
       </c>
       <c r="H91" t="n">
         <v>1500108</v>
@@ -3037,7 +3037,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G92" t="n">
-        <v>13.540075302124</v>
+        <v>13.5400743484497</v>
       </c>
       <c r="H92" t="n">
         <v>3020796</v>
@@ -3066,7 +3066,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>13.6611223220825</v>
+        <v>13.6611213684082</v>
       </c>
       <c r="H93" t="n">
         <v>1486350</v>
@@ -3095,7 +3095,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G94" t="n">
-        <v>13.6005992889404</v>
+        <v>13.6005973815918</v>
       </c>
       <c r="H94" t="n">
         <v>960559</v>
@@ -3124,7 +3124,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G95" t="n">
-        <v>13.5573673248291</v>
+        <v>13.5573663711548</v>
       </c>
       <c r="H95" t="n">
         <v>346697</v>
@@ -3153,7 +3153,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G96" t="n">
-        <v>13.2547473907471</v>
+        <v>13.2547483444214</v>
       </c>
       <c r="H96" t="n">
         <v>1118423</v>
@@ -3182,7 +3182,7 @@
         <v>15.25</v>
       </c>
       <c r="G97" t="n">
-        <v>13.1855773925781</v>
+        <v>13.1855783462524</v>
       </c>
       <c r="H97" t="n">
         <v>724517</v>
@@ -3211,7 +3211,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G98" t="n">
-        <v>12.9867143630981</v>
+        <v>12.9867153167725</v>
       </c>
       <c r="H98" t="n">
         <v>1181840</v>
@@ -3240,7 +3240,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="n">
-        <v>12.9694204330444</v>
+        <v>12.9694194793701</v>
       </c>
       <c r="H99" t="n">
         <v>607656</v>
@@ -3269,7 +3269,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G100" t="n">
-        <v>12.8559598922729</v>
+        <v>12.8559589385986</v>
       </c>
       <c r="H100" t="n">
         <v>894076</v>
@@ -3298,7 +3298,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G101" t="n">
-        <v>13.1788854598999</v>
+        <v>13.1788864135742</v>
       </c>
       <c r="H101" t="n">
         <v>1204794</v>
@@ -3356,7 +3356,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G103" t="n">
-        <v>12.8995962142944</v>
+        <v>12.8995981216431</v>
       </c>
       <c r="H103" t="n">
         <v>641575</v>
@@ -3385,7 +3385,7 @@
         <v>15</v>
       </c>
       <c r="G104" t="n">
-        <v>13.0916080474854</v>
+        <v>13.091607093811</v>
       </c>
       <c r="H104" t="n">
         <v>606719</v>
@@ -3414,7 +3414,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G105" t="n">
-        <v>13.2137956619263</v>
+        <v>13.2137975692749</v>
       </c>
       <c r="H105" t="n">
         <v>358747</v>
@@ -3443,7 +3443,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G106" t="n">
-        <v>13.0828800201416</v>
+        <v>13.0828809738159</v>
       </c>
       <c r="H106" t="n">
         <v>595072</v>
@@ -3472,7 +3472,7 @@
         <v>15</v>
       </c>
       <c r="G107" t="n">
-        <v>13.0916080474854</v>
+        <v>13.091607093811</v>
       </c>
       <c r="H107" t="n">
         <v>430117</v>
@@ -3501,7 +3501,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G108" t="n">
-        <v>13.117790222168</v>
+        <v>13.1177921295166</v>
       </c>
       <c r="H108" t="n">
         <v>331493</v>
@@ -3530,7 +3530,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G109" t="n">
-        <v>12.9868764877319</v>
+        <v>12.9868755340576</v>
       </c>
       <c r="H109" t="n">
         <v>547891</v>
@@ -3559,7 +3559,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G110" t="n">
-        <v>12.9432363510132</v>
+        <v>12.9432373046875</v>
       </c>
       <c r="H110" t="n">
         <v>355749</v>
@@ -3588,7 +3588,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G111" t="n">
-        <v>13.283618927002</v>
+        <v>13.2836198806763</v>
       </c>
       <c r="H111" t="n">
         <v>697700</v>
@@ -3646,7 +3646,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G113" t="n">
-        <v>13.3534412384033</v>
+        <v>13.353440284729</v>
       </c>
       <c r="H113" t="n">
         <v>559424</v>
@@ -3733,7 +3733,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G116" t="n">
-        <v>12.3672046661377</v>
+        <v>12.3672065734863</v>
       </c>
       <c r="H116" t="n">
         <v>976492</v>
@@ -3762,7 +3762,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G117" t="n">
-        <v>12.8385047912598</v>
+        <v>12.8385038375854</v>
       </c>
       <c r="H117" t="n">
         <v>623004</v>
@@ -3791,7 +3791,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G118" t="n">
-        <v>12.498122215271</v>
+        <v>12.4981212615967</v>
       </c>
       <c r="H118" t="n">
         <v>692977</v>
@@ -3820,7 +3820,7 @@
         <v>15</v>
       </c>
       <c r="G119" t="n">
-        <v>13.0916080474854</v>
+        <v>13.091607093811</v>
       </c>
       <c r="H119" t="n">
         <v>1468595</v>
@@ -3878,7 +3878,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G121" t="n">
-        <v>13.2923460006714</v>
+        <v>13.2923450469971</v>
       </c>
       <c r="H121" t="n">
         <v>549643</v>
@@ -3965,7 +3965,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>12.567943572998</v>
+        <v>12.5679445266724</v>
       </c>
       <c r="H124" t="n">
         <v>2192930</v>
@@ -3994,7 +3994,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G125" t="n">
-        <v>11.9570016860962</v>
+        <v>11.9570026397705</v>
       </c>
       <c r="H125" t="n">
         <v>1435455</v>
@@ -4023,7 +4023,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G126" t="n">
-        <v>12.3410234451294</v>
+        <v>12.3410215377808</v>
       </c>
       <c r="H126" t="n">
         <v>1032859</v>
@@ -4052,7 +4052,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G127" t="n">
-        <v>12.3672046661377</v>
+        <v>12.3672065734863</v>
       </c>
       <c r="H127" t="n">
         <v>1000036</v>
@@ -4081,7 +4081,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G128" t="n">
-        <v>12.3410234451294</v>
+        <v>12.3410215377808</v>
       </c>
       <c r="H128" t="n">
         <v>1265115</v>
@@ -4110,7 +4110,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G129" t="n">
-        <v>12.7774105072021</v>
+        <v>12.7774085998535</v>
       </c>
       <c r="H129" t="n">
         <v>1186863</v>
@@ -4139,7 +4139,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G130" t="n">
-        <v>12.6290397644043</v>
+        <v>12.62903881073</v>
       </c>
       <c r="H130" t="n">
         <v>630577</v>
@@ -4168,7 +4168,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G131" t="n">
-        <v>12.3410234451294</v>
+        <v>12.3410215377808</v>
       </c>
       <c r="H131" t="n">
         <v>797500</v>
@@ -4226,7 +4226,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G133" t="n">
-        <v>12.4893941879272</v>
+        <v>12.4893960952759</v>
       </c>
       <c r="H133" t="n">
         <v>1308654</v>
@@ -4255,7 +4255,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G134" t="n">
-        <v>12.5155773162842</v>
+        <v>12.5155763626099</v>
       </c>
       <c r="H134" t="n">
         <v>932643</v>
@@ -4284,7 +4284,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G135" t="n">
-        <v>12.6028537750244</v>
+        <v>12.6028547286987</v>
       </c>
       <c r="H135" t="n">
         <v>793285</v>
@@ -4342,7 +4342,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G137" t="n">
-        <v>12.6290397644043</v>
+        <v>12.62903881073</v>
       </c>
       <c r="H137" t="n">
         <v>864253</v>
@@ -4371,7 +4371,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G138" t="n">
-        <v>12.8035917282104</v>
+        <v>12.8035945892334</v>
       </c>
       <c r="H138" t="n">
         <v>731546</v>
@@ -4400,7 +4400,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G139" t="n">
-        <v>12.594126701355</v>
+        <v>12.5941276550293</v>
       </c>
       <c r="H139" t="n">
         <v>922665</v>
@@ -4458,7 +4458,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G141" t="n">
-        <v>12.4108457565308</v>
+        <v>12.4108448028564</v>
       </c>
       <c r="H141" t="n">
         <v>770225</v>
@@ -4516,7 +4516,7 @@
         <v>15</v>
       </c>
       <c r="G143" t="n">
-        <v>13.0916080474854</v>
+        <v>13.091607093811</v>
       </c>
       <c r="H143" t="n">
         <v>733886</v>
@@ -4574,7 +4574,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G145" t="n">
-        <v>13.7723731994629</v>
+        <v>13.7723703384399</v>
       </c>
       <c r="H145" t="n">
         <v>1113472</v>
@@ -4603,7 +4603,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G146" t="n">
-        <v>13.6676397323608</v>
+        <v>13.6676387786865</v>
       </c>
       <c r="H146" t="n">
         <v>943572</v>
@@ -4661,7 +4661,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G148" t="n">
-        <v>13.6676397323608</v>
+        <v>13.6676387786865</v>
       </c>
       <c r="H148" t="n">
         <v>2107652</v>
@@ -4690,7 +4690,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G149" t="n">
-        <v>13.685094833374</v>
+        <v>13.6850938796997</v>
       </c>
       <c r="H149" t="n">
         <v>1049960</v>
@@ -4748,7 +4748,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G151" t="n">
-        <v>13.1265201568604</v>
+        <v>13.126519203186</v>
       </c>
       <c r="H151" t="n">
         <v>1076792</v>
@@ -4806,7 +4806,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>13.3534412384033</v>
+        <v>13.353440284729</v>
       </c>
       <c r="H153" t="n">
         <v>726750</v>
@@ -4864,7 +4864,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G155" t="n">
-        <v>13.6327295303345</v>
+        <v>13.6327276229858</v>
       </c>
       <c r="H155" t="n">
         <v>1014631</v>
@@ -4893,7 +4893,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G156" t="n">
-        <v>13.6240015029907</v>
+        <v>13.6240005493164</v>
       </c>
       <c r="H156" t="n">
         <v>1027894</v>
@@ -4922,7 +4922,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G157" t="n">
-        <v>13.4581727981567</v>
+        <v>13.4581747055054</v>
       </c>
       <c r="H157" t="n">
         <v>734563</v>
@@ -4980,7 +4980,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G159" t="n">
-        <v>13.6240015029907</v>
+        <v>13.6240005493164</v>
       </c>
       <c r="H159" t="n">
         <v>657159</v>
@@ -5009,7 +5009,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G160" t="n">
-        <v>13.5978155136108</v>
+        <v>13.5978174209595</v>
       </c>
       <c r="H160" t="n">
         <v>650235</v>
@@ -5067,7 +5067,7 @@
         <v>15.5</v>
       </c>
       <c r="G162" t="n">
-        <v>13.5279960632324</v>
+        <v>13.5279951095581</v>
       </c>
       <c r="H162" t="n">
         <v>324617</v>
@@ -5154,7 +5154,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G165" t="n">
-        <v>13.5978155136108</v>
+        <v>13.5978174209595</v>
       </c>
       <c r="H165" t="n">
         <v>353663</v>
@@ -5212,7 +5212,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G167" t="n">
-        <v>13.3708944320679</v>
+        <v>13.3708953857422</v>
       </c>
       <c r="H167" t="n">
         <v>437224</v>
@@ -5328,7 +5328,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G171" t="n">
-        <v>12.9781475067139</v>
+        <v>12.9781484603882</v>
       </c>
       <c r="H171" t="n">
         <v>563248</v>
@@ -5415,7 +5415,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G174" t="n">
-        <v>13.3359861373901</v>
+        <v>13.3359851837158</v>
       </c>
       <c r="H174" t="n">
         <v>489538</v>
@@ -5444,7 +5444,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G175" t="n">
-        <v>13.152702331543</v>
+        <v>13.1527013778687</v>
       </c>
       <c r="H175" t="n">
         <v>482525</v>
@@ -5473,7 +5473,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G176" t="n">
-        <v>13.3185291290283</v>
+        <v>13.3185300827026</v>
       </c>
       <c r="H176" t="n">
         <v>770559</v>
@@ -5502,7 +5502,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G177" t="n">
-        <v>13.283618927002</v>
+        <v>13.2836198806763</v>
       </c>
       <c r="H177" t="n">
         <v>844806</v>
@@ -5531,7 +5531,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G178" t="n">
-        <v>13.2137956619263</v>
+        <v>13.2137975692749</v>
       </c>
       <c r="H178" t="n">
         <v>613140</v>
@@ -5560,7 +5560,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>13.3534412384033</v>
+        <v>13.353440284729</v>
       </c>
       <c r="H179" t="n">
         <v>1294130</v>
@@ -5589,7 +5589,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G180" t="n">
-        <v>13.51926612854</v>
+        <v>13.5192670822144</v>
       </c>
       <c r="H180" t="n">
         <v>1280281</v>
@@ -5676,7 +5676,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G183" t="n">
-        <v>13.2312517166138</v>
+        <v>13.2312536239624</v>
       </c>
       <c r="H183" t="n">
         <v>2771661</v>
@@ -5705,7 +5705,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>13.6152725219727</v>
+        <v>13.615273475647</v>
       </c>
       <c r="H184" t="n">
         <v>1463002</v>
@@ -5734,7 +5734,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>13.6152725219727</v>
+        <v>13.615273475647</v>
       </c>
       <c r="H185" t="n">
         <v>933573</v>
@@ -5792,7 +5792,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G187" t="n">
-        <v>13.6327295303345</v>
+        <v>13.6327276229858</v>
       </c>
       <c r="H187" t="n">
         <v>872087</v>
@@ -5821,7 +5821,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G188" t="n">
-        <v>13.3359861373901</v>
+        <v>13.3359851837158</v>
       </c>
       <c r="H188" t="n">
         <v>3908497</v>
@@ -5879,7 +5879,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G190" t="n">
-        <v>13.0741529464722</v>
+        <v>13.0741519927979</v>
       </c>
       <c r="H190" t="n">
         <v>1511981</v>
@@ -5908,7 +5908,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G191" t="n">
-        <v>13.2661619186401</v>
+        <v>13.2661628723145</v>
       </c>
       <c r="H191" t="n">
         <v>1036074</v>
@@ -5937,7 +5937,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G192" t="n">
-        <v>13.1265201568604</v>
+        <v>13.126519203186</v>
       </c>
       <c r="H192" t="n">
         <v>944837</v>
@@ -5966,7 +5966,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G193" t="n">
-        <v>13.2574348449707</v>
+        <v>13.257435798645</v>
       </c>
       <c r="H193" t="n">
         <v>1437271</v>
@@ -6024,7 +6024,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G195" t="n">
-        <v>13.3185291290283</v>
+        <v>13.3185300827026</v>
       </c>
       <c r="H195" t="n">
         <v>1190087</v>
@@ -6053,7 +6053,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G196" t="n">
-        <v>13.4581727981567</v>
+        <v>13.4581747055054</v>
       </c>
       <c r="H196" t="n">
         <v>1148496</v>
@@ -6082,7 +6082,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G197" t="n">
-        <v>13.3970804214478</v>
+        <v>13.3970794677734</v>
       </c>
       <c r="H197" t="n">
         <v>1055119</v>
@@ -6111,7 +6111,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G198" t="n">
-        <v>13.1003360748291</v>
+        <v>13.1003351211548</v>
       </c>
       <c r="H198" t="n">
         <v>977738</v>
@@ -6198,7 +6198,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G201" t="n">
-        <v>13.3970804214478</v>
+        <v>13.3970794677734</v>
       </c>
       <c r="H201" t="n">
         <v>644615</v>
@@ -6227,7 +6227,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>13.1788854598999</v>
+        <v>13.1788864135742</v>
       </c>
       <c r="H202" t="n">
         <v>1049363</v>
@@ -6256,7 +6256,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G203" t="n">
-        <v>13.3534412384033</v>
+        <v>13.353440284729</v>
       </c>
       <c r="H203" t="n">
         <v>987488</v>
@@ -6343,7 +6343,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G206" t="n">
-        <v>13.5978155136108</v>
+        <v>13.5978174209595</v>
       </c>
       <c r="H206" t="n">
         <v>739958</v>
@@ -6401,7 +6401,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G208" t="n">
-        <v>13.6240015029907</v>
+        <v>13.6240005493164</v>
       </c>
       <c r="H208" t="n">
         <v>769623</v>
@@ -6430,7 +6430,7 @@
         <v>15.5</v>
       </c>
       <c r="G209" t="n">
-        <v>13.5279960632324</v>
+        <v>13.5279951095581</v>
       </c>
       <c r="H209" t="n">
         <v>858588</v>
@@ -6517,7 +6517,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>13.4843559265137</v>
+        <v>13.484356880188</v>
       </c>
       <c r="H212" t="n">
         <v>471242</v>
@@ -6546,7 +6546,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G213" t="n">
-        <v>13.4058055877686</v>
+        <v>13.4058065414429</v>
       </c>
       <c r="H213" t="n">
         <v>718789</v>
@@ -6575,7 +6575,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G214" t="n">
-        <v>13.2399797439575</v>
+        <v>13.2399787902832</v>
       </c>
       <c r="H214" t="n">
         <v>676142</v>
@@ -6662,7 +6662,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G217" t="n">
-        <v>13.0217866897583</v>
+        <v>13.0217876434326</v>
       </c>
       <c r="H217" t="n">
         <v>745307</v>
@@ -6691,7 +6691,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G218" t="n">
-        <v>13.0130586624146</v>
+        <v>13.0130577087402</v>
       </c>
       <c r="H218" t="n">
         <v>873594</v>
@@ -6720,7 +6720,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G219" t="n">
-        <v>12.7774105072021</v>
+        <v>12.7774085998535</v>
       </c>
       <c r="H219" t="n">
         <v>1250147</v>
@@ -6778,7 +6778,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>13.1090650558472</v>
+        <v>13.1090660095215</v>
       </c>
       <c r="H221" t="n">
         <v>1750977</v>
@@ -6807,7 +6807,7 @@
         <v>15</v>
       </c>
       <c r="G222" t="n">
-        <v>13.0916080474854</v>
+        <v>13.091607093811</v>
       </c>
       <c r="H222" t="n">
         <v>981759</v>
@@ -6865,7 +6865,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G224" t="n">
-        <v>13.1265201568604</v>
+        <v>13.126519203186</v>
       </c>
       <c r="H224" t="n">
         <v>583246</v>
@@ -6894,7 +6894,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G225" t="n">
-        <v>13.0217866897583</v>
+        <v>13.0217876434326</v>
       </c>
       <c r="H225" t="n">
         <v>728427</v>
@@ -6923,7 +6923,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G226" t="n">
-        <v>12.9868764877319</v>
+        <v>12.9868755340576</v>
       </c>
       <c r="H226" t="n">
         <v>721836</v>
@@ -6981,7 +6981,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G228" t="n">
-        <v>12.9606924057007</v>
+        <v>12.960693359375</v>
       </c>
       <c r="H228" t="n">
         <v>827739</v>
@@ -7010,7 +7010,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G229" t="n">
-        <v>13.1265201568604</v>
+        <v>13.126519203186</v>
       </c>
       <c r="H229" t="n">
         <v>794243</v>
@@ -7097,7 +7097,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G232" t="n">
-        <v>13.1003360748291</v>
+        <v>13.1003351211548</v>
       </c>
       <c r="H232" t="n">
         <v>428003</v>
@@ -7126,7 +7126,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>13.1788854598999</v>
+        <v>13.1788864135742</v>
       </c>
       <c r="H233" t="n">
         <v>316602</v>
@@ -7155,7 +7155,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G234" t="n">
-        <v>12.9519662857056</v>
+        <v>12.9519643783569</v>
       </c>
       <c r="H234" t="n">
         <v>601686</v>
@@ -7184,7 +7184,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G235" t="n">
-        <v>13.2923460006714</v>
+        <v>13.2923450469971</v>
       </c>
       <c r="H235" t="n">
         <v>641282</v>
@@ -7242,7 +7242,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G237" t="n">
-        <v>13.4756288528442</v>
+        <v>13.4756269454956</v>
       </c>
       <c r="H237" t="n">
         <v>997768</v>
@@ -7329,7 +7329,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G240" t="n">
-        <v>14.2349424362183</v>
+        <v>14.2349405288696</v>
       </c>
       <c r="H240" t="n">
         <v>1871570</v>
@@ -7358,7 +7358,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>14.2262134552002</v>
+        <v>14.2262144088745</v>
       </c>
       <c r="H241" t="n">
         <v>1730095</v>
@@ -7387,7 +7387,7 @@
         <v>16.6100006103516</v>
       </c>
       <c r="G242" t="n">
-        <v>14.4967746734619</v>
+        <v>14.4967756271362</v>
       </c>
       <c r="H242" t="n">
         <v>1500151</v>
@@ -7416,7 +7416,7 @@
         <v>16.8099994659424</v>
       </c>
       <c r="G243" t="n">
-        <v>14.671329498291</v>
+        <v>14.6713285446167</v>
       </c>
       <c r="H243" t="n">
         <v>1336897</v>
@@ -7445,7 +7445,7 @@
         <v>16.75</v>
       </c>
       <c r="G244" t="n">
-        <v>14.6189622879028</v>
+        <v>14.6189632415771</v>
       </c>
       <c r="H244" t="n">
         <v>993746</v>
@@ -7474,7 +7474,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G245" t="n">
-        <v>14.479320526123</v>
+        <v>14.4793176651001</v>
       </c>
       <c r="H245" t="n">
         <v>1162278</v>
@@ -7503,7 +7503,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>14.1389379501343</v>
+        <v>14.1389389038086</v>
       </c>
       <c r="H246" t="n">
         <v>3408964</v>
@@ -7561,7 +7561,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G248" t="n">
-        <v>14.3571329116821</v>
+        <v>14.3571300506592</v>
       </c>
       <c r="H248" t="n">
         <v>1359703</v>
@@ -7590,7 +7590,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G249" t="n">
-        <v>14.4531335830688</v>
+        <v>14.4531354904175</v>
       </c>
       <c r="H249" t="n">
         <v>812808</v>
@@ -7619,7 +7619,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G250" t="n">
-        <v>14.479320526123</v>
+        <v>14.4793176651001</v>
       </c>
       <c r="H250" t="n">
         <v>680184</v>
@@ -7648,7 +7648,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G251" t="n">
-        <v>14.3745851516724</v>
+        <v>14.3745861053467</v>
       </c>
       <c r="H251" t="n">
         <v>659941</v>
@@ -7677,7 +7677,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G252" t="n">
-        <v>14.243670463562</v>
+        <v>14.2436695098877</v>
       </c>
       <c r="H252" t="n">
         <v>505924</v>
@@ -7706,7 +7706,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G253" t="n">
-        <v>14.2698535919189</v>
+        <v>14.2698516845703</v>
       </c>
       <c r="H253" t="n">
         <v>555130</v>
@@ -7735,7 +7735,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>14.2698535919189</v>
+        <v>14.2698516845703</v>
       </c>
       <c r="H254" t="n">
         <v>353288</v>
@@ -7764,7 +7764,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G255" t="n">
-        <v>14.2873077392578</v>
+        <v>14.2873096466064</v>
       </c>
       <c r="H255" t="n">
         <v>421235</v>
@@ -7793,7 +7793,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G256" t="n">
-        <v>14.4531335830688</v>
+        <v>14.4531354904175</v>
       </c>
       <c r="H256" t="n">
         <v>713480</v>
@@ -7851,7 +7851,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>14.6626024246216</v>
+        <v>14.6626005172729</v>
       </c>
       <c r="H258" t="n">
         <v>644667</v>
@@ -7909,7 +7909,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G260" t="n">
-        <v>14.2960357666016</v>
+        <v>14.2960367202759</v>
       </c>
       <c r="H260" t="n">
         <v>919366</v>
@@ -7938,7 +7938,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G261" t="n">
-        <v>14.2611265182495</v>
+        <v>14.2611246109009</v>
       </c>
       <c r="H261" t="n">
         <v>927406</v>
@@ -7967,7 +7967,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G262" t="n">
-        <v>14.479320526123</v>
+        <v>14.4793176651001</v>
       </c>
       <c r="H262" t="n">
         <v>720832</v>
@@ -7996,7 +7996,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G263" t="n">
-        <v>14.243670463562</v>
+        <v>14.2436695098877</v>
       </c>
       <c r="H263" t="n">
         <v>725960</v>
@@ -8054,7 +8054,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G265" t="n">
-        <v>15.0029821395874</v>
+        <v>15.002984046936</v>
       </c>
       <c r="H265" t="n">
         <v>2064736</v>
@@ -8112,7 +8112,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G267" t="n">
-        <v>15.2473592758179</v>
+        <v>15.2473611831665</v>
       </c>
       <c r="H267" t="n">
         <v>907647</v>
@@ -8141,7 +8141,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G268" t="n">
-        <v>15.2822723388672</v>
+        <v>15.2822685241699</v>
       </c>
       <c r="H268" t="n">
         <v>1019197</v>
@@ -8170,7 +8170,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G269" t="n">
-        <v>15.0466222763062</v>
+        <v>15.0466203689575</v>
       </c>
       <c r="H269" t="n">
         <v>656150</v>
@@ -8199,7 +8199,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G270" t="n">
-        <v>15.3346376419067</v>
+        <v>15.3346366882324</v>
       </c>
       <c r="H270" t="n">
         <v>1004676</v>
@@ -8257,7 +8257,7 @@
         <v>18</v>
       </c>
       <c r="G272" t="n">
-        <v>15.7099266052246</v>
+        <v>15.7099332809448</v>
       </c>
       <c r="H272" t="n">
         <v>1880234</v>
@@ -8286,7 +8286,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G273" t="n">
-        <v>15.7448406219482</v>
+        <v>15.7448425292969</v>
       </c>
       <c r="H273" t="n">
         <v>1202755</v>
@@ -8315,7 +8315,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G274" t="n">
-        <v>15.7361135482788</v>
+        <v>15.7361116409302</v>
       </c>
       <c r="H274" t="n">
         <v>851879</v>
@@ -8373,7 +8373,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G276" t="n">
-        <v>15.6575679779053</v>
+        <v>15.6575651168823</v>
       </c>
       <c r="H276" t="n">
         <v>643911</v>
@@ -8402,7 +8402,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G277" t="n">
-        <v>15.7361135482788</v>
+        <v>15.7361116409302</v>
       </c>
       <c r="H277" t="n">
         <v>775083</v>
@@ -8431,7 +8431,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G278" t="n">
-        <v>15.5790147781372</v>
+        <v>15.5790157318115</v>
       </c>
       <c r="H278" t="n">
         <v>1068639</v>
@@ -8460,7 +8460,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>15.5353727340698</v>
+        <v>15.5353736877441</v>
       </c>
       <c r="H279" t="n">
         <v>1289110</v>
@@ -8489,7 +8489,7 @@
         <v>18</v>
       </c>
       <c r="G280" t="n">
-        <v>15.7099266052246</v>
+        <v>15.7099332809448</v>
       </c>
       <c r="H280" t="n">
         <v>1252469</v>
@@ -8547,7 +8547,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G282" t="n">
-        <v>15.4655532836914</v>
+        <v>15.4655542373657</v>
       </c>
       <c r="H282" t="n">
         <v>1266777</v>
@@ -8605,7 +8605,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G284" t="n">
-        <v>15.4830083847046</v>
+        <v>15.4830074310303</v>
       </c>
       <c r="H284" t="n">
         <v>860181</v>
@@ -8634,7 +8634,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G285" t="n">
-        <v>15.5266523361206</v>
+        <v>15.5266494750977</v>
       </c>
       <c r="H285" t="n">
         <v>510555</v>
@@ -8663,7 +8663,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G286" t="n">
-        <v>15.5091905593872</v>
+        <v>15.5091943740845</v>
       </c>
       <c r="H286" t="n">
         <v>687555</v>
@@ -8721,7 +8721,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G288" t="n">
-        <v>15.5353727340698</v>
+        <v>15.5353736877441</v>
       </c>
       <c r="H288" t="n">
         <v>585881</v>
@@ -8750,7 +8750,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>15.5353727340698</v>
+        <v>15.5353736877441</v>
       </c>
       <c r="H289" t="n">
         <v>700554</v>
@@ -8779,7 +8779,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G290" t="n">
-        <v>15.4393682479858</v>
+        <v>15.4393701553345</v>
       </c>
       <c r="H290" t="n">
         <v>670079</v>
@@ -8808,7 +8808,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G291" t="n">
-        <v>15.4655532836914</v>
+        <v>15.4655542373657</v>
       </c>
       <c r="H291" t="n">
         <v>633998</v>
@@ -8837,7 +8837,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G292" t="n">
-        <v>15.5266523361206</v>
+        <v>15.5266494750977</v>
       </c>
       <c r="H292" t="n">
         <v>905211</v>
@@ -8866,7 +8866,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G293" t="n">
-        <v>15.7186603546143</v>
+        <v>15.7186574935913</v>
       </c>
       <c r="H293" t="n">
         <v>363621</v>
@@ -8895,7 +8895,7 @@
         <v>18</v>
       </c>
       <c r="G294" t="n">
-        <v>15.7099266052246</v>
+        <v>15.7099332809448</v>
       </c>
       <c r="H294" t="n">
         <v>752656</v>
@@ -8924,7 +8924,7 @@
         <v>17.9300003051758</v>
       </c>
       <c r="G295" t="n">
-        <v>15.6488342285156</v>
+        <v>15.6488351821899</v>
       </c>
       <c r="H295" t="n">
         <v>500672</v>
@@ -8982,7 +8982,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>15.4481019973755</v>
+        <v>15.4480972290039</v>
       </c>
       <c r="H297" t="n">
         <v>818808</v>
@@ -9040,7 +9040,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G299" t="n">
-        <v>15.7273845672607</v>
+        <v>15.7273864746094</v>
       </c>
       <c r="H299" t="n">
         <v>1566803</v>
@@ -9069,7 +9069,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G300" t="n">
-        <v>16.6176147460938</v>
+        <v>16.6176166534424</v>
       </c>
       <c r="H300" t="n">
         <v>7363241</v>
@@ -9127,7 +9127,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G302" t="n">
-        <v>16.6787109375</v>
+        <v>16.6787128448486</v>
       </c>
       <c r="H302" t="n">
         <v>1467071</v>
@@ -9243,7 +9243,7 @@
         <v>19.5</v>
       </c>
       <c r="G306" t="n">
-        <v>17.0190906524658</v>
+        <v>17.0190925598145</v>
       </c>
       <c r="H306" t="n">
         <v>1146962</v>
@@ -9301,7 +9301,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G308" t="n">
-        <v>17.1587333679199</v>
+        <v>17.1587352752686</v>
       </c>
       <c r="H308" t="n">
         <v>663893</v>
@@ -9417,7 +9417,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G312" t="n">
-        <v>17.6649475097656</v>
+        <v>17.6649436950684</v>
       </c>
       <c r="H312" t="n">
         <v>2795629</v>
@@ -9446,7 +9446,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G313" t="n">
-        <v>17.3769283294678</v>
+        <v>17.3769264221191</v>
       </c>
       <c r="H313" t="n">
         <v>1185766</v>
@@ -9475,7 +9475,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G314" t="n">
-        <v>17.5514831542969</v>
+        <v>17.5514850616455</v>
       </c>
       <c r="H314" t="n">
         <v>820655</v>
@@ -9533,7 +9533,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>17.8045845031738</v>
+        <v>17.8045883178711</v>
       </c>
       <c r="H316" t="n">
         <v>669451</v>
@@ -9678,7 +9678,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G321" t="n">
-        <v>17.760950088501</v>
+        <v>17.7609481811523</v>
       </c>
       <c r="H321" t="n">
         <v>888071</v>
@@ -9707,7 +9707,7 @@
         <v>20.5300006866455</v>
       </c>
       <c r="G322" t="n">
-        <v>17.9180488586426</v>
+        <v>17.9180469512939</v>
       </c>
       <c r="H322" t="n">
         <v>790238</v>
@@ -9736,7 +9736,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G323" t="n">
-        <v>18.092601776123</v>
+        <v>18.0926055908203</v>
       </c>
       <c r="H323" t="n">
         <v>1723222</v>
@@ -9765,7 +9765,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>18.3980731964111</v>
+        <v>18.3980712890625</v>
       </c>
       <c r="H324" t="n">
         <v>1303495</v>
@@ -9794,7 +9794,7 @@
         <v>21.4099998474121</v>
       </c>
       <c r="G325" t="n">
-        <v>18.6860885620117</v>
+        <v>18.6860866546631</v>
       </c>
       <c r="H325" t="n">
         <v>1372973</v>
@@ -9823,7 +9823,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G326" t="n">
-        <v>18.6948184967041</v>
+        <v>18.6948146820068</v>
       </c>
       <c r="H326" t="n">
         <v>785335</v>
@@ -9852,7 +9852,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G327" t="n">
-        <v>18.6599044799805</v>
+        <v>18.6599063873291</v>
       </c>
       <c r="H327" t="n">
         <v>1093693</v>
@@ -9881,7 +9881,7 @@
         <v>21.6900005340576</v>
       </c>
       <c r="G328" t="n">
-        <v>18.9304637908936</v>
+        <v>18.9304676055908</v>
       </c>
       <c r="H328" t="n">
         <v>978575</v>
@@ -9910,7 +9910,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G329" t="n">
-        <v>19.0090141296387</v>
+        <v>19.0090179443359</v>
       </c>
       <c r="H329" t="n">
         <v>1297556</v>
@@ -9997,7 +9997,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G332" t="n">
-        <v>18.7733669281006</v>
+        <v>18.7733688354492</v>
       </c>
       <c r="H332" t="n">
         <v>1101120</v>
@@ -10026,7 +10026,7 @@
         <v>21.75</v>
       </c>
       <c r="G333" t="n">
-        <v>18.9828319549561</v>
+        <v>18.9828338623047</v>
       </c>
       <c r="H333" t="n">
         <v>1285458</v>
@@ -10055,7 +10055,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G334" t="n">
-        <v>19.1399307250977</v>
+        <v>19.1399326324463</v>
       </c>
       <c r="H334" t="n">
         <v>854615</v>
@@ -10084,7 +10084,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G335" t="n">
-        <v>18.9130115509033</v>
+        <v>18.9130096435547</v>
       </c>
       <c r="H335" t="n">
         <v>1050359</v>
@@ -10113,7 +10113,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G336" t="n">
-        <v>19.0264663696289</v>
+        <v>19.0264682769775</v>
       </c>
       <c r="H336" t="n">
         <v>1460378</v>
@@ -10200,7 +10200,7 @@
         <v>22.75</v>
       </c>
       <c r="G339" t="n">
-        <v>19.8556079864502</v>
+        <v>19.8556060791016</v>
       </c>
       <c r="H339" t="n">
         <v>980658</v>
@@ -10229,7 +10229,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G340" t="n">
-        <v>19.7770576477051</v>
+        <v>19.7770557403564</v>
       </c>
       <c r="H340" t="n">
         <v>980376</v>
@@ -10258,7 +10258,7 @@
         <v>23.0100002288818</v>
       </c>
       <c r="G341" t="n">
-        <v>20.0825271606445</v>
+        <v>20.0825290679932</v>
       </c>
       <c r="H341" t="n">
         <v>1419124</v>
@@ -10287,7 +10287,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G342" t="n">
-        <v>20.2483539581299</v>
+        <v>20.2483558654785</v>
       </c>
       <c r="H342" t="n">
         <v>1070816</v>
@@ -10316,7 +10316,7 @@
         <v>23.5100002288818</v>
       </c>
       <c r="G343" t="n">
-        <v>20.5189151763916</v>
+        <v>20.518913269043</v>
       </c>
       <c r="H343" t="n">
         <v>1177145</v>
@@ -10345,7 +10345,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G344" t="n">
-        <v>19.8992443084717</v>
+        <v>19.899242401123</v>
       </c>
       <c r="H344" t="n">
         <v>3314939</v>
@@ -10374,7 +10374,7 @@
         <v>22.0300006866455</v>
       </c>
       <c r="G345" t="n">
-        <v>19.2272129058838</v>
+        <v>19.2272071838379</v>
       </c>
       <c r="H345" t="n">
         <v>3104687</v>
@@ -10432,7 +10432,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G347" t="n">
-        <v>19.331937789917</v>
+        <v>19.3319416046143</v>
       </c>
       <c r="H347" t="n">
         <v>1708988</v>
@@ -10490,7 +10490,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G349" t="n">
-        <v>19.3144874572754</v>
+        <v>19.3144855499268</v>
       </c>
       <c r="H349" t="n">
         <v>680641</v>
@@ -10519,7 +10519,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G350" t="n">
-        <v>19.331937789917</v>
+        <v>19.3319416046143</v>
       </c>
       <c r="H350" t="n">
         <v>591698</v>
@@ -10548,7 +10548,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G351" t="n">
-        <v>19.4279479980469</v>
+        <v>19.4279460906982</v>
       </c>
       <c r="H351" t="n">
         <v>624825</v>
@@ -10577,7 +10577,7 @@
         <v>21.4099998474121</v>
       </c>
       <c r="G352" t="n">
-        <v>18.6860885620117</v>
+        <v>18.6860866546631</v>
       </c>
       <c r="H352" t="n">
         <v>1115090</v>
@@ -10635,7 +10635,7 @@
         <v>21.7700004577637</v>
       </c>
       <c r="G354" t="n">
-        <v>19.0002899169922</v>
+        <v>19.0002861022949</v>
       </c>
       <c r="H354" t="n">
         <v>742088</v>
@@ -10722,7 +10722,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>19.0530872344971</v>
+        <v>19.0530910491943</v>
       </c>
       <c r="H357" t="n">
         <v>594084</v>
@@ -10751,7 +10751,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G358" t="n">
-        <v>18.938684463501</v>
+        <v>18.9386825561523</v>
       </c>
       <c r="H358" t="n">
         <v>678100</v>
@@ -10780,7 +10780,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G359" t="n">
-        <v>19.4491138458252</v>
+        <v>19.4491100311279</v>
       </c>
       <c r="H359" t="n">
         <v>953142</v>
@@ -10809,7 +10809,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G360" t="n">
-        <v>18.6922702789307</v>
+        <v>18.692268371582</v>
       </c>
       <c r="H360" t="n">
         <v>819552</v>
@@ -10867,7 +10867,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G362" t="n">
-        <v>19.0794944763184</v>
+        <v>19.0794925689697</v>
       </c>
       <c r="H362" t="n">
         <v>1232561</v>
@@ -10925,7 +10925,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G364" t="n">
-        <v>18.938684463501</v>
+        <v>18.9386825561523</v>
       </c>
       <c r="H364" t="n">
         <v>512638</v>
@@ -10954,7 +10954,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G365" t="n">
-        <v>18.7362747192383</v>
+        <v>18.7362728118896</v>
       </c>
       <c r="H365" t="n">
         <v>535127</v>
@@ -10983,7 +10983,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G366" t="n">
-        <v>18.3930549621582</v>
+        <v>18.3930530548096</v>
       </c>
       <c r="H366" t="n">
         <v>900255</v>
@@ -11012,7 +11012,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G367" t="n">
-        <v>18.4722576141357</v>
+        <v>18.4722557067871</v>
       </c>
       <c r="H367" t="n">
         <v>907954</v>
@@ -11041,7 +11041,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G368" t="n">
-        <v>18.4370555877686</v>
+        <v>18.4370536804199</v>
       </c>
       <c r="H368" t="n">
         <v>580990</v>
@@ -11099,7 +11099,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G370" t="n">
-        <v>18.0586338043213</v>
+        <v>18.0586357116699</v>
       </c>
       <c r="H370" t="n">
         <v>518850</v>
@@ -11128,7 +11128,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G371" t="n">
-        <v>18.305046081543</v>
+        <v>18.3050479888916</v>
       </c>
       <c r="H371" t="n">
         <v>684982</v>
@@ -11157,7 +11157,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G372" t="n">
-        <v>18.5866641998291</v>
+        <v>18.5866661071777</v>
       </c>
       <c r="H372" t="n">
         <v>746226</v>
@@ -11215,7 +11215,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G374" t="n">
-        <v>18.7978744506836</v>
+        <v>18.7978763580322</v>
       </c>
       <c r="H374" t="n">
         <v>1374327</v>
@@ -11244,7 +11244,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G375" t="n">
-        <v>18.6834697723389</v>
+        <v>18.6834678649902</v>
       </c>
       <c r="H375" t="n">
         <v>732330</v>
@@ -11273,7 +11273,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G376" t="n">
-        <v>19.0618934631348</v>
+        <v>19.0618896484375</v>
       </c>
       <c r="H376" t="n">
         <v>1070037</v>
@@ -11302,7 +11302,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G377" t="n">
-        <v>18.6746673583984</v>
+        <v>18.6746692657471</v>
       </c>
       <c r="H377" t="n">
         <v>1742350</v>
@@ -11389,7 +11389,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G380" t="n">
-        <v>18.7802734375</v>
+        <v>18.7802753448486</v>
       </c>
       <c r="H380" t="n">
         <v>474690</v>
@@ -11476,7 +11476,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G383" t="n">
-        <v>17.8562202453613</v>
+        <v>17.85622215271</v>
       </c>
       <c r="H383" t="n">
         <v>1090391</v>
@@ -11534,7 +11534,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G385" t="n">
-        <v>18.1114368438721</v>
+        <v>18.1114387512207</v>
       </c>
       <c r="H385" t="n">
         <v>693518</v>
@@ -11563,7 +11563,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G386" t="n">
-        <v>18.0762348175049</v>
+        <v>18.0762329101562</v>
       </c>
       <c r="H386" t="n">
         <v>635176</v>
@@ -11621,7 +11621,7 @@
         <v>20.6900005340576</v>
       </c>
       <c r="G388" t="n">
-        <v>18.2082424163818</v>
+        <v>18.2082405090332</v>
       </c>
       <c r="H388" t="n">
         <v>708178</v>
@@ -11679,7 +11679,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>18.5690593719482</v>
+        <v>18.5690612792969</v>
       </c>
       <c r="H390" t="n">
         <v>648533</v>
@@ -11708,7 +11708,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G391" t="n">
-        <v>18.5866641998291</v>
+        <v>18.5866661071777</v>
       </c>
       <c r="H391" t="n">
         <v>648000</v>
@@ -11737,7 +11737,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>18.7450714111328</v>
+        <v>18.7450733184814</v>
       </c>
       <c r="H392" t="n">
         <v>567176</v>
@@ -11795,7 +11795,7 @@
         <v>21.4300003051758</v>
       </c>
       <c r="G394" t="n">
-        <v>18.8594779968262</v>
+        <v>18.8594818115234</v>
       </c>
       <c r="H394" t="n">
         <v>316216</v>
@@ -11882,7 +11882,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G397" t="n">
-        <v>18.7802734375</v>
+        <v>18.7802753448486</v>
       </c>
       <c r="H397" t="n">
         <v>744363</v>
@@ -11969,7 +11969,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G400" t="n">
-        <v>18.6570701599121</v>
+        <v>18.6570682525635</v>
       </c>
       <c r="H400" t="n">
         <v>540083</v>
@@ -12027,7 +12027,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G402" t="n">
-        <v>18.7362747192383</v>
+        <v>18.7362728118896</v>
       </c>
       <c r="H402" t="n">
         <v>480284</v>
@@ -12056,7 +12056,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>19.6691265106201</v>
+        <v>19.6691246032715</v>
       </c>
       <c r="H403" t="n">
         <v>2201726</v>
@@ -12172,7 +12172,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G407" t="n">
-        <v>19.6867256164551</v>
+        <v>19.6867275238037</v>
       </c>
       <c r="H407" t="n">
         <v>501188</v>
@@ -12201,7 +12201,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G408" t="n">
-        <v>19.8187313079834</v>
+        <v>19.818733215332</v>
       </c>
       <c r="H408" t="n">
         <v>393563</v>
@@ -12230,7 +12230,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>19.7571315765381</v>
+        <v>19.7571296691895</v>
       </c>
       <c r="H409" t="n">
         <v>480941</v>
@@ -12259,7 +12259,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>19.7571315765381</v>
+        <v>19.7571296691895</v>
       </c>
       <c r="H410" t="n">
         <v>399927</v>
@@ -12317,7 +12317,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G412" t="n">
-        <v>19.8275375366211</v>
+        <v>19.8275356292725</v>
       </c>
       <c r="H412" t="n">
         <v>514863</v>
@@ -12404,7 +12404,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G415" t="n">
-        <v>20.2587585449219</v>
+        <v>20.2587623596191</v>
       </c>
       <c r="H415" t="n">
         <v>763275</v>
@@ -12462,7 +12462,7 @@
         <v>23.7900009155273</v>
       </c>
       <c r="G417" t="n">
-        <v>20.9363975524902</v>
+        <v>20.9364013671875</v>
       </c>
       <c r="H417" t="n">
         <v>843683</v>
@@ -12491,7 +12491,7 @@
         <v>23.6100006103516</v>
       </c>
       <c r="G418" t="n">
-        <v>20.7779903411865</v>
+        <v>20.7779884338379</v>
       </c>
       <c r="H418" t="n">
         <v>801781</v>
@@ -12520,7 +12520,7 @@
         <v>23.5699996948242</v>
       </c>
       <c r="G419" t="n">
-        <v>20.7427864074707</v>
+        <v>20.7427825927734</v>
       </c>
       <c r="H419" t="n">
         <v>492258</v>
@@ -12607,7 +12607,7 @@
         <v>23.5699996948242</v>
       </c>
       <c r="G422" t="n">
-        <v>20.7427864074707</v>
+        <v>20.7427825927734</v>
       </c>
       <c r="H422" t="n">
         <v>599968</v>
@@ -12665,7 +12665,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G424" t="n">
-        <v>20.6107788085938</v>
+        <v>20.6107769012451</v>
       </c>
       <c r="H424" t="n">
         <v>246848</v>
@@ -12723,7 +12723,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G426" t="n">
-        <v>20.672384262085</v>
+        <v>20.6723823547363</v>
       </c>
       <c r="H426" t="n">
         <v>549649</v>
@@ -12781,7 +12781,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G428" t="n">
-        <v>21.2796173095703</v>
+        <v>21.2796211242676</v>
       </c>
       <c r="H428" t="n">
         <v>824280</v>
@@ -12839,7 +12839,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G430" t="n">
-        <v>21.2796173095703</v>
+        <v>21.2796211242676</v>
       </c>
       <c r="H430" t="n">
         <v>835828</v>
@@ -12868,7 +12868,7 @@
         <v>24.0699996948242</v>
       </c>
       <c r="G431" t="n">
-        <v>21.1828117370605</v>
+        <v>21.1828098297119</v>
       </c>
       <c r="H431" t="n">
         <v>632061</v>
@@ -12897,7 +12897,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G432" t="n">
-        <v>21.3764209747314</v>
+        <v>21.3764247894287</v>
       </c>
       <c r="H432" t="n">
         <v>789134</v>
@@ -12926,7 +12926,7 @@
         <v>24.4699993133545</v>
       </c>
       <c r="G433" t="n">
-        <v>21.5348300933838</v>
+        <v>21.5348320007324</v>
       </c>
       <c r="H433" t="n">
         <v>594140</v>
@@ -12984,7 +12984,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>21.737247467041</v>
+        <v>21.7372436523438</v>
       </c>
       <c r="H435" t="n">
         <v>685133</v>
@@ -13013,7 +13013,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G436" t="n">
-        <v>21.9572563171387</v>
+        <v>21.9572582244873</v>
       </c>
       <c r="H436" t="n">
         <v>1130206</v>
@@ -13042,7 +13042,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G437" t="n">
-        <v>21.737247467041</v>
+        <v>21.7372436523438</v>
       </c>
       <c r="H437" t="n">
         <v>752478</v>
@@ -13071,7 +13071,7 @@
         <v>24.9699993133545</v>
       </c>
       <c r="G438" t="n">
-        <v>21.9748554229736</v>
+        <v>21.9748611450195</v>
       </c>
       <c r="H438" t="n">
         <v>1108014</v>
@@ -13100,7 +13100,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G439" t="n">
-        <v>21.8692531585693</v>
+        <v>21.8692493438721</v>
       </c>
       <c r="H439" t="n">
         <v>807660</v>
@@ -13129,7 +13129,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G440" t="n">
-        <v>21.61403465271</v>
+        <v>21.6140365600586</v>
       </c>
       <c r="H440" t="n">
         <v>1123953</v>
@@ -13158,7 +13158,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G441" t="n">
-        <v>21.7548427581787</v>
+        <v>21.754846572876</v>
       </c>
       <c r="H441" t="n">
         <v>653879</v>
@@ -13187,7 +13187,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G442" t="n">
-        <v>21.6052360534668</v>
+        <v>21.6052341461182</v>
       </c>
       <c r="H442" t="n">
         <v>973852</v>
@@ -13216,7 +13216,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G443" t="n">
-        <v>21.5876350402832</v>
+        <v>21.5876369476318</v>
       </c>
       <c r="H443" t="n">
         <v>510207</v>
@@ -13332,7 +13332,7 @@
         <v>24.3700008392334</v>
       </c>
       <c r="G447" t="n">
-        <v>21.4468269348145</v>
+        <v>21.4468288421631</v>
       </c>
       <c r="H447" t="n">
         <v>656480</v>
@@ -13361,7 +13361,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G448" t="n">
-        <v>21.4908294677734</v>
+        <v>21.4908275604248</v>
       </c>
       <c r="H448" t="n">
         <v>524639</v>
@@ -13390,7 +13390,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G449" t="n">
-        <v>21.5172290802002</v>
+        <v>21.5172309875488</v>
       </c>
       <c r="H449" t="n">
         <v>503593</v>
@@ -13448,7 +13448,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G451" t="n">
-        <v>21.2268142700195</v>
+        <v>21.2268161773682</v>
       </c>
       <c r="H451" t="n">
         <v>1286800</v>
@@ -13477,7 +13477,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G452" t="n">
-        <v>21.1388092041016</v>
+        <v>21.1388111114502</v>
       </c>
       <c r="H452" t="n">
         <v>720527</v>
@@ -13506,7 +13506,7 @@
         <v>23.7099990844727</v>
       </c>
       <c r="G453" t="n">
-        <v>20.8659954071045</v>
+        <v>20.8659934997559</v>
       </c>
       <c r="H453" t="n">
         <v>713778</v>
@@ -13564,7 +13564,7 @@
         <v>24.4599990844727</v>
       </c>
       <c r="G455" t="n">
-        <v>21.5260334014893</v>
+        <v>21.526029586792</v>
       </c>
       <c r="H455" t="n">
         <v>810344</v>
@@ -13680,7 +13680,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G459" t="n">
-        <v>21.6580429077148</v>
+        <v>21.6580390930176</v>
       </c>
       <c r="H459" t="n">
         <v>438350</v>
@@ -13738,7 +13738,7 @@
         <v>24.7299995422363</v>
       </c>
       <c r="G461" t="n">
-        <v>21.7636451721191</v>
+        <v>21.7636432647705</v>
       </c>
       <c r="H461" t="n">
         <v>503921</v>
@@ -13796,7 +13796,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G463" t="n">
-        <v>21.8076477050781</v>
+        <v>21.8076457977295</v>
       </c>
       <c r="H463" t="n">
         <v>1172655</v>
@@ -13883,7 +13883,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G466" t="n">
-        <v>21.728443145752</v>
+        <v>21.7284450531006</v>
       </c>
       <c r="H466" t="n">
         <v>2224743</v>
@@ -13912,7 +13912,7 @@
         <v>24.4300003051758</v>
       </c>
       <c r="G467" t="n">
-        <v>21.4996318817139</v>
+        <v>21.4996337890625</v>
       </c>
       <c r="H467" t="n">
         <v>2552427</v>
@@ -13941,7 +13941,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G468" t="n">
-        <v>21.3764209747314</v>
+        <v>21.3764247894287</v>
       </c>
       <c r="H468" t="n">
         <v>956927</v>
@@ -14028,7 +14028,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G471" t="n">
-        <v>21.7548427581787</v>
+        <v>21.754846572876</v>
       </c>
       <c r="H471" t="n">
         <v>905764</v>
@@ -14057,7 +14057,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G472" t="n">
-        <v>21.3852214813232</v>
+        <v>21.3852233886719</v>
       </c>
       <c r="H472" t="n">
         <v>755944</v>
@@ -14086,7 +14086,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G473" t="n">
-        <v>21.3236179351807</v>
+        <v>21.3236217498779</v>
       </c>
       <c r="H473" t="n">
         <v>795656</v>
@@ -14115,7 +14115,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G474" t="n">
-        <v>21.23561668396</v>
+        <v>21.2356128692627</v>
       </c>
       <c r="H474" t="n">
         <v>731965</v>
@@ -14144,7 +14144,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G475" t="n">
-        <v>21.1564121246338</v>
+        <v>21.1564140319824</v>
       </c>
       <c r="H475" t="n">
         <v>691656</v>
@@ -14173,7 +14173,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G476" t="n">
-        <v>20.672384262085</v>
+        <v>20.6723823547363</v>
       </c>
       <c r="H476" t="n">
         <v>1149844</v>
@@ -14202,7 +14202,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G477" t="n">
-        <v>20.0651473999023</v>
+        <v>20.0651454925537</v>
       </c>
       <c r="H477" t="n">
         <v>1679544</v>
@@ -14260,7 +14260,7 @@
         <v>23.2600002288818</v>
       </c>
       <c r="G479" t="n">
-        <v>20.4699726104736</v>
+        <v>20.469970703125</v>
       </c>
       <c r="H479" t="n">
         <v>1439854</v>
@@ -14289,7 +14289,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G480" t="n">
-        <v>20.4171676635742</v>
+        <v>20.4171695709229</v>
       </c>
       <c r="H480" t="n">
         <v>723004</v>
@@ -14318,7 +14318,7 @@
         <v>22.8299999237061</v>
       </c>
       <c r="G481" t="n">
-        <v>20.0915508270264</v>
+        <v>20.0915489196777</v>
       </c>
       <c r="H481" t="n">
         <v>1192351</v>
@@ -14347,7 +14347,7 @@
         <v>22.9400005340576</v>
       </c>
       <c r="G482" t="n">
-        <v>20.1883544921875</v>
+        <v>20.1883583068848</v>
       </c>
       <c r="H482" t="n">
         <v>709541</v>
@@ -14376,7 +14376,7 @@
         <v>22.8099994659424</v>
       </c>
       <c r="G483" t="n">
-        <v>20.0739498138428</v>
+        <v>20.0739479064941</v>
       </c>
       <c r="H483" t="n">
         <v>511071</v>
@@ -14405,7 +14405,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>20.5051708221436</v>
+        <v>20.5051727294922</v>
       </c>
       <c r="H484" t="n">
         <v>875959</v>
@@ -14463,7 +14463,7 @@
         <v>23.2900009155273</v>
       </c>
       <c r="G486" t="n">
-        <v>20.4963722229004</v>
+        <v>20.496374130249</v>
       </c>
       <c r="H486" t="n">
         <v>581964</v>
@@ -14492,7 +14492,7 @@
         <v>23.5699996948242</v>
       </c>
       <c r="G487" t="n">
-        <v>20.7427864074707</v>
+        <v>20.7427825927734</v>
       </c>
       <c r="H487" t="n">
         <v>431355</v>
@@ -14521,7 +14521,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G488" t="n">
-        <v>20.540376663208</v>
+        <v>20.5403747558594</v>
       </c>
       <c r="H488" t="n">
         <v>537404</v>
@@ -14550,7 +14550,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G489" t="n">
-        <v>20.5051708221436</v>
+        <v>20.5051727294922</v>
       </c>
       <c r="H489" t="n">
         <v>630087</v>
@@ -14579,7 +14579,7 @@
         <v>23.2900009155273</v>
       </c>
       <c r="G490" t="n">
-        <v>20.4963722229004</v>
+        <v>20.496374130249</v>
       </c>
       <c r="H490" t="n">
         <v>634554</v>
@@ -14637,7 +14637,7 @@
         <v>23.0300006866455</v>
       </c>
       <c r="G492" t="n">
-        <v>20.2675590515137</v>
+        <v>20.267557144165</v>
       </c>
       <c r="H492" t="n">
         <v>1005663</v>
@@ -14695,7 +14695,7 @@
         <v>23.0599994659424</v>
       </c>
       <c r="G494" t="n">
-        <v>20.2939605712891</v>
+        <v>20.2939624786377</v>
       </c>
       <c r="H494" t="n">
         <v>461715</v>
@@ -14782,7 +14782,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G497" t="n">
-        <v>21.3324222564697</v>
+        <v>21.3324203491211</v>
       </c>
       <c r="H497" t="n">
         <v>1075786</v>
@@ -14811,7 +14811,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G498" t="n">
-        <v>21.8340492248535</v>
+        <v>21.8340473175049</v>
       </c>
       <c r="H498" t="n">
         <v>1202133</v>
@@ -14869,7 +14869,7 @@
         <v>25.2700004577637</v>
       </c>
       <c r="G500" t="n">
-        <v>22.2388744354248</v>
+        <v>22.2388706207275</v>
       </c>
       <c r="H500" t="n">
         <v>1226430</v>
@@ -14898,7 +14898,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G501" t="n">
-        <v>21.6052360534668</v>
+        <v>21.6052341461182</v>
       </c>
       <c r="H501" t="n">
         <v>1183744</v>
@@ -14927,7 +14927,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G502" t="n">
-        <v>21.3764209747314</v>
+        <v>21.3764247894287</v>
       </c>
       <c r="H502" t="n">
         <v>699500</v>
@@ -14985,7 +14985,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G504" t="n">
-        <v>22.1860694885254</v>
+        <v>22.186071395874</v>
       </c>
       <c r="H504" t="n">
         <v>1426844</v>
@@ -15072,7 +15072,7 @@
         <v>25.5</v>
       </c>
       <c r="G507" t="n">
-        <v>22.4412822723389</v>
+        <v>22.4412841796875</v>
       </c>
       <c r="H507" t="n">
         <v>673865</v>
@@ -15101,7 +15101,7 @@
         <v>25.6800003051758</v>
       </c>
       <c r="G508" t="n">
-        <v>22.5996932983398</v>
+        <v>22.5996971130371</v>
       </c>
       <c r="H508" t="n">
         <v>795151</v>
@@ -15217,7 +15217,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G512" t="n">
-        <v>22.7052974700928</v>
+        <v>22.70530128479</v>
       </c>
       <c r="H512" t="n">
         <v>620738</v>
@@ -15246,7 +15246,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>22.5292892456055</v>
+        <v>22.5292911529541</v>
       </c>
       <c r="H513" t="n">
         <v>531486</v>
@@ -15275,7 +15275,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G514" t="n">
-        <v>22.9693164825439</v>
+        <v>22.9693145751953</v>
       </c>
       <c r="H514" t="n">
         <v>802020</v>
@@ -15304,7 +15304,7 @@
         <v>25.9400005340576</v>
       </c>
       <c r="G515" t="n">
-        <v>22.8285083770752</v>
+        <v>22.8285064697266</v>
       </c>
       <c r="H515" t="n">
         <v>784032</v>
@@ -15420,7 +15420,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G519" t="n">
-        <v>22.1772708892822</v>
+        <v>22.1772689819336</v>
       </c>
       <c r="H519" t="n">
         <v>1112297</v>
@@ -15478,7 +15478,7 @@
         <v>25.4400005340576</v>
       </c>
       <c r="G521" t="n">
-        <v>22.3884811401367</v>
+        <v>22.3884830474854</v>
       </c>
       <c r="H521" t="n">
         <v>579102</v>
@@ -15507,7 +15507,7 @@
         <v>25.5</v>
       </c>
       <c r="G522" t="n">
-        <v>22.4412822723389</v>
+        <v>22.4412841796875</v>
       </c>
       <c r="H522" t="n">
         <v>541546</v>
@@ -15565,7 +15565,7 @@
         <v>26.8799991607666</v>
       </c>
       <c r="G524" t="n">
-        <v>23.6557540893555</v>
+        <v>23.6557521820068</v>
       </c>
       <c r="H524" t="n">
         <v>1384834</v>
@@ -15623,7 +15623,7 @@
         <v>26.7800006866455</v>
       </c>
       <c r="G526" t="n">
-        <v>23.5677509307861</v>
+        <v>23.5677471160889</v>
       </c>
       <c r="H526" t="n">
         <v>1061315</v>
@@ -15652,7 +15652,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G527" t="n">
-        <v>23.690954208374</v>
+        <v>23.6909561157227</v>
       </c>
       <c r="H527" t="n">
         <v>628987</v>
@@ -15681,7 +15681,7 @@
         <v>27.0599994659424</v>
       </c>
       <c r="G528" t="n">
-        <v>23.8141613006592</v>
+        <v>23.8141632080078</v>
       </c>
       <c r="H528" t="n">
         <v>897350</v>
@@ -15710,7 +15710,7 @@
         <v>26.7800006866455</v>
       </c>
       <c r="G529" t="n">
-        <v>23.5677509307861</v>
+        <v>23.5677471160889</v>
       </c>
       <c r="H529" t="n">
         <v>1027867</v>
@@ -15826,7 +15826,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G533" t="n">
-        <v>23.3565368652344</v>
+        <v>23.356538772583</v>
       </c>
       <c r="H533" t="n">
         <v>1001892</v>
@@ -15855,7 +15855,7 @@
         <v>26.7399997711182</v>
       </c>
       <c r="G534" t="n">
-        <v>23.532543182373</v>
+        <v>23.5325469970703</v>
       </c>
       <c r="H534" t="n">
         <v>658257</v>
@@ -15884,7 +15884,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G535" t="n">
-        <v>22.8989105224609</v>
+        <v>22.8989124298096</v>
       </c>
       <c r="H535" t="n">
         <v>532342</v>
@@ -15942,7 +15942,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>22.5292892456055</v>
+        <v>22.5292911529541</v>
       </c>
       <c r="H537" t="n">
         <v>1119529</v>
@@ -16029,7 +16029,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G540" t="n">
-        <v>22.634895324707</v>
+        <v>22.6348934173584</v>
       </c>
       <c r="H540" t="n">
         <v>1326975</v>
@@ -16145,7 +16145,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G544" t="n">
-        <v>24.949426651001</v>
+        <v>24.9494285583496</v>
       </c>
       <c r="H544" t="n">
         <v>1953200</v>
@@ -16174,7 +16174,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G545" t="n">
-        <v>25.0374298095703</v>
+        <v>25.0374317169189</v>
       </c>
       <c r="H545" t="n">
         <v>1152409</v>
@@ -16203,7 +16203,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G546" t="n">
-        <v>24.7118148803711</v>
+        <v>24.7118186950684</v>
       </c>
       <c r="H546" t="n">
         <v>1021909</v>
@@ -16232,7 +16232,7 @@
         <v>28.2299995422363</v>
       </c>
       <c r="G547" t="n">
-        <v>24.8438205718994</v>
+        <v>24.843822479248</v>
       </c>
       <c r="H547" t="n">
         <v>1406010</v>
@@ -16261,7 +16261,7 @@
         <v>28.25</v>
       </c>
       <c r="G548" t="n">
-        <v>24.8614234924316</v>
+        <v>24.861421585083</v>
       </c>
       <c r="H548" t="n">
         <v>958804</v>
@@ -16319,7 +16319,7 @@
         <v>28.0400009155273</v>
       </c>
       <c r="G550" t="n">
-        <v>24.6766166687012</v>
+        <v>24.6766147613525</v>
       </c>
       <c r="H550" t="n">
         <v>888530</v>
@@ -16348,7 +16348,7 @@
         <v>28.3099994659424</v>
       </c>
       <c r="G551" t="n">
-        <v>24.9142246246338</v>
+        <v>24.9142265319824</v>
       </c>
       <c r="H551" t="n">
         <v>3273175</v>
@@ -16377,7 +16377,7 @@
         <v>28.8600006103516</v>
       </c>
       <c r="G552" t="n">
-        <v>25.3982543945312</v>
+        <v>25.3982524871826</v>
       </c>
       <c r="H552" t="n">
         <v>2501270</v>
@@ -16435,7 +16435,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G554" t="n">
-        <v>24.6062088012695</v>
+        <v>24.6062068939209</v>
       </c>
       <c r="H554" t="n">
         <v>1402406</v>
@@ -16493,7 +16493,7 @@
         <v>28.3799991607666</v>
       </c>
       <c r="G556" t="n">
-        <v>24.9758262634277</v>
+        <v>24.9758281707764</v>
       </c>
       <c r="H556" t="n">
         <v>1231907</v>
@@ -16522,7 +16522,7 @@
         <v>28.2399997711182</v>
       </c>
       <c r="G557" t="n">
-        <v>24.8526229858398</v>
+        <v>24.8526210784912</v>
       </c>
       <c r="H557" t="n">
         <v>798613</v>
@@ -16580,7 +16580,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G559" t="n">
-        <v>25.6622676849365</v>
+        <v>25.6622714996338</v>
       </c>
       <c r="H559" t="n">
         <v>1026309</v>
@@ -16609,7 +16609,7 @@
         <v>29.2700004577637</v>
       </c>
       <c r="G560" t="n">
-        <v>25.7590732574463</v>
+        <v>25.7590770721436</v>
       </c>
       <c r="H560" t="n">
         <v>1076660</v>
@@ -16638,7 +16638,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G561" t="n">
-        <v>25.9174842834473</v>
+        <v>25.9174861907959</v>
       </c>
       <c r="H561" t="n">
         <v>1040116</v>
@@ -16667,7 +16667,7 @@
         <v>29.25</v>
       </c>
       <c r="G562" t="n">
-        <v>25.7414741516113</v>
+        <v>25.7414703369141</v>
       </c>
       <c r="H562" t="n">
         <v>966757</v>
@@ -16725,7 +16725,7 @@
         <v>29.6100006103516</v>
       </c>
       <c r="G564" t="n">
-        <v>26.0582942962646</v>
+        <v>26.0582885742188</v>
       </c>
       <c r="H564" t="n">
         <v>887659</v>
@@ -16783,7 +16783,7 @@
         <v>29.7700004577637</v>
       </c>
       <c r="G566" t="n">
-        <v>26.1991004943848</v>
+        <v>26.1990985870361</v>
       </c>
       <c r="H566" t="n">
         <v>958755</v>
@@ -16812,7 +16812,7 @@
         <v>30.3299999237061</v>
       </c>
       <c r="G567" t="n">
-        <v>26.6919269561768</v>
+        <v>26.6919288635254</v>
       </c>
       <c r="H567" t="n">
         <v>1756654</v>
@@ -16870,7 +16870,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G569" t="n">
-        <v>26.7975330352783</v>
+        <v>26.797534942627</v>
       </c>
       <c r="H569" t="n">
         <v>2456285</v>
@@ -16986,7 +16986,7 @@
         <v>30.8299999237061</v>
       </c>
       <c r="G573" t="n">
-        <v>27.131950378418</v>
+        <v>27.1319522857666</v>
       </c>
       <c r="H573" t="n">
         <v>995555</v>
@@ -17015,7 +17015,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>27.1935539245605</v>
+        <v>27.1935577392578</v>
       </c>
       <c r="H574" t="n">
         <v>942142</v>
@@ -17044,7 +17044,7 @@
         <v>32.8699989318848</v>
       </c>
       <c r="G575" t="n">
-        <v>28.9272537231445</v>
+        <v>28.9272556304932</v>
       </c>
       <c r="H575" t="n">
         <v>4195540</v>
@@ -17073,7 +17073,7 @@
         <v>32.5</v>
       </c>
       <c r="G576" t="n">
-        <v>28.601634979248</v>
+        <v>28.6016330718994</v>
       </c>
       <c r="H576" t="n">
         <v>1611053</v>
@@ -17102,7 +17102,7 @@
         <v>32.9199981689453</v>
       </c>
       <c r="G577" t="n">
-        <v>28.9712600708008</v>
+        <v>28.9712581634521</v>
       </c>
       <c r="H577" t="n">
         <v>2075439</v>
@@ -17131,7 +17131,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G578" t="n">
-        <v>29.3056774139404</v>
+        <v>29.3056793212891</v>
       </c>
       <c r="H578" t="n">
         <v>1355277</v>
@@ -17160,7 +17160,7 @@
         <v>33.3899993896484</v>
       </c>
       <c r="G579" t="n">
-        <v>29.3848781585693</v>
+        <v>29.384880065918</v>
       </c>
       <c r="H579" t="n">
         <v>1397575</v>
@@ -17189,7 +17189,7 @@
         <v>33.0299987792969</v>
       </c>
       <c r="G580" t="n">
-        <v>29.0680637359619</v>
+        <v>29.0680618286133</v>
       </c>
       <c r="H580" t="n">
         <v>1597550</v>
@@ -17218,7 +17218,7 @@
         <v>33.75</v>
       </c>
       <c r="G581" t="n">
-        <v>29.7017002105713</v>
+        <v>29.701696395874</v>
       </c>
       <c r="H581" t="n">
         <v>1401063</v>
@@ -17247,7 +17247,7 @@
         <v>33.75</v>
       </c>
       <c r="G582" t="n">
-        <v>29.7017002105713</v>
+        <v>29.701696395874</v>
       </c>
       <c r="H582" t="n">
         <v>1363549</v>
@@ -17276,7 +17276,7 @@
         <v>34.0400009155273</v>
       </c>
       <c r="G583" t="n">
-        <v>29.956916809082</v>
+        <v>29.9569149017334</v>
       </c>
       <c r="H583" t="n">
         <v>1366041</v>
@@ -17305,7 +17305,7 @@
         <v>33.6599998474121</v>
       </c>
       <c r="G584" t="n">
-        <v>29.6224956512451</v>
+        <v>29.6224975585938</v>
       </c>
       <c r="H584" t="n">
         <v>2010222</v>
@@ -17334,7 +17334,7 @@
         <v>34.4599990844727</v>
       </c>
       <c r="G585" t="n">
-        <v>30.3265361785889</v>
+        <v>30.3265342712402</v>
       </c>
       <c r="H585" t="n">
         <v>1696501</v>
@@ -17363,7 +17363,7 @@
         <v>35.2299995422363</v>
       </c>
       <c r="G586" t="n">
-        <v>31.0041770935059</v>
+        <v>31.0041751861572</v>
       </c>
       <c r="H586" t="n">
         <v>2160276</v>
@@ -17392,7 +17392,7 @@
         <v>35.0200004577637</v>
       </c>
       <c r="G587" t="n">
-        <v>30.8193664550781</v>
+        <v>30.8193588256836</v>
       </c>
       <c r="H587" t="n">
         <v>2202729</v>
@@ -17450,7 +17450,7 @@
         <v>35.25</v>
       </c>
       <c r="G589" t="n">
-        <v>31.0217781066895</v>
+        <v>31.0217742919922</v>
       </c>
       <c r="H589" t="n">
         <v>1091262</v>
@@ -17479,7 +17479,7 @@
         <v>36.0200004577637</v>
       </c>
       <c r="G590" t="n">
-        <v>31.6994190216064</v>
+        <v>31.6994132995605</v>
       </c>
       <c r="H590" t="n">
         <v>1503377</v>
@@ -17508,7 +17508,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G591" t="n">
-        <v>31.7698211669922</v>
+        <v>31.7698192596436</v>
       </c>
       <c r="H591" t="n">
         <v>1358065</v>
@@ -17537,7 +17537,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G592" t="n">
-        <v>32.0338363647461</v>
+        <v>32.0338325500488</v>
       </c>
       <c r="H592" t="n">
         <v>1074472</v>
@@ -17566,7 +17566,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>32.5178604125977</v>
+        <v>32.5178642272949</v>
       </c>
       <c r="H593" t="n">
         <v>1243389</v>
@@ -17624,7 +17624,7 @@
         <v>38</v>
       </c>
       <c r="G595" t="n">
-        <v>33.4419136047363</v>
+        <v>33.4419174194336</v>
       </c>
       <c r="H595" t="n">
         <v>2666019</v>
@@ -17653,7 +17653,7 @@
         <v>36.5</v>
       </c>
       <c r="G596" t="n">
-        <v>32.1218452453613</v>
+        <v>32.1218376159668</v>
       </c>
       <c r="H596" t="n">
         <v>2985277</v>
@@ -17682,7 +17682,7 @@
         <v>35.6699981689453</v>
       </c>
       <c r="G597" t="n">
-        <v>31.3913955688477</v>
+        <v>31.391393661499</v>
       </c>
       <c r="H597" t="n">
         <v>3500622</v>
@@ -17711,7 +17711,7 @@
         <v>35.25</v>
       </c>
       <c r="G598" t="n">
-        <v>31.0217781066895</v>
+        <v>31.0217742919922</v>
       </c>
       <c r="H598" t="n">
         <v>2947165</v>
@@ -17740,7 +17740,7 @@
         <v>36.4799995422363</v>
       </c>
       <c r="G599" t="n">
-        <v>32.1042327880859</v>
+        <v>32.1042366027832</v>
       </c>
       <c r="H599" t="n">
         <v>1602446</v>
@@ -17769,7 +17769,7 @@
         <v>36.5299987792969</v>
       </c>
       <c r="G600" t="n">
-        <v>32.1482391357422</v>
+        <v>32.1482429504395</v>
       </c>
       <c r="H600" t="n">
         <v>1348380</v>
@@ -17798,7 +17798,7 @@
         <v>36.7900009155273</v>
       </c>
       <c r="G601" t="n">
-        <v>32.3770523071289</v>
+        <v>32.3770561218262</v>
       </c>
       <c r="H601" t="n">
         <v>1404087</v>
@@ -17827,7 +17827,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>32.7378807067871</v>
+        <v>32.7378692626953</v>
       </c>
       <c r="H602" t="n">
         <v>881437</v>
@@ -17914,7 +17914,7 @@
         <v>37.9799995422363</v>
       </c>
       <c r="G605" t="n">
-        <v>33.4243125915527</v>
+        <v>33.4243087768555</v>
       </c>
       <c r="H605" t="n">
         <v>1363658</v>
@@ -17972,7 +17972,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G607" t="n">
-        <v>34.6739845275879</v>
+        <v>34.6739883422852</v>
       </c>
       <c r="H607" t="n">
         <v>2017540</v>
@@ -18001,7 +18001,7 @@
         <v>38.8600006103516</v>
       </c>
       <c r="G608" t="n">
-        <v>34.4435348510742</v>
+        <v>34.4435386657715</v>
       </c>
       <c r="H608" t="n">
         <v>1119804</v>
@@ -18030,7 +18030,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G609" t="n">
-        <v>33.5040054321289</v>
+        <v>33.5039978027344</v>
       </c>
       <c r="H609" t="n">
         <v>1962179</v>
@@ -18059,7 +18059,7 @@
         <v>36.9799995422363</v>
       </c>
       <c r="G610" t="n">
-        <v>32.7771987915039</v>
+        <v>32.7771949768066</v>
       </c>
       <c r="H610" t="n">
         <v>2393499</v>
@@ -18088,7 +18088,7 @@
         <v>37.8300018310547</v>
       </c>
       <c r="G611" t="n">
-        <v>33.5305976867676</v>
+        <v>33.530590057373</v>
       </c>
       <c r="H611" t="n">
         <v>1649342</v>
@@ -18117,7 +18117,7 @@
         <v>39.2599983215332</v>
       </c>
       <c r="G612" t="n">
-        <v>34.7980690002441</v>
+        <v>34.7980728149414</v>
       </c>
       <c r="H612" t="n">
         <v>2416786</v>
@@ -18204,7 +18204,7 @@
         <v>38.5499992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>34.168758392334</v>
+        <v>34.1687622070312</v>
       </c>
       <c r="H615" t="n">
         <v>2341279</v>
@@ -18233,7 +18233,7 @@
         <v>39.2700004577637</v>
       </c>
       <c r="G616" t="n">
-        <v>34.806941986084</v>
+        <v>34.8069381713867</v>
       </c>
       <c r="H616" t="n">
         <v>18139790</v>
@@ -18291,7 +18291,7 @@
         <v>39.8400001525879</v>
       </c>
       <c r="G618" t="n">
-        <v>35.3121528625488</v>
+        <v>35.3121566772461</v>
       </c>
       <c r="H618" t="n">
         <v>1295859</v>
@@ -18378,7 +18378,7 @@
         <v>39.8400001525879</v>
       </c>
       <c r="G621" t="n">
-        <v>35.3121528625488</v>
+        <v>35.3121566772461</v>
       </c>
       <c r="H621" t="n">
         <v>1637304</v>
@@ -18407,7 +18407,7 @@
         <v>39.75</v>
       </c>
       <c r="G622" t="n">
-        <v>35.2323875427246</v>
+        <v>35.2323837280273</v>
       </c>
       <c r="H622" t="n">
         <v>1264800</v>
@@ -18494,7 +18494,7 @@
         <v>41.560001373291</v>
       </c>
       <c r="G625" t="n">
-        <v>36.8366737365723</v>
+        <v>36.8366775512695</v>
       </c>
       <c r="H625" t="n">
         <v>920031</v>
@@ -18581,7 +18581,7 @@
         <v>41.4700012207031</v>
       </c>
       <c r="G628" t="n">
-        <v>36.7569046020508</v>
+        <v>36.756908416748</v>
       </c>
       <c r="H628" t="n">
         <v>821599</v>
@@ -18610,7 +18610,7 @@
         <v>40.189998626709</v>
       </c>
       <c r="G629" t="n">
-        <v>35.6223793029785</v>
+        <v>35.6223754882812</v>
       </c>
       <c r="H629" t="n">
         <v>1546782</v>
@@ -18639,7 +18639,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G630" t="n">
-        <v>35.3210144042969</v>
+        <v>35.3210182189941</v>
       </c>
       <c r="H630" t="n">
         <v>1011172</v>
@@ -18668,7 +18668,7 @@
         <v>39.7799987792969</v>
       </c>
       <c r="G631" t="n">
-        <v>35.258975982666</v>
+        <v>35.2589683532715</v>
       </c>
       <c r="H631" t="n">
         <v>993775</v>
@@ -18697,7 +18697,7 @@
         <v>39.5699996948242</v>
       </c>
       <c r="G632" t="n">
-        <v>35.0728416442871</v>
+        <v>35.0728378295898</v>
       </c>
       <c r="H632" t="n">
         <v>629661</v>
@@ -18726,7 +18726,7 @@
         <v>38.8300018310547</v>
       </c>
       <c r="G633" t="n">
-        <v>34.4169502258301</v>
+        <v>34.4169464111328</v>
       </c>
       <c r="H633" t="n">
         <v>912183</v>
@@ -18755,7 +18755,7 @@
         <v>38.810001373291</v>
       </c>
       <c r="G634" t="n">
-        <v>34.3992156982422</v>
+        <v>34.3992195129395</v>
       </c>
       <c r="H634" t="n">
         <v>1259802</v>
@@ -18784,7 +18784,7 @@
         <v>38.939998626709</v>
       </c>
       <c r="G635" t="n">
-        <v>34.5144386291504</v>
+        <v>34.5144424438477</v>
       </c>
       <c r="H635" t="n">
         <v>1183997</v>
@@ -18842,7 +18842,7 @@
         <v>39</v>
       </c>
       <c r="G637" t="n">
-        <v>34.5676231384277</v>
+        <v>34.5676193237305</v>
       </c>
       <c r="H637" t="n">
         <v>854719</v>
@@ -18871,7 +18871,7 @@
         <v>38.7599983215332</v>
       </c>
       <c r="G638" t="n">
-        <v>34.3549003601074</v>
+        <v>34.3548965454102</v>
       </c>
       <c r="H638" t="n">
         <v>1297277</v>
@@ -18900,7 +18900,7 @@
         <v>39.2700004577637</v>
       </c>
       <c r="G639" t="n">
-        <v>34.806941986084</v>
+        <v>34.8069381713867</v>
       </c>
       <c r="H639" t="n">
         <v>875723</v>
@@ -18929,7 +18929,7 @@
         <v>37.8499984741211</v>
       </c>
       <c r="G640" t="n">
-        <v>33.5483131408691</v>
+        <v>33.5483207702637</v>
       </c>
       <c r="H640" t="n">
         <v>955148</v>
@@ -18958,7 +18958,7 @@
         <v>37.2299995422363</v>
       </c>
       <c r="G641" t="n">
-        <v>32.9987831115723</v>
+        <v>32.998779296875</v>
       </c>
       <c r="H641" t="n">
         <v>1638462</v>
@@ -19016,7 +19016,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G643" t="n">
-        <v>33.3267288208008</v>
+        <v>33.326732635498</v>
       </c>
       <c r="H643" t="n">
         <v>960730</v>
@@ -19045,7 +19045,7 @@
         <v>38.439998626709</v>
       </c>
       <c r="G644" t="n">
-        <v>34.0712699890137</v>
+        <v>34.0712661743164</v>
       </c>
       <c r="H644" t="n">
         <v>929686</v>
@@ -19074,7 +19074,7 @@
         <v>37.4799995422363</v>
       </c>
       <c r="G645" t="n">
-        <v>33.2203636169434</v>
+        <v>33.2203750610352</v>
       </c>
       <c r="H645" t="n">
         <v>828797</v>
@@ -19132,7 +19132,7 @@
         <v>39.0299987792969</v>
       </c>
       <c r="G647" t="n">
-        <v>34.5942115783691</v>
+        <v>34.5942077636719</v>
       </c>
       <c r="H647" t="n">
         <v>822041</v>
@@ -19190,7 +19190,7 @@
         <v>39.060001373291</v>
       </c>
       <c r="G649" t="n">
-        <v>34.6208038330078</v>
+        <v>34.6208076477051</v>
       </c>
       <c r="H649" t="n">
         <v>560716</v>
@@ -19219,7 +19219,7 @@
         <v>39</v>
       </c>
       <c r="G650" t="n">
-        <v>34.5676231384277</v>
+        <v>34.5676193237305</v>
       </c>
       <c r="H650" t="n">
         <v>662049</v>
@@ -19306,7 +19306,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>34.3903503417969</v>
+        <v>34.3903541564941</v>
       </c>
       <c r="H653" t="n">
         <v>591268</v>
@@ -19364,7 +19364,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G655" t="n">
-        <v>35.1437530517578</v>
+        <v>35.1437492370605</v>
       </c>
       <c r="H655" t="n">
         <v>1201207</v>
@@ -19451,7 +19451,7 @@
         <v>37.0699996948242</v>
       </c>
       <c r="G658" t="n">
-        <v>32.8569602966309</v>
+        <v>32.8569717407227</v>
       </c>
       <c r="H658" t="n">
         <v>637192</v>
@@ -19480,7 +19480,7 @@
         <v>37.7200012207031</v>
       </c>
       <c r="G659" t="n">
-        <v>33.4330940246582</v>
+        <v>33.4331016540527</v>
       </c>
       <c r="H659" t="n">
         <v>880738</v>
@@ -19567,7 +19567,7 @@
         <v>36.9799995422363</v>
       </c>
       <c r="G662" t="n">
-        <v>32.7771987915039</v>
+        <v>32.7771949768066</v>
       </c>
       <c r="H662" t="n">
         <v>935055</v>
@@ -19596,7 +19596,7 @@
         <v>37.5699996948242</v>
       </c>
       <c r="G663" t="n">
-        <v>33.3001480102539</v>
+        <v>33.3001403808594</v>
       </c>
       <c r="H663" t="n">
         <v>655079</v>
@@ -19625,7 +19625,7 @@
         <v>38.5499992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>34.168758392334</v>
+        <v>34.1687622070312</v>
       </c>
       <c r="H664" t="n">
         <v>851691</v>
@@ -19654,7 +19654,7 @@
         <v>37.689998626709</v>
       </c>
       <c r="G665" t="n">
-        <v>33.4065017700195</v>
+        <v>33.4065055847168</v>
       </c>
       <c r="H665" t="n">
         <v>599833</v>
@@ -19712,7 +19712,7 @@
         <v>37.0699996948242</v>
       </c>
       <c r="G667" t="n">
-        <v>32.8569602966309</v>
+        <v>32.8569717407227</v>
       </c>
       <c r="H667" t="n">
         <v>962818</v>
@@ -19770,7 +19770,7 @@
         <v>37.9599990844727</v>
       </c>
       <c r="G669" t="n">
-        <v>33.6458206176758</v>
+        <v>33.6458168029785</v>
       </c>
       <c r="H669" t="n">
         <v>462152</v>
@@ -19799,7 +19799,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G670" t="n">
-        <v>33.5040054321289</v>
+        <v>33.5039978027344</v>
       </c>
       <c r="H670" t="n">
         <v>939024</v>
@@ -19828,7 +19828,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G671" t="n">
-        <v>33.0608253479004</v>
+        <v>33.0608291625977</v>
       </c>
       <c r="H671" t="n">
         <v>557639</v>
@@ -19857,7 +19857,7 @@
         <v>38.1800003051758</v>
       </c>
       <c r="G672" t="n">
-        <v>33.8408164978027</v>
+        <v>33.8408203125</v>
       </c>
       <c r="H672" t="n">
         <v>474647</v>
@@ -19886,7 +19886,7 @@
         <v>37.810001373291</v>
       </c>
       <c r="G673" t="n">
-        <v>33.512866973877</v>
+        <v>33.5128631591797</v>
       </c>
       <c r="H673" t="n">
         <v>460717</v>
@@ -19915,7 +19915,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G674" t="n">
-        <v>33.8142280578613</v>
+        <v>33.8142318725586</v>
       </c>
       <c r="H674" t="n">
         <v>498965</v>
@@ -19973,7 +19973,7 @@
         <v>39.0099983215332</v>
       </c>
       <c r="G676" t="n">
-        <v>34.576488494873</v>
+        <v>34.5764846801758</v>
       </c>
       <c r="H676" t="n">
         <v>720063</v>
@@ -20002,7 +20002,7 @@
         <v>39.7099990844727</v>
       </c>
       <c r="G677" t="n">
-        <v>35.1969299316406</v>
+        <v>35.1969337463379</v>
       </c>
       <c r="H677" t="n">
         <v>498198</v>
@@ -20060,7 +20060,7 @@
         <v>39.8199996948242</v>
       </c>
       <c r="G679" t="n">
-        <v>35.2944259643555</v>
+        <v>35.2944297790527</v>
       </c>
       <c r="H679" t="n">
         <v>437405</v>
@@ -20089,7 +20089,7 @@
         <v>39.7799987792969</v>
       </c>
       <c r="G680" t="n">
-        <v>35.258975982666</v>
+        <v>35.2589683532715</v>
       </c>
       <c r="H680" t="n">
         <v>555816</v>
@@ -20147,7 +20147,7 @@
         <v>38.9300003051758</v>
       </c>
       <c r="G682" t="n">
-        <v>34.5055770874023</v>
+        <v>34.5055809020996</v>
       </c>
       <c r="H682" t="n">
         <v>365722</v>
@@ -20176,7 +20176,7 @@
         <v>38.5</v>
       </c>
       <c r="G683" t="n">
-        <v>34.1244468688965</v>
+        <v>34.1244430541992</v>
       </c>
       <c r="H683" t="n">
         <v>964295</v>
@@ -20205,7 +20205,7 @@
         <v>36.9799995422363</v>
       </c>
       <c r="G684" t="n">
-        <v>32.7771987915039</v>
+        <v>32.7771949768066</v>
       </c>
       <c r="H684" t="n">
         <v>1524454</v>
@@ -20292,7 +20292,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G687" t="n">
-        <v>33.3710556030273</v>
+        <v>33.3710479736328</v>
       </c>
       <c r="H687" t="n">
         <v>858773</v>
@@ -20321,7 +20321,7 @@
         <v>37.6100006103516</v>
       </c>
       <c r="G688" t="n">
-        <v>33.3355941772461</v>
+        <v>33.3355979919434</v>
       </c>
       <c r="H688" t="n">
         <v>775565</v>
@@ -20379,7 +20379,7 @@
         <v>37.2599983215332</v>
       </c>
       <c r="G690" t="n">
-        <v>33.0253715515137</v>
+        <v>33.0253753662109</v>
       </c>
       <c r="H690" t="n">
         <v>749361</v>
@@ -20408,7 +20408,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G691" t="n">
-        <v>33.6369552612305</v>
+        <v>33.6369514465332</v>
       </c>
       <c r="H691" t="n">
         <v>872939</v>
@@ -20437,7 +20437,7 @@
         <v>37.7400016784668</v>
       </c>
       <c r="G692" t="n">
-        <v>33.4508247375488</v>
+        <v>33.4508209228516</v>
       </c>
       <c r="H692" t="n">
         <v>1047439</v>
@@ -20466,7 +20466,7 @@
         <v>37.9300003051758</v>
       </c>
       <c r="G693" t="n">
-        <v>33.6192245483398</v>
+        <v>33.6192283630371</v>
       </c>
       <c r="H693" t="n">
         <v>1080085</v>
@@ -20495,7 +20495,7 @@
         <v>37.8499984741211</v>
       </c>
       <c r="G694" t="n">
-        <v>33.5483131408691</v>
+        <v>33.5483207702637</v>
       </c>
       <c r="H694" t="n">
         <v>941395</v>
@@ -20524,7 +20524,7 @@
         <v>37.8400001525879</v>
       </c>
       <c r="G695" t="n">
-        <v>33.5394630432129</v>
+        <v>33.5394592285156</v>
       </c>
       <c r="H695" t="n">
         <v>1005962</v>
@@ -20553,7 +20553,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G696" t="n">
-        <v>33.6369552612305</v>
+        <v>33.6369514465332</v>
       </c>
       <c r="H696" t="n">
         <v>1603224</v>
@@ -20611,7 +20611,7 @@
         <v>37.8300018310547</v>
       </c>
       <c r="G698" t="n">
-        <v>33.5305976867676</v>
+        <v>33.530590057373</v>
       </c>
       <c r="H698" t="n">
         <v>655566</v>
@@ -20640,7 +20640,7 @@
         <v>37.7299995422363</v>
       </c>
       <c r="G699" t="n">
-        <v>33.4419555664062</v>
+        <v>33.4419631958008</v>
       </c>
       <c r="H699" t="n">
         <v>453942</v>
@@ -20669,7 +20669,7 @@
         <v>38.0099983215332</v>
       </c>
       <c r="G700" t="n">
-        <v>33.6901359558105</v>
+        <v>33.6901321411133</v>
       </c>
       <c r="H700" t="n">
         <v>534553</v>
@@ -20727,7 +20727,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G702" t="n">
-        <v>34.3903503417969</v>
+        <v>34.3903541564941</v>
       </c>
       <c r="H702" t="n">
         <v>1292766</v>
@@ -20785,7 +20785,7 @@
         <v>38.310001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>33.9560432434082</v>
+        <v>33.9560470581055</v>
       </c>
       <c r="H704" t="n">
         <v>540842</v>
@@ -20814,7 +20814,7 @@
         <v>36.1599998474121</v>
       </c>
       <c r="G705" t="n">
-        <v>32.0503845214844</v>
+        <v>32.0503921508789</v>
       </c>
       <c r="H705" t="n">
         <v>1298576</v>
@@ -20901,7 +20901,7 @@
         <v>35.5900001525879</v>
       </c>
       <c r="G708" t="n">
-        <v>31.5451679229736</v>
+        <v>31.5451717376709</v>
       </c>
       <c r="H708" t="n">
         <v>990650</v>
@@ -20930,7 +20930,7 @@
         <v>31.7299995422363</v>
       </c>
       <c r="G709" t="n">
-        <v>28.1238594055176</v>
+        <v>28.1238632202148</v>
       </c>
       <c r="H709" t="n">
         <v>3800188</v>
@@ -20959,7 +20959,7 @@
         <v>31.2800006866455</v>
       </c>
       <c r="G710" t="n">
-        <v>27.7250099182129</v>
+        <v>27.725004196167</v>
       </c>
       <c r="H710" t="n">
         <v>3957912</v>
@@ -21075,7 +21075,7 @@
         <v>31.1399993896484</v>
       </c>
       <c r="G714" t="n">
-        <v>27.6009140014648</v>
+        <v>27.6009178161621</v>
       </c>
       <c r="H714" t="n">
         <v>2190535</v>
@@ -21104,7 +21104,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>27.6540966033936</v>
+        <v>27.6541004180908</v>
       </c>
       <c r="H715" t="n">
         <v>1356889</v>
@@ -21249,7 +21249,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>27.1222877502441</v>
+        <v>27.1222896575928</v>
       </c>
       <c r="H720" t="n">
         <v>3234856</v>
@@ -21278,7 +21278,7 @@
         <v>30.2299995422363</v>
       </c>
       <c r="G721" t="n">
-        <v>26.794340133667</v>
+        <v>26.7943363189697</v>
       </c>
       <c r="H721" t="n">
         <v>1800816</v>
@@ -21307,7 +21307,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G722" t="n">
-        <v>26.4132099151611</v>
+        <v>26.4132080078125</v>
       </c>
       <c r="H722" t="n">
         <v>1796370</v>
@@ -21365,7 +21365,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>27.2109241485596</v>
+        <v>27.2109222412109</v>
       </c>
       <c r="H724" t="n">
         <v>1719539</v>
@@ -21481,7 +21481,7 @@
         <v>31.7700004577637</v>
       </c>
       <c r="G728" t="n">
-        <v>28.1593170166016</v>
+        <v>28.1593189239502</v>
       </c>
       <c r="H728" t="n">
         <v>924294</v>
@@ -21626,7 +21626,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G733" t="n">
-        <v>27.6540966033936</v>
+        <v>27.6541004180908</v>
       </c>
       <c r="H733" t="n">
         <v>1242713</v>
@@ -21655,7 +21655,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G734" t="n">
-        <v>28.2213611602783</v>
+        <v>28.2213649749756</v>
       </c>
       <c r="H734" t="n">
         <v>1625490</v>
@@ -21684,7 +21684,7 @@
         <v>30.7299995422363</v>
       </c>
       <c r="G735" t="n">
-        <v>27.2375106811523</v>
+        <v>27.2375144958496</v>
       </c>
       <c r="H735" t="n">
         <v>1500072</v>
@@ -21742,7 +21742,7 @@
         <v>29.9899997711182</v>
       </c>
       <c r="G737" t="n">
-        <v>26.581615447998</v>
+        <v>26.5816173553467</v>
       </c>
       <c r="H737" t="n">
         <v>906568</v>
@@ -21887,7 +21887,7 @@
         <v>30.7299995422363</v>
       </c>
       <c r="G742" t="n">
-        <v>27.2375106811523</v>
+        <v>27.2375144958496</v>
       </c>
       <c r="H742" t="n">
         <v>1040510</v>
@@ -21945,7 +21945,7 @@
         <v>29.3099994659424</v>
       </c>
       <c r="G744" t="n">
-        <v>25.9788970947266</v>
+        <v>25.9788990020752</v>
       </c>
       <c r="H744" t="n">
         <v>831873</v>
@@ -22003,7 +22003,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G746" t="n">
-        <v>25.5091323852539</v>
+        <v>25.5091361999512</v>
       </c>
       <c r="H746" t="n">
         <v>2134397</v>
@@ -22032,7 +22032,7 @@
         <v>30.4899997711182</v>
       </c>
       <c r="G747" t="n">
-        <v>27.024787902832</v>
+        <v>27.0247898101807</v>
       </c>
       <c r="H747" t="n">
         <v>1638374</v>
@@ -22061,7 +22061,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>26.0143508911133</v>
+        <v>26.0143527984619</v>
       </c>
       <c r="H748" t="n">
         <v>1130216</v>
@@ -22119,7 +22119,7 @@
         <v>29.0699996948242</v>
       </c>
       <c r="G750" t="n">
-        <v>25.7661743164062</v>
+        <v>25.7661762237549</v>
       </c>
       <c r="H750" t="n">
         <v>1146861</v>
@@ -22206,7 +22206,7 @@
         <v>27.7700004577637</v>
       </c>
       <c r="G753" t="n">
-        <v>24.6139221191406</v>
+        <v>24.613920211792</v>
       </c>
       <c r="H753" t="n">
         <v>1406234</v>
@@ -22235,7 +22235,7 @@
         <v>28.4599990844727</v>
       </c>
       <c r="G754" t="n">
-        <v>25.2255001068115</v>
+        <v>25.2255020141602</v>
       </c>
       <c r="H754" t="n">
         <v>881877</v>
@@ -22293,7 +22293,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>24.4189224243164</v>
+        <v>24.418924331665</v>
       </c>
       <c r="H756" t="n">
         <v>1276363</v>
@@ -22351,7 +22351,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G758" t="n">
-        <v>24.4632377624512</v>
+        <v>24.4632396697998</v>
       </c>
       <c r="H758" t="n">
         <v>1620255</v>
@@ -22409,7 +22409,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G760" t="n">
-        <v>24.4366493225098</v>
+        <v>24.4366512298584</v>
       </c>
       <c r="H760" t="n">
         <v>895518</v>
@@ -22438,7 +22438,7 @@
         <v>27.7900009155273</v>
       </c>
       <c r="G761" t="n">
-        <v>24.6316452026367</v>
+        <v>24.631649017334</v>
       </c>
       <c r="H761" t="n">
         <v>1104468</v>
@@ -22496,7 +22496,7 @@
         <v>28.9300003051758</v>
       </c>
       <c r="G763" t="n">
-        <v>25.6420841217041</v>
+        <v>25.6420860290527</v>
       </c>
       <c r="H763" t="n">
         <v>922395</v>
@@ -22525,7 +22525,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G764" t="n">
-        <v>25.8459434509277</v>
+        <v>25.8459453582764</v>
       </c>
       <c r="H764" t="n">
         <v>767016</v>
@@ -22583,7 +22583,7 @@
         <v>29.0200004577637</v>
       </c>
       <c r="G766" t="n">
-        <v>25.7218589782715</v>
+        <v>25.7218570709229</v>
       </c>
       <c r="H766" t="n">
         <v>1425551</v>
@@ -22612,7 +22612,7 @@
         <v>29.8099994659424</v>
       </c>
       <c r="G767" t="n">
-        <v>26.4220714569092</v>
+        <v>26.4220695495605</v>
       </c>
       <c r="H767" t="n">
         <v>918961</v>
@@ -22641,7 +22641,7 @@
         <v>30.6299991607666</v>
       </c>
       <c r="G768" t="n">
-        <v>27.1488780975342</v>
+        <v>27.1488800048828</v>
       </c>
       <c r="H768" t="n">
         <v>1024849</v>
@@ -22699,7 +22699,7 @@
         <v>30.8600006103516</v>
       </c>
       <c r="G770" t="n">
-        <v>27.3527393341064</v>
+        <v>27.3527412414551</v>
       </c>
       <c r="H770" t="n">
         <v>1430045</v>
@@ -22786,7 +22786,7 @@
         <v>29.6399993896484</v>
       </c>
       <c r="G773" t="n">
-        <v>26.2713947296143</v>
+        <v>26.2713928222656</v>
       </c>
       <c r="H773" t="n">
         <v>693348</v>
@@ -22902,7 +22902,7 @@
         <v>30.5900001525879</v>
       </c>
       <c r="G777" t="n">
-        <v>27.1134262084961</v>
+        <v>27.1134243011475</v>
       </c>
       <c r="H777" t="n">
         <v>530815</v>
@@ -22960,7 +22960,7 @@
         <v>30.0200004577637</v>
       </c>
       <c r="G779" t="n">
-        <v>26.6082038879395</v>
+        <v>26.6082057952881</v>
       </c>
       <c r="H779" t="n">
         <v>757681</v>
@@ -22989,7 +22989,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>27.1222877502441</v>
+        <v>27.1222896575928</v>
       </c>
       <c r="H780" t="n">
         <v>1098776</v>
@@ -23018,7 +23018,7 @@
         <v>30.6499996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>27.1666069030762</v>
+        <v>27.1666049957275</v>
       </c>
       <c r="H781" t="n">
         <v>753799</v>
@@ -23047,7 +23047,7 @@
         <v>30.5699996948242</v>
       </c>
       <c r="G782" t="n">
-        <v>27.0956974029541</v>
+        <v>27.0956954956055</v>
       </c>
       <c r="H782" t="n">
         <v>604836</v>
@@ -23076,7 +23076,7 @@
         <v>30.9599990844727</v>
       </c>
       <c r="G783" t="n">
-        <v>27.4413719177246</v>
+        <v>27.441370010376</v>
       </c>
       <c r="H783" t="n">
         <v>1036861</v>
@@ -23134,7 +23134,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G785" t="n">
-        <v>29.1608943939209</v>
+        <v>29.1608924865723</v>
       </c>
       <c r="H785" t="n">
         <v>1615118</v>
@@ -23163,7 +23163,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G786" t="n">
-        <v>29.7370128631592</v>
+        <v>29.7370147705078</v>
       </c>
       <c r="H786" t="n">
         <v>1741406</v>
@@ -23192,7 +23192,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>29.7370128631592</v>
+        <v>29.7370147705078</v>
       </c>
       <c r="H787" t="n">
         <v>1067159</v>
@@ -23221,7 +23221,7 @@
         <v>33.7700004577637</v>
       </c>
       <c r="G788" t="n">
-        <v>29.9320125579834</v>
+        <v>29.9320163726807</v>
       </c>
       <c r="H788" t="n">
         <v>682186</v>
@@ -23250,7 +23250,7 @@
         <v>34.2099990844727</v>
       </c>
       <c r="G789" t="n">
-        <v>30.3220043182373</v>
+        <v>30.3220081329346</v>
       </c>
       <c r="H789" t="n">
         <v>1701124</v>
@@ -23279,7 +23279,7 @@
         <v>33.3800010681152</v>
       </c>
       <c r="G790" t="n">
-        <v>29.5863418579102</v>
+        <v>29.5863399505615</v>
       </c>
       <c r="H790" t="n">
         <v>1071605</v>
@@ -23308,7 +23308,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G791" t="n">
-        <v>29.7813377380371</v>
+        <v>29.7813339233398</v>
       </c>
       <c r="H791" t="n">
         <v>926123</v>
@@ -23337,7 +23337,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G792" t="n">
-        <v>30.0649719238281</v>
+        <v>30.0649662017822</v>
       </c>
       <c r="H792" t="n">
         <v>850712</v>
@@ -23366,7 +23366,7 @@
         <v>34.7599983215332</v>
       </c>
       <c r="G793" t="n">
-        <v>30.809497833252</v>
+        <v>30.8095016479492</v>
       </c>
       <c r="H793" t="n">
         <v>1670028</v>
@@ -23395,7 +23395,7 @@
         <v>34.9900016784668</v>
       </c>
       <c r="G794" t="n">
-        <v>31.0133647918701</v>
+        <v>31.0133609771729</v>
       </c>
       <c r="H794" t="n">
         <v>1207749</v>
@@ -23424,7 +23424,7 @@
         <v>34.6500015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>30.7120018005371</v>
+        <v>30.712007522583</v>
       </c>
       <c r="H795" t="n">
         <v>1435515</v>
@@ -23453,7 +23453,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G796" t="n">
-        <v>30.4460945129395</v>
+        <v>30.4460983276367</v>
       </c>
       <c r="H796" t="n">
         <v>1441009</v>
@@ -23482,7 +23482,7 @@
         <v>34.8800010681152</v>
       </c>
       <c r="G797" t="n">
-        <v>30.9158687591553</v>
+        <v>30.915864944458</v>
       </c>
       <c r="H797" t="n">
         <v>659300</v>
@@ -23511,7 +23511,7 @@
         <v>34.8400001525879</v>
       </c>
       <c r="G798" t="n">
-        <v>30.880407333374</v>
+        <v>30.8804111480713</v>
       </c>
       <c r="H798" t="n">
         <v>634325</v>
@@ -23540,7 +23540,7 @@
         <v>34.7099990844727</v>
       </c>
       <c r="G799" t="n">
-        <v>30.7651844024658</v>
+        <v>30.7651863098145</v>
       </c>
       <c r="H799" t="n">
         <v>823941</v>
@@ -23569,7 +23569,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G800" t="n">
-        <v>30.756326675415</v>
+        <v>30.7563247680664</v>
       </c>
       <c r="H800" t="n">
         <v>1405682</v>
@@ -23598,7 +23598,7 @@
         <v>34.5099983215332</v>
       </c>
       <c r="G801" t="n">
-        <v>30.5879135131836</v>
+        <v>30.587911605835</v>
       </c>
       <c r="H801" t="n">
         <v>920024</v>
@@ -23685,7 +23685,7 @@
         <v>34.2099990844727</v>
       </c>
       <c r="G804" t="n">
-        <v>30.3220043182373</v>
+        <v>30.3220081329346</v>
       </c>
       <c r="H804" t="n">
         <v>1006399</v>
@@ -23714,7 +23714,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G805" t="n">
-        <v>29.8876991271973</v>
+        <v>29.8876972198486</v>
       </c>
       <c r="H805" t="n">
         <v>1297265</v>
@@ -23743,7 +23743,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G806" t="n">
-        <v>33.1937789916992</v>
+        <v>33.1937828063965</v>
       </c>
       <c r="H806" t="n">
         <v>5810745</v>
@@ -23801,7 +23801,7 @@
         <v>36.0999984741211</v>
       </c>
       <c r="G808" t="n">
-        <v>31.9972133636475</v>
+        <v>31.9972057342529</v>
       </c>
       <c r="H808" t="n">
         <v>1604293</v>
@@ -23830,7 +23830,7 @@
         <v>36</v>
       </c>
       <c r="G809" t="n">
-        <v>31.9085712432861</v>
+        <v>31.9085750579834</v>
       </c>
       <c r="H809" t="n">
         <v>1045374</v>
@@ -23859,7 +23859,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G810" t="n">
-        <v>31.7756233215332</v>
+        <v>31.7756214141846</v>
       </c>
       <c r="H810" t="n">
         <v>1116850</v>
@@ -23888,7 +23888,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>31.5983486175537</v>
+        <v>31.598352432251</v>
       </c>
       <c r="H811" t="n">
         <v>809991</v>
@@ -23917,7 +23917,7 @@
         <v>35.7200012207031</v>
       </c>
       <c r="G812" t="n">
-        <v>31.660400390625</v>
+        <v>31.6603984832764</v>
       </c>
       <c r="H812" t="n">
         <v>1039812</v>
@@ -23946,7 +23946,7 @@
         <v>35.560001373291</v>
       </c>
       <c r="G813" t="n">
-        <v>31.5185813903809</v>
+        <v>31.5185852050781</v>
       </c>
       <c r="H813" t="n">
         <v>434769</v>
@@ -23975,7 +23975,7 @@
         <v>36.0900001525879</v>
       </c>
       <c r="G814" t="n">
-        <v>31.9883460998535</v>
+        <v>31.9883403778076</v>
       </c>
       <c r="H814" t="n">
         <v>1074919</v>
@@ -24149,7 +24149,7 @@
         <v>36</v>
       </c>
       <c r="G820" t="n">
-        <v>31.9085712432861</v>
+        <v>31.9085750579834</v>
       </c>
       <c r="H820" t="n">
         <v>1016518</v>
@@ -24178,7 +24178,7 @@
         <v>35.3400001525879</v>
       </c>
       <c r="G821" t="n">
-        <v>31.3235855102539</v>
+        <v>31.3235836029053</v>
       </c>
       <c r="H821" t="n">
         <v>1262625</v>
@@ -24207,7 +24207,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G822" t="n">
-        <v>30.8449535369873</v>
+        <v>30.8449554443359</v>
       </c>
       <c r="H822" t="n">
         <v>1377576</v>
@@ -24236,7 +24236,7 @@
         <v>35.5699996948242</v>
       </c>
       <c r="G823" t="n">
-        <v>31.5274448394775</v>
+        <v>31.5274410247803</v>
       </c>
       <c r="H823" t="n">
         <v>1008251</v>
@@ -24265,7 +24265,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G824" t="n">
-        <v>31.5983486175537</v>
+        <v>31.598352432251</v>
       </c>
       <c r="H824" t="n">
         <v>896495</v>
@@ -24294,7 +24294,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G825" t="n">
-        <v>31.5983486175537</v>
+        <v>31.598352432251</v>
       </c>
       <c r="H825" t="n">
         <v>699585</v>
@@ -24323,7 +24323,7 @@
         <v>35.9199981689453</v>
       </c>
       <c r="G826" t="n">
-        <v>31.8376636505127</v>
+        <v>31.8376655578613</v>
       </c>
       <c r="H826" t="n">
         <v>884296</v>
@@ -24352,7 +24352,7 @@
         <v>36.7400016784668</v>
       </c>
       <c r="G827" t="n">
-        <v>32.5644721984863</v>
+        <v>32.5644683837891</v>
       </c>
       <c r="H827" t="n">
         <v>1157500</v>
@@ -24439,7 +24439,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G830" t="n">
-        <v>32.9721984863281</v>
+        <v>32.9721908569336</v>
       </c>
       <c r="H830" t="n">
         <v>781643</v>
@@ -24526,7 +24526,7 @@
         <v>35.9799995422363</v>
       </c>
       <c r="G833" t="n">
-        <v>31.8908443450928</v>
+        <v>31.8908424377441</v>
       </c>
       <c r="H833" t="n">
         <v>924927</v>
@@ -24555,7 +24555,7 @@
         <v>35.810001373291</v>
       </c>
       <c r="G834" t="n">
-        <v>31.7401714324951</v>
+        <v>31.7401733398438</v>
       </c>
       <c r="H834" t="n">
         <v>781363</v>
@@ -24613,7 +24613,7 @@
         <v>36.5</v>
       </c>
       <c r="G836" t="n">
-        <v>32.3517570495605</v>
+        <v>32.3517532348633</v>
       </c>
       <c r="H836" t="n">
         <v>603024</v>
@@ -24729,7 +24729,7 @@
         <v>36.5200004577637</v>
       </c>
       <c r="G840" t="n">
-        <v>32.3694801330566</v>
+        <v>32.3694763183594</v>
       </c>
       <c r="H840" t="n">
         <v>1017677</v>
@@ -24787,7 +24787,7 @@
         <v>37.1399993896484</v>
       </c>
       <c r="G842" t="n">
-        <v>32.919017791748</v>
+        <v>32.9190139770508</v>
       </c>
       <c r="H842" t="n">
         <v>1249902</v>
@@ -24845,7 +24845,7 @@
         <v>36.25</v>
       </c>
       <c r="G844" t="n">
-        <v>32.1301651000977</v>
+        <v>32.1301612854004</v>
       </c>
       <c r="H844" t="n">
         <v>666434</v>
@@ -24874,7 +24874,7 @@
         <v>36.560001373291</v>
       </c>
       <c r="G845" t="n">
-        <v>32.4049301147461</v>
+        <v>32.4049263000488</v>
       </c>
       <c r="H845" t="n">
         <v>358003</v>
@@ -24932,7 +24932,7 @@
         <v>36.439998626709</v>
       </c>
       <c r="G847" t="n">
-        <v>32.2985725402832</v>
+        <v>32.2985687255859</v>
       </c>
       <c r="H847" t="n">
         <v>831033</v>
@@ -24961,7 +24961,7 @@
         <v>37.189998626709</v>
       </c>
       <c r="G848" t="n">
-        <v>32.9633255004883</v>
+        <v>32.963321685791</v>
       </c>
       <c r="H848" t="n">
         <v>662987</v>
@@ -24990,7 +24990,7 @@
         <v>36.3600006103516</v>
       </c>
       <c r="G849" t="n">
-        <v>32.2276649475098</v>
+        <v>32.2276611328125</v>
       </c>
       <c r="H849" t="n">
         <v>560045</v>
@@ -25019,7 +25019,7 @@
         <v>35.5699996948242</v>
       </c>
       <c r="G850" t="n">
-        <v>31.5274448394775</v>
+        <v>31.5274410247803</v>
       </c>
       <c r="H850" t="n">
         <v>985193</v>
@@ -25077,7 +25077,7 @@
         <v>35.5299987792969</v>
       </c>
       <c r="G852" t="n">
-        <v>31.4919872283936</v>
+        <v>31.4919910430908</v>
       </c>
       <c r="H852" t="n">
         <v>1325314</v>
@@ -25106,7 +25106,7 @@
         <v>36.6699981689453</v>
       </c>
       <c r="G853" t="n">
-        <v>32.5024261474609</v>
+        <v>32.5024299621582</v>
       </c>
       <c r="H853" t="n">
         <v>1275675</v>
@@ -25135,7 +25135,7 @@
         <v>35.0299987792969</v>
       </c>
       <c r="G854" t="n">
-        <v>31.0488147735596</v>
+        <v>31.0488109588623</v>
       </c>
       <c r="H854" t="n">
         <v>1086383</v>
@@ -25164,7 +25164,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G855" t="n">
-        <v>31.5983486175537</v>
+        <v>31.598352432251</v>
       </c>
       <c r="H855" t="n">
         <v>833148</v>
@@ -25193,7 +25193,7 @@
         <v>35.8400001525879</v>
       </c>
       <c r="G856" t="n">
-        <v>31.7667598724365</v>
+        <v>31.7667617797852</v>
       </c>
       <c r="H856" t="n">
         <v>937200</v>
@@ -25222,7 +25222,7 @@
         <v>35.2299995422363</v>
       </c>
       <c r="G857" t="n">
-        <v>31.2260875701904</v>
+        <v>31.2260837554932</v>
       </c>
       <c r="H857" t="n">
         <v>1038179</v>
@@ -25251,7 +25251,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>31.6426734924316</v>
+        <v>31.6426677703857</v>
       </c>
       <c r="H858" t="n">
         <v>793440</v>
@@ -25309,7 +25309,7 @@
         <v>34.5699996948242</v>
       </c>
       <c r="G860" t="n">
-        <v>30.9883003234863</v>
+        <v>30.988302230835</v>
       </c>
       <c r="H860" t="n">
         <v>723455</v>
@@ -25338,7 +25338,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G861" t="n">
-        <v>31.9115867614746</v>
+        <v>31.9115886688232</v>
       </c>
       <c r="H861" t="n">
         <v>939052</v>
@@ -25367,7 +25367,7 @@
         <v>34.5400009155273</v>
       </c>
       <c r="G862" t="n">
-        <v>30.9614124298096</v>
+        <v>30.9614143371582</v>
       </c>
       <c r="H862" t="n">
         <v>797919</v>
@@ -25512,7 +25512,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G867" t="n">
-        <v>29.7602443695068</v>
+        <v>29.7602462768555</v>
       </c>
       <c r="H867" t="n">
         <v>926560</v>
@@ -25628,7 +25628,7 @@
         <v>34.5</v>
       </c>
       <c r="G871" t="n">
-        <v>30.92555809021</v>
+        <v>30.9255561828613</v>
       </c>
       <c r="H871" t="n">
         <v>939585</v>
@@ -25657,7 +25657,7 @@
         <v>34.5</v>
       </c>
       <c r="G872" t="n">
-        <v>30.92555809021</v>
+        <v>30.9255561828613</v>
       </c>
       <c r="H872" t="n">
         <v>651824</v>
@@ -25686,7 +25686,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G873" t="n">
-        <v>31.1048355102539</v>
+        <v>31.1048374176025</v>
       </c>
       <c r="H873" t="n">
         <v>701678</v>
@@ -25773,7 +25773,7 @@
         <v>34.4099998474121</v>
       </c>
       <c r="G876" t="n">
-        <v>30.8448791503906</v>
+        <v>30.8448810577393</v>
       </c>
       <c r="H876" t="n">
         <v>644732</v>
@@ -25860,7 +25860,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G879" t="n">
-        <v>31.732307434082</v>
+        <v>31.7323093414307</v>
       </c>
       <c r="H879" t="n">
         <v>523035</v>
@@ -26005,7 +26005,7 @@
         <v>37.310001373291</v>
       </c>
       <c r="G884" t="n">
-        <v>33.4444198608398</v>
+        <v>33.4444160461426</v>
       </c>
       <c r="H884" t="n">
         <v>646016</v>
@@ -26034,7 +26034,7 @@
         <v>36.6300010681152</v>
       </c>
       <c r="G885" t="n">
-        <v>32.8348731994629</v>
+        <v>32.8348770141602</v>
       </c>
       <c r="H885" t="n">
         <v>674726</v>
@@ -26353,7 +26353,7 @@
         <v>38.3300018310547</v>
       </c>
       <c r="G896" t="n">
-        <v>34.3587417602539</v>
+        <v>34.3587379455566</v>
       </c>
       <c r="H896" t="n">
         <v>545003</v>
@@ -26701,7 +26701,7 @@
         <v>38.9900016784668</v>
       </c>
       <c r="G908" t="n">
-        <v>34.9503555297852</v>
+        <v>34.9503593444824</v>
       </c>
       <c r="H908" t="n">
         <v>754832</v>
@@ -26846,7 +26846,7 @@
         <v>36.2599983215332</v>
       </c>
       <c r="G913" t="n">
-        <v>32.5032005310059</v>
+        <v>32.5032043457031</v>
       </c>
       <c r="H913" t="n">
         <v>849140</v>
@@ -26875,7 +26875,7 @@
         <v>34.4099998474121</v>
       </c>
       <c r="G914" t="n">
-        <v>30.8448791503906</v>
+        <v>30.8448810577393</v>
       </c>
       <c r="H914" t="n">
         <v>1764920</v>
@@ -26904,7 +26904,7 @@
         <v>34.1100006103516</v>
       </c>
       <c r="G915" t="n">
-        <v>30.575963973999</v>
+        <v>30.5759620666504</v>
       </c>
       <c r="H915" t="n">
         <v>1143849</v>
@@ -27020,7 +27020,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G919" t="n">
-        <v>31.4992485046387</v>
+        <v>31.4992504119873</v>
       </c>
       <c r="H919" t="n">
         <v>793970</v>
@@ -27107,7 +27107,7 @@
         <v>33.8600006103516</v>
       </c>
       <c r="G922" t="n">
-        <v>30.3518676757812</v>
+        <v>30.3518657684326</v>
       </c>
       <c r="H922" t="n">
         <v>941134</v>
@@ -27194,7 +27194,7 @@
         <v>35.4599990844727</v>
       </c>
       <c r="G925" t="n">
-        <v>31.7860870361328</v>
+        <v>31.7860889434814</v>
       </c>
       <c r="H925" t="n">
         <v>463094</v>
@@ -27223,7 +27223,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>31.1048355102539</v>
+        <v>31.1048374176025</v>
       </c>
       <c r="H926" t="n">
         <v>520663</v>
@@ -27600,7 +27600,7 @@
         <v>35.2799987792969</v>
       </c>
       <c r="G939" t="n">
-        <v>31.6247444152832</v>
+        <v>31.6247425079346</v>
       </c>
       <c r="H939" t="n">
         <v>731144</v>
@@ -27658,7 +27658,7 @@
         <v>35.3899993896484</v>
       </c>
       <c r="G941" t="n">
-        <v>31.7233467102051</v>
+        <v>31.7233428955078</v>
       </c>
       <c r="H941" t="n">
         <v>889173</v>
@@ -27832,7 +27832,7 @@
         <v>32.6199989318848</v>
       </c>
       <c r="G947" t="n">
-        <v>29.2403373718262</v>
+        <v>29.2403354644775</v>
       </c>
       <c r="H947" t="n">
         <v>1413678</v>
@@ -27861,7 +27861,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G948" t="n">
-        <v>28.7742118835449</v>
+        <v>28.7742099761963</v>
       </c>
       <c r="H948" t="n">
         <v>749802</v>
@@ -27890,7 +27890,7 @@
         <v>32.2299995422363</v>
       </c>
       <c r="G949" t="n">
-        <v>28.8907432556152</v>
+        <v>28.8907413482666</v>
       </c>
       <c r="H949" t="n">
         <v>619789</v>
@@ -27919,7 +27919,7 @@
         <v>32.1399993896484</v>
       </c>
       <c r="G950" t="n">
-        <v>28.8100700378418</v>
+        <v>28.8100681304932</v>
       </c>
       <c r="H950" t="n">
         <v>758436</v>
@@ -27948,7 +27948,7 @@
         <v>32.3600006103516</v>
       </c>
       <c r="G951" t="n">
-        <v>29.0072765350342</v>
+        <v>29.0072746276855</v>
       </c>
       <c r="H951" t="n">
         <v>627632</v>
@@ -28093,7 +28093,7 @@
         <v>32.1100006103516</v>
       </c>
       <c r="G956" t="n">
-        <v>28.7831783294678</v>
+        <v>28.7831764221191</v>
       </c>
       <c r="H956" t="n">
         <v>1443982</v>
@@ -28238,7 +28238,7 @@
         <v>33.8199996948242</v>
       </c>
       <c r="G961" t="n">
-        <v>30.3160095214844</v>
+        <v>30.3160076141357</v>
       </c>
       <c r="H961" t="n">
         <v>1679318</v>
@@ -28267,7 +28267,7 @@
         <v>34.4799995422363</v>
       </c>
       <c r="G962" t="n">
-        <v>30.9076271057129</v>
+        <v>30.9076290130615</v>
       </c>
       <c r="H962" t="n">
         <v>1438118</v>
@@ -28354,7 +28354,7 @@
         <v>33.6399993896484</v>
       </c>
       <c r="G965" t="n">
-        <v>30.154655456543</v>
+        <v>30.1546535491943</v>
       </c>
       <c r="H965" t="n">
         <v>712337</v>
@@ -28412,7 +28412,7 @@
         <v>32.1699981689453</v>
       </c>
       <c r="G967" t="n">
-        <v>28.8369579315186</v>
+        <v>28.8369560241699</v>
       </c>
       <c r="H967" t="n">
         <v>1772518</v>
@@ -28528,7 +28528,7 @@
         <v>32.4900016784668</v>
       </c>
       <c r="G971" t="n">
-        <v>29.1238079071045</v>
+        <v>29.1238059997559</v>
       </c>
       <c r="H971" t="n">
         <v>1098341</v>
@@ -28557,7 +28557,7 @@
         <v>36.1699981689453</v>
       </c>
       <c r="G972" t="n">
-        <v>32.4225311279297</v>
+        <v>32.4225273132324</v>
       </c>
       <c r="H972" t="n">
         <v>5202585</v>
@@ -28673,7 +28673,7 @@
         <v>34.5400009155273</v>
       </c>
       <c r="G976" t="n">
-        <v>30.9614124298096</v>
+        <v>30.9614143371582</v>
       </c>
       <c r="H976" t="n">
         <v>782683</v>
@@ -28702,7 +28702,7 @@
         <v>35.1699981689453</v>
       </c>
       <c r="G977" t="n">
-        <v>31.5261383056641</v>
+        <v>31.5261363983154</v>
       </c>
       <c r="H977" t="n">
         <v>759688</v>
@@ -28731,7 +28731,7 @@
         <v>35.2900009155273</v>
       </c>
       <c r="G978" t="n">
-        <v>31.6337089538574</v>
+        <v>31.6337108612061</v>
       </c>
       <c r="H978" t="n">
         <v>977368</v>
@@ -28760,7 +28760,7 @@
         <v>35.0299987792969</v>
       </c>
       <c r="G979" t="n">
-        <v>31.4006404876709</v>
+        <v>31.4006385803223</v>
       </c>
       <c r="H979" t="n">
         <v>874014</v>
@@ -28789,7 +28789,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G980" t="n">
-        <v>31.732307434082</v>
+        <v>31.7323093414307</v>
       </c>
       <c r="H980" t="n">
         <v>711442</v>
@@ -28847,7 +28847,7 @@
         <v>37.6399993896484</v>
       </c>
       <c r="G982" t="n">
-        <v>33.7402305603027</v>
+        <v>33.7402267456055</v>
       </c>
       <c r="H982" t="n">
         <v>3080867</v>
@@ -28934,7 +28934,7 @@
         <v>36.8699989318848</v>
       </c>
       <c r="G985" t="n">
-        <v>33.0500068664551</v>
+        <v>33.0500030517578</v>
       </c>
       <c r="H985" t="n">
         <v>1228882</v>
@@ -28963,7 +28963,7 @@
         <v>36.439998626709</v>
       </c>
       <c r="G986" t="n">
-        <v>32.6645545959473</v>
+        <v>32.6645584106445</v>
       </c>
       <c r="H986" t="n">
         <v>616275</v>
@@ -29050,7 +29050,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>33.2561798095703</v>
+        <v>33.256175994873</v>
       </c>
       <c r="H989" t="n">
         <v>882177</v>
@@ -29079,7 +29079,7 @@
         <v>37.75</v>
       </c>
       <c r="G990" t="n">
-        <v>33.8388328552246</v>
+        <v>33.8388290405273</v>
       </c>
       <c r="H990" t="n">
         <v>1387769</v>
@@ -29137,7 +29137,7 @@
         <v>37.310001373291</v>
       </c>
       <c r="G992" t="n">
-        <v>33.4444198608398</v>
+        <v>33.4444160461426</v>
       </c>
       <c r="H992" t="n">
         <v>854679</v>
@@ -29224,7 +29224,7 @@
         <v>39.189998626709</v>
       </c>
       <c r="G995" t="n">
-        <v>35.1296348571777</v>
+        <v>35.129638671875</v>
       </c>
       <c r="H995" t="n">
         <v>1135892</v>
@@ -29311,7 +29311,7 @@
         <v>38.7900009155273</v>
       </c>
       <c r="G998" t="n">
-        <v>34.7710838317871</v>
+        <v>34.7710876464844</v>
       </c>
       <c r="H998" t="n">
         <v>1542216</v>
@@ -29514,7 +29514,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1005" t="n">
-        <v>37.0210266113281</v>
+        <v>37.0210304260254</v>
       </c>
       <c r="H1005" t="n">
         <v>2188303</v>
@@ -29601,7 +29601,7 @@
         <v>40.2799987792969</v>
       </c>
       <c r="G1008" t="n">
-        <v>36.1067085266113</v>
+        <v>36.1067047119141</v>
       </c>
       <c r="H1008" t="n">
         <v>1453949</v>
@@ -29978,7 +29978,7 @@
         <v>41.1399993896484</v>
       </c>
       <c r="G1021" t="n">
-        <v>36.8776016235352</v>
+        <v>36.8775978088379</v>
       </c>
       <c r="H1021" t="n">
         <v>948024</v>
@@ -30036,7 +30036,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G1023" t="n">
-        <v>36.5728302001953</v>
+        <v>36.572826385498</v>
       </c>
       <c r="H1023" t="n">
         <v>593054</v>
@@ -30094,7 +30094,7 @@
         <v>42.7200012207031</v>
       </c>
       <c r="G1025" t="n">
-        <v>38.2939071655273</v>
+        <v>38.2939033508301</v>
       </c>
       <c r="H1025" t="n">
         <v>1447893</v>
@@ -30152,7 +30152,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1027" t="n">
-        <v>38.2759780883789</v>
+        <v>38.2759742736816</v>
       </c>
       <c r="H1027" t="n">
         <v>904274</v>
@@ -30181,7 +30181,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1028" t="n">
-        <v>37.065845489502</v>
+        <v>37.0658493041992</v>
       </c>
       <c r="H1028" t="n">
         <v>998529</v>
@@ -30210,7 +30210,7 @@
         <v>40.4300003051758</v>
       </c>
       <c r="G1029" t="n">
-        <v>36.2411689758301</v>
+        <v>36.2411651611328</v>
       </c>
       <c r="H1029" t="n">
         <v>1517804</v>
@@ -30326,7 +30326,7 @@
         <v>38.8600006103516</v>
       </c>
       <c r="G1033" t="n">
-        <v>34.8338279724121</v>
+        <v>34.8338317871094</v>
       </c>
       <c r="H1033" t="n">
         <v>2285540</v>
@@ -30413,7 +30413,7 @@
         <v>39.560001373291</v>
       </c>
       <c r="G1036" t="n">
-        <v>35.4613037109375</v>
+        <v>35.4613075256348</v>
       </c>
       <c r="H1036" t="n">
         <v>1121921</v>
@@ -30471,7 +30471,7 @@
         <v>39.4300003051758</v>
       </c>
       <c r="G1038" t="n">
-        <v>35.3447723388672</v>
+        <v>35.3447761535645</v>
       </c>
       <c r="H1038" t="n">
         <v>917482</v>
@@ -30529,7 +30529,7 @@
         <v>40.4099998474121</v>
       </c>
       <c r="G1040" t="n">
-        <v>36.2232398986816</v>
+        <v>36.2232360839844</v>
       </c>
       <c r="H1040" t="n">
         <v>1074543</v>
@@ -30616,7 +30616,7 @@
         <v>39.7299995422363</v>
       </c>
       <c r="G1043" t="n">
-        <v>35.6136932373047</v>
+        <v>35.6136894226074</v>
       </c>
       <c r="H1043" t="n">
         <v>1401681</v>
@@ -30674,7 +30674,7 @@
         <v>39.310001373291</v>
       </c>
       <c r="G1045" t="n">
-        <v>35.2372016906738</v>
+        <v>35.2372055053711</v>
       </c>
       <c r="H1045" t="n">
         <v>1912884</v>
@@ -30732,7 +30732,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G1047" t="n">
-        <v>34.1525650024414</v>
+        <v>34.1525688171387</v>
       </c>
       <c r="H1047" t="n">
         <v>988718</v>
@@ -30790,7 +30790,7 @@
         <v>37.6399993896484</v>
       </c>
       <c r="G1049" t="n">
-        <v>33.7402305603027</v>
+        <v>33.7402267456055</v>
       </c>
       <c r="H1049" t="n">
         <v>1048207</v>
@@ -30935,7 +30935,7 @@
         <v>35.1300010681152</v>
       </c>
       <c r="G1054" t="n">
-        <v>31.4902877807617</v>
+        <v>31.4902858734131</v>
       </c>
       <c r="H1054" t="n">
         <v>2116137</v>
@@ -30993,7 +30993,7 @@
         <v>35.2599983215332</v>
       </c>
       <c r="G1056" t="n">
-        <v>31.6068153381348</v>
+        <v>31.6068115234375</v>
       </c>
       <c r="H1056" t="n">
         <v>1857517</v>
@@ -31022,7 +31022,7 @@
         <v>35.2200012207031</v>
       </c>
       <c r="G1057" t="n">
-        <v>31.5709609985352</v>
+        <v>31.5709590911865</v>
       </c>
       <c r="H1057" t="n">
         <v>2535243</v>
@@ -31080,7 +31080,7 @@
         <v>34.5</v>
       </c>
       <c r="G1059" t="n">
-        <v>30.92555809021</v>
+        <v>30.9255561828613</v>
       </c>
       <c r="H1059" t="n">
         <v>1559647</v>
@@ -31167,7 +31167,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G1062" t="n">
-        <v>30.2263698577881</v>
+        <v>30.2263679504395</v>
       </c>
       <c r="H1062" t="n">
         <v>1792726</v>
@@ -31254,7 +31254,7 @@
         <v>29.3600006103516</v>
       </c>
       <c r="G1065" t="n">
-        <v>26.3180961608887</v>
+        <v>26.31809425354</v>
       </c>
       <c r="H1065" t="n">
         <v>2855782</v>
@@ -31312,7 +31312,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1067" t="n">
-        <v>26.6228713989258</v>
+        <v>26.6228694915771</v>
       </c>
       <c r="H1067" t="n">
         <v>4220010</v>
@@ -31660,7 +31660,7 @@
         <v>33.2900009155273</v>
       </c>
       <c r="G1079" t="n">
-        <v>29.8409214019775</v>
+        <v>29.8409194946289</v>
       </c>
       <c r="H1079" t="n">
         <v>1159294</v>
@@ -31689,7 +31689,7 @@
         <v>32.3899993896484</v>
       </c>
       <c r="G1080" t="n">
-        <v>29.0341663360596</v>
+        <v>29.0341644287109</v>
       </c>
       <c r="H1080" t="n">
         <v>802534</v>
@@ -31834,7 +31834,7 @@
         <v>32.6399993896484</v>
       </c>
       <c r="G1085" t="n">
-        <v>29.258264541626</v>
+        <v>29.2582626342773</v>
       </c>
       <c r="H1085" t="n">
         <v>638911</v>
@@ -31863,7 +31863,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G1086" t="n">
-        <v>29.4465084075928</v>
+        <v>29.4465103149414</v>
       </c>
       <c r="H1086" t="n">
         <v>604539</v>
@@ -31892,7 +31892,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1087" t="n">
-        <v>30.2084445953369</v>
+        <v>30.2084426879883</v>
       </c>
       <c r="H1087" t="n">
         <v>830697</v>
@@ -31950,7 +31950,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G1089" t="n">
-        <v>29.4465084075928</v>
+        <v>29.4465103149414</v>
       </c>
       <c r="H1089" t="n">
         <v>854571</v>
@@ -32095,7 +32095,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G1094" t="n">
-        <v>29.7154235839844</v>
+        <v>29.715425491333</v>
       </c>
       <c r="H1094" t="n">
         <v>731600</v>
@@ -32182,7 +32182,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G1097" t="n">
-        <v>30.8807353973389</v>
+        <v>30.8807373046875</v>
       </c>
       <c r="H1097" t="n">
         <v>596149</v>
@@ -32298,7 +32298,7 @@
         <v>33.3600006103516</v>
       </c>
       <c r="G1101" t="n">
-        <v>29.9036712646484</v>
+        <v>29.9036731719971</v>
       </c>
       <c r="H1101" t="n">
         <v>328634</v>
@@ -32356,7 +32356,7 @@
         <v>33.2900009155273</v>
       </c>
       <c r="G1103" t="n">
-        <v>29.8409214019775</v>
+        <v>29.8409194946289</v>
       </c>
       <c r="H1103" t="n">
         <v>1188345</v>
@@ -32443,7 +32443,7 @@
         <v>32.7700004577637</v>
       </c>
       <c r="G1106" t="n">
-        <v>29.3747978210449</v>
+        <v>29.3747959136963</v>
       </c>
       <c r="H1106" t="n">
         <v>804603</v>
@@ -32472,7 +32472,7 @@
         <v>31.8899993896484</v>
       </c>
       <c r="G1107" t="n">
-        <v>28.5859661102295</v>
+        <v>28.5859680175781</v>
       </c>
       <c r="H1107" t="n">
         <v>621457</v>
@@ -32617,7 +32617,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1112" t="n">
-        <v>29.025203704834</v>
+        <v>29.0252017974854</v>
       </c>
       <c r="H1112" t="n">
         <v>712773</v>
@@ -32646,7 +32646,7 @@
         <v>31.8899993896484</v>
       </c>
       <c r="G1113" t="n">
-        <v>28.5859661102295</v>
+        <v>28.5859680175781</v>
       </c>
       <c r="H1113" t="n">
         <v>769259</v>
@@ -32733,7 +32733,7 @@
         <v>33.3899993896484</v>
       </c>
       <c r="G1116" t="n">
-        <v>29.9305591583252</v>
+        <v>29.9305610656738</v>
       </c>
       <c r="H1116" t="n">
         <v>1107671</v>
@@ -32820,7 +32820,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G1119" t="n">
-        <v>29.9843425750732</v>
+        <v>29.9843444824219</v>
       </c>
       <c r="H1119" t="n">
         <v>2062579</v>
@@ -32849,7 +32849,7 @@
         <v>33.689998626709</v>
       </c>
       <c r="G1120" t="n">
-        <v>30.1994781494141</v>
+        <v>30.1994762420654</v>
       </c>
       <c r="H1120" t="n">
         <v>713925</v>
@@ -32936,7 +32936,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G1123" t="n">
-        <v>30.9972667694092</v>
+        <v>30.9972686767578</v>
       </c>
       <c r="H1123" t="n">
         <v>863955</v>
@@ -32994,7 +32994,7 @@
         <v>34.7299995422363</v>
       </c>
       <c r="G1125" t="n">
-        <v>31.1317195892334</v>
+        <v>31.131721496582</v>
       </c>
       <c r="H1125" t="n">
         <v>1136308</v>
@@ -33052,7 +33052,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1127" t="n">
-        <v>31.732307434082</v>
+        <v>31.7323093414307</v>
       </c>
       <c r="H1127" t="n">
         <v>1456634</v>
@@ -33226,7 +33226,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G1133" t="n">
-        <v>31.4992485046387</v>
+        <v>31.4992504119873</v>
       </c>
       <c r="H1133" t="n">
         <v>698680</v>
@@ -33255,7 +33255,7 @@
         <v>35.2299995422363</v>
       </c>
       <c r="G1134" t="n">
-        <v>31.5799217224121</v>
+        <v>31.5799198150635</v>
       </c>
       <c r="H1134" t="n">
         <v>1177999</v>
@@ -33284,7 +33284,7 @@
         <v>35.5200004577637</v>
       </c>
       <c r="G1135" t="n">
-        <v>31.8398780822754</v>
+        <v>31.8398742675781</v>
       </c>
       <c r="H1135" t="n">
         <v>629000</v>
@@ -33342,7 +33342,7 @@
         <v>34.7900009155273</v>
       </c>
       <c r="G1137" t="n">
-        <v>31.1855087280273</v>
+        <v>31.185510635376</v>
       </c>
       <c r="H1137" t="n">
         <v>1094459</v>
@@ -33777,7 +33777,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G1152" t="n">
-        <v>30.9972667694092</v>
+        <v>30.9972686767578</v>
       </c>
       <c r="H1152" t="n">
         <v>836843</v>
@@ -33806,7 +33806,7 @@
         <v>33.9900016784668</v>
       </c>
       <c r="G1153" t="n">
-        <v>30.4683971405029</v>
+        <v>30.4683952331543</v>
       </c>
       <c r="H1153" t="n">
         <v>921541</v>
@@ -33835,7 +33835,7 @@
         <v>33.2299995422363</v>
       </c>
       <c r="G1154" t="n">
-        <v>29.7871360778809</v>
+        <v>29.7871379852295</v>
       </c>
       <c r="H1154" t="n">
         <v>1032463</v>
@@ -33893,7 +33893,7 @@
         <v>34.5</v>
       </c>
       <c r="G1156" t="n">
-        <v>30.92555809021</v>
+        <v>30.9255561828613</v>
       </c>
       <c r="H1156" t="n">
         <v>1491319</v>
@@ -34067,7 +34067,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1162" t="n">
-        <v>29.7602443695068</v>
+        <v>29.7602462768555</v>
       </c>
       <c r="H1162" t="n">
         <v>686920</v>
@@ -34183,7 +34183,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1166" t="n">
-        <v>28.5949325561523</v>
+        <v>28.594934463501</v>
       </c>
       <c r="H1166" t="n">
         <v>856225</v>
@@ -34212,7 +34212,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1167" t="n">
-        <v>29.025203704834</v>
+        <v>29.0252017974854</v>
       </c>
       <c r="H1167" t="n">
         <v>768051</v>
@@ -34241,7 +34241,7 @@
         <v>32.0699996948242</v>
       </c>
       <c r="G1168" t="n">
-        <v>28.7473201751709</v>
+        <v>28.7473220825195</v>
       </c>
       <c r="H1168" t="n">
         <v>1018271</v>
@@ -34415,7 +34415,7 @@
         <v>32.8800010681152</v>
       </c>
       <c r="G1174" t="n">
-        <v>29.4734001159668</v>
+        <v>29.4734020233154</v>
       </c>
       <c r="H1174" t="n">
         <v>689163</v>
@@ -34502,7 +34502,7 @@
         <v>32.2299995422363</v>
       </c>
       <c r="G1177" t="n">
-        <v>28.8907432556152</v>
+        <v>28.8907413482666</v>
       </c>
       <c r="H1177" t="n">
         <v>558791</v>
@@ -34531,7 +34531,7 @@
         <v>32.0200004577637</v>
       </c>
       <c r="G1178" t="n">
-        <v>28.7024993896484</v>
+        <v>28.7025012969971</v>
       </c>
       <c r="H1178" t="n">
         <v>507381</v>
@@ -34647,7 +34647,7 @@
         <v>33.1599998474121</v>
       </c>
       <c r="G1182" t="n">
-        <v>29.7243881225586</v>
+        <v>29.72438621521</v>
       </c>
       <c r="H1182" t="n">
         <v>424634</v>
@@ -34676,7 +34676,7 @@
         <v>32.6199989318848</v>
       </c>
       <c r="G1183" t="n">
-        <v>29.2403373718262</v>
+        <v>29.2403354644775</v>
       </c>
       <c r="H1183" t="n">
         <v>685213</v>
@@ -34821,7 +34821,7 @@
         <v>33.3899993896484</v>
       </c>
       <c r="G1188" t="n">
-        <v>29.9305591583252</v>
+        <v>29.9305610656738</v>
       </c>
       <c r="H1188" t="n">
         <v>940955</v>
@@ -34879,7 +34879,7 @@
         <v>34.4700012207031</v>
       </c>
       <c r="G1190" t="n">
-        <v>30.8986644744873</v>
+        <v>30.8986663818359</v>
       </c>
       <c r="H1190" t="n">
         <v>689525</v>
@@ -34937,7 +34937,7 @@
         <v>34.4700012207031</v>
       </c>
       <c r="G1192" t="n">
-        <v>30.8986644744873</v>
+        <v>30.8986663818359</v>
       </c>
       <c r="H1192" t="n">
         <v>988286</v>
@@ -34995,7 +34995,7 @@
         <v>34.8899993896484</v>
       </c>
       <c r="G1194" t="n">
-        <v>31.275146484375</v>
+        <v>31.2751445770264</v>
       </c>
       <c r="H1194" t="n">
         <v>816452</v>
@@ -35024,7 +35024,7 @@
         <v>35.2099990844727</v>
       </c>
       <c r="G1195" t="n">
-        <v>31.5619926452637</v>
+        <v>31.5619945526123</v>
       </c>
       <c r="H1195" t="n">
         <v>701870</v>
@@ -35140,7 +35140,7 @@
         <v>36.5</v>
       </c>
       <c r="G1199" t="n">
-        <v>32.7183418273926</v>
+        <v>32.7183456420898</v>
       </c>
       <c r="H1199" t="n">
         <v>1511426</v>
@@ -35285,7 +35285,7 @@
         <v>34.7400016784668</v>
       </c>
       <c r="G1204" t="n">
-        <v>31.1406860351562</v>
+        <v>31.1406879425049</v>
       </c>
       <c r="H1204" t="n">
         <v>608760</v>
@@ -35314,7 +35314,7 @@
         <v>35.1800003051758</v>
       </c>
       <c r="G1205" t="n">
-        <v>31.5351028442383</v>
+        <v>31.5351047515869</v>
       </c>
       <c r="H1205" t="n">
         <v>518246</v>
@@ -35401,7 +35401,7 @@
         <v>35.6100006103516</v>
       </c>
       <c r="G1208" t="n">
-        <v>31.9205513000488</v>
+        <v>31.9205532073975</v>
       </c>
       <c r="H1208" t="n">
         <v>604471</v>
@@ -35430,7 +35430,7 @@
         <v>35.4700012207031</v>
       </c>
       <c r="G1209" t="n">
-        <v>31.7950553894043</v>
+        <v>31.7950572967529</v>
       </c>
       <c r="H1209" t="n">
         <v>510994</v>
@@ -35459,7 +35459,7 @@
         <v>36.1699981689453</v>
       </c>
       <c r="G1210" t="n">
-        <v>32.4225311279297</v>
+        <v>32.4225273132324</v>
       </c>
       <c r="H1210" t="n">
         <v>839946</v>
@@ -35517,7 +35517,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G1212" t="n">
-        <v>32.8976173400879</v>
+        <v>32.8976211547852</v>
       </c>
       <c r="H1212" t="n">
         <v>699032</v>
@@ -35575,7 +35575,7 @@
         <v>36.3899993896484</v>
       </c>
       <c r="G1214" t="n">
-        <v>32.6197357177734</v>
+        <v>32.6197395324707</v>
       </c>
       <c r="H1214" t="n">
         <v>695087</v>
@@ -35691,7 +35691,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G1218" t="n">
-        <v>31.6874885559082</v>
+        <v>31.6874866485596</v>
       </c>
       <c r="H1218" t="n">
         <v>1078936</v>
@@ -35720,7 +35720,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1219" t="n">
-        <v>32.9872550964355</v>
+        <v>32.9872589111328</v>
       </c>
       <c r="H1219" t="n">
         <v>1280510</v>
@@ -35923,7 +35923,7 @@
         <v>37</v>
       </c>
       <c r="G1226" t="n">
-        <v>33.1665382385254</v>
+        <v>33.1665344238281</v>
       </c>
       <c r="H1226" t="n">
         <v>895873</v>
@@ -35952,7 +35952,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>31.2841129302979</v>
+        <v>31.2841110229492</v>
       </c>
       <c r="H1227" t="n">
         <v>1375490</v>
@@ -36068,7 +36068,7 @@
         <v>36</v>
       </c>
       <c r="G1231" t="n">
-        <v>32.2701416015625</v>
+        <v>32.2701454162598</v>
       </c>
       <c r="H1231" t="n">
         <v>837191</v>
@@ -36097,7 +36097,7 @@
         <v>36.3699989318848</v>
       </c>
       <c r="G1232" t="n">
-        <v>32.6018104553223</v>
+        <v>32.6018142700195</v>
       </c>
       <c r="H1232" t="n">
         <v>1092932</v>
@@ -36155,7 +36155,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G1234" t="n">
-        <v>33.6595573425293</v>
+        <v>33.659553527832</v>
       </c>
       <c r="H1234" t="n">
         <v>568472</v>
@@ -36184,7 +36184,7 @@
         <v>39.6800003051758</v>
       </c>
       <c r="G1235" t="n">
-        <v>35.5688743591309</v>
+        <v>35.5688705444336</v>
       </c>
       <c r="H1235" t="n">
         <v>1940190</v>
@@ -36242,7 +36242,7 @@
         <v>40.4900016784668</v>
       </c>
       <c r="G1237" t="n">
-        <v>36.2949523925781</v>
+        <v>36.2949485778809</v>
       </c>
       <c r="H1237" t="n">
         <v>882600</v>
@@ -36329,7 +36329,7 @@
         <v>41.0800018310547</v>
       </c>
       <c r="G1240" t="n">
-        <v>36.8238258361816</v>
+        <v>36.8238220214844</v>
       </c>
       <c r="H1240" t="n">
         <v>944829</v>
@@ -36358,7 +36358,7 @@
         <v>41.060001373291</v>
       </c>
       <c r="G1241" t="n">
-        <v>36.8058967590332</v>
+        <v>36.8058929443359</v>
       </c>
       <c r="H1241" t="n">
         <v>651551</v>
@@ -36387,7 +36387,7 @@
         <v>40.7799987792969</v>
       </c>
       <c r="G1242" t="n">
-        <v>36.5549011230469</v>
+        <v>36.5549049377441</v>
       </c>
       <c r="H1242" t="n">
         <v>793611</v>
@@ -36474,7 +36474,7 @@
         <v>41.689998626709</v>
       </c>
       <c r="G1245" t="n">
-        <v>37.3706169128418</v>
+        <v>37.3706207275391</v>
       </c>
       <c r="H1245" t="n">
         <v>790759</v>
@@ -36648,7 +36648,7 @@
         <v>41.0900001525879</v>
       </c>
       <c r="G1251" t="n">
-        <v>36.8327827453613</v>
+        <v>36.8327865600586</v>
       </c>
       <c r="H1251" t="n">
         <v>363163</v>
@@ -36706,7 +36706,7 @@
         <v>42.5900001525879</v>
       </c>
       <c r="G1253" t="n">
-        <v>38.177375793457</v>
+        <v>38.1773719787598</v>
       </c>
       <c r="H1253" t="n">
         <v>934680</v>
@@ -36764,7 +36764,7 @@
         <v>44</v>
       </c>
       <c r="G1255" t="n">
-        <v>39.4412879943848</v>
+        <v>39.4412841796875</v>
       </c>
       <c r="H1255" t="n">
         <v>2134898</v>
@@ -36967,7 +36967,7 @@
         <v>48.7099990844727</v>
       </c>
       <c r="G1262" t="n">
-        <v>43.6632995605469</v>
+        <v>43.6632957458496</v>
       </c>
       <c r="H1262" t="n">
         <v>968756</v>
@@ -36996,7 +36996,7 @@
         <v>49</v>
       </c>
       <c r="G1263" t="n">
-        <v>43.9232521057129</v>
+        <v>43.9232559204102</v>
       </c>
       <c r="H1263" t="n">
         <v>948149</v>
@@ -37025,7 +37025,7 @@
         <v>48.5</v>
       </c>
       <c r="G1264" t="n">
-        <v>43.4750595092773</v>
+        <v>43.4750556945801</v>
       </c>
       <c r="H1264" t="n">
         <v>1163548</v>
@@ -37112,7 +37112,7 @@
         <v>48.2099990844727</v>
       </c>
       <c r="G1267" t="n">
-        <v>43.2151031494141</v>
+        <v>43.2150993347168</v>
       </c>
       <c r="H1267" t="n">
         <v>405890</v>
@@ -37170,7 +37170,7 @@
         <v>50.2999992370605</v>
       </c>
       <c r="G1269" t="n">
-        <v>45.0885620117188</v>
+        <v>45.088565826416</v>
       </c>
       <c r="H1269" t="n">
         <v>658618</v>
@@ -37344,7 +37344,7 @@
         <v>48.060001373291</v>
       </c>
       <c r="G1275" t="n">
-        <v>43.0806465148926</v>
+        <v>43.0806427001953</v>
       </c>
       <c r="H1275" t="n">
         <v>971009</v>
@@ -37373,7 +37373,7 @@
         <v>48</v>
       </c>
       <c r="G1276" t="n">
-        <v>43.0268592834473</v>
+        <v>43.02685546875</v>
       </c>
       <c r="H1276" t="n">
         <v>779555</v>
@@ -37431,7 +37431,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1278" t="n">
-        <v>43.161319732666</v>
+        <v>43.1613159179688</v>
       </c>
       <c r="H1278" t="n">
         <v>859462</v>
@@ -37460,7 +37460,7 @@
         <v>47.7799987792969</v>
       </c>
       <c r="G1279" t="n">
-        <v>42.8296508789062</v>
+        <v>42.8296546936035</v>
       </c>
       <c r="H1279" t="n">
         <v>657222</v>
@@ -37547,7 +37547,7 @@
         <v>47.6500015258789</v>
       </c>
       <c r="G1282" t="n">
-        <v>42.7131233215332</v>
+        <v>42.7131271362305</v>
       </c>
       <c r="H1282" t="n">
         <v>536282</v>
@@ -37663,7 +37663,7 @@
         <v>47.3400001525879</v>
       </c>
       <c r="G1286" t="n">
-        <v>42.4352378845215</v>
+        <v>42.4352416992188</v>
       </c>
       <c r="H1286" t="n">
         <v>547777</v>
@@ -37692,7 +37692,7 @@
         <v>48.1500015258789</v>
       </c>
       <c r="G1287" t="n">
-        <v>43.161319732666</v>
+        <v>43.1613159179688</v>
       </c>
       <c r="H1287" t="n">
         <v>571676</v>
@@ -37866,7 +37866,7 @@
         <v>47.9300003051758</v>
       </c>
       <c r="G1293" t="n">
-        <v>42.9641151428223</v>
+        <v>42.964111328125</v>
       </c>
       <c r="H1293" t="n">
         <v>606640</v>
@@ -37895,7 +37895,7 @@
         <v>50.0200004577637</v>
       </c>
       <c r="G1294" t="n">
-        <v>44.8375701904297</v>
+        <v>44.837574005127</v>
       </c>
       <c r="H1294" t="n">
         <v>1070314</v>
@@ -37982,7 +37982,7 @@
         <v>52.1199989318848</v>
       </c>
       <c r="G1297" t="n">
-        <v>46.7199974060059</v>
+        <v>46.7200012207031</v>
       </c>
       <c r="H1297" t="n">
         <v>657479</v>
@@ -38040,7 +38040,7 @@
         <v>51.9799995422363</v>
       </c>
       <c r="G1299" t="n">
-        <v>46.5945053100586</v>
+        <v>46.5945014953613</v>
       </c>
       <c r="H1299" t="n">
         <v>356607</v>
@@ -38098,7 +38098,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G1301" t="n">
-        <v>46.7917137145996</v>
+        <v>46.7917175292969</v>
       </c>
       <c r="H1301" t="n">
         <v>493298</v>
@@ -38156,7 +38156,7 @@
         <v>50.6399993896484</v>
       </c>
       <c r="G1303" t="n">
-        <v>45.3933372497559</v>
+        <v>45.3933334350586</v>
       </c>
       <c r="H1303" t="n">
         <v>873315</v>
@@ -38185,7 +38185,7 @@
         <v>50.5800018310547</v>
       </c>
       <c r="G1304" t="n">
-        <v>45.3395538330078</v>
+        <v>45.3395500183105</v>
       </c>
       <c r="H1304" t="n">
         <v>646850</v>
@@ -38446,7 +38446,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G1313" t="n">
-        <v>46.3435134887695</v>
+        <v>46.3435096740723</v>
       </c>
       <c r="H1313" t="n">
         <v>647143</v>
@@ -38649,7 +38649,7 @@
         <v>52.0400009155273</v>
       </c>
       <c r="G1320" t="n">
-        <v>46.6482925415039</v>
+        <v>46.6482887268066</v>
       </c>
       <c r="H1320" t="n">
         <v>501531</v>
@@ -38707,7 +38707,7 @@
         <v>51.439998626709</v>
       </c>
       <c r="G1322" t="n">
-        <v>46.1104545593262</v>
+        <v>46.1104507446289</v>
       </c>
       <c r="H1322" t="n">
         <v>633519</v>
@@ -38794,7 +38794,7 @@
         <v>49.439998626709</v>
       </c>
       <c r="G1325" t="n">
-        <v>44.3176651000977</v>
+        <v>44.3176689147949</v>
       </c>
       <c r="H1325" t="n">
         <v>1268886</v>
@@ -38852,7 +38852,7 @@
         <v>47.9500007629395</v>
       </c>
       <c r="G1327" t="n">
-        <v>42.9820442199707</v>
+        <v>42.9820404052734</v>
       </c>
       <c r="H1327" t="n">
         <v>1034091</v>
@@ -38939,7 +38939,7 @@
         <v>47.9500007629395</v>
       </c>
       <c r="G1330" t="n">
-        <v>42.9820442199707</v>
+        <v>42.9820404052734</v>
       </c>
       <c r="H1330" t="n">
         <v>610263</v>
@@ -39026,7 +39026,7 @@
         <v>48.8699989318848</v>
       </c>
       <c r="G1333" t="n">
-        <v>43.8067169189453</v>
+        <v>43.8067207336426</v>
       </c>
       <c r="H1333" t="n">
         <v>664214</v>
@@ -39055,7 +39055,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G1334" t="n">
-        <v>44.5507278442383</v>
+        <v>44.5507316589355</v>
       </c>
       <c r="H1334" t="n">
         <v>574721</v>
@@ -39113,7 +39113,7 @@
         <v>49.5</v>
       </c>
       <c r="G1336" t="n">
-        <v>44.3714447021484</v>
+        <v>44.3714485168457</v>
       </c>
       <c r="H1336" t="n">
         <v>774621</v>
@@ -39548,7 +39548,7 @@
         <v>50.9199981689453</v>
       </c>
       <c r="G1351" t="n">
-        <v>45.6443290710449</v>
+        <v>45.6443252563477</v>
       </c>
       <c r="H1351" t="n">
         <v>488954</v>
@@ -39577,7 +39577,7 @@
         <v>50.9599990844727</v>
       </c>
       <c r="G1352" t="n">
-        <v>45.6801872253418</v>
+        <v>45.6801834106445</v>
       </c>
       <c r="H1352" t="n">
         <v>748447</v>
@@ -39606,7 +39606,7 @@
         <v>51.0200004577637</v>
       </c>
       <c r="G1353" t="n">
-        <v>45.7339668273926</v>
+        <v>45.7339630126953</v>
       </c>
       <c r="H1353" t="n">
         <v>558678</v>
@@ -39664,7 +39664,7 @@
         <v>50.2799987792969</v>
       </c>
       <c r="G1355" t="n">
-        <v>45.0706329345703</v>
+        <v>45.0706367492676</v>
       </c>
       <c r="H1355" t="n">
         <v>600986</v>
@@ -39838,7 +39838,7 @@
         <v>50.939998626709</v>
       </c>
       <c r="G1361" t="n">
-        <v>45.6622581481934</v>
+        <v>45.6622543334961</v>
       </c>
       <c r="H1361" t="n">
         <v>555578</v>
@@ -39925,7 +39925,7 @@
         <v>51.9599990844727</v>
       </c>
       <c r="G1364" t="n">
-        <v>46.5765762329102</v>
+        <v>46.5765724182129</v>
       </c>
       <c r="H1364" t="n">
         <v>378481</v>
@@ -40099,7 +40099,7 @@
         <v>54.9599990844727</v>
       </c>
       <c r="G1370" t="n">
-        <v>49.6830253601074</v>
+        <v>49.6830215454102</v>
       </c>
       <c r="H1370" t="n">
         <v>687075</v>
@@ -40244,7 +40244,7 @@
         <v>57.4599990844727</v>
       </c>
       <c r="G1375" t="n">
-        <v>51.9429893493652</v>
+        <v>51.942985534668</v>
       </c>
       <c r="H1375" t="n">
         <v>833040</v>
@@ -40302,7 +40302,7 @@
         <v>58.1800003051758</v>
       </c>
       <c r="G1377" t="n">
-        <v>52.5938606262207</v>
+        <v>52.5938568115234</v>
       </c>
       <c r="H1377" t="n">
         <v>526769</v>
@@ -40331,7 +40331,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G1378" t="n">
-        <v>52.7023391723633</v>
+        <v>52.702335357666</v>
       </c>
       <c r="H1378" t="n">
         <v>509502</v>
@@ -40389,7 +40389,7 @@
         <v>58.9199981689453</v>
       </c>
       <c r="G1380" t="n">
-        <v>53.2628059387207</v>
+        <v>53.2628021240234</v>
       </c>
       <c r="H1380" t="n">
         <v>537394</v>
@@ -40418,7 +40418,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G1381" t="n">
-        <v>52.0695419311523</v>
+        <v>52.0695457458496</v>
       </c>
       <c r="H1381" t="n">
         <v>659000</v>
@@ -40476,7 +40476,7 @@
         <v>56.8400001525879</v>
       </c>
       <c r="G1383" t="n">
-        <v>51.3825187683105</v>
+        <v>51.3825149536133</v>
       </c>
       <c r="H1383" t="n">
         <v>486048</v>
@@ -40563,7 +40563,7 @@
         <v>58.3199996948242</v>
       </c>
       <c r="G1386" t="n">
-        <v>52.7204132080078</v>
+        <v>52.7204093933105</v>
       </c>
       <c r="H1386" t="n">
         <v>428132</v>
@@ -40592,7 +40592,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G1387" t="n">
-        <v>52.9735260009766</v>
+        <v>52.9735298156738</v>
       </c>
       <c r="H1387" t="n">
         <v>501161</v>
@@ -40737,7 +40737,7 @@
         <v>57.4599990844727</v>
       </c>
       <c r="G1392" t="n">
-        <v>51.9429893493652</v>
+        <v>51.942985534668</v>
       </c>
       <c r="H1392" t="n">
         <v>697252</v>
@@ -40766,7 +40766,7 @@
         <v>57.7200012207031</v>
       </c>
       <c r="G1393" t="n">
-        <v>52.1780204772949</v>
+        <v>52.1780242919922</v>
       </c>
       <c r="H1393" t="n">
         <v>350259</v>
@@ -40824,7 +40824,7 @@
         <v>57.6199989318848</v>
       </c>
       <c r="G1395" t="n">
-        <v>52.0876274108887</v>
+        <v>52.0876235961914</v>
       </c>
       <c r="H1395" t="n">
         <v>250109</v>
@@ -40853,7 +40853,7 @@
         <v>57.060001373291</v>
       </c>
       <c r="G1396" t="n">
-        <v>51.5813941955566</v>
+        <v>51.5813980102539</v>
       </c>
       <c r="H1396" t="n">
         <v>394733</v>
@@ -40882,7 +40882,7 @@
         <v>57.4799995422363</v>
       </c>
       <c r="G1397" t="n">
-        <v>51.961067199707</v>
+        <v>51.9610633850098</v>
       </c>
       <c r="H1397" t="n">
         <v>354507</v>
@@ -40911,7 +40911,7 @@
         <v>57.3199996948242</v>
       </c>
       <c r="G1398" t="n">
-        <v>51.8164329528809</v>
+        <v>51.8164291381836</v>
       </c>
       <c r="H1398" t="n">
         <v>168655</v>
@@ -40969,7 +40969,7 @@
         <v>57.0200004577637</v>
       </c>
       <c r="G1400" t="n">
-        <v>51.5452308654785</v>
+        <v>51.5452346801758</v>
       </c>
       <c r="H1400" t="n">
         <v>265319</v>
@@ -41056,7 +41056,7 @@
         <v>56.3600006103516</v>
       </c>
       <c r="G1403" t="n">
-        <v>50.9486045837402</v>
+        <v>50.9486083984375</v>
       </c>
       <c r="H1403" t="n">
         <v>545358</v>
@@ -41143,7 +41143,7 @@
         <v>58.439998626709</v>
       </c>
       <c r="G1406" t="n">
-        <v>52.8288917541504</v>
+        <v>52.8288955688477</v>
       </c>
       <c r="H1406" t="n">
         <v>359329</v>
@@ -41201,7 +41201,7 @@
         <v>56.7400016784668</v>
       </c>
       <c r="G1408" t="n">
-        <v>51.2921142578125</v>
+        <v>51.2921180725098</v>
       </c>
       <c r="H1408" t="n">
         <v>689323</v>
@@ -41549,7 +41549,7 @@
         <v>58.7400016784668</v>
       </c>
       <c r="G1420" t="n">
-        <v>53.1000862121582</v>
+        <v>53.1000900268555</v>
       </c>
       <c r="H1420" t="n">
         <v>470799</v>
@@ -41607,7 +41607,7 @@
         <v>58.7400016784668</v>
       </c>
       <c r="G1422" t="n">
-        <v>53.1000862121582</v>
+        <v>53.1000900268555</v>
       </c>
       <c r="H1422" t="n">
         <v>495805</v>
@@ -41636,7 +41636,7 @@
         <v>58.6199989318848</v>
       </c>
       <c r="G1423" t="n">
-        <v>52.9916114807129</v>
+        <v>52.9916076660156</v>
       </c>
       <c r="H1423" t="n">
         <v>686976</v>
@@ -41984,7 +41984,7 @@
         <v>54.6599998474121</v>
       </c>
       <c r="G1435" t="n">
-        <v>49.4118270874023</v>
+        <v>49.4118309020996</v>
       </c>
       <c r="H1435" t="n">
         <v>671471</v>
@@ -42013,7 +42013,7 @@
         <v>54.5800018310547</v>
       </c>
       <c r="G1436" t="n">
-        <v>49.3395118713379</v>
+        <v>49.3395156860352</v>
       </c>
       <c r="H1436" t="n">
         <v>415180</v>
@@ -42216,7 +42216,7 @@
         <v>54.0200004577637</v>
       </c>
       <c r="G1443" t="n">
-        <v>48.8332786560059</v>
+        <v>48.8332748413086</v>
       </c>
       <c r="H1443" t="n">
         <v>584736</v>
@@ -42419,7 +42419,7 @@
         <v>54.5999984741211</v>
       </c>
       <c r="G1450" t="n">
-        <v>49.3575897216797</v>
+        <v>49.3575859069824</v>
       </c>
       <c r="H1450" t="n">
         <v>623960</v>
@@ -42448,7 +42448,7 @@
         <v>51.7799987792969</v>
       </c>
       <c r="G1451" t="n">
-        <v>46.808349609375</v>
+        <v>46.8083534240723</v>
       </c>
       <c r="H1451" t="n">
         <v>1244373</v>
@@ -42477,7 +42477,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G1452" t="n">
-        <v>46.7360305786133</v>
+        <v>46.7360343933105</v>
       </c>
       <c r="H1452" t="n">
         <v>908760</v>
@@ -42564,7 +42564,7 @@
         <v>52.6800003051758</v>
       </c>
       <c r="G1455" t="n">
-        <v>47.621940612793</v>
+        <v>47.6219367980957</v>
       </c>
       <c r="H1455" t="n">
         <v>539487</v>
@@ -42593,7 +42593,7 @@
         <v>54.3600006103516</v>
       </c>
       <c r="G1456" t="n">
-        <v>49.1406326293945</v>
+        <v>49.1406364440918</v>
       </c>
       <c r="H1456" t="n">
         <v>835925</v>
@@ -42651,7 +42651,7 @@
         <v>55</v>
       </c>
       <c r="G1458" t="n">
-        <v>49.7191848754883</v>
+        <v>49.719181060791</v>
       </c>
       <c r="H1458" t="n">
         <v>615681</v>
@@ -42883,7 +42883,7 @@
         <v>55.8800010681152</v>
       </c>
       <c r="G1466" t="n">
-        <v>50.5146865844727</v>
+        <v>50.5146903991699</v>
       </c>
       <c r="H1466" t="n">
         <v>1018635</v>
@@ -42912,7 +42912,7 @@
         <v>56.9599990844727</v>
       </c>
       <c r="G1467" t="n">
-        <v>51.4909934997559</v>
+        <v>51.4909896850586</v>
       </c>
       <c r="H1467" t="n">
         <v>747678</v>
@@ -42941,7 +42941,7 @@
         <v>56.439998626709</v>
       </c>
       <c r="G1468" t="n">
-        <v>51.020923614502</v>
+        <v>51.0209274291992</v>
       </c>
       <c r="H1468" t="n">
         <v>339395</v>
@@ -42970,7 +42970,7 @@
         <v>57.0200004577637</v>
       </c>
       <c r="G1469" t="n">
-        <v>51.5452308654785</v>
+        <v>51.5452346801758</v>
       </c>
       <c r="H1469" t="n">
         <v>420662</v>
@@ -43173,7 +43173,7 @@
         <v>59.7400016784668</v>
       </c>
       <c r="G1476" t="n">
-        <v>54.0040740966797</v>
+        <v>54.004077911377</v>
       </c>
       <c r="H1476" t="n">
         <v>649440</v>
@@ -43289,7 +43289,7 @@
         <v>60.6199989318848</v>
       </c>
       <c r="G1480" t="n">
-        <v>54.7995796203613</v>
+        <v>54.7995758056641</v>
       </c>
       <c r="H1480" t="n">
         <v>579896</v>
@@ -43347,7 +43347,7 @@
         <v>61.2200012207031</v>
       </c>
       <c r="G1482" t="n">
-        <v>55.3419723510742</v>
+        <v>55.3419761657715</v>
       </c>
       <c r="H1482" t="n">
         <v>637932</v>
@@ -43376,7 +43376,7 @@
         <v>62.1199989318848</v>
       </c>
       <c r="G1483" t="n">
-        <v>56.1555595397949</v>
+        <v>56.1555557250977</v>
       </c>
       <c r="H1483" t="n">
         <v>1114603</v>
@@ -43405,7 +43405,7 @@
         <v>63.9000015258789</v>
       </c>
       <c r="G1484" t="n">
-        <v>57.7646522521973</v>
+        <v>57.7646560668945</v>
       </c>
       <c r="H1484" t="n">
         <v>729046</v>
@@ -43463,7 +43463,7 @@
         <v>63.6800003051758</v>
       </c>
       <c r="G1486" t="n">
-        <v>57.5657768249512</v>
+        <v>57.5657806396484</v>
       </c>
       <c r="H1486" t="n">
         <v>725952</v>
@@ -43492,7 +43492,7 @@
         <v>66.2799987792969</v>
       </c>
       <c r="G1487" t="n">
-        <v>59.9161415100098</v>
+        <v>59.9161376953125</v>
       </c>
       <c r="H1487" t="n">
         <v>1248855</v>
@@ -43550,7 +43550,7 @@
         <v>68.1600036621094</v>
       </c>
       <c r="G1489" t="n">
-        <v>61.6156387329102</v>
+        <v>61.6156349182129</v>
       </c>
       <c r="H1489" t="n">
         <v>747874</v>
@@ -43637,7 +43637,7 @@
         <v>66.4599990844727</v>
       </c>
       <c r="G1492" t="n">
-        <v>60.0788497924805</v>
+        <v>60.0788536071777</v>
       </c>
       <c r="H1492" t="n">
         <v>723413</v>
@@ -43666,7 +43666,7 @@
         <v>67.6600036621094</v>
       </c>
       <c r="G1493" t="n">
-        <v>61.1636390686035</v>
+        <v>61.1636352539062</v>
       </c>
       <c r="H1493" t="n">
         <v>607924</v>
@@ -43695,7 +43695,7 @@
         <v>68.5400009155273</v>
       </c>
       <c r="G1494" t="n">
-        <v>61.9591407775879</v>
+        <v>61.9591445922852</v>
       </c>
       <c r="H1494" t="n">
         <v>548265</v>
@@ -43782,7 +43782,7 @@
         <v>68.3399963378906</v>
       </c>
       <c r="G1497" t="n">
-        <v>61.7783393859863</v>
+        <v>61.7783432006836</v>
       </c>
       <c r="H1497" t="n">
         <v>1103847</v>
@@ -43869,7 +43869,7 @@
         <v>66.1600036621094</v>
       </c>
       <c r="G1500" t="n">
-        <v>59.8076667785645</v>
+        <v>59.8076629638672</v>
       </c>
       <c r="H1500" t="n">
         <v>1062917</v>
@@ -43927,7 +43927,7 @@
         <v>67</v>
       </c>
       <c r="G1502" t="n">
-        <v>60.5670051574707</v>
+        <v>60.567008972168</v>
       </c>
       <c r="H1502" t="n">
         <v>286229</v>
@@ -43985,7 +43985,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G1504" t="n">
-        <v>58.3974380493164</v>
+        <v>58.3974418640137</v>
       </c>
       <c r="H1504" t="n">
         <v>908575</v>
@@ -44014,7 +44014,7 @@
         <v>64.0800018310547</v>
       </c>
       <c r="G1505" t="n">
-        <v>57.9273719787598</v>
+        <v>57.9273681640625</v>
       </c>
       <c r="H1505" t="n">
         <v>1041382</v>
@@ -44043,7 +44043,7 @@
         <v>65.620002746582</v>
       </c>
       <c r="G1506" t="n">
-        <v>59.3195037841797</v>
+        <v>59.3194999694824</v>
       </c>
       <c r="H1506" t="n">
         <v>803677</v>
@@ -44130,7 +44130,7 @@
         <v>66.3199996948242</v>
       </c>
       <c r="G1509" t="n">
-        <v>59.9522972106934</v>
+        <v>59.9522933959961</v>
       </c>
       <c r="H1509" t="n">
         <v>470818</v>
@@ -44246,7 +44246,7 @@
         <v>66.0599975585938</v>
       </c>
       <c r="G1513" t="n">
-        <v>59.7172584533691</v>
+        <v>59.7172622680664</v>
       </c>
       <c r="H1513" t="n">
         <v>575102</v>
@@ -44333,7 +44333,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1516" t="n">
-        <v>58.4878387451172</v>
+        <v>58.4878349304199</v>
       </c>
       <c r="H1516" t="n">
         <v>666887</v>
@@ -44420,7 +44420,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1519" t="n">
-        <v>56.589469909668</v>
+        <v>56.5894737243652</v>
       </c>
       <c r="H1519" t="n">
         <v>443012</v>
@@ -44449,7 +44449,7 @@
         <v>62.2000007629395</v>
       </c>
       <c r="G1520" t="n">
-        <v>56.2278785705566</v>
+        <v>56.2278747558594</v>
       </c>
       <c r="H1520" t="n">
         <v>382113</v>
@@ -44478,7 +44478,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G1521" t="n">
-        <v>56.6798706054688</v>
+        <v>56.6798667907715</v>
       </c>
       <c r="H1521" t="n">
         <v>312156</v>
@@ -44536,7 +44536,7 @@
         <v>64.0800018310547</v>
       </c>
       <c r="G1523" t="n">
-        <v>57.9273719787598</v>
+        <v>57.9273681640625</v>
       </c>
       <c r="H1523" t="n">
         <v>233565</v>
@@ -44565,7 +44565,7 @@
         <v>64.2399978637695</v>
       </c>
       <c r="G1524" t="n">
-        <v>58.0720062255859</v>
+        <v>58.0720024108887</v>
       </c>
       <c r="H1524" t="n">
         <v>265608</v>
@@ -44681,7 +44681,7 @@
         <v>65</v>
       </c>
       <c r="G1528" t="n">
-        <v>58.759033203125</v>
+        <v>58.7590370178223</v>
       </c>
       <c r="H1528" t="n">
         <v>522653</v>
@@ -44710,7 +44710,7 @@
         <v>65.5</v>
       </c>
       <c r="G1529" t="n">
-        <v>59.2110290527344</v>
+        <v>59.2110252380371</v>
       </c>
       <c r="H1529" t="n">
         <v>373035</v>
@@ -44797,7 +44797,7 @@
         <v>60.6199989318848</v>
       </c>
       <c r="G1532" t="n">
-        <v>54.7995796203613</v>
+        <v>54.7995758056641</v>
       </c>
       <c r="H1532" t="n">
         <v>717719</v>
@@ -44942,7 +44942,7 @@
         <v>57.7400016784668</v>
       </c>
       <c r="G1537" t="n">
-        <v>52.196102142334</v>
+        <v>52.1961059570312</v>
       </c>
       <c r="H1537" t="n">
         <v>615447</v>
@@ -45203,7 +45203,7 @@
         <v>55.439998626709</v>
       </c>
       <c r="G1546" t="n">
-        <v>50.1169357299805</v>
+        <v>50.1169395446777</v>
       </c>
       <c r="H1546" t="n">
         <v>892110</v>
@@ -45261,7 +45261,7 @@
         <v>59.0200004577637</v>
       </c>
       <c r="G1548" t="n">
-        <v>53.353199005127</v>
+        <v>53.3532028198242</v>
       </c>
       <c r="H1548" t="n">
         <v>1181627</v>
@@ -45319,7 +45319,7 @@
         <v>57.8800010681152</v>
       </c>
       <c r="G1550" t="n">
-        <v>52.3226585388184</v>
+        <v>52.3226623535156</v>
       </c>
       <c r="H1550" t="n">
         <v>707003</v>
@@ -45377,7 +45377,7 @@
         <v>57.6199989318848</v>
       </c>
       <c r="G1552" t="n">
-        <v>52.0876274108887</v>
+        <v>52.0876235961914</v>
       </c>
       <c r="H1552" t="n">
         <v>468353</v>
@@ -45406,7 +45406,7 @@
         <v>56.8400001525879</v>
       </c>
       <c r="G1553" t="n">
-        <v>51.3825187683105</v>
+        <v>51.3825149536133</v>
       </c>
       <c r="H1553" t="n">
         <v>399743</v>
@@ -45493,7 +45493,7 @@
         <v>55.5200004577637</v>
       </c>
       <c r="G1556" t="n">
-        <v>50.1892547607422</v>
+        <v>50.1892585754395</v>
       </c>
       <c r="H1556" t="n">
         <v>639440</v>
@@ -45522,7 +45522,7 @@
         <v>54.439998626709</v>
       </c>
       <c r="G1557" t="n">
-        <v>49.212947845459</v>
+        <v>49.2129516601562</v>
       </c>
       <c r="H1557" t="n">
         <v>1122290</v>
@@ -45580,7 +45580,7 @@
         <v>55.8800010681152</v>
       </c>
       <c r="G1559" t="n">
-        <v>50.5146865844727</v>
+        <v>50.5146903991699</v>
       </c>
       <c r="H1559" t="n">
         <v>390477</v>
@@ -45928,7 +45928,7 @@
         <v>45.0200004577637</v>
       </c>
       <c r="G1571" t="n">
-        <v>40.6974105834961</v>
+        <v>40.6974143981934</v>
       </c>
       <c r="H1571" t="n">
         <v>1444933</v>
@@ -46015,7 +46015,7 @@
         <v>48.3499984741211</v>
       </c>
       <c r="G1574" t="n">
-        <v>43.7076835632324</v>
+        <v>43.7076873779297</v>
       </c>
       <c r="H1574" t="n">
         <v>1336574</v>
@@ -46073,7 +46073,7 @@
         <v>47.9700012207031</v>
       </c>
       <c r="G1576" t="n">
-        <v>43.3641738891602</v>
+        <v>43.3641700744629</v>
       </c>
       <c r="H1576" t="n">
         <v>987254</v>
@@ -46102,7 +46102,7 @@
         <v>48</v>
       </c>
       <c r="G1577" t="n">
-        <v>43.3912925720215</v>
+        <v>43.3912887573242</v>
       </c>
       <c r="H1577" t="n">
         <v>713950</v>
@@ -46131,7 +46131,7 @@
         <v>46.4900016784668</v>
       </c>
       <c r="G1578" t="n">
-        <v>42.0262718200684</v>
+        <v>42.0262756347656</v>
       </c>
       <c r="H1578" t="n">
         <v>1241906</v>
@@ -46189,7 +46189,7 @@
         <v>50.2999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>45.4704551696777</v>
+        <v>45.4704513549805</v>
       </c>
       <c r="H1580" t="n">
         <v>877443</v>
@@ -46247,7 +46247,7 @@
         <v>50.6399993896484</v>
       </c>
       <c r="G1582" t="n">
-        <v>45.7778015136719</v>
+        <v>45.7778053283691</v>
       </c>
       <c r="H1582" t="n">
         <v>538124</v>
@@ -46537,7 +46537,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G1592" t="n">
-        <v>47.5496215820312</v>
+        <v>47.549617767334</v>
       </c>
       <c r="H1592" t="n">
         <v>651612</v>
@@ -46624,7 +46624,7 @@
         <v>49.439998626709</v>
       </c>
       <c r="G1595" t="n">
-        <v>44.6930274963379</v>
+        <v>44.6930236816406</v>
       </c>
       <c r="H1595" t="n">
         <v>562356</v>
@@ -46769,7 +46769,7 @@
         <v>50.560001373291</v>
       </c>
       <c r="G1600" t="n">
-        <v>45.7054862976074</v>
+        <v>45.7054901123047</v>
       </c>
       <c r="H1600" t="n">
         <v>660425</v>
@@ -46943,7 +46943,7 @@
         <v>47.1199989318848</v>
       </c>
       <c r="G1606" t="n">
-        <v>42.5957794189453</v>
+        <v>42.5957832336426</v>
       </c>
       <c r="H1606" t="n">
         <v>680527</v>
@@ -47001,7 +47001,7 @@
         <v>49.7400016784668</v>
       </c>
       <c r="G1608" t="n">
-        <v>44.9642219543457</v>
+        <v>44.964225769043</v>
       </c>
       <c r="H1608" t="n">
         <v>771679</v>
@@ -47059,7 +47059,7 @@
         <v>48.9900016784668</v>
       </c>
       <c r="G1610" t="n">
-        <v>44.2862396240234</v>
+        <v>44.2862358093262</v>
       </c>
       <c r="H1610" t="n">
         <v>721793</v>
@@ -47117,7 +47117,7 @@
         <v>47.2599983215332</v>
       </c>
       <c r="G1612" t="n">
-        <v>42.7223358154297</v>
+        <v>42.722339630127</v>
       </c>
       <c r="H1612" t="n">
         <v>991991</v>
@@ -47291,7 +47291,7 @@
         <v>43.8699989318848</v>
       </c>
       <c r="G1618" t="n">
-        <v>39.6578254699707</v>
+        <v>39.657829284668</v>
       </c>
       <c r="H1618" t="n">
         <v>735193</v>
@@ -47320,7 +47320,7 @@
         <v>45.3600006103516</v>
       </c>
       <c r="G1619" t="n">
-        <v>41.004768371582</v>
+        <v>41.0047645568848</v>
       </c>
       <c r="H1619" t="n">
         <v>610123</v>
@@ -47378,7 +47378,7 @@
         <v>45.2700004577637</v>
       </c>
       <c r="G1621" t="n">
-        <v>40.9234085083008</v>
+        <v>40.923412322998</v>
       </c>
       <c r="H1621" t="n">
         <v>524847</v>
@@ -47436,7 +47436,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G1623" t="n">
-        <v>38.9617576599121</v>
+        <v>38.9617614746094</v>
       </c>
       <c r="H1623" t="n">
         <v>934998</v>
@@ -80125,6 +80125,35 @@
         <v>753156</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>42.810001373291</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>42.9000015258789</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>42.1199989318848</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>42.1199989318848</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>42.1199989318848</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>1335119</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>
